--- a/files/temp-work.xlsx
+++ b/files/temp-work.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/coltongearhart/Desktop/exam5/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC2927A-962F-3041-A061-A20446BC0AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{529DD912-7E81-BB4F-BA05-659E96ABE747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" activeTab="2" xr2:uid="{BB8505BC-BCB7-B340-A120-C046C43AD7BD}"/>
+    <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" activeTab="3" xr2:uid="{BB8505BC-BCB7-B340-A120-C046C43AD7BD}"/>
   </bookViews>
   <sheets>
     <sheet name="2.2.1" sheetId="1" r:id="rId1"/>
     <sheet name="2.2.2" sheetId="2" r:id="rId2"/>
     <sheet name="2.3.1" sheetId="3" r:id="rId3"/>
+    <sheet name="2.3.3" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="177">
   <si>
     <t>Ratio to SAWW</t>
   </si>
@@ -337,15 +338,262 @@
   <si>
     <t xml:space="preserve"> </t>
   </si>
+  <si>
+    <t>Accident Year</t>
+  </si>
+  <si>
+    <t>Incremental Reported Claims by Age ($US Millions)</t>
+  </si>
+  <si>
+    <t>12 Months</t>
+  </si>
+  <si>
+    <t>24 Months</t>
+  </si>
+  <si>
+    <t>36 Months</t>
+  </si>
+  <si>
+    <t>48 Months</t>
+  </si>
+  <si>
+    <t>60 Months</t>
+  </si>
+  <si>
+    <t>12-24</t>
+  </si>
+  <si>
+    <t>24-36</t>
+  </si>
+  <si>
+    <t>36-48</t>
+  </si>
+  <si>
+    <t>48-60</t>
+  </si>
+  <si>
+    <t>Age-to-age factors (months)</t>
+  </si>
+  <si>
+    <t>Factor</t>
+  </si>
+  <si>
+    <t>Age-to-age</t>
+  </si>
+  <si>
+    <t>Volume-weighted factor</t>
+  </si>
+  <si>
+    <t>60-Ult (tail)</t>
+  </si>
+  <si>
+    <t>(given)</t>
+  </si>
+  <si>
+    <t>Age-Ult</t>
+  </si>
+  <si>
+    <t>12-Ult</t>
+  </si>
+  <si>
+    <t>24-Ult</t>
+  </si>
+  <si>
+    <t>36-Ult</t>
+  </si>
+  <si>
+    <t>48-Ult</t>
+  </si>
+  <si>
+    <t>=PRODUCT(C19:C23)</t>
+  </si>
+  <si>
+    <t>60-Ult</t>
+  </si>
+  <si>
+    <t>Projected ultimate reported claims</t>
+  </si>
+  <si>
+    <t>12 months</t>
+  </si>
+  <si>
+    <t>24 months</t>
+  </si>
+  <si>
+    <t>36 months</t>
+  </si>
+  <si>
+    <t>48 months</t>
+  </si>
+  <si>
+    <t>60 months</t>
+  </si>
+  <si>
+    <t>Cumulative Reported Claims by Age ($US Millions)</t>
+  </si>
+  <si>
+    <t>=SUM(D13:D16)/SUM(C13:C16)</t>
+  </si>
+  <si>
+    <t>Months</t>
+  </si>
+  <si>
+    <t>AY 2021 reported claims</t>
+  </si>
+  <si>
+    <t>=C40*C33</t>
+  </si>
+  <si>
+    <t>=SUM(D40:D44)</t>
+  </si>
+  <si>
+    <t>(actually not needed cause volume-weighted method)</t>
+  </si>
+  <si>
+    <t>As of December 31, 2012</t>
+  </si>
+  <si>
+    <t>Paid Losses</t>
+  </si>
+  <si>
+    <t>Case Reserves</t>
+  </si>
+  <si>
+    <t>Incurred losses</t>
+  </si>
+  <si>
+    <t>=SUM(J51:K51)</t>
+  </si>
+  <si>
+    <t>-&gt; This is the latest diagonal because of 'As of 12/12/2012'</t>
+  </si>
+  <si>
+    <t>Estimated ultimate losses AY 2010 @ 36 months (as of 12/12/2012)</t>
+  </si>
+  <si>
+    <t>Factor (link ratio)</t>
+  </si>
+  <si>
+    <t>(solve for X ==&gt;</t>
+  </si>
+  <si>
+    <t>Estimated ultimate losses AY 2011 @ 24 months (as of 12/12/2012)</t>
+  </si>
+  <si>
+    <t>AY 2011 incurred losses</t>
+  </si>
+  <si>
+    <t>=L52*PRODUCT(J59)</t>
+  </si>
+  <si>
+    <t>&lt; using age-to-ult factors (CDFs) &gt;</t>
+  </si>
+  <si>
+    <t>=L53*PRODUCT(J58:J59)</t>
+  </si>
+  <si>
+    <t>Cumulative Paid Claims ($000s)</t>
+  </si>
+  <si>
+    <t>Age of Development (Months)</t>
+  </si>
+  <si>
+    <t>Earned Exposures</t>
+  </si>
+  <si>
+    <t>Age to Age (Months)</t>
+  </si>
+  <si>
+    <t>Medial average factor</t>
+  </si>
+  <si>
+    <t>Age-to-ult</t>
+  </si>
+  <si>
+    <t>=PRODUCT(R92:R95)</t>
+  </si>
+  <si>
+    <t>Estimated ult paid claims</t>
+  </si>
+  <si>
+    <t>=S81*R98</t>
+  </si>
+  <si>
+    <t>==&gt; Unpaid:</t>
+  </si>
+  <si>
+    <t>=S109-R109</t>
+  </si>
+  <si>
+    <t>Company Data</t>
+  </si>
+  <si>
+    <t>Age-age factors (months)</t>
+  </si>
+  <si>
+    <t>Factor (simple average method)</t>
+  </si>
+  <si>
+    <t>=AVERAGE(Z126:Z128)</t>
+  </si>
+  <si>
+    <t>12-ult</t>
+  </si>
+  <si>
+    <t>24-ult</t>
+  </si>
+  <si>
+    <t>36-ult</t>
+  </si>
+  <si>
+    <t>CDF</t>
+  </si>
+  <si>
+    <t>=PRODUCT(Z131:Z133)</t>
+  </si>
+  <si>
+    <t>AY 2014 paid claims</t>
+  </si>
+  <si>
+    <t>AY 2014 Paid Claims</t>
+  </si>
+  <si>
+    <t>=Z141*Z136</t>
+  </si>
+  <si>
+    <t>--&gt; Another option is to just use the most recent year's factors (i.e. the latest diagonal)</t>
+  </si>
+  <si>
+    <t>--&gt; simple average is good for stability</t>
+  </si>
+  <si>
+    <t>Paid Claims Age-to-Age Factors</t>
+  </si>
+  <si>
+    <t>Industry Data</t>
+  </si>
+  <si>
+    <t>=PRODUCT(Z158:Z160)</t>
+  </si>
+  <si>
+    <t>=Z168*Z163</t>
+  </si>
+  <si>
+    <t>=AVERAGE(Z153:Z155)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="7">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="170" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000"/>
+    <numFmt numFmtId="173" formatCode="0.000"/>
+    <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -427,12 +675,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -535,7 +789,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -573,18 +827,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -618,12 +866,60 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="176" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="6" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="8" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1698,26 +1994,26 @@
       </c>
     </row>
     <row r="23" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="M23" s="40"/>
-      <c r="N23" s="41"/>
-      <c r="O23" s="37" t="s">
+      <c r="M23" s="42"/>
+      <c r="N23" s="43"/>
+      <c r="O23" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="P23" s="38"/>
-      <c r="Q23" s="38"/>
-      <c r="R23" s="39"/>
-      <c r="S23" s="37" t="s">
+      <c r="P23" s="40"/>
+      <c r="Q23" s="40"/>
+      <c r="R23" s="41"/>
+      <c r="S23" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="T23" s="38"/>
-      <c r="U23" s="38"/>
-      <c r="V23" s="39"/>
-      <c r="W23" s="37" t="s">
+      <c r="T23" s="40"/>
+      <c r="U23" s="40"/>
+      <c r="V23" s="41"/>
+      <c r="W23" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="X23" s="38"/>
-      <c r="Y23" s="38"/>
-      <c r="Z23" s="39"/>
+      <c r="X23" s="40"/>
+      <c r="Y23" s="40"/>
+      <c r="Z23" s="41"/>
     </row>
     <row r="24" spans="2:33" x14ac:dyDescent="0.2">
       <c r="M24" s="24" t="s">
@@ -1783,35 +2079,35 @@
       <c r="R25" s="30">
         <v>0</v>
       </c>
-      <c r="S25" s="46">
+      <c r="S25" s="48">
         <f>SUMPRODUCT(O25:O27,$N$25:$N$27)</f>
         <v>1.0568750000000002</v>
       </c>
-      <c r="T25" s="44">
+      <c r="T25" s="46">
         <f t="shared" ref="T25:V25" si="2">SUMPRODUCT(P25:P27,$N$25:$N$27)</f>
         <v>1.089375</v>
       </c>
-      <c r="U25" s="44">
+      <c r="U25" s="46">
         <f t="shared" si="2"/>
         <v>1.1156250000000001</v>
       </c>
-      <c r="V25" s="42">
+      <c r="V25" s="44">
         <f t="shared" si="2"/>
         <v>1.1418750000000002</v>
       </c>
-      <c r="W25" s="46">
+      <c r="W25" s="48">
         <f>$N$27/S25</f>
         <v>1.0928444707273803</v>
       </c>
-      <c r="X25" s="44">
+      <c r="X25" s="46">
         <f t="shared" ref="X25:Z25" si="3">$N$27/T25</f>
         <v>1.060240963855422</v>
       </c>
-      <c r="Y25" s="44">
+      <c r="Y25" s="46">
         <f t="shared" si="3"/>
         <v>1.0352941176470589</v>
       </c>
-      <c r="Z25" s="42">
+      <c r="Z25" s="44">
         <f t="shared" si="3"/>
         <v>1.0114942528735633</v>
       </c>
@@ -1836,14 +2132,14 @@
       <c r="R26" s="30">
         <v>0.125</v>
       </c>
-      <c r="S26" s="46"/>
-      <c r="T26" s="44"/>
-      <c r="U26" s="44"/>
-      <c r="V26" s="42"/>
-      <c r="W26" s="46"/>
-      <c r="X26" s="44"/>
-      <c r="Y26" s="44"/>
-      <c r="Z26" s="42"/>
+      <c r="S26" s="48"/>
+      <c r="T26" s="46"/>
+      <c r="U26" s="46"/>
+      <c r="V26" s="44"/>
+      <c r="W26" s="48"/>
+      <c r="X26" s="46"/>
+      <c r="Y26" s="46"/>
+      <c r="Z26" s="44"/>
     </row>
     <row r="27" spans="2:33" x14ac:dyDescent="0.2">
       <c r="M27" s="28">
@@ -1865,14 +2161,14 @@
       <c r="R27" s="31">
         <v>0.875</v>
       </c>
-      <c r="S27" s="47"/>
-      <c r="T27" s="45"/>
-      <c r="U27" s="45"/>
-      <c r="V27" s="43"/>
-      <c r="W27" s="47"/>
-      <c r="X27" s="45"/>
-      <c r="Y27" s="45"/>
-      <c r="Z27" s="43"/>
+      <c r="S27" s="49"/>
+      <c r="T27" s="47"/>
+      <c r="U27" s="47"/>
+      <c r="V27" s="45"/>
+      <c r="W27" s="49"/>
+      <c r="X27" s="47"/>
+      <c r="Y27" s="47"/>
+      <c r="Z27" s="45"/>
     </row>
     <row r="28" spans="2:33" x14ac:dyDescent="0.2">
       <c r="N28" s="32" t="s">
@@ -1953,23 +2249,23 @@
       </c>
     </row>
     <row r="37" spans="15:41" x14ac:dyDescent="0.2">
-      <c r="AE37" s="34"/>
-      <c r="AF37" s="34"/>
-      <c r="AG37" s="35" t="s">
+      <c r="AE37" s="52"/>
+      <c r="AF37" s="52"/>
+      <c r="AG37" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="AH37" s="35"/>
-      <c r="AI37" s="35"/>
-      <c r="AJ37" s="35" t="s">
+      <c r="AH37" s="51"/>
+      <c r="AI37" s="51"/>
+      <c r="AJ37" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="AK37" s="35"/>
-      <c r="AL37" s="35"/>
-      <c r="AM37" s="35" t="s">
+      <c r="AK37" s="51"/>
+      <c r="AL37" s="51"/>
+      <c r="AM37" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="AN37" s="35"/>
-      <c r="AO37" s="35"/>
+      <c r="AN37" s="51"/>
+      <c r="AO37" s="51"/>
     </row>
     <row r="38" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE38" s="15" t="s">
@@ -2018,18 +2314,18 @@
         <f>0.5*3/4*3/4</f>
         <v>0.28125</v>
       </c>
-      <c r="AJ39" s="33"/>
-      <c r="AK39" s="33">
+      <c r="AJ39" s="50"/>
+      <c r="AK39" s="50">
         <f>SUMPRODUCT(AH39:AH42,AF39:AF42)</f>
         <v>1.0636875000000001</v>
       </c>
-      <c r="AL39" s="33"/>
-      <c r="AM39" s="33"/>
-      <c r="AN39" s="33">
+      <c r="AL39" s="50"/>
+      <c r="AM39" s="50"/>
+      <c r="AN39" s="50">
         <f>$AF$42/AK39</f>
         <v>1.0512015982137612</v>
       </c>
-      <c r="AO39" s="33"/>
+      <c r="AO39" s="50"/>
     </row>
     <row r="40" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE40">
@@ -2043,12 +2339,12 @@
         <f>1-AH39-AH41</f>
         <v>0.59375</v>
       </c>
-      <c r="AJ40" s="33"/>
-      <c r="AK40" s="33"/>
-      <c r="AL40" s="33"/>
-      <c r="AM40" s="33"/>
-      <c r="AN40" s="33"/>
-      <c r="AO40" s="33"/>
+      <c r="AJ40" s="50"/>
+      <c r="AK40" s="50"/>
+      <c r="AL40" s="50"/>
+      <c r="AM40" s="50"/>
+      <c r="AN40" s="50"/>
+      <c r="AO40" s="50"/>
     </row>
     <row r="41" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE41">
@@ -2061,12 +2357,12 @@
       <c r="AH41">
         <v>0.125</v>
       </c>
-      <c r="AJ41" s="33"/>
-      <c r="AK41" s="33"/>
-      <c r="AL41" s="33"/>
-      <c r="AM41" s="33"/>
-      <c r="AN41" s="33"/>
-      <c r="AO41" s="33"/>
+      <c r="AJ41" s="50"/>
+      <c r="AK41" s="50"/>
+      <c r="AL41" s="50"/>
+      <c r="AM41" s="50"/>
+      <c r="AN41" s="50"/>
+      <c r="AO41" s="50"/>
     </row>
     <row r="42" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE42">
@@ -2079,31 +2375,31 @@
       <c r="AH42">
         <v>0</v>
       </c>
-      <c r="AJ42" s="33"/>
-      <c r="AK42" s="33"/>
-      <c r="AL42" s="33"/>
-      <c r="AM42" s="33"/>
-      <c r="AN42" s="33"/>
-      <c r="AO42" s="33"/>
+      <c r="AJ42" s="50"/>
+      <c r="AK42" s="50"/>
+      <c r="AL42" s="50"/>
+      <c r="AM42" s="50"/>
+      <c r="AN42" s="50"/>
+      <c r="AO42" s="50"/>
     </row>
     <row r="44" spans="15:41" x14ac:dyDescent="0.2">
-      <c r="AE44" s="34"/>
-      <c r="AF44" s="34"/>
-      <c r="AG44" s="35" t="s">
+      <c r="AE44" s="52"/>
+      <c r="AF44" s="52"/>
+      <c r="AG44" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="AH44" s="35"/>
-      <c r="AI44" s="35"/>
-      <c r="AJ44" s="35" t="s">
+      <c r="AH44" s="51"/>
+      <c r="AI44" s="51"/>
+      <c r="AJ44" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="AK44" s="35"/>
-      <c r="AL44" s="35"/>
-      <c r="AM44" s="35" t="s">
+      <c r="AK44" s="51"/>
+      <c r="AL44" s="51"/>
+      <c r="AM44" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="AN44" s="35"/>
-      <c r="AO44" s="35"/>
+      <c r="AN44" s="51"/>
+      <c r="AO44" s="51"/>
     </row>
     <row r="45" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE45" s="15" t="s">
@@ -2151,18 +2447,18 @@
       <c r="AH46">
         <v>0</v>
       </c>
-      <c r="AJ46" s="33"/>
-      <c r="AK46" s="33">
+      <c r="AJ46" s="50"/>
+      <c r="AK46" s="50">
         <f>SUMPRODUCT(AH46:AH49,AF46:AF49)</f>
         <v>1.1161437500000002</v>
       </c>
-      <c r="AL46" s="33"/>
-      <c r="AM46" s="33"/>
-      <c r="AN46" s="33">
+      <c r="AL46" s="50"/>
+      <c r="AM46" s="50"/>
+      <c r="AN46" s="50">
         <f>$AF$49/AK46</f>
         <v>1.0017974835230676</v>
       </c>
-      <c r="AO46" s="33"/>
+      <c r="AO46" s="50"/>
     </row>
     <row r="47" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE47">
@@ -2175,12 +2471,12 @@
       <c r="AH47">
         <v>0.5</v>
       </c>
-      <c r="AJ47" s="33"/>
-      <c r="AK47" s="33"/>
-      <c r="AL47" s="33"/>
-      <c r="AM47" s="33"/>
-      <c r="AN47" s="33"/>
-      <c r="AO47" s="33"/>
+      <c r="AJ47" s="50"/>
+      <c r="AK47" s="50"/>
+      <c r="AL47" s="50"/>
+      <c r="AM47" s="50"/>
+      <c r="AN47" s="50"/>
+      <c r="AO47" s="50"/>
     </row>
     <row r="48" spans="15:41" x14ac:dyDescent="0.2">
       <c r="O48" t="s">
@@ -2196,12 +2492,12 @@
       <c r="AH48">
         <v>0.375</v>
       </c>
-      <c r="AJ48" s="33"/>
-      <c r="AK48" s="33"/>
-      <c r="AL48" s="33"/>
-      <c r="AM48" s="33"/>
-      <c r="AN48" s="33"/>
-      <c r="AO48" s="33"/>
+      <c r="AJ48" s="50"/>
+      <c r="AK48" s="50"/>
+      <c r="AL48" s="50"/>
+      <c r="AM48" s="50"/>
+      <c r="AN48" s="50"/>
+      <c r="AO48" s="50"/>
     </row>
     <row r="49" spans="31:52" x14ac:dyDescent="0.2">
       <c r="AE49">
@@ -2214,12 +2510,12 @@
       <c r="AH49">
         <v>0.125</v>
       </c>
-      <c r="AJ49" s="33"/>
-      <c r="AK49" s="33"/>
-      <c r="AL49" s="33"/>
-      <c r="AM49" s="33"/>
-      <c r="AN49" s="33"/>
-      <c r="AO49" s="33"/>
+      <c r="AJ49" s="50"/>
+      <c r="AK49" s="50"/>
+      <c r="AL49" s="50"/>
+      <c r="AM49" s="50"/>
+      <c r="AN49" s="50"/>
+      <c r="AO49" s="50"/>
     </row>
     <row r="53" spans="31:52" x14ac:dyDescent="0.2">
       <c r="AS53" s="15" t="s">
@@ -2269,20 +2565,20 @@
       </c>
     </row>
     <row r="58" spans="31:52" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="AS58" s="34"/>
-      <c r="AT58" s="34"/>
-      <c r="AU58" s="35" t="s">
+      <c r="AS58" s="52"/>
+      <c r="AT58" s="52"/>
+      <c r="AU58" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="AV58" s="35"/>
-      <c r="AW58" s="36" t="s">
+      <c r="AV58" s="51"/>
+      <c r="AW58" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="AX58" s="36"/>
-      <c r="AY58" s="35" t="s">
+      <c r="AX58" s="53"/>
+      <c r="AY58" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="AZ58" s="35"/>
+      <c r="AZ58" s="51"/>
     </row>
     <row r="59" spans="31:52" x14ac:dyDescent="0.2">
       <c r="AS59" s="15" t="s">
@@ -2322,13 +2618,13 @@
         <f>1/16</f>
         <v>6.25E-2</v>
       </c>
-      <c r="AW60" s="33"/>
-      <c r="AX60" s="33">
+      <c r="AW60" s="50"/>
+      <c r="AX60" s="50">
         <f>SUMPRODUCT(AV60:AV62,AT60:AT62)</f>
         <v>1.0993750000000002</v>
       </c>
-      <c r="AY60" s="33"/>
-      <c r="AZ60" s="33">
+      <c r="AY60" s="50"/>
+      <c r="AZ60" s="50">
         <f>$AT$62/AX60</f>
         <v>1.0505969300739058</v>
       </c>
@@ -2345,10 +2641,10 @@
         <f>0.5-AV60</f>
         <v>0.4375</v>
       </c>
-      <c r="AW61" s="33"/>
-      <c r="AX61" s="33"/>
-      <c r="AY61" s="33"/>
-      <c r="AZ61" s="33"/>
+      <c r="AW61" s="50"/>
+      <c r="AX61" s="50"/>
+      <c r="AY61" s="50"/>
+      <c r="AZ61" s="50"/>
     </row>
     <row r="62" spans="31:52" x14ac:dyDescent="0.2">
       <c r="AS62">
@@ -2361,10 +2657,10 @@
       <c r="AV62">
         <v>0.5</v>
       </c>
-      <c r="AW62" s="33"/>
-      <c r="AX62" s="33"/>
-      <c r="AY62" s="33"/>
-      <c r="AZ62" s="33"/>
+      <c r="AW62" s="50"/>
+      <c r="AX62" s="50"/>
+      <c r="AY62" s="50"/>
+      <c r="AZ62" s="50"/>
     </row>
     <row r="63" spans="31:52" x14ac:dyDescent="0.2">
       <c r="AW63" s="23"/>
@@ -2374,23 +2670,15 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="W23:Z23"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="Z25:Z27"/>
-    <mergeCell ref="Y25:Y27"/>
-    <mergeCell ref="X25:X27"/>
-    <mergeCell ref="W25:W27"/>
-    <mergeCell ref="O23:R23"/>
-    <mergeCell ref="S25:S27"/>
-    <mergeCell ref="T25:T27"/>
-    <mergeCell ref="U25:U27"/>
-    <mergeCell ref="V25:V27"/>
-    <mergeCell ref="S23:V23"/>
-    <mergeCell ref="AJ46:AJ49"/>
-    <mergeCell ref="AK46:AK49"/>
-    <mergeCell ref="AL46:AL49"/>
-    <mergeCell ref="AM46:AM49"/>
-    <mergeCell ref="AN46:AN49"/>
+    <mergeCell ref="AW60:AW62"/>
+    <mergeCell ref="AZ60:AZ62"/>
+    <mergeCell ref="AY60:AY62"/>
+    <mergeCell ref="AX60:AX62"/>
+    <mergeCell ref="AO46:AO49"/>
+    <mergeCell ref="AS58:AT58"/>
+    <mergeCell ref="AU58:AV58"/>
+    <mergeCell ref="AW58:AX58"/>
+    <mergeCell ref="AY58:AZ58"/>
     <mergeCell ref="AM37:AO37"/>
     <mergeCell ref="AE44:AF44"/>
     <mergeCell ref="AG44:AI44"/>
@@ -2405,15 +2693,23 @@
     <mergeCell ref="AL39:AL42"/>
     <mergeCell ref="AK39:AK42"/>
     <mergeCell ref="AJ39:AJ42"/>
-    <mergeCell ref="AW60:AW62"/>
-    <mergeCell ref="AZ60:AZ62"/>
-    <mergeCell ref="AY60:AY62"/>
-    <mergeCell ref="AX60:AX62"/>
-    <mergeCell ref="AO46:AO49"/>
-    <mergeCell ref="AS58:AT58"/>
-    <mergeCell ref="AU58:AV58"/>
-    <mergeCell ref="AW58:AX58"/>
-    <mergeCell ref="AY58:AZ58"/>
+    <mergeCell ref="AJ46:AJ49"/>
+    <mergeCell ref="AK46:AK49"/>
+    <mergeCell ref="AL46:AL49"/>
+    <mergeCell ref="AM46:AM49"/>
+    <mergeCell ref="AN46:AN49"/>
+    <mergeCell ref="W23:Z23"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="Z25:Z27"/>
+    <mergeCell ref="Y25:Y27"/>
+    <mergeCell ref="X25:X27"/>
+    <mergeCell ref="W25:W27"/>
+    <mergeCell ref="O23:R23"/>
+    <mergeCell ref="S25:S27"/>
+    <mergeCell ref="T25:T27"/>
+    <mergeCell ref="U25:U27"/>
+    <mergeCell ref="V25:V27"/>
+    <mergeCell ref="S23:V23"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2432,7 +2728,7 @@
       <c r="J4" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="O4" s="51" t="s">
+      <c r="O4" s="36" t="s">
         <v>94</v>
       </c>
     </row>
@@ -2466,27 +2762,27 @@
       <c r="B6" s="12">
         <v>2014</v>
       </c>
-      <c r="C6" s="48">
+      <c r="C6" s="33">
         <v>1150</v>
       </c>
-      <c r="D6" s="48">
+      <c r="D6" s="33">
         <v>2250</v>
       </c>
-      <c r="E6" s="48">
+      <c r="E6" s="33">
         <v>3000</v>
       </c>
       <c r="I6" s="12">
         <v>2014</v>
       </c>
-      <c r="J6" s="49">
+      <c r="J6" s="34">
         <f>C6/C13</f>
         <v>0.22330097087378642</v>
       </c>
-      <c r="K6" s="49">
+      <c r="K6" s="34">
         <f t="shared" ref="K6:L6" si="0">D6/D13</f>
         <v>0.3125</v>
       </c>
-      <c r="L6" s="49">
+      <c r="L6" s="34">
         <f t="shared" si="0"/>
         <v>0.375</v>
       </c>
@@ -2495,42 +2791,42 @@
       <c r="B7" s="12">
         <v>2015</v>
       </c>
-      <c r="C7" s="48">
+      <c r="C7" s="33">
         <v>1250</v>
       </c>
-      <c r="D7" s="48">
+      <c r="D7" s="33">
         <v>2400</v>
       </c>
       <c r="E7" s="12"/>
       <c r="I7" s="12">
         <v>2015</v>
       </c>
-      <c r="J7" s="49">
+      <c r="J7" s="34">
         <f>C7/C14</f>
         <v>0.26041666666666669</v>
       </c>
-      <c r="K7" s="49">
+      <c r="K7" s="34">
         <f>D7/D14</f>
         <v>0.35820895522388058</v>
       </c>
-      <c r="L7" s="50"/>
+      <c r="L7" s="35"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B8" s="12">
         <v>2016</v>
       </c>
-      <c r="C8" s="48">
+      <c r="C8" s="33">
         <v>1550</v>
       </c>
       <c r="D8" s="12"/>
       <c r="I8" s="12">
         <v>2016</v>
       </c>
-      <c r="J8" s="49">
+      <c r="J8" s="34">
         <f>C8/C15</f>
         <v>0.32631578947368423</v>
       </c>
-      <c r="K8" s="50"/>
+      <c r="K8" s="35"/>
       <c r="L8" s="22"/>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.2">
@@ -2540,7 +2836,7 @@
       <c r="J11" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="O11" s="51" t="s">
+      <c r="O11" s="36" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2574,27 +2870,27 @@
       <c r="B13" s="12">
         <v>2014</v>
       </c>
-      <c r="C13" s="48">
+      <c r="C13" s="33">
         <v>5150</v>
       </c>
-      <c r="D13" s="48">
+      <c r="D13" s="33">
         <v>7200</v>
       </c>
-      <c r="E13" s="48">
+      <c r="E13" s="33">
         <v>8000</v>
       </c>
       <c r="I13" s="12">
         <v>2014</v>
       </c>
-      <c r="J13" s="49">
+      <c r="J13" s="34">
         <f>(C20-C27)/C20</f>
         <v>0.49019607843137253</v>
       </c>
-      <c r="K13" s="49">
+      <c r="K13" s="34">
         <f t="shared" ref="K13:L13" si="1">(D20-D27)/D20</f>
         <v>0.73831775700934577</v>
       </c>
-      <c r="L13" s="49">
+      <c r="L13" s="34">
         <f t="shared" si="1"/>
         <v>0.88888888888888884</v>
       </c>
@@ -2603,42 +2899,42 @@
       <c r="B14" s="12">
         <v>2015</v>
       </c>
-      <c r="C14" s="48">
+      <c r="C14" s="33">
         <v>4800</v>
       </c>
-      <c r="D14" s="48">
+      <c r="D14" s="33">
         <v>6700</v>
       </c>
       <c r="E14" s="12"/>
       <c r="I14" s="12">
         <v>2015</v>
       </c>
-      <c r="J14" s="49">
-        <f t="shared" ref="J14:K15" si="2">(C21-C28)/C21</f>
+      <c r="J14" s="34">
+        <f t="shared" ref="J14:J15" si="2">(C21-C28)/C21</f>
         <v>0.52083333333333337</v>
       </c>
-      <c r="K14" s="49">
+      <c r="K14" s="34">
         <f>(D21-D28)/D21</f>
         <v>0.75247524752475248</v>
       </c>
-      <c r="L14" s="50"/>
+      <c r="L14" s="35"/>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B15" s="12">
         <v>2016</v>
       </c>
-      <c r="C15" s="48">
+      <c r="C15" s="33">
         <v>4750</v>
       </c>
       <c r="D15" s="12"/>
       <c r="I15" s="12">
         <v>2016</v>
       </c>
-      <c r="J15" s="49">
+      <c r="J15" s="34">
         <f t="shared" si="2"/>
         <v>0.5757575757575758</v>
       </c>
-      <c r="K15" s="50"/>
+      <c r="K15" s="35"/>
       <c r="L15" s="22"/>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.2">
@@ -2649,7 +2945,7 @@
       <c r="J18" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="O18" s="51" t="s">
+      <c r="O18" s="36" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2695,15 +2991,15 @@
       <c r="I20" s="12">
         <v>2014</v>
       </c>
-      <c r="J20" s="52">
+      <c r="J20" s="37">
         <f>(C13-C6)/C27</f>
         <v>76.92307692307692</v>
       </c>
-      <c r="K20" s="52">
+      <c r="K20" s="37">
         <f t="shared" ref="K20:L20" si="3">(D13-D6)/D27</f>
         <v>176.78571428571428</v>
       </c>
-      <c r="L20" s="52">
+      <c r="L20" s="37">
         <f t="shared" si="3"/>
         <v>416.66666666666669</v>
       </c>
@@ -2722,15 +3018,15 @@
       <c r="I21" s="12">
         <v>2015</v>
       </c>
-      <c r="J21" s="52">
+      <c r="J21" s="37">
         <f t="shared" ref="J21:K22" si="4">(C14-C7)/C28</f>
         <v>77.173913043478265</v>
       </c>
-      <c r="K21" s="52">
+      <c r="K21" s="37">
         <f t="shared" si="4"/>
         <v>172</v>
       </c>
-      <c r="L21" s="52"/>
+      <c r="L21" s="37"/>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B22" s="12">
@@ -2743,12 +3039,12 @@
       <c r="I22" s="12">
         <v>2016</v>
       </c>
-      <c r="J22" s="52">
+      <c r="J22" s="37">
         <f t="shared" si="4"/>
         <v>76.19047619047619</v>
       </c>
-      <c r="K22" s="52"/>
-      <c r="L22" s="53"/>
+      <c r="K22" s="37"/>
+      <c r="L22" s="38"/>
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C25" s="11" t="s">
@@ -2812,4 +3108,1737 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6AFCFE6-F211-E246-984A-FC86F03460FF}">
+  <dimension ref="B3:AC172"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="4" width="10.83203125" customWidth="1"/>
+    <col min="9" max="9" width="21.83203125" customWidth="1"/>
+    <col min="10" max="10" width="21" customWidth="1"/>
+    <col min="11" max="11" width="21.6640625" customWidth="1"/>
+    <col min="17" max="17" width="14.5" customWidth="1"/>
+    <col min="18" max="18" width="18" customWidth="1"/>
+    <col min="19" max="19" width="14.6640625" customWidth="1"/>
+    <col min="21" max="21" width="10.83203125" customWidth="1"/>
+    <col min="25" max="25" width="14.33203125" customWidth="1"/>
+    <col min="26" max="26" width="19" customWidth="1"/>
+    <col min="27" max="27" width="15.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B3" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B4" s="55"/>
+      <c r="C4" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B5" s="12">
+        <v>2017</v>
+      </c>
+      <c r="C5" s="12">
+        <v>231</v>
+      </c>
+      <c r="D5" s="12">
+        <v>82</v>
+      </c>
+      <c r="E5" s="12">
+        <v>51</v>
+      </c>
+      <c r="F5" s="12">
+        <v>32</v>
+      </c>
+      <c r="G5" s="12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B6" s="12">
+        <v>2018</v>
+      </c>
+      <c r="C6" s="12">
+        <v>218</v>
+      </c>
+      <c r="D6" s="12">
+        <v>77</v>
+      </c>
+      <c r="E6" s="12">
+        <v>46</v>
+      </c>
+      <c r="F6" s="12">
+        <v>30</v>
+      </c>
+      <c r="G6" s="12"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B7" s="12">
+        <v>2019</v>
+      </c>
+      <c r="C7" s="12">
+        <v>257</v>
+      </c>
+      <c r="D7" s="12">
+        <v>85</v>
+      </c>
+      <c r="E7" s="12">
+        <v>54</v>
+      </c>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B8" s="12">
+        <v>2020</v>
+      </c>
+      <c r="C8" s="12">
+        <v>290</v>
+      </c>
+      <c r="D8" s="12">
+        <v>96</v>
+      </c>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B9" s="12">
+        <v>2021</v>
+      </c>
+      <c r="C9" s="12">
+        <v>310</v>
+      </c>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B11" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B12" s="55"/>
+      <c r="C12" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B13" s="12">
+        <v>2017</v>
+      </c>
+      <c r="C13" s="12">
+        <f>SUM(C5)</f>
+        <v>231</v>
+      </c>
+      <c r="D13" s="12">
+        <f>SUM(C5:D5)</f>
+        <v>313</v>
+      </c>
+      <c r="E13" s="12">
+        <f>SUM(C5:E5)</f>
+        <v>364</v>
+      </c>
+      <c r="F13" s="12">
+        <f>SUM(C5:F5)</f>
+        <v>396</v>
+      </c>
+      <c r="G13" s="12">
+        <f>SUM(C5:G5)</f>
+        <v>410</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B14" s="12">
+        <v>2018</v>
+      </c>
+      <c r="C14" s="12">
+        <f>SUM(C6)</f>
+        <v>218</v>
+      </c>
+      <c r="D14" s="12">
+        <f t="shared" ref="D14:D16" si="0">SUM(C6:D6)</f>
+        <v>295</v>
+      </c>
+      <c r="E14" s="12">
+        <f t="shared" ref="E14:E15" si="1">SUM(C6:E6)</f>
+        <v>341</v>
+      </c>
+      <c r="F14" s="12">
+        <f>SUM(C6:F6)</f>
+        <v>371</v>
+      </c>
+      <c r="G14" s="12"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B15" s="12">
+        <v>2019</v>
+      </c>
+      <c r="C15" s="12">
+        <f>SUM(C7)</f>
+        <v>257</v>
+      </c>
+      <c r="D15" s="12">
+        <f t="shared" si="0"/>
+        <v>342</v>
+      </c>
+      <c r="E15" s="12">
+        <f t="shared" si="1"/>
+        <v>396</v>
+      </c>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B16" s="12">
+        <v>2020</v>
+      </c>
+      <c r="C16" s="12">
+        <f>SUM(C8)</f>
+        <v>290</v>
+      </c>
+      <c r="D16" s="12">
+        <f t="shared" si="0"/>
+        <v>386</v>
+      </c>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B18" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B19" s="55"/>
+      <c r="C19" s="56" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" s="57" t="s">
+        <v>104</v>
+      </c>
+      <c r="E19" s="57" t="s">
+        <v>105</v>
+      </c>
+      <c r="F19" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="G19" s="11"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B20" s="12">
+        <v>2017</v>
+      </c>
+      <c r="C20" s="58">
+        <f>D13/C13</f>
+        <v>1.3549783549783549</v>
+      </c>
+      <c r="D20" s="58">
+        <f t="shared" ref="D20:F21" si="2">E13/D13</f>
+        <v>1.1629392971246006</v>
+      </c>
+      <c r="E20" s="58">
+        <f t="shared" si="2"/>
+        <v>1.0879120879120878</v>
+      </c>
+      <c r="F20" s="58">
+        <f t="shared" si="2"/>
+        <v>1.0353535353535352</v>
+      </c>
+      <c r="G20" s="12"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B21" s="12">
+        <v>2018</v>
+      </c>
+      <c r="C21" s="58">
+        <f t="shared" ref="C21:D23" si="3">D14/C14</f>
+        <v>1.3532110091743119</v>
+      </c>
+      <c r="D21" s="58">
+        <f t="shared" si="3"/>
+        <v>1.1559322033898305</v>
+      </c>
+      <c r="E21" s="58">
+        <f>F14/E14</f>
+        <v>1.0879765395894427</v>
+      </c>
+      <c r="F21" s="35"/>
+      <c r="G21" s="12"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B22" s="12">
+        <v>2019</v>
+      </c>
+      <c r="C22" s="58">
+        <f t="shared" si="3"/>
+        <v>1.3307392996108949</v>
+      </c>
+      <c r="D22" s="58">
+        <f t="shared" si="3"/>
+        <v>1.1578947368421053</v>
+      </c>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="12" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B23" s="12">
+        <v>2020</v>
+      </c>
+      <c r="C23" s="58">
+        <f t="shared" si="3"/>
+        <v>1.3310344827586207</v>
+      </c>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="12"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B25" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B26" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C26" s="60">
+        <f>SUM(D13:D16)/SUM(C13:C16)</f>
+        <v>1.3413654618473896</v>
+      </c>
+      <c r="D26" s="36" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B27" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C27" s="60">
+        <f>SUM(E13:E15)/SUM(D13:D15)</f>
+        <v>1.1589473684210527</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B28" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" s="60">
+        <f>SUM(F13:F14)/SUM(E13:E14)</f>
+        <v>1.0879432624113474</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B29" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C29" s="60">
+        <f>G13/F13</f>
+        <v>1.0353535353535352</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B30" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C30">
+        <v>1.02</v>
+      </c>
+      <c r="D30" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B32" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B33" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C33" s="60">
+        <f>PRODUCT(C26:C30)</f>
+        <v>1.786100626933401</v>
+      </c>
+      <c r="D33" s="36" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B34" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C34" s="60">
+        <f>PRODUCT(C27:C30)</f>
+        <v>1.3315540601988531</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B35" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C35" s="60">
+        <f>PRODUCT(C28:C30)</f>
+        <v>1.1489340210616805</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B36" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C36" s="60">
+        <f>PRODUCT(C29:C30)</f>
+        <v>1.0560606060606059</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B37" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C37" s="60">
+        <f>PRODUCT(C30:C30)</f>
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="B39" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="C39" s="61" t="s">
+        <v>129</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B40" s="65" t="s">
+        <v>121</v>
+      </c>
+      <c r="C40" s="66">
+        <v>310</v>
+      </c>
+      <c r="D40" s="67">
+        <f>C40*C33</f>
+        <v>553.6911943493543</v>
+      </c>
+      <c r="E40" s="68" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B41" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C41">
+        <v>96</v>
+      </c>
+      <c r="D41" s="62">
+        <f t="shared" ref="D41:D44" si="4">C41*C34</f>
+        <v>127.8291897790899</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B42" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="C42">
+        <v>54</v>
+      </c>
+      <c r="D42" s="62">
+        <f t="shared" si="4"/>
+        <v>62.042437137330751</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B43" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C43">
+        <v>30</v>
+      </c>
+      <c r="D43" s="62">
+        <f t="shared" si="4"/>
+        <v>31.681818181818176</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B44" s="63" t="s">
+        <v>125</v>
+      </c>
+      <c r="C44" s="1">
+        <v>14</v>
+      </c>
+      <c r="D44" s="64">
+        <f>C44*C37</f>
+        <v>14.280000000000001</v>
+      </c>
+      <c r="E44" s="1"/>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B45" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="80">
+        <f>SUM(C40:C44)</f>
+        <v>504</v>
+      </c>
+      <c r="D45" s="62">
+        <f>SUM(D40:D44)</f>
+        <v>789.52463944759313</v>
+      </c>
+      <c r="E45" s="36" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="49" spans="9:13" x14ac:dyDescent="0.2">
+      <c r="I49" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="J49" s="11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="50" spans="9:13" x14ac:dyDescent="0.2">
+      <c r="I50" s="55"/>
+      <c r="J50" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="K50" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="L50" s="15" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="51" spans="9:13" x14ac:dyDescent="0.2">
+      <c r="I51" s="12">
+        <v>2009</v>
+      </c>
+      <c r="J51" s="69">
+        <v>16000</v>
+      </c>
+      <c r="K51" s="69">
+        <v>3000</v>
+      </c>
+      <c r="L51" s="70">
+        <f>SUM(J51:K51)</f>
+        <v>19000</v>
+      </c>
+      <c r="M51" s="36" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="52" spans="9:13" x14ac:dyDescent="0.2">
+      <c r="I52" s="12">
+        <v>2010</v>
+      </c>
+      <c r="J52" s="69">
+        <v>12000</v>
+      </c>
+      <c r="K52" s="69">
+        <v>4000</v>
+      </c>
+      <c r="L52" s="70">
+        <f t="shared" ref="L52:L54" si="5">SUM(J52:K52)</f>
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="53" spans="9:13" x14ac:dyDescent="0.2">
+      <c r="I53" s="12">
+        <v>2011</v>
+      </c>
+      <c r="J53" s="69">
+        <v>10000</v>
+      </c>
+      <c r="K53" s="69">
+        <v>7000</v>
+      </c>
+      <c r="L53" s="70">
+        <f t="shared" si="5"/>
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="54" spans="9:13" x14ac:dyDescent="0.2">
+      <c r="I54" s="12">
+        <v>2012</v>
+      </c>
+      <c r="J54" s="69">
+        <v>5000</v>
+      </c>
+      <c r="K54" s="69">
+        <v>8000</v>
+      </c>
+      <c r="L54" s="70">
+        <f t="shared" si="5"/>
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="55" spans="9:13" x14ac:dyDescent="0.2">
+      <c r="L55" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="56" spans="9:13" x14ac:dyDescent="0.2">
+      <c r="I56" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="J56" s="15" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="57" spans="9:13" x14ac:dyDescent="0.2">
+      <c r="I57" s="71" t="s">
+        <v>103</v>
+      </c>
+      <c r="J57" s="72">
+        <v>1.2</v>
+      </c>
+      <c r="K57" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="58" spans="9:13" x14ac:dyDescent="0.2">
+      <c r="I58" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J58">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="K58" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="59" spans="9:13" x14ac:dyDescent="0.2">
+      <c r="I59" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="J59" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="K59" s="59"/>
+    </row>
+    <row r="60" spans="9:13" x14ac:dyDescent="0.2">
+      <c r="I60" s="3"/>
+      <c r="J60" s="73"/>
+      <c r="K60" s="59"/>
+    </row>
+    <row r="61" spans="9:13" x14ac:dyDescent="0.2">
+      <c r="I61" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="J61" s="73"/>
+      <c r="K61" s="59"/>
+    </row>
+    <row r="63" spans="9:13" x14ac:dyDescent="0.2">
+      <c r="I63" s="15" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="64" spans="9:13" x14ac:dyDescent="0.2">
+      <c r="I64" s="69">
+        <v>18000</v>
+      </c>
+      <c r="J64" s="74" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="65" spans="9:23" x14ac:dyDescent="0.2">
+      <c r="I65" t="s">
+        <v>112</v>
+      </c>
+      <c r="J65" t="s">
+        <v>141</v>
+      </c>
+      <c r="K65" s="60">
+        <f>I64/L52</f>
+        <v>1.125</v>
+      </c>
+      <c r="L65" s="3"/>
+    </row>
+    <row r="67" spans="9:23" x14ac:dyDescent="0.2">
+      <c r="I67" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="J67" s="15" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="68" spans="9:23" x14ac:dyDescent="0.2">
+      <c r="I68" s="69">
+        <v>17000</v>
+      </c>
+      <c r="J68" s="75">
+        <f>I68*PRODUCT(J58,K65)</f>
+        <v>21993.75</v>
+      </c>
+      <c r="K68" s="74" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="69" spans="9:23" x14ac:dyDescent="0.2">
+      <c r="I69" t="s">
+        <v>112</v>
+      </c>
+      <c r="K69" s="60"/>
+    </row>
+    <row r="73" spans="9:23" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" spans="9:23" x14ac:dyDescent="0.2">
+      <c r="Q74" s="77" t="s">
+        <v>149</v>
+      </c>
+      <c r="R74" s="77" t="s">
+        <v>96</v>
+      </c>
+      <c r="S74" s="76" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="75" spans="9:23" x14ac:dyDescent="0.2">
+      <c r="Q75" s="77"/>
+      <c r="R75" s="77"/>
+      <c r="S75" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="76" spans="9:23" x14ac:dyDescent="0.2">
+      <c r="Q76" s="77"/>
+      <c r="R76" s="77"/>
+      <c r="S76" s="11">
+        <v>12</v>
+      </c>
+      <c r="T76" s="11">
+        <v>24</v>
+      </c>
+      <c r="U76" s="11">
+        <v>36</v>
+      </c>
+      <c r="V76" s="11">
+        <v>48</v>
+      </c>
+      <c r="W76" s="11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="77" spans="9:23" x14ac:dyDescent="0.2">
+      <c r="Q77" s="33">
+        <v>50000</v>
+      </c>
+      <c r="R77" s="12">
+        <v>2010</v>
+      </c>
+      <c r="S77" s="12">
+        <v>500</v>
+      </c>
+      <c r="T77" s="12">
+        <v>550</v>
+      </c>
+      <c r="U77" s="12">
+        <v>660</v>
+      </c>
+      <c r="V77" s="12">
+        <v>660</v>
+      </c>
+      <c r="W77" s="12">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="78" spans="9:23" x14ac:dyDescent="0.2">
+      <c r="Q78" s="33">
+        <v>50000</v>
+      </c>
+      <c r="R78" s="12">
+        <v>2011</v>
+      </c>
+      <c r="S78" s="12">
+        <v>465</v>
+      </c>
+      <c r="T78" s="12">
+        <v>545</v>
+      </c>
+      <c r="U78" s="12">
+        <v>645</v>
+      </c>
+      <c r="V78" s="12">
+        <v>645</v>
+      </c>
+      <c r="W78" s="12"/>
+    </row>
+    <row r="79" spans="9:23" x14ac:dyDescent="0.2">
+      <c r="Q79" s="33">
+        <v>50000</v>
+      </c>
+      <c r="R79" s="12">
+        <v>2012</v>
+      </c>
+      <c r="S79" s="12">
+        <v>500</v>
+      </c>
+      <c r="T79" s="12">
+        <v>540</v>
+      </c>
+      <c r="U79" s="12">
+        <v>675</v>
+      </c>
+      <c r="V79" s="12"/>
+      <c r="W79" s="12"/>
+    </row>
+    <row r="80" spans="9:23" x14ac:dyDescent="0.2">
+      <c r="Q80" s="33">
+        <v>50000</v>
+      </c>
+      <c r="R80" s="12">
+        <v>2013</v>
+      </c>
+      <c r="S80" s="12">
+        <v>500</v>
+      </c>
+      <c r="T80" s="12">
+        <v>545</v>
+      </c>
+      <c r="U80" s="12"/>
+      <c r="V80" s="12"/>
+      <c r="W80" s="12"/>
+    </row>
+    <row r="81" spans="17:23" x14ac:dyDescent="0.2">
+      <c r="Q81" s="33">
+        <v>50000</v>
+      </c>
+      <c r="R81" s="12">
+        <v>2014</v>
+      </c>
+      <c r="S81" s="12">
+        <v>510</v>
+      </c>
+      <c r="T81" s="12"/>
+      <c r="U81" s="12"/>
+    </row>
+    <row r="83" spans="17:23" x14ac:dyDescent="0.2">
+      <c r="Q83" s="77" t="s">
+        <v>149</v>
+      </c>
+      <c r="R83" s="77" t="s">
+        <v>96</v>
+      </c>
+      <c r="S83" s="76" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="84" spans="17:23" x14ac:dyDescent="0.2">
+      <c r="Q84" s="77"/>
+      <c r="R84" s="77"/>
+      <c r="S84" s="11" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="85" spans="17:23" x14ac:dyDescent="0.2">
+      <c r="Q85" s="77"/>
+      <c r="R85" s="77"/>
+      <c r="S85" s="56" t="s">
+        <v>103</v>
+      </c>
+      <c r="T85" s="57" t="s">
+        <v>104</v>
+      </c>
+      <c r="U85" s="57" t="s">
+        <v>105</v>
+      </c>
+      <c r="V85" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="W85" s="11"/>
+    </row>
+    <row r="86" spans="17:23" x14ac:dyDescent="0.2">
+      <c r="Q86" s="33">
+        <v>50000</v>
+      </c>
+      <c r="R86" s="12">
+        <v>2010</v>
+      </c>
+      <c r="S86" s="58">
+        <f>T77/S77</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="T86" s="58">
+        <f t="shared" ref="T86:V86" si="6">U77/T77</f>
+        <v>1.2</v>
+      </c>
+      <c r="U86" s="58">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="V86" s="58">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="W86" s="12"/>
+    </row>
+    <row r="87" spans="17:23" x14ac:dyDescent="0.2">
+      <c r="Q87" s="33">
+        <v>50000</v>
+      </c>
+      <c r="R87" s="12">
+        <v>2011</v>
+      </c>
+      <c r="S87" s="58">
+        <f t="shared" ref="S87:U89" si="7">T78/S78</f>
+        <v>1.1720430107526882</v>
+      </c>
+      <c r="T87" s="58">
+        <f t="shared" si="7"/>
+        <v>1.1834862385321101</v>
+      </c>
+      <c r="U87" s="58">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="V87" s="35"/>
+      <c r="W87" s="12"/>
+    </row>
+    <row r="88" spans="17:23" x14ac:dyDescent="0.2">
+      <c r="Q88" s="33">
+        <v>50000</v>
+      </c>
+      <c r="R88" s="12">
+        <v>2012</v>
+      </c>
+      <c r="S88" s="58">
+        <f t="shared" si="7"/>
+        <v>1.08</v>
+      </c>
+      <c r="T88" s="58">
+        <f t="shared" si="7"/>
+        <v>1.25</v>
+      </c>
+      <c r="U88" s="78"/>
+      <c r="V88" s="35"/>
+      <c r="W88" s="12"/>
+    </row>
+    <row r="89" spans="17:23" x14ac:dyDescent="0.2">
+      <c r="Q89" s="33">
+        <v>50000</v>
+      </c>
+      <c r="R89" s="12">
+        <v>2013</v>
+      </c>
+      <c r="S89" s="58">
+        <f t="shared" si="7"/>
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="T89" s="58"/>
+      <c r="U89" s="35"/>
+      <c r="V89" s="35"/>
+      <c r="W89" s="12"/>
+    </row>
+    <row r="90" spans="17:23" x14ac:dyDescent="0.2">
+      <c r="Q90" s="33"/>
+      <c r="R90" s="12"/>
+      <c r="S90" s="12"/>
+      <c r="T90" s="12"/>
+      <c r="U90" s="12"/>
+    </row>
+    <row r="91" spans="17:23" x14ac:dyDescent="0.2">
+      <c r="Q91" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="R91" s="15" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="92" spans="17:23" x14ac:dyDescent="0.2">
+      <c r="Q92" s="56" t="s">
+        <v>103</v>
+      </c>
+      <c r="R92" s="60">
+        <f>AVERAGE(S86,S89)</f>
+        <v>1.0950000000000002</v>
+      </c>
+    </row>
+    <row r="93" spans="17:23" x14ac:dyDescent="0.2">
+      <c r="Q93" s="57" t="s">
+        <v>104</v>
+      </c>
+      <c r="R93" s="60">
+        <f>AVERAGE(T86)</f>
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="94" spans="17:23" x14ac:dyDescent="0.2">
+      <c r="Q94" s="57" t="s">
+        <v>105</v>
+      </c>
+      <c r="R94" s="60">
+        <f>AVERAGE(U86:U87)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="17:23" x14ac:dyDescent="0.2">
+      <c r="Q95" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="R95" s="60">
+        <f>AVERAGE(V86)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="17:22" x14ac:dyDescent="0.2">
+      <c r="Q97" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="R97" s="15" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="98" spans="17:22" x14ac:dyDescent="0.2">
+      <c r="Q98" s="56" t="s">
+        <v>103</v>
+      </c>
+      <c r="R98" s="60">
+        <f>PRODUCT(R92:R95)</f>
+        <v>1.3140000000000003</v>
+      </c>
+      <c r="S98" s="36" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="99" spans="17:22" x14ac:dyDescent="0.2">
+      <c r="Q99" s="57" t="s">
+        <v>104</v>
+      </c>
+      <c r="R99" s="60">
+        <f>PRODUCT(R93:R95)</f>
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="100" spans="17:22" x14ac:dyDescent="0.2">
+      <c r="Q100" s="57" t="s">
+        <v>105</v>
+      </c>
+      <c r="R100" s="60">
+        <f>PRODUCT(R94:R95)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="17:22" x14ac:dyDescent="0.2">
+      <c r="Q101" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="R101" s="60">
+        <f>PRODUCT(R95)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="17:22" x14ac:dyDescent="0.2">
+      <c r="Q103" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="R103" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="S103" s="15" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="104" spans="17:22" x14ac:dyDescent="0.2">
+      <c r="Q104" s="79" t="s">
+        <v>121</v>
+      </c>
+      <c r="R104">
+        <v>510</v>
+      </c>
+      <c r="S104" s="62">
+        <f>R104*R98</f>
+        <v>670.1400000000001</v>
+      </c>
+      <c r="T104" s="36" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="105" spans="17:22" x14ac:dyDescent="0.2">
+      <c r="Q105" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="R105">
+        <v>545</v>
+      </c>
+      <c r="S105" s="62">
+        <f t="shared" ref="S105:S108" si="8">R105*R99</f>
+        <v>654</v>
+      </c>
+    </row>
+    <row r="106" spans="17:22" x14ac:dyDescent="0.2">
+      <c r="Q106" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="R106">
+        <v>675</v>
+      </c>
+      <c r="S106" s="62">
+        <f t="shared" si="8"/>
+        <v>675</v>
+      </c>
+    </row>
+    <row r="107" spans="17:22" x14ac:dyDescent="0.2">
+      <c r="Q107" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="R107">
+        <v>645</v>
+      </c>
+      <c r="S107" s="62">
+        <f t="shared" si="8"/>
+        <v>645</v>
+      </c>
+    </row>
+    <row r="108" spans="17:22" x14ac:dyDescent="0.2">
+      <c r="Q108" s="63" t="s">
+        <v>125</v>
+      </c>
+      <c r="R108" s="1">
+        <v>660</v>
+      </c>
+      <c r="S108" s="64">
+        <f>R108</f>
+        <v>660</v>
+      </c>
+    </row>
+    <row r="109" spans="17:22" x14ac:dyDescent="0.2">
+      <c r="Q109" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="R109" s="80">
+        <f>SUM(R104:R108)</f>
+        <v>3035</v>
+      </c>
+      <c r="S109" s="62">
+        <f>SUM(S104:S108)</f>
+        <v>3304.1400000000003</v>
+      </c>
+      <c r="T109" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="U109" s="81">
+        <f>S109-R109</f>
+        <v>269.14000000000033</v>
+      </c>
+      <c r="V109" s="36" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="116" spans="25:29" x14ac:dyDescent="0.2">
+      <c r="Y116" s="54" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z116" s="54"/>
+      <c r="AA116" s="54"/>
+      <c r="AB116" s="54"/>
+      <c r="AC116" s="54"/>
+    </row>
+    <row r="117" spans="25:29" x14ac:dyDescent="0.2">
+      <c r="Y117" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z117" s="76" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="118" spans="25:29" x14ac:dyDescent="0.2">
+      <c r="Y118" s="55"/>
+      <c r="Z118" s="11">
+        <v>12</v>
+      </c>
+      <c r="AA118" s="11">
+        <v>24</v>
+      </c>
+      <c r="AB118" s="11">
+        <v>36</v>
+      </c>
+      <c r="AC118" s="11">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="119" spans="25:29" x14ac:dyDescent="0.2">
+      <c r="Y119" s="12">
+        <v>2012</v>
+      </c>
+      <c r="Z119" s="12">
+        <v>850</v>
+      </c>
+      <c r="AA119" s="12">
+        <v>950</v>
+      </c>
+      <c r="AB119" s="33">
+        <v>1950</v>
+      </c>
+      <c r="AC119" s="33">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="120" spans="25:29" x14ac:dyDescent="0.2">
+      <c r="Y120" s="12">
+        <v>2013</v>
+      </c>
+      <c r="Z120" s="12">
+        <v>700</v>
+      </c>
+      <c r="AA120" s="33">
+        <v>2200</v>
+      </c>
+      <c r="AB120" s="33">
+        <v>3300</v>
+      </c>
+      <c r="AC120" s="12"/>
+    </row>
+    <row r="121" spans="25:29" x14ac:dyDescent="0.2">
+      <c r="Y121" s="12">
+        <v>2014</v>
+      </c>
+      <c r="Z121" s="12">
+        <v>900</v>
+      </c>
+      <c r="AA121" s="33">
+        <v>1600</v>
+      </c>
+      <c r="AB121" s="12"/>
+      <c r="AC121" s="12"/>
+    </row>
+    <row r="122" spans="25:29" x14ac:dyDescent="0.2">
+      <c r="Y122" s="12">
+        <v>2015</v>
+      </c>
+      <c r="Z122" s="33">
+        <v>1000</v>
+      </c>
+      <c r="AA122" s="12"/>
+      <c r="AB122" s="12"/>
+    </row>
+    <row r="124" spans="25:29" x14ac:dyDescent="0.2">
+      <c r="Y124" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z124" s="76" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="125" spans="25:29" x14ac:dyDescent="0.2">
+      <c r="Y125" s="55"/>
+      <c r="Z125" s="57" t="s">
+        <v>103</v>
+      </c>
+      <c r="AA125" s="57" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB125" s="57" t="s">
+        <v>105</v>
+      </c>
+      <c r="AC125" s="11"/>
+    </row>
+    <row r="126" spans="25:29" x14ac:dyDescent="0.2">
+      <c r="Y126" s="12">
+        <v>2012</v>
+      </c>
+      <c r="Z126" s="58">
+        <f>AA119/Z119</f>
+        <v>1.1176470588235294</v>
+      </c>
+      <c r="AA126" s="58">
+        <f t="shared" ref="AA126:AB127" si="9">AB119/AA119</f>
+        <v>2.0526315789473686</v>
+      </c>
+      <c r="AB126" s="58">
+        <f t="shared" si="9"/>
+        <v>1.2564102564102564</v>
+      </c>
+      <c r="AC126" s="33"/>
+    </row>
+    <row r="127" spans="25:29" x14ac:dyDescent="0.2">
+      <c r="Y127" s="12">
+        <v>2013</v>
+      </c>
+      <c r="Z127" s="58">
+        <f t="shared" ref="Z127:Z128" si="10">AA120/Z120</f>
+        <v>3.1428571428571428</v>
+      </c>
+      <c r="AA127" s="58">
+        <f t="shared" si="9"/>
+        <v>1.5</v>
+      </c>
+      <c r="AB127" s="58"/>
+      <c r="AC127" s="12"/>
+    </row>
+    <row r="128" spans="25:29" x14ac:dyDescent="0.2">
+      <c r="Y128" s="12">
+        <v>2014</v>
+      </c>
+      <c r="Z128" s="58">
+        <f t="shared" si="10"/>
+        <v>1.7777777777777777</v>
+      </c>
+      <c r="AA128" s="58"/>
+      <c r="AB128" s="58"/>
+      <c r="AC128" s="12"/>
+    </row>
+    <row r="129" spans="25:29" x14ac:dyDescent="0.2">
+      <c r="Y129" s="12"/>
+      <c r="Z129" s="33"/>
+      <c r="AA129" s="12"/>
+      <c r="AB129" s="12"/>
+    </row>
+    <row r="130" spans="25:29" x14ac:dyDescent="0.2">
+      <c r="Y130" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z130" s="15" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="131" spans="25:29" x14ac:dyDescent="0.2">
+      <c r="Y131" s="82" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z131" s="60">
+        <f>AVERAGE(Z126:Z128)</f>
+        <v>2.0127606598194832</v>
+      </c>
+      <c r="AA131" s="36" t="s">
+        <v>161</v>
+      </c>
+      <c r="AC131" s="36" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="132" spans="25:29" x14ac:dyDescent="0.2">
+      <c r="Y132" s="82" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z132" s="60">
+        <f>AVERAGE(AA126:AA127)</f>
+        <v>1.7763157894736843</v>
+      </c>
+      <c r="AA132" s="36" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="133" spans="25:29" x14ac:dyDescent="0.2">
+      <c r="Y133" s="82" t="s">
+        <v>105</v>
+      </c>
+      <c r="Z133" s="60">
+        <f>AVERAGE(AB126)</f>
+        <v>1.2564102564102564</v>
+      </c>
+    </row>
+    <row r="135" spans="25:29" x14ac:dyDescent="0.2">
+      <c r="Y135" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="Z135" s="15" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="136" spans="25:29" x14ac:dyDescent="0.2">
+      <c r="Y136" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z136" s="60">
+        <f>PRODUCT(Z131:Z133)</f>
+        <v>4.4920417559736441</v>
+      </c>
+      <c r="AA136" s="36" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="137" spans="25:29" x14ac:dyDescent="0.2">
+      <c r="Y137" t="s">
+        <v>163</v>
+      </c>
+      <c r="Z137" s="60">
+        <f>PRODUCT(Z132:Z133)</f>
+        <v>2.2317813765182186</v>
+      </c>
+    </row>
+    <row r="138" spans="25:29" x14ac:dyDescent="0.2">
+      <c r="Y138" t="s">
+        <v>164</v>
+      </c>
+      <c r="Z138" s="60">
+        <f>PRODUCT(Z133)</f>
+        <v>1.2564102564102564</v>
+      </c>
+    </row>
+    <row r="140" spans="25:29" x14ac:dyDescent="0.2">
+      <c r="Y140" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="Z140" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA140" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="141" spans="25:29" x14ac:dyDescent="0.2">
+      <c r="Y141">
+        <v>12</v>
+      </c>
+      <c r="Z141">
+        <v>1000</v>
+      </c>
+      <c r="AA141" s="67">
+        <f t="shared" ref="AA141:AA142" si="11">Z141*Z136</f>
+        <v>4492.0417559736443</v>
+      </c>
+      <c r="AB141" s="36" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="142" spans="25:29" x14ac:dyDescent="0.2">
+      <c r="Y142">
+        <v>24</v>
+      </c>
+      <c r="Z142">
+        <v>1600</v>
+      </c>
+      <c r="AA142" s="62">
+        <f t="shared" si="11"/>
+        <v>3570.8502024291497</v>
+      </c>
+    </row>
+    <row r="143" spans="25:29" x14ac:dyDescent="0.2">
+      <c r="Y143">
+        <v>36</v>
+      </c>
+      <c r="Z143">
+        <v>3300</v>
+      </c>
+      <c r="AA143" s="62">
+        <f>Z143*Z138</f>
+        <v>4146.1538461538457</v>
+      </c>
+    </row>
+    <row r="144" spans="25:29" x14ac:dyDescent="0.2">
+      <c r="Y144" s="1">
+        <v>48</v>
+      </c>
+      <c r="Z144" s="1">
+        <v>2450</v>
+      </c>
+      <c r="AA144" s="64">
+        <f>Z144</f>
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="145" spans="25:28" x14ac:dyDescent="0.2">
+      <c r="Y145" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z145" s="80">
+        <f>SUM(Z141:Z144)</f>
+        <v>8350</v>
+      </c>
+      <c r="AA145" s="62">
+        <f>SUM(AA141:AA144)</f>
+        <v>14659.045804556639</v>
+      </c>
+    </row>
+    <row r="148" spans="25:28" x14ac:dyDescent="0.2">
+      <c r="Y148" s="3"/>
+    </row>
+    <row r="150" spans="25:28" x14ac:dyDescent="0.2">
+      <c r="Y150" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z150" s="51"/>
+      <c r="AA150" s="51"/>
+      <c r="AB150" s="51"/>
+    </row>
+    <row r="151" spans="25:28" x14ac:dyDescent="0.2">
+      <c r="Y151" s="83" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z151" s="76" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="152" spans="25:28" x14ac:dyDescent="0.2">
+      <c r="Y152" s="83"/>
+      <c r="Z152" s="57" t="s">
+        <v>103</v>
+      </c>
+      <c r="AA152" s="57" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB152" s="57" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="153" spans="25:28" x14ac:dyDescent="0.2">
+      <c r="Y153" s="12">
+        <v>2012</v>
+      </c>
+      <c r="Z153" s="12">
+        <v>1.97</v>
+      </c>
+      <c r="AA153" s="12">
+        <v>1.24</v>
+      </c>
+      <c r="AB153" s="12">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="154" spans="25:28" x14ac:dyDescent="0.2">
+      <c r="Y154" s="12">
+        <v>2013</v>
+      </c>
+      <c r="Z154" s="12">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AA154" s="12">
+        <v>1.27</v>
+      </c>
+      <c r="AB154" s="12"/>
+    </row>
+    <row r="155" spans="25:28" x14ac:dyDescent="0.2">
+      <c r="Y155" s="12">
+        <v>2014</v>
+      </c>
+      <c r="Z155" s="12">
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="AA155" s="12"/>
+    </row>
+    <row r="157" spans="25:28" x14ac:dyDescent="0.2">
+      <c r="Y157" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z157" s="15" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="158" spans="25:28" x14ac:dyDescent="0.2">
+      <c r="Y158" s="82" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z158" s="60">
+        <f>AVERAGE(Z153:Z155)</f>
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="AA158" s="36" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="159" spans="25:28" x14ac:dyDescent="0.2">
+      <c r="Y159" s="82" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z159" s="60">
+        <f>AVERAGE(AA153:AA154)</f>
+        <v>1.2549999999999999</v>
+      </c>
+    </row>
+    <row r="160" spans="25:28" x14ac:dyDescent="0.2">
+      <c r="Y160" s="82" t="s">
+        <v>105</v>
+      </c>
+      <c r="Z160" s="60">
+        <f>AVERAGE(AB153)</f>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="162" spans="25:28" x14ac:dyDescent="0.2">
+      <c r="Y162" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="Z162" s="15" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="163" spans="25:28" x14ac:dyDescent="0.2">
+      <c r="Y163" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z163" s="60">
+        <f>PRODUCT(Z158:Z160)</f>
+        <v>2.7748049999999997</v>
+      </c>
+      <c r="AA163" s="36" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="164" spans="25:28" x14ac:dyDescent="0.2">
+      <c r="Y164" t="s">
+        <v>163</v>
+      </c>
+      <c r="Z164" s="60">
+        <f>PRODUCT(Z159:Z160)</f>
+        <v>1.3805000000000001</v>
+      </c>
+    </row>
+    <row r="165" spans="25:28" x14ac:dyDescent="0.2">
+      <c r="Y165" t="s">
+        <v>164</v>
+      </c>
+      <c r="Z165" s="60">
+        <f>PRODUCT(Z160)</f>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="167" spans="25:28" x14ac:dyDescent="0.2">
+      <c r="Y167" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="Z167" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA167" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="168" spans="25:28" x14ac:dyDescent="0.2">
+      <c r="Y168">
+        <v>12</v>
+      </c>
+      <c r="Z168">
+        <v>1000</v>
+      </c>
+      <c r="AA168" s="67">
+        <f>Z168*Z163</f>
+        <v>2774.8049999999998</v>
+      </c>
+      <c r="AB168" s="36" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="169" spans="25:28" x14ac:dyDescent="0.2">
+      <c r="Y169">
+        <v>24</v>
+      </c>
+      <c r="Z169">
+        <v>1600</v>
+      </c>
+      <c r="AA169" s="62">
+        <f t="shared" ref="AA168:AA169" si="12">Z169*Z164</f>
+        <v>2208.8000000000002</v>
+      </c>
+    </row>
+    <row r="170" spans="25:28" x14ac:dyDescent="0.2">
+      <c r="Y170">
+        <v>36</v>
+      </c>
+      <c r="Z170">
+        <v>3300</v>
+      </c>
+      <c r="AA170" s="62">
+        <f>Z170*Z165</f>
+        <v>3630.0000000000005</v>
+      </c>
+    </row>
+    <row r="171" spans="25:28" x14ac:dyDescent="0.2">
+      <c r="Y171" s="1">
+        <v>48</v>
+      </c>
+      <c r="Z171" s="1">
+        <v>2450</v>
+      </c>
+      <c r="AA171" s="64">
+        <f>Z171</f>
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="172" spans="25:28" x14ac:dyDescent="0.2">
+      <c r="Y172" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z172" s="80">
+        <f>SUM(Z168:Z171)</f>
+        <v>8350</v>
+      </c>
+      <c r="AA172" s="62">
+        <f>SUM(AA168:AA171)</f>
+        <v>11063.605</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="Y124:Y125"/>
+    <mergeCell ref="Y151:Y152"/>
+    <mergeCell ref="Y150:AB150"/>
+    <mergeCell ref="R74:R76"/>
+    <mergeCell ref="Q74:Q76"/>
+    <mergeCell ref="Q83:Q85"/>
+    <mergeCell ref="R83:R85"/>
+    <mergeCell ref="Y117:Y118"/>
+    <mergeCell ref="Y116:AC116"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="I49:I50"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/files/temp-work.xlsx
+++ b/files/temp-work.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/coltongearhart/Desktop/exam5/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{529DD912-7E81-BB4F-BA05-659E96ABE747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7E6E09D-C3D2-A84F-8E96-8B0FAB504BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" activeTab="3" xr2:uid="{BB8505BC-BCB7-B340-A120-C046C43AD7BD}"/>
+    <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" activeTab="4" xr2:uid="{BB8505BC-BCB7-B340-A120-C046C43AD7BD}"/>
   </bookViews>
   <sheets>
     <sheet name="2.2.1" sheetId="1" r:id="rId1"/>
     <sheet name="2.2.2" sheetId="2" r:id="rId2"/>
     <sheet name="2.3.1" sheetId="3" r:id="rId3"/>
     <sheet name="2.3.3" sheetId="4" r:id="rId4"/>
+    <sheet name="2.4.3" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="187">
   <si>
     <t>Ratio to SAWW</t>
   </si>
@@ -581,6 +582,36 @@
   <si>
     <t>=AVERAGE(Z153:Z155)</t>
   </si>
+  <si>
+    <t>Claim</t>
+  </si>
+  <si>
+    <t>Ground-up Loss</t>
+  </si>
+  <si>
+    <t>Loss in 50 xs 100</t>
+  </si>
+  <si>
+    <t>Layer</t>
+  </si>
+  <si>
+    <t>Trended Ground-up Loss</t>
+  </si>
+  <si>
+    <t>Inflation rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">excess of </t>
+  </si>
+  <si>
+    <t>=IF(C6&gt;$E$2,MIN(C6-$E$2,$C$2),0)</t>
+  </si>
+  <si>
+    <t>=D17/D10-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50k excess of 100k trend= </t>
+  </si>
 </sst>
 </file>
 
@@ -592,8 +623,8 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
-    <numFmt numFmtId="173" formatCode="0.000"/>
-    <numFmt numFmtId="176" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -789,7 +820,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -833,6 +864,46 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="167" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="6" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="8" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -866,60 +937,27 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="176" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="6" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="6" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="8" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="8" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="9" fontId="7" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="6" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="6" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1994,26 +2032,26 @@
       </c>
     </row>
     <row r="23" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="M23" s="42"/>
-      <c r="N23" s="43"/>
-      <c r="O23" s="39" t="s">
+      <c r="M23" s="70"/>
+      <c r="N23" s="71"/>
+      <c r="O23" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="P23" s="40"/>
-      <c r="Q23" s="40"/>
-      <c r="R23" s="41"/>
-      <c r="S23" s="39" t="s">
+      <c r="P23" s="68"/>
+      <c r="Q23" s="68"/>
+      <c r="R23" s="69"/>
+      <c r="S23" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="T23" s="40"/>
-      <c r="U23" s="40"/>
-      <c r="V23" s="41"/>
-      <c r="W23" s="39" t="s">
+      <c r="T23" s="68"/>
+      <c r="U23" s="68"/>
+      <c r="V23" s="69"/>
+      <c r="W23" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="X23" s="40"/>
-      <c r="Y23" s="40"/>
-      <c r="Z23" s="41"/>
+      <c r="X23" s="68"/>
+      <c r="Y23" s="68"/>
+      <c r="Z23" s="69"/>
     </row>
     <row r="24" spans="2:33" x14ac:dyDescent="0.2">
       <c r="M24" s="24" t="s">
@@ -2079,35 +2117,35 @@
       <c r="R25" s="30">
         <v>0</v>
       </c>
-      <c r="S25" s="48">
+      <c r="S25" s="76">
         <f>SUMPRODUCT(O25:O27,$N$25:$N$27)</f>
         <v>1.0568750000000002</v>
       </c>
-      <c r="T25" s="46">
+      <c r="T25" s="74">
         <f t="shared" ref="T25:V25" si="2">SUMPRODUCT(P25:P27,$N$25:$N$27)</f>
         <v>1.089375</v>
       </c>
-      <c r="U25" s="46">
+      <c r="U25" s="74">
         <f t="shared" si="2"/>
         <v>1.1156250000000001</v>
       </c>
-      <c r="V25" s="44">
+      <c r="V25" s="72">
         <f t="shared" si="2"/>
         <v>1.1418750000000002</v>
       </c>
-      <c r="W25" s="48">
+      <c r="W25" s="76">
         <f>$N$27/S25</f>
         <v>1.0928444707273803</v>
       </c>
-      <c r="X25" s="46">
+      <c r="X25" s="74">
         <f t="shared" ref="X25:Z25" si="3">$N$27/T25</f>
         <v>1.060240963855422</v>
       </c>
-      <c r="Y25" s="46">
+      <c r="Y25" s="74">
         <f t="shared" si="3"/>
         <v>1.0352941176470589</v>
       </c>
-      <c r="Z25" s="44">
+      <c r="Z25" s="72">
         <f t="shared" si="3"/>
         <v>1.0114942528735633</v>
       </c>
@@ -2132,14 +2170,14 @@
       <c r="R26" s="30">
         <v>0.125</v>
       </c>
-      <c r="S26" s="48"/>
-      <c r="T26" s="46"/>
-      <c r="U26" s="46"/>
-      <c r="V26" s="44"/>
-      <c r="W26" s="48"/>
-      <c r="X26" s="46"/>
-      <c r="Y26" s="46"/>
-      <c r="Z26" s="44"/>
+      <c r="S26" s="76"/>
+      <c r="T26" s="74"/>
+      <c r="U26" s="74"/>
+      <c r="V26" s="72"/>
+      <c r="W26" s="76"/>
+      <c r="X26" s="74"/>
+      <c r="Y26" s="74"/>
+      <c r="Z26" s="72"/>
     </row>
     <row r="27" spans="2:33" x14ac:dyDescent="0.2">
       <c r="M27" s="28">
@@ -2161,14 +2199,14 @@
       <c r="R27" s="31">
         <v>0.875</v>
       </c>
-      <c r="S27" s="49"/>
-      <c r="T27" s="47"/>
-      <c r="U27" s="47"/>
-      <c r="V27" s="45"/>
-      <c r="W27" s="49"/>
-      <c r="X27" s="47"/>
-      <c r="Y27" s="47"/>
-      <c r="Z27" s="45"/>
+      <c r="S27" s="77"/>
+      <c r="T27" s="75"/>
+      <c r="U27" s="75"/>
+      <c r="V27" s="73"/>
+      <c r="W27" s="77"/>
+      <c r="X27" s="75"/>
+      <c r="Y27" s="75"/>
+      <c r="Z27" s="73"/>
     </row>
     <row r="28" spans="2:33" x14ac:dyDescent="0.2">
       <c r="N28" s="32" t="s">
@@ -2249,23 +2287,23 @@
       </c>
     </row>
     <row r="37" spans="15:41" x14ac:dyDescent="0.2">
-      <c r="AE37" s="52"/>
-      <c r="AF37" s="52"/>
-      <c r="AG37" s="51" t="s">
+      <c r="AE37" s="64"/>
+      <c r="AF37" s="64"/>
+      <c r="AG37" s="65" t="s">
         <v>72</v>
       </c>
-      <c r="AH37" s="51"/>
-      <c r="AI37" s="51"/>
-      <c r="AJ37" s="51" t="s">
+      <c r="AH37" s="65"/>
+      <c r="AI37" s="65"/>
+      <c r="AJ37" s="65" t="s">
         <v>76</v>
       </c>
-      <c r="AK37" s="51"/>
-      <c r="AL37" s="51"/>
-      <c r="AM37" s="51" t="s">
+      <c r="AK37" s="65"/>
+      <c r="AL37" s="65"/>
+      <c r="AM37" s="65" t="s">
         <v>77</v>
       </c>
-      <c r="AN37" s="51"/>
-      <c r="AO37" s="51"/>
+      <c r="AN37" s="65"/>
+      <c r="AO37" s="65"/>
     </row>
     <row r="38" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE38" s="15" t="s">
@@ -2314,18 +2352,18 @@
         <f>0.5*3/4*3/4</f>
         <v>0.28125</v>
       </c>
-      <c r="AJ39" s="50"/>
-      <c r="AK39" s="50">
+      <c r="AJ39" s="63"/>
+      <c r="AK39" s="63">
         <f>SUMPRODUCT(AH39:AH42,AF39:AF42)</f>
         <v>1.0636875000000001</v>
       </c>
-      <c r="AL39" s="50"/>
-      <c r="AM39" s="50"/>
-      <c r="AN39" s="50">
+      <c r="AL39" s="63"/>
+      <c r="AM39" s="63"/>
+      <c r="AN39" s="63">
         <f>$AF$42/AK39</f>
         <v>1.0512015982137612</v>
       </c>
-      <c r="AO39" s="50"/>
+      <c r="AO39" s="63"/>
     </row>
     <row r="40" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE40">
@@ -2339,12 +2377,12 @@
         <f>1-AH39-AH41</f>
         <v>0.59375</v>
       </c>
-      <c r="AJ40" s="50"/>
-      <c r="AK40" s="50"/>
-      <c r="AL40" s="50"/>
-      <c r="AM40" s="50"/>
-      <c r="AN40" s="50"/>
-      <c r="AO40" s="50"/>
+      <c r="AJ40" s="63"/>
+      <c r="AK40" s="63"/>
+      <c r="AL40" s="63"/>
+      <c r="AM40" s="63"/>
+      <c r="AN40" s="63"/>
+      <c r="AO40" s="63"/>
     </row>
     <row r="41" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE41">
@@ -2357,12 +2395,12 @@
       <c r="AH41">
         <v>0.125</v>
       </c>
-      <c r="AJ41" s="50"/>
-      <c r="AK41" s="50"/>
-      <c r="AL41" s="50"/>
-      <c r="AM41" s="50"/>
-      <c r="AN41" s="50"/>
-      <c r="AO41" s="50"/>
+      <c r="AJ41" s="63"/>
+      <c r="AK41" s="63"/>
+      <c r="AL41" s="63"/>
+      <c r="AM41" s="63"/>
+      <c r="AN41" s="63"/>
+      <c r="AO41" s="63"/>
     </row>
     <row r="42" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE42">
@@ -2375,31 +2413,31 @@
       <c r="AH42">
         <v>0</v>
       </c>
-      <c r="AJ42" s="50"/>
-      <c r="AK42" s="50"/>
-      <c r="AL42" s="50"/>
-      <c r="AM42" s="50"/>
-      <c r="AN42" s="50"/>
-      <c r="AO42" s="50"/>
+      <c r="AJ42" s="63"/>
+      <c r="AK42" s="63"/>
+      <c r="AL42" s="63"/>
+      <c r="AM42" s="63"/>
+      <c r="AN42" s="63"/>
+      <c r="AO42" s="63"/>
     </row>
     <row r="44" spans="15:41" x14ac:dyDescent="0.2">
-      <c r="AE44" s="52"/>
-      <c r="AF44" s="52"/>
-      <c r="AG44" s="51" t="s">
+      <c r="AE44" s="64"/>
+      <c r="AF44" s="64"/>
+      <c r="AG44" s="65" t="s">
         <v>72</v>
       </c>
-      <c r="AH44" s="51"/>
-      <c r="AI44" s="51"/>
-      <c r="AJ44" s="51" t="s">
+      <c r="AH44" s="65"/>
+      <c r="AI44" s="65"/>
+      <c r="AJ44" s="65" t="s">
         <v>76</v>
       </c>
-      <c r="AK44" s="51"/>
-      <c r="AL44" s="51"/>
-      <c r="AM44" s="51" t="s">
+      <c r="AK44" s="65"/>
+      <c r="AL44" s="65"/>
+      <c r="AM44" s="65" t="s">
         <v>77</v>
       </c>
-      <c r="AN44" s="51"/>
-      <c r="AO44" s="51"/>
+      <c r="AN44" s="65"/>
+      <c r="AO44" s="65"/>
     </row>
     <row r="45" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE45" s="15" t="s">
@@ -2447,18 +2485,18 @@
       <c r="AH46">
         <v>0</v>
       </c>
-      <c r="AJ46" s="50"/>
-      <c r="AK46" s="50">
+      <c r="AJ46" s="63"/>
+      <c r="AK46" s="63">
         <f>SUMPRODUCT(AH46:AH49,AF46:AF49)</f>
         <v>1.1161437500000002</v>
       </c>
-      <c r="AL46" s="50"/>
-      <c r="AM46" s="50"/>
-      <c r="AN46" s="50">
+      <c r="AL46" s="63"/>
+      <c r="AM46" s="63"/>
+      <c r="AN46" s="63">
         <f>$AF$49/AK46</f>
         <v>1.0017974835230676</v>
       </c>
-      <c r="AO46" s="50"/>
+      <c r="AO46" s="63"/>
     </row>
     <row r="47" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE47">
@@ -2471,12 +2509,12 @@
       <c r="AH47">
         <v>0.5</v>
       </c>
-      <c r="AJ47" s="50"/>
-      <c r="AK47" s="50"/>
-      <c r="AL47" s="50"/>
-      <c r="AM47" s="50"/>
-      <c r="AN47" s="50"/>
-      <c r="AO47" s="50"/>
+      <c r="AJ47" s="63"/>
+      <c r="AK47" s="63"/>
+      <c r="AL47" s="63"/>
+      <c r="AM47" s="63"/>
+      <c r="AN47" s="63"/>
+      <c r="AO47" s="63"/>
     </row>
     <row r="48" spans="15:41" x14ac:dyDescent="0.2">
       <c r="O48" t="s">
@@ -2492,12 +2530,12 @@
       <c r="AH48">
         <v>0.375</v>
       </c>
-      <c r="AJ48" s="50"/>
-      <c r="AK48" s="50"/>
-      <c r="AL48" s="50"/>
-      <c r="AM48" s="50"/>
-      <c r="AN48" s="50"/>
-      <c r="AO48" s="50"/>
+      <c r="AJ48" s="63"/>
+      <c r="AK48" s="63"/>
+      <c r="AL48" s="63"/>
+      <c r="AM48" s="63"/>
+      <c r="AN48" s="63"/>
+      <c r="AO48" s="63"/>
     </row>
     <row r="49" spans="31:52" x14ac:dyDescent="0.2">
       <c r="AE49">
@@ -2510,12 +2548,12 @@
       <c r="AH49">
         <v>0.125</v>
       </c>
-      <c r="AJ49" s="50"/>
-      <c r="AK49" s="50"/>
-      <c r="AL49" s="50"/>
-      <c r="AM49" s="50"/>
-      <c r="AN49" s="50"/>
-      <c r="AO49" s="50"/>
+      <c r="AJ49" s="63"/>
+      <c r="AK49" s="63"/>
+      <c r="AL49" s="63"/>
+      <c r="AM49" s="63"/>
+      <c r="AN49" s="63"/>
+      <c r="AO49" s="63"/>
     </row>
     <row r="53" spans="31:52" x14ac:dyDescent="0.2">
       <c r="AS53" s="15" t="s">
@@ -2565,20 +2603,20 @@
       </c>
     </row>
     <row r="58" spans="31:52" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="AS58" s="52"/>
-      <c r="AT58" s="52"/>
-      <c r="AU58" s="51" t="s">
+      <c r="AS58" s="64"/>
+      <c r="AT58" s="64"/>
+      <c r="AU58" s="65" t="s">
         <v>72</v>
       </c>
-      <c r="AV58" s="51"/>
-      <c r="AW58" s="53" t="s">
+      <c r="AV58" s="65"/>
+      <c r="AW58" s="66" t="s">
         <v>76</v>
       </c>
-      <c r="AX58" s="53"/>
-      <c r="AY58" s="51" t="s">
+      <c r="AX58" s="66"/>
+      <c r="AY58" s="65" t="s">
         <v>77</v>
       </c>
-      <c r="AZ58" s="51"/>
+      <c r="AZ58" s="65"/>
     </row>
     <row r="59" spans="31:52" x14ac:dyDescent="0.2">
       <c r="AS59" s="15" t="s">
@@ -2618,13 +2656,13 @@
         <f>1/16</f>
         <v>6.25E-2</v>
       </c>
-      <c r="AW60" s="50"/>
-      <c r="AX60" s="50">
+      <c r="AW60" s="63"/>
+      <c r="AX60" s="63">
         <f>SUMPRODUCT(AV60:AV62,AT60:AT62)</f>
         <v>1.0993750000000002</v>
       </c>
-      <c r="AY60" s="50"/>
-      <c r="AZ60" s="50">
+      <c r="AY60" s="63"/>
+      <c r="AZ60" s="63">
         <f>$AT$62/AX60</f>
         <v>1.0505969300739058</v>
       </c>
@@ -2641,10 +2679,10 @@
         <f>0.5-AV60</f>
         <v>0.4375</v>
       </c>
-      <c r="AW61" s="50"/>
-      <c r="AX61" s="50"/>
-      <c r="AY61" s="50"/>
-      <c r="AZ61" s="50"/>
+      <c r="AW61" s="63"/>
+      <c r="AX61" s="63"/>
+      <c r="AY61" s="63"/>
+      <c r="AZ61" s="63"/>
     </row>
     <row r="62" spans="31:52" x14ac:dyDescent="0.2">
       <c r="AS62">
@@ -2657,10 +2695,10 @@
       <c r="AV62">
         <v>0.5</v>
       </c>
-      <c r="AW62" s="50"/>
-      <c r="AX62" s="50"/>
-      <c r="AY62" s="50"/>
-      <c r="AZ62" s="50"/>
+      <c r="AW62" s="63"/>
+      <c r="AX62" s="63"/>
+      <c r="AY62" s="63"/>
+      <c r="AZ62" s="63"/>
     </row>
     <row r="63" spans="31:52" x14ac:dyDescent="0.2">
       <c r="AW63" s="23"/>
@@ -2670,15 +2708,23 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="AW60:AW62"/>
-    <mergeCell ref="AZ60:AZ62"/>
-    <mergeCell ref="AY60:AY62"/>
-    <mergeCell ref="AX60:AX62"/>
-    <mergeCell ref="AO46:AO49"/>
-    <mergeCell ref="AS58:AT58"/>
-    <mergeCell ref="AU58:AV58"/>
-    <mergeCell ref="AW58:AX58"/>
-    <mergeCell ref="AY58:AZ58"/>
+    <mergeCell ref="W23:Z23"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="Z25:Z27"/>
+    <mergeCell ref="Y25:Y27"/>
+    <mergeCell ref="X25:X27"/>
+    <mergeCell ref="W25:W27"/>
+    <mergeCell ref="O23:R23"/>
+    <mergeCell ref="S25:S27"/>
+    <mergeCell ref="T25:T27"/>
+    <mergeCell ref="U25:U27"/>
+    <mergeCell ref="V25:V27"/>
+    <mergeCell ref="S23:V23"/>
+    <mergeCell ref="AJ46:AJ49"/>
+    <mergeCell ref="AK46:AK49"/>
+    <mergeCell ref="AL46:AL49"/>
+    <mergeCell ref="AM46:AM49"/>
+    <mergeCell ref="AN46:AN49"/>
     <mergeCell ref="AM37:AO37"/>
     <mergeCell ref="AE44:AF44"/>
     <mergeCell ref="AG44:AI44"/>
@@ -2693,23 +2739,15 @@
     <mergeCell ref="AL39:AL42"/>
     <mergeCell ref="AK39:AK42"/>
     <mergeCell ref="AJ39:AJ42"/>
-    <mergeCell ref="AJ46:AJ49"/>
-    <mergeCell ref="AK46:AK49"/>
-    <mergeCell ref="AL46:AL49"/>
-    <mergeCell ref="AM46:AM49"/>
-    <mergeCell ref="AN46:AN49"/>
-    <mergeCell ref="W23:Z23"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="Z25:Z27"/>
-    <mergeCell ref="Y25:Y27"/>
-    <mergeCell ref="X25:X27"/>
-    <mergeCell ref="W25:W27"/>
-    <mergeCell ref="O23:R23"/>
-    <mergeCell ref="S25:S27"/>
-    <mergeCell ref="T25:T27"/>
-    <mergeCell ref="U25:U27"/>
-    <mergeCell ref="V25:V27"/>
-    <mergeCell ref="S23:V23"/>
+    <mergeCell ref="AW60:AW62"/>
+    <mergeCell ref="AZ60:AZ62"/>
+    <mergeCell ref="AY60:AY62"/>
+    <mergeCell ref="AX60:AX62"/>
+    <mergeCell ref="AO46:AO49"/>
+    <mergeCell ref="AS58:AT58"/>
+    <mergeCell ref="AU58:AV58"/>
+    <mergeCell ref="AW58:AX58"/>
+    <mergeCell ref="AY58:AZ58"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3129,7 +3167,7 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="78" t="s">
         <v>96</v>
       </c>
       <c r="C3" s="11" t="s">
@@ -3137,7 +3175,7 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="55"/>
+      <c r="B4" s="78"/>
       <c r="C4" s="11" t="s">
         <v>98</v>
       </c>
@@ -3241,7 +3279,7 @@
       <c r="F10" s="12"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B11" s="55" t="s">
+      <c r="B11" s="78" t="s">
         <v>96</v>
       </c>
       <c r="C11" s="11" t="s">
@@ -3249,7 +3287,7 @@
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B12" s="55"/>
+      <c r="B12" s="78"/>
       <c r="C12" s="11" t="s">
         <v>98</v>
       </c>
@@ -3349,7 +3387,7 @@
       <c r="G16" s="12"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B18" s="55" t="s">
+      <c r="B18" s="78" t="s">
         <v>96</v>
       </c>
       <c r="C18" s="11" t="s">
@@ -3357,17 +3395,17 @@
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B19" s="55"/>
-      <c r="C19" s="56" t="s">
+      <c r="B19" s="78"/>
+      <c r="C19" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="D19" s="57" t="s">
+      <c r="D19" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="E19" s="57" t="s">
+      <c r="E19" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="F19" s="57" t="s">
+      <c r="F19" s="40" t="s">
         <v>106</v>
       </c>
       <c r="G19" s="11"/>
@@ -3376,19 +3414,19 @@
       <c r="B20" s="12">
         <v>2017</v>
       </c>
-      <c r="C20" s="58">
+      <c r="C20" s="41">
         <f>D13/C13</f>
         <v>1.3549783549783549</v>
       </c>
-      <c r="D20" s="58">
-        <f t="shared" ref="D20:F21" si="2">E13/D13</f>
+      <c r="D20" s="41">
+        <f t="shared" ref="D20:F20" si="2">E13/D13</f>
         <v>1.1629392971246006</v>
       </c>
-      <c r="E20" s="58">
+      <c r="E20" s="41">
         <f t="shared" si="2"/>
         <v>1.0879120879120878</v>
       </c>
-      <c r="F20" s="58">
+      <c r="F20" s="41">
         <f t="shared" si="2"/>
         <v>1.0353535353535352</v>
       </c>
@@ -3398,15 +3436,15 @@
       <c r="B21" s="12">
         <v>2018</v>
       </c>
-      <c r="C21" s="58">
+      <c r="C21" s="41">
         <f t="shared" ref="C21:D23" si="3">D14/C14</f>
         <v>1.3532110091743119</v>
       </c>
-      <c r="D21" s="58">
+      <c r="D21" s="41">
         <f t="shared" si="3"/>
         <v>1.1559322033898305</v>
       </c>
-      <c r="E21" s="58">
+      <c r="E21" s="41">
         <f>F14/E14</f>
         <v>1.0879765395894427</v>
       </c>
@@ -3417,11 +3455,11 @@
       <c r="B22" s="12">
         <v>2019</v>
       </c>
-      <c r="C22" s="58">
+      <c r="C22" s="41">
         <f t="shared" si="3"/>
         <v>1.3307392996108949</v>
       </c>
-      <c r="D22" s="58">
+      <c r="D22" s="41">
         <f t="shared" si="3"/>
         <v>1.1578947368421053</v>
       </c>
@@ -3435,7 +3473,7 @@
       <c r="B23" s="12">
         <v>2020</v>
       </c>
-      <c r="C23" s="58">
+      <c r="C23" s="41">
         <f t="shared" si="3"/>
         <v>1.3310344827586207</v>
       </c>
@@ -3463,7 +3501,7 @@
       <c r="B26" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C26" s="60">
+      <c r="C26" s="43">
         <f>SUM(D13:D16)/SUM(C13:C16)</f>
         <v>1.3413654618473896</v>
       </c>
@@ -3475,7 +3513,7 @@
       <c r="B27" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C27" s="60">
+      <c r="C27" s="43">
         <f>SUM(E13:E15)/SUM(D13:D15)</f>
         <v>1.1589473684210527</v>
       </c>
@@ -3484,7 +3522,7 @@
       <c r="B28" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C28" s="60">
+      <c r="C28" s="43">
         <f>SUM(F13:F14)/SUM(E13:E14)</f>
         <v>1.0879432624113474</v>
       </c>
@@ -3493,7 +3531,7 @@
       <c r="B29" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C29" s="60">
+      <c r="C29" s="43">
         <f>G13/F13</f>
         <v>1.0353535353535352</v>
       </c>
@@ -3521,7 +3559,7 @@
       <c r="B33" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C33" s="60">
+      <c r="C33" s="43">
         <f>PRODUCT(C26:C30)</f>
         <v>1.786100626933401</v>
       </c>
@@ -3533,7 +3571,7 @@
       <c r="B34" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C34" s="60">
+      <c r="C34" s="43">
         <f>PRODUCT(C27:C30)</f>
         <v>1.3315540601988531</v>
       </c>
@@ -3542,7 +3580,7 @@
       <c r="B35" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C35" s="60">
+      <c r="C35" s="43">
         <f>PRODUCT(C28:C30)</f>
         <v>1.1489340210616805</v>
       </c>
@@ -3551,7 +3589,7 @@
       <c r="B36" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C36" s="60">
+      <c r="C36" s="43">
         <f>PRODUCT(C29:C30)</f>
         <v>1.0560606060606059</v>
       </c>
@@ -3560,7 +3598,7 @@
       <c r="B37" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C37" s="60">
+      <c r="C37" s="43">
         <f>PRODUCT(C30:C30)</f>
         <v>1.02</v>
       </c>
@@ -3569,7 +3607,7 @@
       <c r="B39" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="C39" s="61" t="s">
+      <c r="C39" s="44" t="s">
         <v>129</v>
       </c>
       <c r="D39" s="15" t="s">
@@ -3577,17 +3615,17 @@
       </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B40" s="65" t="s">
+      <c r="B40" s="48" t="s">
         <v>121</v>
       </c>
-      <c r="C40" s="66">
+      <c r="C40" s="49">
         <v>310</v>
       </c>
-      <c r="D40" s="67">
+      <c r="D40" s="50">
         <f>C40*C33</f>
         <v>553.6911943493543</v>
       </c>
-      <c r="E40" s="68" t="s">
+      <c r="E40" s="51" t="s">
         <v>130</v>
       </c>
     </row>
@@ -3598,8 +3636,8 @@
       <c r="C41">
         <v>96</v>
       </c>
-      <c r="D41" s="62">
-        <f t="shared" ref="D41:D44" si="4">C41*C34</f>
+      <c r="D41" s="45">
+        <f t="shared" ref="D41:D43" si="4">C41*C34</f>
         <v>127.8291897790899</v>
       </c>
     </row>
@@ -3610,7 +3648,7 @@
       <c r="C42">
         <v>54</v>
       </c>
-      <c r="D42" s="62">
+      <c r="D42" s="45">
         <f t="shared" si="4"/>
         <v>62.042437137330751</v>
       </c>
@@ -3622,19 +3660,19 @@
       <c r="C43">
         <v>30</v>
       </c>
-      <c r="D43" s="62">
+      <c r="D43" s="45">
         <f t="shared" si="4"/>
         <v>31.681818181818176</v>
       </c>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B44" s="63" t="s">
+      <c r="B44" s="46" t="s">
         <v>125</v>
       </c>
       <c r="C44" s="1">
         <v>14</v>
       </c>
-      <c r="D44" s="64">
+      <c r="D44" s="47">
         <f>C44*C37</f>
         <v>14.280000000000001</v>
       </c>
@@ -3644,11 +3682,11 @@
       <c r="B45" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C45" s="80">
+      <c r="C45" s="60">
         <f>SUM(C40:C44)</f>
         <v>504</v>
       </c>
-      <c r="D45" s="62">
+      <c r="D45" s="45">
         <f>SUM(D40:D44)</f>
         <v>789.52463944759313</v>
       </c>
@@ -3657,7 +3695,7 @@
       </c>
     </row>
     <row r="49" spans="9:13" x14ac:dyDescent="0.2">
-      <c r="I49" s="55" t="s">
+      <c r="I49" s="78" t="s">
         <v>96</v>
       </c>
       <c r="J49" s="11" t="s">
@@ -3665,7 +3703,7 @@
       </c>
     </row>
     <row r="50" spans="9:13" x14ac:dyDescent="0.2">
-      <c r="I50" s="55"/>
+      <c r="I50" s="78"/>
       <c r="J50" s="11" t="s">
         <v>134</v>
       </c>
@@ -3680,13 +3718,13 @@
       <c r="I51" s="12">
         <v>2009</v>
       </c>
-      <c r="J51" s="69">
+      <c r="J51" s="52">
         <v>16000</v>
       </c>
-      <c r="K51" s="69">
+      <c r="K51" s="52">
         <v>3000</v>
       </c>
-      <c r="L51" s="70">
+      <c r="L51" s="53">
         <f>SUM(J51:K51)</f>
         <v>19000</v>
       </c>
@@ -3698,13 +3736,13 @@
       <c r="I52" s="12">
         <v>2010</v>
       </c>
-      <c r="J52" s="69">
+      <c r="J52" s="52">
         <v>12000</v>
       </c>
-      <c r="K52" s="69">
+      <c r="K52" s="52">
         <v>4000</v>
       </c>
-      <c r="L52" s="70">
+      <c r="L52" s="53">
         <f t="shared" ref="L52:L54" si="5">SUM(J52:K52)</f>
         <v>16000</v>
       </c>
@@ -3713,13 +3751,13 @@
       <c r="I53" s="12">
         <v>2011</v>
       </c>
-      <c r="J53" s="69">
+      <c r="J53" s="52">
         <v>10000</v>
       </c>
-      <c r="K53" s="69">
+      <c r="K53" s="52">
         <v>7000</v>
       </c>
-      <c r="L53" s="70">
+      <c r="L53" s="53">
         <f t="shared" si="5"/>
         <v>17000</v>
       </c>
@@ -3728,13 +3766,13 @@
       <c r="I54" s="12">
         <v>2012</v>
       </c>
-      <c r="J54" s="69">
+      <c r="J54" s="52">
         <v>5000</v>
       </c>
-      <c r="K54" s="69">
+      <c r="K54" s="52">
         <v>8000</v>
       </c>
-      <c r="L54" s="70">
+      <c r="L54" s="53">
         <f t="shared" si="5"/>
         <v>13000</v>
       </c>
@@ -3753,10 +3791,10 @@
       </c>
     </row>
     <row r="57" spans="9:13" x14ac:dyDescent="0.2">
-      <c r="I57" s="71" t="s">
+      <c r="I57" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="J57" s="72">
+      <c r="J57" s="55">
         <v>1.2</v>
       </c>
       <c r="K57" t="s">
@@ -3778,22 +3816,22 @@
       <c r="I59" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="J59" s="73" t="s">
+      <c r="J59" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="K59" s="59"/>
+      <c r="K59" s="42"/>
     </row>
     <row r="60" spans="9:13" x14ac:dyDescent="0.2">
       <c r="I60" s="3"/>
-      <c r="J60" s="73"/>
-      <c r="K60" s="59"/>
+      <c r="J60" s="56"/>
+      <c r="K60" s="42"/>
     </row>
     <row r="61" spans="9:13" x14ac:dyDescent="0.2">
       <c r="I61" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="J61" s="73"/>
-      <c r="K61" s="59"/>
+      <c r="J61" s="56"/>
+      <c r="K61" s="42"/>
     </row>
     <row r="63" spans="9:13" x14ac:dyDescent="0.2">
       <c r="I63" s="15" t="s">
@@ -3801,10 +3839,10 @@
       </c>
     </row>
     <row r="64" spans="9:13" x14ac:dyDescent="0.2">
-      <c r="I64" s="69">
+      <c r="I64" s="52">
         <v>18000</v>
       </c>
-      <c r="J64" s="74" t="s">
+      <c r="J64" s="57" t="s">
         <v>144</v>
       </c>
     </row>
@@ -3815,7 +3853,7 @@
       <c r="J65" t="s">
         <v>141</v>
       </c>
-      <c r="K65" s="60">
+      <c r="K65" s="43">
         <f>I64/L52</f>
         <v>1.125</v>
       </c>
@@ -3830,14 +3868,14 @@
       </c>
     </row>
     <row r="68" spans="9:23" x14ac:dyDescent="0.2">
-      <c r="I68" s="69">
+      <c r="I68" s="52">
         <v>17000</v>
       </c>
-      <c r="J68" s="75">
+      <c r="J68" s="58">
         <f>I68*PRODUCT(J58,K65)</f>
         <v>21993.75</v>
       </c>
-      <c r="K68" s="74" t="s">
+      <c r="K68" s="57" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3845,30 +3883,30 @@
       <c r="I69" t="s">
         <v>112</v>
       </c>
-      <c r="K69" s="60"/>
+      <c r="K69" s="43"/>
     </row>
     <row r="73" spans="9:23" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="74" spans="9:23" x14ac:dyDescent="0.2">
-      <c r="Q74" s="77" t="s">
+      <c r="Q74" s="80" t="s">
         <v>149</v>
       </c>
-      <c r="R74" s="77" t="s">
+      <c r="R74" s="80" t="s">
         <v>96</v>
       </c>
-      <c r="S74" s="76" t="s">
+      <c r="S74" s="11" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="75" spans="9:23" x14ac:dyDescent="0.2">
-      <c r="Q75" s="77"/>
-      <c r="R75" s="77"/>
+      <c r="Q75" s="80"/>
+      <c r="R75" s="80"/>
       <c r="S75" s="11" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="76" spans="9:23" x14ac:dyDescent="0.2">
-      <c r="Q76" s="77"/>
-      <c r="R76" s="77"/>
+      <c r="Q76" s="80"/>
+      <c r="R76" s="80"/>
       <c r="S76" s="11">
         <v>12</v>
       </c>
@@ -3979,36 +4017,36 @@
       <c r="U81" s="12"/>
     </row>
     <row r="83" spans="17:23" x14ac:dyDescent="0.2">
-      <c r="Q83" s="77" t="s">
+      <c r="Q83" s="80" t="s">
         <v>149</v>
       </c>
-      <c r="R83" s="77" t="s">
+      <c r="R83" s="80" t="s">
         <v>96</v>
       </c>
-      <c r="S83" s="76" t="s">
+      <c r="S83" s="11" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="84" spans="17:23" x14ac:dyDescent="0.2">
-      <c r="Q84" s="77"/>
-      <c r="R84" s="77"/>
+      <c r="Q84" s="80"/>
+      <c r="R84" s="80"/>
       <c r="S84" s="11" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="85" spans="17:23" x14ac:dyDescent="0.2">
-      <c r="Q85" s="77"/>
-      <c r="R85" s="77"/>
-      <c r="S85" s="56" t="s">
+      <c r="Q85" s="80"/>
+      <c r="R85" s="80"/>
+      <c r="S85" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="T85" s="57" t="s">
+      <c r="T85" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="U85" s="57" t="s">
+      <c r="U85" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="V85" s="57" t="s">
+      <c r="V85" s="40" t="s">
         <v>106</v>
       </c>
       <c r="W85" s="11"/>
@@ -4020,19 +4058,19 @@
       <c r="R86" s="12">
         <v>2010</v>
       </c>
-      <c r="S86" s="58">
+      <c r="S86" s="41">
         <f>T77/S77</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="T86" s="58">
+      <c r="T86" s="41">
         <f t="shared" ref="T86:V86" si="6">U77/T77</f>
         <v>1.2</v>
       </c>
-      <c r="U86" s="58">
+      <c r="U86" s="41">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="V86" s="58">
+      <c r="V86" s="41">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
@@ -4045,15 +4083,15 @@
       <c r="R87" s="12">
         <v>2011</v>
       </c>
-      <c r="S87" s="58">
+      <c r="S87" s="41">
         <f t="shared" ref="S87:U89" si="7">T78/S78</f>
         <v>1.1720430107526882</v>
       </c>
-      <c r="T87" s="58">
+      <c r="T87" s="41">
         <f t="shared" si="7"/>
         <v>1.1834862385321101</v>
       </c>
-      <c r="U87" s="58">
+      <c r="U87" s="41">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
@@ -4067,15 +4105,15 @@
       <c r="R88" s="12">
         <v>2012</v>
       </c>
-      <c r="S88" s="58">
+      <c r="S88" s="41">
         <f t="shared" si="7"/>
         <v>1.08</v>
       </c>
-      <c r="T88" s="58">
+      <c r="T88" s="41">
         <f t="shared" si="7"/>
         <v>1.25</v>
       </c>
-      <c r="U88" s="78"/>
+      <c r="U88" s="59"/>
       <c r="V88" s="35"/>
       <c r="W88" s="12"/>
     </row>
@@ -4086,11 +4124,11 @@
       <c r="R89" s="12">
         <v>2013</v>
       </c>
-      <c r="S89" s="58">
+      <c r="S89" s="41">
         <f t="shared" si="7"/>
         <v>1.0900000000000001</v>
       </c>
-      <c r="T89" s="58"/>
+      <c r="T89" s="41"/>
       <c r="U89" s="35"/>
       <c r="V89" s="35"/>
       <c r="W89" s="12"/>
@@ -4111,37 +4149,37 @@
       </c>
     </row>
     <row r="92" spans="17:23" x14ac:dyDescent="0.2">
-      <c r="Q92" s="56" t="s">
+      <c r="Q92" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="R92" s="60">
+      <c r="R92" s="43">
         <f>AVERAGE(S86,S89)</f>
         <v>1.0950000000000002</v>
       </c>
     </row>
     <row r="93" spans="17:23" x14ac:dyDescent="0.2">
-      <c r="Q93" s="57" t="s">
+      <c r="Q93" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="R93" s="60">
+      <c r="R93" s="43">
         <f>AVERAGE(T86)</f>
         <v>1.2</v>
       </c>
     </row>
     <row r="94" spans="17:23" x14ac:dyDescent="0.2">
-      <c r="Q94" s="57" t="s">
+      <c r="Q94" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="R94" s="60">
+      <c r="R94" s="43">
         <f>AVERAGE(U86:U87)</f>
         <v>1</v>
       </c>
     </row>
     <row r="95" spans="17:23" x14ac:dyDescent="0.2">
-      <c r="Q95" s="57" t="s">
+      <c r="Q95" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="R95" s="60">
+      <c r="R95" s="43">
         <f>AVERAGE(V86)</f>
         <v>1</v>
       </c>
@@ -4155,10 +4193,10 @@
       </c>
     </row>
     <row r="98" spans="17:22" x14ac:dyDescent="0.2">
-      <c r="Q98" s="56" t="s">
+      <c r="Q98" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="R98" s="60">
+      <c r="R98" s="43">
         <f>PRODUCT(R92:R95)</f>
         <v>1.3140000000000003</v>
       </c>
@@ -4167,28 +4205,28 @@
       </c>
     </row>
     <row r="99" spans="17:22" x14ac:dyDescent="0.2">
-      <c r="Q99" s="57" t="s">
+      <c r="Q99" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="R99" s="60">
+      <c r="R99" s="43">
         <f>PRODUCT(R93:R95)</f>
         <v>1.2</v>
       </c>
     </row>
     <row r="100" spans="17:22" x14ac:dyDescent="0.2">
-      <c r="Q100" s="57" t="s">
+      <c r="Q100" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="R100" s="60">
+      <c r="R100" s="43">
         <f>PRODUCT(R94:R95)</f>
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="17:22" x14ac:dyDescent="0.2">
-      <c r="Q101" s="57" t="s">
+      <c r="Q101" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="R101" s="60">
+      <c r="R101" s="43">
         <f>PRODUCT(R95)</f>
         <v>1</v>
       </c>
@@ -4205,13 +4243,13 @@
       </c>
     </row>
     <row r="104" spans="17:22" x14ac:dyDescent="0.2">
-      <c r="Q104" s="79" t="s">
+      <c r="Q104" s="12" t="s">
         <v>121</v>
       </c>
       <c r="R104">
         <v>510</v>
       </c>
-      <c r="S104" s="62">
+      <c r="S104" s="45">
         <f>R104*R98</f>
         <v>670.1400000000001</v>
       </c>
@@ -4226,8 +4264,8 @@
       <c r="R105">
         <v>545</v>
       </c>
-      <c r="S105" s="62">
-        <f t="shared" ref="S105:S108" si="8">R105*R99</f>
+      <c r="S105" s="45">
+        <f t="shared" ref="S105:S107" si="8">R105*R99</f>
         <v>654</v>
       </c>
     </row>
@@ -4238,7 +4276,7 @@
       <c r="R106">
         <v>675</v>
       </c>
-      <c r="S106" s="62">
+      <c r="S106" s="45">
         <f t="shared" si="8"/>
         <v>675</v>
       </c>
@@ -4250,19 +4288,19 @@
       <c r="R107">
         <v>645</v>
       </c>
-      <c r="S107" s="62">
+      <c r="S107" s="45">
         <f t="shared" si="8"/>
         <v>645</v>
       </c>
     </row>
     <row r="108" spans="17:22" x14ac:dyDescent="0.2">
-      <c r="Q108" s="63" t="s">
+      <c r="Q108" s="46" t="s">
         <v>125</v>
       </c>
       <c r="R108" s="1">
         <v>660</v>
       </c>
-      <c r="S108" s="64">
+      <c r="S108" s="47">
         <f>R108</f>
         <v>660</v>
       </c>
@@ -4271,18 +4309,18 @@
       <c r="Q109" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="R109" s="80">
+      <c r="R109" s="60">
         <f>SUM(R104:R108)</f>
         <v>3035</v>
       </c>
-      <c r="S109" s="62">
+      <c r="S109" s="45">
         <f>SUM(S104:S108)</f>
         <v>3304.1400000000003</v>
       </c>
       <c r="T109" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="U109" s="81">
+      <c r="U109" s="61">
         <f>S109-R109</f>
         <v>269.14000000000033</v>
       </c>
@@ -4291,24 +4329,24 @@
       </c>
     </row>
     <row r="116" spans="25:29" x14ac:dyDescent="0.2">
-      <c r="Y116" s="54" t="s">
+      <c r="Y116" s="81" t="s">
         <v>158</v>
       </c>
-      <c r="Z116" s="54"/>
-      <c r="AA116" s="54"/>
-      <c r="AB116" s="54"/>
-      <c r="AC116" s="54"/>
+      <c r="Z116" s="81"/>
+      <c r="AA116" s="81"/>
+      <c r="AB116" s="81"/>
+      <c r="AC116" s="81"/>
     </row>
     <row r="117" spans="25:29" x14ac:dyDescent="0.2">
-      <c r="Y117" s="55" t="s">
+      <c r="Y117" s="78" t="s">
         <v>96</v>
       </c>
-      <c r="Z117" s="76" t="s">
+      <c r="Z117" s="11" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="118" spans="25:29" x14ac:dyDescent="0.2">
-      <c r="Y118" s="55"/>
+      <c r="Y118" s="78"/>
       <c r="Z118" s="11">
         <v>12</v>
       </c>
@@ -4378,22 +4416,22 @@
       <c r="AB122" s="12"/>
     </row>
     <row r="124" spans="25:29" x14ac:dyDescent="0.2">
-      <c r="Y124" s="55" t="s">
+      <c r="Y124" s="78" t="s">
         <v>96</v>
       </c>
-      <c r="Z124" s="76" t="s">
+      <c r="Z124" s="11" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="125" spans="25:29" x14ac:dyDescent="0.2">
-      <c r="Y125" s="55"/>
-      <c r="Z125" s="57" t="s">
+      <c r="Y125" s="78"/>
+      <c r="Z125" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="AA125" s="57" t="s">
+      <c r="AA125" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="AB125" s="57" t="s">
+      <c r="AB125" s="40" t="s">
         <v>105</v>
       </c>
       <c r="AC125" s="11"/>
@@ -4402,15 +4440,15 @@
       <c r="Y126" s="12">
         <v>2012</v>
       </c>
-      <c r="Z126" s="58">
+      <c r="Z126" s="41">
         <f>AA119/Z119</f>
         <v>1.1176470588235294</v>
       </c>
-      <c r="AA126" s="58">
+      <c r="AA126" s="41">
         <f t="shared" ref="AA126:AB127" si="9">AB119/AA119</f>
         <v>2.0526315789473686</v>
       </c>
-      <c r="AB126" s="58">
+      <c r="AB126" s="41">
         <f t="shared" si="9"/>
         <v>1.2564102564102564</v>
       </c>
@@ -4420,27 +4458,27 @@
       <c r="Y127" s="12">
         <v>2013</v>
       </c>
-      <c r="Z127" s="58">
+      <c r="Z127" s="41">
         <f t="shared" ref="Z127:Z128" si="10">AA120/Z120</f>
         <v>3.1428571428571428</v>
       </c>
-      <c r="AA127" s="58">
+      <c r="AA127" s="41">
         <f t="shared" si="9"/>
         <v>1.5</v>
       </c>
-      <c r="AB127" s="58"/>
+      <c r="AB127" s="41"/>
       <c r="AC127" s="12"/>
     </row>
     <row r="128" spans="25:29" x14ac:dyDescent="0.2">
       <c r="Y128" s="12">
         <v>2014</v>
       </c>
-      <c r="Z128" s="58">
+      <c r="Z128" s="41">
         <f t="shared" si="10"/>
         <v>1.7777777777777777</v>
       </c>
-      <c r="AA128" s="58"/>
-      <c r="AB128" s="58"/>
+      <c r="AA128" s="41"/>
+      <c r="AB128" s="41"/>
       <c r="AC128" s="12"/>
     </row>
     <row r="129" spans="25:29" x14ac:dyDescent="0.2">
@@ -4458,10 +4496,10 @@
       </c>
     </row>
     <row r="131" spans="25:29" x14ac:dyDescent="0.2">
-      <c r="Y131" s="82" t="s">
+      <c r="Y131" s="62" t="s">
         <v>103</v>
       </c>
-      <c r="Z131" s="60">
+      <c r="Z131" s="43">
         <f>AVERAGE(Z126:Z128)</f>
         <v>2.0127606598194832</v>
       </c>
@@ -4473,10 +4511,10 @@
       </c>
     </row>
     <row r="132" spans="25:29" x14ac:dyDescent="0.2">
-      <c r="Y132" s="82" t="s">
+      <c r="Y132" s="62" t="s">
         <v>104</v>
       </c>
-      <c r="Z132" s="60">
+      <c r="Z132" s="43">
         <f>AVERAGE(AA126:AA127)</f>
         <v>1.7763157894736843</v>
       </c>
@@ -4485,10 +4523,10 @@
       </c>
     </row>
     <row r="133" spans="25:29" x14ac:dyDescent="0.2">
-      <c r="Y133" s="82" t="s">
+      <c r="Y133" s="62" t="s">
         <v>105</v>
       </c>
-      <c r="Z133" s="60">
+      <c r="Z133" s="43">
         <f>AVERAGE(AB126)</f>
         <v>1.2564102564102564</v>
       </c>
@@ -4505,7 +4543,7 @@
       <c r="Y136" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="Z136" s="60">
+      <c r="Z136" s="43">
         <f>PRODUCT(Z131:Z133)</f>
         <v>4.4920417559736441</v>
       </c>
@@ -4517,7 +4555,7 @@
       <c r="Y137" t="s">
         <v>163</v>
       </c>
-      <c r="Z137" s="60">
+      <c r="Z137" s="43">
         <f>PRODUCT(Z132:Z133)</f>
         <v>2.2317813765182186</v>
       </c>
@@ -4526,7 +4564,7 @@
       <c r="Y138" t="s">
         <v>164</v>
       </c>
-      <c r="Z138" s="60">
+      <c r="Z138" s="43">
         <f>PRODUCT(Z133)</f>
         <v>1.2564102564102564</v>
       </c>
@@ -4549,7 +4587,7 @@
       <c r="Z141">
         <v>1000</v>
       </c>
-      <c r="AA141" s="67">
+      <c r="AA141" s="50">
         <f t="shared" ref="AA141:AA142" si="11">Z141*Z136</f>
         <v>4492.0417559736443</v>
       </c>
@@ -4564,7 +4602,7 @@
       <c r="Z142">
         <v>1600</v>
       </c>
-      <c r="AA142" s="62">
+      <c r="AA142" s="45">
         <f t="shared" si="11"/>
         <v>3570.8502024291497</v>
       </c>
@@ -4576,7 +4614,7 @@
       <c r="Z143">
         <v>3300</v>
       </c>
-      <c r="AA143" s="62">
+      <c r="AA143" s="45">
         <f>Z143*Z138</f>
         <v>4146.1538461538457</v>
       </c>
@@ -4588,7 +4626,7 @@
       <c r="Z144" s="1">
         <v>2450</v>
       </c>
-      <c r="AA144" s="64">
+      <c r="AA144" s="47">
         <f>Z144</f>
         <v>2450</v>
       </c>
@@ -4597,11 +4635,11 @@
       <c r="Y145" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="Z145" s="80">
+      <c r="Z145" s="60">
         <f>SUM(Z141:Z144)</f>
         <v>8350</v>
       </c>
-      <c r="AA145" s="62">
+      <c r="AA145" s="45">
         <f>SUM(AA141:AA144)</f>
         <v>14659.045804556639</v>
       </c>
@@ -4610,30 +4648,30 @@
       <c r="Y148" s="3"/>
     </row>
     <row r="150" spans="25:28" x14ac:dyDescent="0.2">
-      <c r="Y150" s="51" t="s">
+      <c r="Y150" s="65" t="s">
         <v>173</v>
       </c>
-      <c r="Z150" s="51"/>
-      <c r="AA150" s="51"/>
-      <c r="AB150" s="51"/>
+      <c r="Z150" s="65"/>
+      <c r="AA150" s="65"/>
+      <c r="AB150" s="65"/>
     </row>
     <row r="151" spans="25:28" x14ac:dyDescent="0.2">
-      <c r="Y151" s="83" t="s">
+      <c r="Y151" s="79" t="s">
         <v>96</v>
       </c>
-      <c r="Z151" s="76" t="s">
+      <c r="Z151" s="11" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="152" spans="25:28" x14ac:dyDescent="0.2">
-      <c r="Y152" s="83"/>
-      <c r="Z152" s="57" t="s">
+      <c r="Y152" s="79"/>
+      <c r="Z152" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="AA152" s="57" t="s">
+      <c r="AA152" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="AB152" s="57" t="s">
+      <c r="AB152" s="40" t="s">
         <v>105</v>
       </c>
     </row>
@@ -4681,10 +4719,10 @@
       </c>
     </row>
     <row r="158" spans="25:28" x14ac:dyDescent="0.2">
-      <c r="Y158" s="82" t="s">
+      <c r="Y158" s="62" t="s">
         <v>103</v>
       </c>
-      <c r="Z158" s="60">
+      <c r="Z158" s="43">
         <f>AVERAGE(Z153:Z155)</f>
         <v>2.0099999999999998</v>
       </c>
@@ -4693,19 +4731,19 @@
       </c>
     </row>
     <row r="159" spans="25:28" x14ac:dyDescent="0.2">
-      <c r="Y159" s="82" t="s">
+      <c r="Y159" s="62" t="s">
         <v>104</v>
       </c>
-      <c r="Z159" s="60">
+      <c r="Z159" s="43">
         <f>AVERAGE(AA153:AA154)</f>
         <v>1.2549999999999999</v>
       </c>
     </row>
     <row r="160" spans="25:28" x14ac:dyDescent="0.2">
-      <c r="Y160" s="82" t="s">
+      <c r="Y160" s="62" t="s">
         <v>105</v>
       </c>
-      <c r="Z160" s="60">
+      <c r="Z160" s="43">
         <f>AVERAGE(AB153)</f>
         <v>1.1000000000000001</v>
       </c>
@@ -4722,7 +4760,7 @@
       <c r="Y163" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="Z163" s="60">
+      <c r="Z163" s="43">
         <f>PRODUCT(Z158:Z160)</f>
         <v>2.7748049999999997</v>
       </c>
@@ -4734,7 +4772,7 @@
       <c r="Y164" t="s">
         <v>163</v>
       </c>
-      <c r="Z164" s="60">
+      <c r="Z164" s="43">
         <f>PRODUCT(Z159:Z160)</f>
         <v>1.3805000000000001</v>
       </c>
@@ -4743,7 +4781,7 @@
       <c r="Y165" t="s">
         <v>164</v>
       </c>
-      <c r="Z165" s="60">
+      <c r="Z165" s="43">
         <f>PRODUCT(Z160)</f>
         <v>1.1000000000000001</v>
       </c>
@@ -4766,7 +4804,7 @@
       <c r="Z168">
         <v>1000</v>
       </c>
-      <c r="AA168" s="67">
+      <c r="AA168" s="50">
         <f>Z168*Z163</f>
         <v>2774.8049999999998</v>
       </c>
@@ -4781,8 +4819,8 @@
       <c r="Z169">
         <v>1600</v>
       </c>
-      <c r="AA169" s="62">
-        <f t="shared" ref="AA168:AA169" si="12">Z169*Z164</f>
+      <c r="AA169" s="45">
+        <f t="shared" ref="AA169" si="12">Z169*Z164</f>
         <v>2208.8000000000002</v>
       </c>
     </row>
@@ -4793,7 +4831,7 @@
       <c r="Z170">
         <v>3300</v>
       </c>
-      <c r="AA170" s="62">
+      <c r="AA170" s="45">
         <f>Z170*Z165</f>
         <v>3630.0000000000005</v>
       </c>
@@ -4805,7 +4843,7 @@
       <c r="Z171" s="1">
         <v>2450</v>
       </c>
-      <c r="AA171" s="64">
+      <c r="AA171" s="47">
         <f>Z171</f>
         <v>2450</v>
       </c>
@@ -4814,17 +4852,21 @@
       <c r="Y172" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="Z172" s="80">
+      <c r="Z172" s="60">
         <f>SUM(Z168:Z171)</f>
         <v>8350</v>
       </c>
-      <c r="AA172" s="62">
+      <c r="AA172" s="45">
         <f>SUM(AA168:AA171)</f>
         <v>11063.605</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="I49:I50"/>
     <mergeCell ref="Y124:Y125"/>
     <mergeCell ref="Y151:Y152"/>
     <mergeCell ref="Y150:AB150"/>
@@ -4834,11 +4876,205 @@
     <mergeCell ref="R83:R85"/>
     <mergeCell ref="Y117:Y118"/>
     <mergeCell ref="Y116:AC116"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="I49:I50"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CEABBE1-93F4-6A42-86E6-4D91298C2F20}">
+  <dimension ref="B2:E19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="29.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2" s="82">
+        <v>50000</v>
+      </c>
+      <c r="D2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E2" s="82">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C3" s="19">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B5" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B6" s="12">
+        <v>1</v>
+      </c>
+      <c r="C6" s="52">
+        <v>75000</v>
+      </c>
+      <c r="D6" s="53">
+        <f t="shared" ref="D6:D8" si="0">IF(C6&gt;$E$2,MIN(C6-$E$2,$C$2),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B7" s="12">
+        <v>2</v>
+      </c>
+      <c r="C7" s="52">
+        <v>100000</v>
+      </c>
+      <c r="D7" s="53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B8" s="12">
+        <v>3</v>
+      </c>
+      <c r="C8" s="52">
+        <v>125000</v>
+      </c>
+      <c r="D8" s="53">
+        <f t="shared" si="0"/>
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B9" s="46">
+        <v>4</v>
+      </c>
+      <c r="C9" s="83">
+        <v>150000</v>
+      </c>
+      <c r="D9" s="86">
+        <f>IF(C9&gt;$E$2,MIN(C9-$E$2,$C$2),0)</f>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B10" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="53">
+        <f>SUM(C6:C9)</f>
+        <v>450000</v>
+      </c>
+      <c r="D10" s="53">
+        <f>SUM(D6:D9)</f>
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B12" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B13" s="12">
+        <v>1</v>
+      </c>
+      <c r="C13" s="87">
+        <f>C6*(1+$C$3)</f>
+        <v>82500</v>
+      </c>
+      <c r="D13" s="53">
+        <f t="shared" ref="D13:D15" si="1">IF(C13&gt;$E$2,MIN(C13-$E$2,$C$2),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B14" s="12">
+        <v>2</v>
+      </c>
+      <c r="C14" s="87">
+        <f t="shared" ref="C14:C15" si="2">C7*(1+$C$3)</f>
+        <v>110000.00000000001</v>
+      </c>
+      <c r="D14" s="53">
+        <f t="shared" si="1"/>
+        <v>10000.000000000015</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B15" s="12">
+        <v>3</v>
+      </c>
+      <c r="C15" s="87">
+        <f t="shared" si="2"/>
+        <v>137500</v>
+      </c>
+      <c r="D15" s="53">
+        <f t="shared" si="1"/>
+        <v>37500</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B16" s="46">
+        <v>4</v>
+      </c>
+      <c r="C16" s="88">
+        <f>C9*(1+$C$3)</f>
+        <v>165000</v>
+      </c>
+      <c r="D16" s="86">
+        <f>IF(C16&gt;$E$2,MIN(C16-$E$2,$C$2),0)</f>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B17" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="53">
+        <f>SUM(C13:C16)</f>
+        <v>495000</v>
+      </c>
+      <c r="D17" s="53">
+        <f>SUM(D13:D16)</f>
+        <v>97500.000000000015</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="C19" s="84" t="s">
+        <v>186</v>
+      </c>
+      <c r="D19" s="85">
+        <f>D17/D10-1</f>
+        <v>0.30000000000000027</v>
+      </c>
+      <c r="E19" s="36" t="s">
+        <v>185</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/files/temp-work.xlsx
+++ b/files/temp-work.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/coltongearhart/Desktop/exam5/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7E6E09D-C3D2-A84F-8E96-8B0FAB504BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3149601-6926-F14E-BCA9-42D79DCD5816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" activeTab="4" xr2:uid="{BB8505BC-BCB7-B340-A120-C046C43AD7BD}"/>
+    <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" activeTab="5" xr2:uid="{BB8505BC-BCB7-B340-A120-C046C43AD7BD}"/>
   </bookViews>
   <sheets>
     <sheet name="2.2.1" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="2.3.1" sheetId="3" r:id="rId3"/>
     <sheet name="2.3.3" sheetId="4" r:id="rId4"/>
     <sheet name="2.4.3" sheetId="5" r:id="rId5"/>
+    <sheet name="2.5.3" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="283">
   <si>
     <t>Ratio to SAWW</t>
   </si>
@@ -612,12 +613,300 @@
   <si>
     <t xml:space="preserve">50k excess of 100k trend= </t>
   </si>
+  <si>
+    <t>Annual Policy Period</t>
+  </si>
+  <si>
+    <t>Countrywide Other Acquisition</t>
+  </si>
+  <si>
+    <t>Statewide Taxes, Licenses, and Fees</t>
+  </si>
+  <si>
+    <t>Statewide Commissions and Brokerage</t>
+  </si>
+  <si>
+    <t>Countrywide General Expenses</t>
+  </si>
+  <si>
+    <t>Statewide Earned Premium</t>
+  </si>
+  <si>
+    <t>Statewide Written Premium</t>
+  </si>
+  <si>
+    <t>Countrywide Earned Premium</t>
+  </si>
+  <si>
+    <t>Countrywide Written Premium</t>
+  </si>
+  <si>
+    <t>=E7/E$10</t>
+  </si>
+  <si>
+    <t>Selection</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>Justification</t>
+  </si>
+  <si>
+    <t>-&gt; Use statewide EP for 'Statewide' expenses obviously</t>
+  </si>
+  <si>
+    <t>All-year average</t>
+  </si>
+  <si>
+    <t>Stable over the three years</t>
+  </si>
+  <si>
+    <t>Average of latest two years</t>
+  </si>
+  <si>
+    <t>Exclude 2021 because of unusually high expenses, then stable after that</t>
+  </si>
+  <si>
+    <t>Latest year's ratio</t>
+  </si>
+  <si>
+    <t>Expenses continually decrease</t>
+  </si>
+  <si>
+    <t>=SUM(I15:I18)</t>
+  </si>
+  <si>
+    <t>All-variable expense method</t>
+  </si>
+  <si>
+    <t>Premium-based projection method</t>
+  </si>
+  <si>
+    <t>&lt; same selections as above, just divvy out between fixed and variable expenses &gt;</t>
+  </si>
+  <si>
+    <t>Expense Category</t>
+  </si>
+  <si>
+    <t>% Fixed</t>
+  </si>
+  <si>
+    <t>Other Acquisition</t>
+  </si>
+  <si>
+    <t>Taxes, Licenses, and Fees</t>
+  </si>
+  <si>
+    <t>Commissions and Brokerage</t>
+  </si>
+  <si>
+    <t>General Expenses</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>=$I15*$C25</t>
+  </si>
+  <si>
+    <t>=$I15*(1-$C25)</t>
+  </si>
+  <si>
+    <t>=SUM(J25:J28)</t>
+  </si>
+  <si>
+    <t>=SUM(I25:I28)</t>
+  </si>
+  <si>
+    <t>Divide general expenses by EP because they are incurred throughout the policy period, but divide all other expenses by their respective WP because they are incurred at the onset of the policy period</t>
+  </si>
+  <si>
+    <t>=E4/E$11</t>
+  </si>
+  <si>
+    <t>=E5/E$9</t>
+  </si>
+  <si>
+    <t>=E6/E$9</t>
+  </si>
+  <si>
+    <t>Fixed General Expense as Percentage of General Expense</t>
+  </si>
+  <si>
+    <t>Countrywide Earned Exposures</t>
+  </si>
+  <si>
+    <t>Countrywide Written Exposures</t>
+  </si>
+  <si>
+    <t>$475,00</t>
+  </si>
+  <si>
+    <t>Projected Expense Provisions</t>
+  </si>
+  <si>
+    <t>Fixed expenses - General</t>
+  </si>
+  <si>
+    <t>General expense per exposure</t>
+  </si>
+  <si>
+    <t>Fixed expense</t>
+  </si>
+  <si>
+    <t>Trend period (years)</t>
+  </si>
+  <si>
+    <t>Trended fixed expense per exposure</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>=R35/R37</t>
+  </si>
+  <si>
+    <t>=V35*R36</t>
+  </si>
+  <si>
+    <t>=W35*(1+$R$47)^X35</t>
+  </si>
+  <si>
+    <t>=Y37+SUM(R43:R45)</t>
+  </si>
+  <si>
+    <t>=AVERAGE(Y35:Y36)</t>
+  </si>
+  <si>
+    <t>Fixed expense trend</t>
+  </si>
+  <si>
+    <t>Variable expenses - General</t>
+  </si>
+  <si>
+    <t>Ratio</t>
+  </si>
+  <si>
+    <t>Divide by EP because incurred throughout policy period</t>
+  </si>
+  <si>
+    <t>=AVERAGE(V43:V44)</t>
+  </si>
+  <si>
+    <t>=V45+SUM(S43:S45)</t>
+  </si>
+  <si>
+    <t>Variable expense</t>
+  </si>
+  <si>
+    <t>=R35*(1-R36)</t>
+  </si>
+  <si>
+    <t>=V43/R39</t>
+  </si>
+  <si>
+    <t>2020 Data</t>
+  </si>
+  <si>
+    <t>Earned Premium</t>
+  </si>
+  <si>
+    <t>Written Premium</t>
+  </si>
+  <si>
+    <t>Written Exposures</t>
+  </si>
+  <si>
+    <t>Fixed expense provision using the Exposure-Based Projection Method</t>
+  </si>
+  <si>
+    <t>Expense per exposure</t>
+  </si>
+  <si>
+    <t>WP</t>
+  </si>
+  <si>
+    <t>Based on (divided by)</t>
+  </si>
+  <si>
+    <t>EE</t>
+  </si>
+  <si>
+    <t>WE</t>
+  </si>
+  <si>
+    <t>* To average earned / written date for proposed rates</t>
+  </si>
+  <si>
+    <t>Trended expense per exposure</t>
+  </si>
+  <si>
+    <t>=SUM(AO51:AO54)</t>
+  </si>
+  <si>
+    <t>Variable expense ratio</t>
+  </si>
+  <si>
+    <t>=SUM(AM57:AM60)</t>
+  </si>
+  <si>
+    <t>Trend period ^</t>
+  </si>
+  <si>
+    <t>Variable Permissable Loss Ratio</t>
+  </si>
+  <si>
+    <t>Target UW Profit</t>
+  </si>
+  <si>
+    <t>=AL51*AH51</t>
+  </si>
+  <si>
+    <t>=AG51*(1-AH51)</t>
+  </si>
+  <si>
+    <t>=AL57/AG55</t>
+  </si>
+  <si>
+    <t>=AL58/$AG$56</t>
+  </si>
+  <si>
+    <t>=AM51*(1+$AG$60)^AN51</t>
+  </si>
+  <si>
+    <t>=1-AM62-AG61</t>
+  </si>
+  <si>
+    <t>Permissible loss ratio that would result from using the Premium-Based Projection Method</t>
+  </si>
+  <si>
+    <t>=AL68/AG55</t>
+  </si>
+  <si>
+    <t>'=AL58/$AG$56</t>
+  </si>
+  <si>
+    <t>'=SUM(AM57:AM60)</t>
+  </si>
+  <si>
+    <t>PLR</t>
+  </si>
+  <si>
+    <t>=1-AM72-AM62-AG61</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -625,8 +914,9 @@
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="172" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -705,6 +995,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF202834"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF202834"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFFC000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -720,7 +1034,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -814,13 +1128,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -892,18 +1215,15 @@
     <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="6" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="9" fontId="7" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="6" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="6" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -937,6 +1257,18 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -949,15 +1281,50 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="6" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="6" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="6" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="10" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="14" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="15" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="10" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="6" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="6" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="8" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="172" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="7" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="6" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -2032,26 +2399,26 @@
       </c>
     </row>
     <row r="23" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="M23" s="70"/>
-      <c r="N23" s="71"/>
-      <c r="O23" s="67" t="s">
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
+      <c r="O23" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="P23" s="68"/>
-      <c r="Q23" s="68"/>
-      <c r="R23" s="69"/>
-      <c r="S23" s="67" t="s">
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="72"/>
+      <c r="S23" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="T23" s="68"/>
-      <c r="U23" s="68"/>
-      <c r="V23" s="69"/>
-      <c r="W23" s="67" t="s">
+      <c r="T23" s="71"/>
+      <c r="U23" s="71"/>
+      <c r="V23" s="72"/>
+      <c r="W23" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="X23" s="68"/>
-      <c r="Y23" s="68"/>
-      <c r="Z23" s="69"/>
+      <c r="X23" s="71"/>
+      <c r="Y23" s="71"/>
+      <c r="Z23" s="72"/>
     </row>
     <row r="24" spans="2:33" x14ac:dyDescent="0.2">
       <c r="M24" s="24" t="s">
@@ -2117,35 +2484,35 @@
       <c r="R25" s="30">
         <v>0</v>
       </c>
-      <c r="S25" s="76">
+      <c r="S25" s="79">
         <f>SUMPRODUCT(O25:O27,$N$25:$N$27)</f>
         <v>1.0568750000000002</v>
       </c>
-      <c r="T25" s="74">
+      <c r="T25" s="77">
         <f t="shared" ref="T25:V25" si="2">SUMPRODUCT(P25:P27,$N$25:$N$27)</f>
         <v>1.089375</v>
       </c>
-      <c r="U25" s="74">
+      <c r="U25" s="77">
         <f t="shared" si="2"/>
         <v>1.1156250000000001</v>
       </c>
-      <c r="V25" s="72">
+      <c r="V25" s="75">
         <f t="shared" si="2"/>
         <v>1.1418750000000002</v>
       </c>
-      <c r="W25" s="76">
+      <c r="W25" s="79">
         <f>$N$27/S25</f>
         <v>1.0928444707273803</v>
       </c>
-      <c r="X25" s="74">
+      <c r="X25" s="77">
         <f t="shared" ref="X25:Z25" si="3">$N$27/T25</f>
         <v>1.060240963855422</v>
       </c>
-      <c r="Y25" s="74">
+      <c r="Y25" s="77">
         <f t="shared" si="3"/>
         <v>1.0352941176470589</v>
       </c>
-      <c r="Z25" s="72">
+      <c r="Z25" s="75">
         <f t="shared" si="3"/>
         <v>1.0114942528735633</v>
       </c>
@@ -2170,14 +2537,14 @@
       <c r="R26" s="30">
         <v>0.125</v>
       </c>
-      <c r="S26" s="76"/>
-      <c r="T26" s="74"/>
-      <c r="U26" s="74"/>
-      <c r="V26" s="72"/>
-      <c r="W26" s="76"/>
-      <c r="X26" s="74"/>
-      <c r="Y26" s="74"/>
-      <c r="Z26" s="72"/>
+      <c r="S26" s="79"/>
+      <c r="T26" s="77"/>
+      <c r="U26" s="77"/>
+      <c r="V26" s="75"/>
+      <c r="W26" s="79"/>
+      <c r="X26" s="77"/>
+      <c r="Y26" s="77"/>
+      <c r="Z26" s="75"/>
     </row>
     <row r="27" spans="2:33" x14ac:dyDescent="0.2">
       <c r="M27" s="28">
@@ -2199,14 +2566,14 @@
       <c r="R27" s="31">
         <v>0.875</v>
       </c>
-      <c r="S27" s="77"/>
-      <c r="T27" s="75"/>
-      <c r="U27" s="75"/>
-      <c r="V27" s="73"/>
-      <c r="W27" s="77"/>
-      <c r="X27" s="75"/>
-      <c r="Y27" s="75"/>
-      <c r="Z27" s="73"/>
+      <c r="S27" s="80"/>
+      <c r="T27" s="78"/>
+      <c r="U27" s="78"/>
+      <c r="V27" s="76"/>
+      <c r="W27" s="80"/>
+      <c r="X27" s="78"/>
+      <c r="Y27" s="78"/>
+      <c r="Z27" s="76"/>
     </row>
     <row r="28" spans="2:33" x14ac:dyDescent="0.2">
       <c r="N28" s="32" t="s">
@@ -2287,23 +2654,23 @@
       </c>
     </row>
     <row r="37" spans="15:41" x14ac:dyDescent="0.2">
-      <c r="AE37" s="64"/>
-      <c r="AF37" s="64"/>
-      <c r="AG37" s="65" t="s">
+      <c r="AE37" s="83"/>
+      <c r="AF37" s="83"/>
+      <c r="AG37" s="82" t="s">
         <v>72</v>
       </c>
-      <c r="AH37" s="65"/>
-      <c r="AI37" s="65"/>
-      <c r="AJ37" s="65" t="s">
+      <c r="AH37" s="82"/>
+      <c r="AI37" s="82"/>
+      <c r="AJ37" s="82" t="s">
         <v>76</v>
       </c>
-      <c r="AK37" s="65"/>
-      <c r="AL37" s="65"/>
-      <c r="AM37" s="65" t="s">
+      <c r="AK37" s="82"/>
+      <c r="AL37" s="82"/>
+      <c r="AM37" s="82" t="s">
         <v>77</v>
       </c>
-      <c r="AN37" s="65"/>
-      <c r="AO37" s="65"/>
+      <c r="AN37" s="82"/>
+      <c r="AO37" s="82"/>
     </row>
     <row r="38" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE38" s="15" t="s">
@@ -2352,18 +2719,18 @@
         <f>0.5*3/4*3/4</f>
         <v>0.28125</v>
       </c>
-      <c r="AJ39" s="63"/>
-      <c r="AK39" s="63">
+      <c r="AJ39" s="81"/>
+      <c r="AK39" s="81">
         <f>SUMPRODUCT(AH39:AH42,AF39:AF42)</f>
         <v>1.0636875000000001</v>
       </c>
-      <c r="AL39" s="63"/>
-      <c r="AM39" s="63"/>
-      <c r="AN39" s="63">
+      <c r="AL39" s="81"/>
+      <c r="AM39" s="81"/>
+      <c r="AN39" s="81">
         <f>$AF$42/AK39</f>
         <v>1.0512015982137612</v>
       </c>
-      <c r="AO39" s="63"/>
+      <c r="AO39" s="81"/>
     </row>
     <row r="40" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE40">
@@ -2377,12 +2744,12 @@
         <f>1-AH39-AH41</f>
         <v>0.59375</v>
       </c>
-      <c r="AJ40" s="63"/>
-      <c r="AK40" s="63"/>
-      <c r="AL40" s="63"/>
-      <c r="AM40" s="63"/>
-      <c r="AN40" s="63"/>
-      <c r="AO40" s="63"/>
+      <c r="AJ40" s="81"/>
+      <c r="AK40" s="81"/>
+      <c r="AL40" s="81"/>
+      <c r="AM40" s="81"/>
+      <c r="AN40" s="81"/>
+      <c r="AO40" s="81"/>
     </row>
     <row r="41" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE41">
@@ -2395,12 +2762,12 @@
       <c r="AH41">
         <v>0.125</v>
       </c>
-      <c r="AJ41" s="63"/>
-      <c r="AK41" s="63"/>
-      <c r="AL41" s="63"/>
-      <c r="AM41" s="63"/>
-      <c r="AN41" s="63"/>
-      <c r="AO41" s="63"/>
+      <c r="AJ41" s="81"/>
+      <c r="AK41" s="81"/>
+      <c r="AL41" s="81"/>
+      <c r="AM41" s="81"/>
+      <c r="AN41" s="81"/>
+      <c r="AO41" s="81"/>
     </row>
     <row r="42" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE42">
@@ -2413,31 +2780,31 @@
       <c r="AH42">
         <v>0</v>
       </c>
-      <c r="AJ42" s="63"/>
-      <c r="AK42" s="63"/>
-      <c r="AL42" s="63"/>
-      <c r="AM42" s="63"/>
-      <c r="AN42" s="63"/>
-      <c r="AO42" s="63"/>
+      <c r="AJ42" s="81"/>
+      <c r="AK42" s="81"/>
+      <c r="AL42" s="81"/>
+      <c r="AM42" s="81"/>
+      <c r="AN42" s="81"/>
+      <c r="AO42" s="81"/>
     </row>
     <row r="44" spans="15:41" x14ac:dyDescent="0.2">
-      <c r="AE44" s="64"/>
-      <c r="AF44" s="64"/>
-      <c r="AG44" s="65" t="s">
+      <c r="AE44" s="83"/>
+      <c r="AF44" s="83"/>
+      <c r="AG44" s="82" t="s">
         <v>72</v>
       </c>
-      <c r="AH44" s="65"/>
-      <c r="AI44" s="65"/>
-      <c r="AJ44" s="65" t="s">
+      <c r="AH44" s="82"/>
+      <c r="AI44" s="82"/>
+      <c r="AJ44" s="82" t="s">
         <v>76</v>
       </c>
-      <c r="AK44" s="65"/>
-      <c r="AL44" s="65"/>
-      <c r="AM44" s="65" t="s">
+      <c r="AK44" s="82"/>
+      <c r="AL44" s="82"/>
+      <c r="AM44" s="82" t="s">
         <v>77</v>
       </c>
-      <c r="AN44" s="65"/>
-      <c r="AO44" s="65"/>
+      <c r="AN44" s="82"/>
+      <c r="AO44" s="82"/>
     </row>
     <row r="45" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE45" s="15" t="s">
@@ -2485,18 +2852,18 @@
       <c r="AH46">
         <v>0</v>
       </c>
-      <c r="AJ46" s="63"/>
-      <c r="AK46" s="63">
+      <c r="AJ46" s="81"/>
+      <c r="AK46" s="81">
         <f>SUMPRODUCT(AH46:AH49,AF46:AF49)</f>
         <v>1.1161437500000002</v>
       </c>
-      <c r="AL46" s="63"/>
-      <c r="AM46" s="63"/>
-      <c r="AN46" s="63">
+      <c r="AL46" s="81"/>
+      <c r="AM46" s="81"/>
+      <c r="AN46" s="81">
         <f>$AF$49/AK46</f>
         <v>1.0017974835230676</v>
       </c>
-      <c r="AO46" s="63"/>
+      <c r="AO46" s="81"/>
     </row>
     <row r="47" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE47">
@@ -2509,12 +2876,12 @@
       <c r="AH47">
         <v>0.5</v>
       </c>
-      <c r="AJ47" s="63"/>
-      <c r="AK47" s="63"/>
-      <c r="AL47" s="63"/>
-      <c r="AM47" s="63"/>
-      <c r="AN47" s="63"/>
-      <c r="AO47" s="63"/>
+      <c r="AJ47" s="81"/>
+      <c r="AK47" s="81"/>
+      <c r="AL47" s="81"/>
+      <c r="AM47" s="81"/>
+      <c r="AN47" s="81"/>
+      <c r="AO47" s="81"/>
     </row>
     <row r="48" spans="15:41" x14ac:dyDescent="0.2">
       <c r="O48" t="s">
@@ -2530,12 +2897,12 @@
       <c r="AH48">
         <v>0.375</v>
       </c>
-      <c r="AJ48" s="63"/>
-      <c r="AK48" s="63"/>
-      <c r="AL48" s="63"/>
-      <c r="AM48" s="63"/>
-      <c r="AN48" s="63"/>
-      <c r="AO48" s="63"/>
+      <c r="AJ48" s="81"/>
+      <c r="AK48" s="81"/>
+      <c r="AL48" s="81"/>
+      <c r="AM48" s="81"/>
+      <c r="AN48" s="81"/>
+      <c r="AO48" s="81"/>
     </row>
     <row r="49" spans="31:52" x14ac:dyDescent="0.2">
       <c r="AE49">
@@ -2548,12 +2915,12 @@
       <c r="AH49">
         <v>0.125</v>
       </c>
-      <c r="AJ49" s="63"/>
-      <c r="AK49" s="63"/>
-      <c r="AL49" s="63"/>
-      <c r="AM49" s="63"/>
-      <c r="AN49" s="63"/>
-      <c r="AO49" s="63"/>
+      <c r="AJ49" s="81"/>
+      <c r="AK49" s="81"/>
+      <c r="AL49" s="81"/>
+      <c r="AM49" s="81"/>
+      <c r="AN49" s="81"/>
+      <c r="AO49" s="81"/>
     </row>
     <row r="53" spans="31:52" x14ac:dyDescent="0.2">
       <c r="AS53" s="15" t="s">
@@ -2603,20 +2970,20 @@
       </c>
     </row>
     <row r="58" spans="31:52" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="AS58" s="64"/>
-      <c r="AT58" s="64"/>
-      <c r="AU58" s="65" t="s">
+      <c r="AS58" s="83"/>
+      <c r="AT58" s="83"/>
+      <c r="AU58" s="82" t="s">
         <v>72</v>
       </c>
-      <c r="AV58" s="65"/>
-      <c r="AW58" s="66" t="s">
+      <c r="AV58" s="82"/>
+      <c r="AW58" s="84" t="s">
         <v>76</v>
       </c>
-      <c r="AX58" s="66"/>
-      <c r="AY58" s="65" t="s">
+      <c r="AX58" s="84"/>
+      <c r="AY58" s="82" t="s">
         <v>77</v>
       </c>
-      <c r="AZ58" s="65"/>
+      <c r="AZ58" s="82"/>
     </row>
     <row r="59" spans="31:52" x14ac:dyDescent="0.2">
       <c r="AS59" s="15" t="s">
@@ -2656,13 +3023,13 @@
         <f>1/16</f>
         <v>6.25E-2</v>
       </c>
-      <c r="AW60" s="63"/>
-      <c r="AX60" s="63">
+      <c r="AW60" s="81"/>
+      <c r="AX60" s="81">
         <f>SUMPRODUCT(AV60:AV62,AT60:AT62)</f>
         <v>1.0993750000000002</v>
       </c>
-      <c r="AY60" s="63"/>
-      <c r="AZ60" s="63">
+      <c r="AY60" s="81"/>
+      <c r="AZ60" s="81">
         <f>$AT$62/AX60</f>
         <v>1.0505969300739058</v>
       </c>
@@ -2679,10 +3046,10 @@
         <f>0.5-AV60</f>
         <v>0.4375</v>
       </c>
-      <c r="AW61" s="63"/>
-      <c r="AX61" s="63"/>
-      <c r="AY61" s="63"/>
-      <c r="AZ61" s="63"/>
+      <c r="AW61" s="81"/>
+      <c r="AX61" s="81"/>
+      <c r="AY61" s="81"/>
+      <c r="AZ61" s="81"/>
     </row>
     <row r="62" spans="31:52" x14ac:dyDescent="0.2">
       <c r="AS62">
@@ -2695,10 +3062,10 @@
       <c r="AV62">
         <v>0.5</v>
       </c>
-      <c r="AW62" s="63"/>
-      <c r="AX62" s="63"/>
-      <c r="AY62" s="63"/>
-      <c r="AZ62" s="63"/>
+      <c r="AW62" s="81"/>
+      <c r="AX62" s="81"/>
+      <c r="AY62" s="81"/>
+      <c r="AZ62" s="81"/>
     </row>
     <row r="63" spans="31:52" x14ac:dyDescent="0.2">
       <c r="AW63" s="23"/>
@@ -2708,23 +3075,15 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="W23:Z23"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="Z25:Z27"/>
-    <mergeCell ref="Y25:Y27"/>
-    <mergeCell ref="X25:X27"/>
-    <mergeCell ref="W25:W27"/>
-    <mergeCell ref="O23:R23"/>
-    <mergeCell ref="S25:S27"/>
-    <mergeCell ref="T25:T27"/>
-    <mergeCell ref="U25:U27"/>
-    <mergeCell ref="V25:V27"/>
-    <mergeCell ref="S23:V23"/>
-    <mergeCell ref="AJ46:AJ49"/>
-    <mergeCell ref="AK46:AK49"/>
-    <mergeCell ref="AL46:AL49"/>
-    <mergeCell ref="AM46:AM49"/>
-    <mergeCell ref="AN46:AN49"/>
+    <mergeCell ref="AW60:AW62"/>
+    <mergeCell ref="AZ60:AZ62"/>
+    <mergeCell ref="AY60:AY62"/>
+    <mergeCell ref="AX60:AX62"/>
+    <mergeCell ref="AO46:AO49"/>
+    <mergeCell ref="AS58:AT58"/>
+    <mergeCell ref="AU58:AV58"/>
+    <mergeCell ref="AW58:AX58"/>
+    <mergeCell ref="AY58:AZ58"/>
     <mergeCell ref="AM37:AO37"/>
     <mergeCell ref="AE44:AF44"/>
     <mergeCell ref="AG44:AI44"/>
@@ -2739,15 +3098,23 @@
     <mergeCell ref="AL39:AL42"/>
     <mergeCell ref="AK39:AK42"/>
     <mergeCell ref="AJ39:AJ42"/>
-    <mergeCell ref="AW60:AW62"/>
-    <mergeCell ref="AZ60:AZ62"/>
-    <mergeCell ref="AY60:AY62"/>
-    <mergeCell ref="AX60:AX62"/>
-    <mergeCell ref="AO46:AO49"/>
-    <mergeCell ref="AS58:AT58"/>
-    <mergeCell ref="AU58:AV58"/>
-    <mergeCell ref="AW58:AX58"/>
-    <mergeCell ref="AY58:AZ58"/>
+    <mergeCell ref="AJ46:AJ49"/>
+    <mergeCell ref="AK46:AK49"/>
+    <mergeCell ref="AL46:AL49"/>
+    <mergeCell ref="AM46:AM49"/>
+    <mergeCell ref="AN46:AN49"/>
+    <mergeCell ref="W23:Z23"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="Z25:Z27"/>
+    <mergeCell ref="Y25:Y27"/>
+    <mergeCell ref="X25:X27"/>
+    <mergeCell ref="W25:W27"/>
+    <mergeCell ref="O23:R23"/>
+    <mergeCell ref="S25:S27"/>
+    <mergeCell ref="T25:T27"/>
+    <mergeCell ref="U25:U27"/>
+    <mergeCell ref="V25:V27"/>
+    <mergeCell ref="S23:V23"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3167,7 +3534,7 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B3" s="78" t="s">
+      <c r="B3" s="85" t="s">
         <v>96</v>
       </c>
       <c r="C3" s="11" t="s">
@@ -3175,7 +3542,7 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="78"/>
+      <c r="B4" s="85"/>
       <c r="C4" s="11" t="s">
         <v>98</v>
       </c>
@@ -3279,7 +3646,7 @@
       <c r="F10" s="12"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B11" s="78" t="s">
+      <c r="B11" s="85" t="s">
         <v>96</v>
       </c>
       <c r="C11" s="11" t="s">
@@ -3287,7 +3654,7 @@
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B12" s="78"/>
+      <c r="B12" s="85"/>
       <c r="C12" s="11" t="s">
         <v>98</v>
       </c>
@@ -3387,7 +3754,7 @@
       <c r="G16" s="12"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B18" s="78" t="s">
+      <c r="B18" s="85" t="s">
         <v>96</v>
       </c>
       <c r="C18" s="11" t="s">
@@ -3395,7 +3762,7 @@
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B19" s="78"/>
+      <c r="B19" s="85"/>
       <c r="C19" s="39" t="s">
         <v>103</v>
       </c>
@@ -3695,7 +4062,7 @@
       </c>
     </row>
     <row r="49" spans="9:13" x14ac:dyDescent="0.2">
-      <c r="I49" s="78" t="s">
+      <c r="I49" s="85" t="s">
         <v>96</v>
       </c>
       <c r="J49" s="11" t="s">
@@ -3703,7 +4070,7 @@
       </c>
     </row>
     <row r="50" spans="9:13" x14ac:dyDescent="0.2">
-      <c r="I50" s="78"/>
+      <c r="I50" s="85"/>
       <c r="J50" s="11" t="s">
         <v>134</v>
       </c>
@@ -3887,10 +4254,10 @@
     </row>
     <row r="73" spans="9:23" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="74" spans="9:23" x14ac:dyDescent="0.2">
-      <c r="Q74" s="80" t="s">
+      <c r="Q74" s="87" t="s">
         <v>149</v>
       </c>
-      <c r="R74" s="80" t="s">
+      <c r="R74" s="87" t="s">
         <v>96</v>
       </c>
       <c r="S74" s="11" t="s">
@@ -3898,15 +4265,15 @@
       </c>
     </row>
     <row r="75" spans="9:23" x14ac:dyDescent="0.2">
-      <c r="Q75" s="80"/>
-      <c r="R75" s="80"/>
+      <c r="Q75" s="87"/>
+      <c r="R75" s="87"/>
       <c r="S75" s="11" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="76" spans="9:23" x14ac:dyDescent="0.2">
-      <c r="Q76" s="80"/>
-      <c r="R76" s="80"/>
+      <c r="Q76" s="87"/>
+      <c r="R76" s="87"/>
       <c r="S76" s="11">
         <v>12</v>
       </c>
@@ -4017,10 +4384,10 @@
       <c r="U81" s="12"/>
     </row>
     <row r="83" spans="17:23" x14ac:dyDescent="0.2">
-      <c r="Q83" s="80" t="s">
+      <c r="Q83" s="87" t="s">
         <v>149</v>
       </c>
-      <c r="R83" s="80" t="s">
+      <c r="R83" s="87" t="s">
         <v>96</v>
       </c>
       <c r="S83" s="11" t="s">
@@ -4028,15 +4395,15 @@
       </c>
     </row>
     <row r="84" spans="17:23" x14ac:dyDescent="0.2">
-      <c r="Q84" s="80"/>
-      <c r="R84" s="80"/>
+      <c r="Q84" s="87"/>
+      <c r="R84" s="87"/>
       <c r="S84" s="11" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="85" spans="17:23" x14ac:dyDescent="0.2">
-      <c r="Q85" s="80"/>
-      <c r="R85" s="80"/>
+      <c r="Q85" s="87"/>
+      <c r="R85" s="87"/>
       <c r="S85" s="39" t="s">
         <v>103</v>
       </c>
@@ -4329,16 +4696,16 @@
       </c>
     </row>
     <row r="116" spans="25:29" x14ac:dyDescent="0.2">
-      <c r="Y116" s="81" t="s">
+      <c r="Y116" s="88" t="s">
         <v>158</v>
       </c>
-      <c r="Z116" s="81"/>
-      <c r="AA116" s="81"/>
-      <c r="AB116" s="81"/>
-      <c r="AC116" s="81"/>
+      <c r="Z116" s="88"/>
+      <c r="AA116" s="88"/>
+      <c r="AB116" s="88"/>
+      <c r="AC116" s="88"/>
     </row>
     <row r="117" spans="25:29" x14ac:dyDescent="0.2">
-      <c r="Y117" s="78" t="s">
+      <c r="Y117" s="85" t="s">
         <v>96</v>
       </c>
       <c r="Z117" s="11" t="s">
@@ -4346,7 +4713,7 @@
       </c>
     </row>
     <row r="118" spans="25:29" x14ac:dyDescent="0.2">
-      <c r="Y118" s="78"/>
+      <c r="Y118" s="85"/>
       <c r="Z118" s="11">
         <v>12</v>
       </c>
@@ -4416,7 +4783,7 @@
       <c r="AB122" s="12"/>
     </row>
     <row r="124" spans="25:29" x14ac:dyDescent="0.2">
-      <c r="Y124" s="78" t="s">
+      <c r="Y124" s="85" t="s">
         <v>96</v>
       </c>
       <c r="Z124" s="11" t="s">
@@ -4424,7 +4791,7 @@
       </c>
     </row>
     <row r="125" spans="25:29" x14ac:dyDescent="0.2">
-      <c r="Y125" s="78"/>
+      <c r="Y125" s="85"/>
       <c r="Z125" s="40" t="s">
         <v>103</v>
       </c>
@@ -4648,15 +5015,15 @@
       <c r="Y148" s="3"/>
     </row>
     <row r="150" spans="25:28" x14ac:dyDescent="0.2">
-      <c r="Y150" s="65" t="s">
+      <c r="Y150" s="82" t="s">
         <v>173</v>
       </c>
-      <c r="Z150" s="65"/>
-      <c r="AA150" s="65"/>
-      <c r="AB150" s="65"/>
+      <c r="Z150" s="82"/>
+      <c r="AA150" s="82"/>
+      <c r="AB150" s="82"/>
     </row>
     <row r="151" spans="25:28" x14ac:dyDescent="0.2">
-      <c r="Y151" s="79" t="s">
+      <c r="Y151" s="86" t="s">
         <v>96</v>
       </c>
       <c r="Z151" s="11" t="s">
@@ -4664,7 +5031,7 @@
       </c>
     </row>
     <row r="152" spans="25:28" x14ac:dyDescent="0.2">
-      <c r="Y152" s="79"/>
+      <c r="Y152" s="86"/>
       <c r="Z152" s="40" t="s">
         <v>103</v>
       </c>
@@ -4863,11 +5230,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="Y124:Y125"/>
     <mergeCell ref="Y151:Y152"/>
     <mergeCell ref="Y150:AB150"/>
     <mergeCell ref="R74:R76"/>
@@ -4876,6 +5238,11 @@
     <mergeCell ref="R83:R85"/>
     <mergeCell ref="Y117:Y118"/>
     <mergeCell ref="Y116:AC116"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="Y124:Y125"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4893,13 +5260,13 @@
       <c r="B2" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="82">
+      <c r="C2" s="63">
         <v>50000</v>
       </c>
       <c r="D2" t="s">
         <v>183</v>
       </c>
-      <c r="E2" s="82">
+      <c r="E2" s="63">
         <v>100000</v>
       </c>
     </row>
@@ -4965,10 +5332,10 @@
       <c r="B9" s="46">
         <v>4</v>
       </c>
-      <c r="C9" s="83">
+      <c r="C9" s="64">
         <v>150000</v>
       </c>
-      <c r="D9" s="86">
+      <c r="D9" s="67">
         <f>IF(C9&gt;$E$2,MIN(C9-$E$2,$C$2),0)</f>
         <v>50000</v>
       </c>
@@ -5001,7 +5368,7 @@
       <c r="B13" s="12">
         <v>1</v>
       </c>
-      <c r="C13" s="87">
+      <c r="C13" s="68">
         <f>C6*(1+$C$3)</f>
         <v>82500</v>
       </c>
@@ -5014,7 +5381,7 @@
       <c r="B14" s="12">
         <v>2</v>
       </c>
-      <c r="C14" s="87">
+      <c r="C14" s="68">
         <f t="shared" ref="C14:C15" si="2">C7*(1+$C$3)</f>
         <v>110000.00000000001</v>
       </c>
@@ -5027,7 +5394,7 @@
       <c r="B15" s="12">
         <v>3</v>
       </c>
-      <c r="C15" s="87">
+      <c r="C15" s="68">
         <f t="shared" si="2"/>
         <v>137500</v>
       </c>
@@ -5040,11 +5407,11 @@
       <c r="B16" s="46">
         <v>4</v>
       </c>
-      <c r="C16" s="88">
+      <c r="C16" s="69">
         <f>C9*(1+$C$3)</f>
         <v>165000</v>
       </c>
-      <c r="D16" s="86">
+      <c r="D16" s="67">
         <f>IF(C16&gt;$E$2,MIN(C16-$E$2,$C$2),0)</f>
         <v>50000</v>
       </c>
@@ -5063,10 +5430,10 @@
       </c>
     </row>
     <row r="19" spans="2:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="C19" s="84" t="s">
+      <c r="C19" s="65" t="s">
         <v>186</v>
       </c>
-      <c r="D19" s="85">
+      <c r="D19" s="66">
         <f>D17/D10-1</f>
         <v>0.30000000000000027</v>
       </c>
@@ -5077,4 +5444,1237 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{219ACF41-794C-7C44-8041-B413283265E7}">
+  <dimension ref="B2:AP74"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="37.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="37.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="60" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="26.83203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="31.83203125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="29.1640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="28" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="32" customWidth="1"/>
+    <col min="37" max="37" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B2" s="83"/>
+      <c r="C2" s="92" t="s">
+        <v>187</v>
+      </c>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B3" s="83"/>
+      <c r="C3" s="89">
+        <v>2021</v>
+      </c>
+      <c r="D3" s="89">
+        <v>2022</v>
+      </c>
+      <c r="E3" s="89">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B4" s="90" t="s">
+        <v>188</v>
+      </c>
+      <c r="C4" s="91">
+        <v>10000</v>
+      </c>
+      <c r="D4" s="91">
+        <v>11100</v>
+      </c>
+      <c r="E4" s="91">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B5" s="90" t="s">
+        <v>189</v>
+      </c>
+      <c r="C5" s="91">
+        <v>900</v>
+      </c>
+      <c r="D5" s="91">
+        <v>888</v>
+      </c>
+      <c r="E5" s="91">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B6" s="90" t="s">
+        <v>190</v>
+      </c>
+      <c r="C6" s="91">
+        <v>9000</v>
+      </c>
+      <c r="D6" s="91">
+        <v>2850</v>
+      </c>
+      <c r="E6" s="91">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B7" s="90" t="s">
+        <v>191</v>
+      </c>
+      <c r="C7" s="91">
+        <v>40800</v>
+      </c>
+      <c r="D7" s="91">
+        <v>36500</v>
+      </c>
+      <c r="E7" s="91">
+        <v>32200</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B8" s="90" t="s">
+        <v>192</v>
+      </c>
+      <c r="C8" s="91">
+        <v>32000</v>
+      </c>
+      <c r="D8" s="91">
+        <v>33500</v>
+      </c>
+      <c r="E8" s="91">
+        <v>37000</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B9" s="90" t="s">
+        <v>193</v>
+      </c>
+      <c r="C9" s="91">
+        <v>33000</v>
+      </c>
+      <c r="D9" s="91">
+        <v>36000</v>
+      </c>
+      <c r="E9" s="91">
+        <v>38500</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B10" s="90" t="s">
+        <v>194</v>
+      </c>
+      <c r="C10" s="91">
+        <v>500500</v>
+      </c>
+      <c r="D10" s="91">
+        <v>513000</v>
+      </c>
+      <c r="E10" s="91">
+        <v>518500</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B11" s="90" t="s">
+        <v>195</v>
+      </c>
+      <c r="C11" s="91">
+        <v>545000</v>
+      </c>
+      <c r="D11" s="91">
+        <v>560000</v>
+      </c>
+      <c r="E11" s="91">
+        <v>565000</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B13" s="83"/>
+      <c r="C13" s="92" t="s">
+        <v>187</v>
+      </c>
+      <c r="D13" s="92"/>
+      <c r="E13" s="92"/>
+      <c r="H13" s="15" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B14" s="83"/>
+      <c r="C14" s="89">
+        <v>2021</v>
+      </c>
+      <c r="D14" s="89">
+        <v>2022</v>
+      </c>
+      <c r="E14" s="89">
+        <v>2023</v>
+      </c>
+      <c r="H14" s="89"/>
+      <c r="I14" s="94" t="s">
+        <v>197</v>
+      </c>
+      <c r="J14" s="94" t="s">
+        <v>198</v>
+      </c>
+      <c r="K14" s="94" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B15" s="90" t="s">
+        <v>188</v>
+      </c>
+      <c r="C15" s="93">
+        <f>C4/C$11</f>
+        <v>1.834862385321101E-2</v>
+      </c>
+      <c r="D15" s="93">
+        <f t="shared" ref="D15:E15" si="0">D4/D$11</f>
+        <v>1.982142857142857E-2</v>
+      </c>
+      <c r="E15" s="93">
+        <f t="shared" si="0"/>
+        <v>1.8584070796460177E-2</v>
+      </c>
+      <c r="F15" s="36" t="s">
+        <v>224</v>
+      </c>
+      <c r="G15" s="36"/>
+      <c r="H15" s="90" t="s">
+        <v>188</v>
+      </c>
+      <c r="I15" s="93">
+        <f>AVERAGE(C15:E15)</f>
+        <v>1.8918041073699921E-2</v>
+      </c>
+      <c r="J15" s="95" t="s">
+        <v>201</v>
+      </c>
+      <c r="K15" s="95" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B16" s="90" t="s">
+        <v>189</v>
+      </c>
+      <c r="C16" s="93">
+        <f>C5/C$9</f>
+        <v>2.7272727272727271E-2</v>
+      </c>
+      <c r="D16" s="93">
+        <f t="shared" ref="D16:E16" si="1">D5/D$9</f>
+        <v>2.4666666666666667E-2</v>
+      </c>
+      <c r="E16" s="93">
+        <f t="shared" si="1"/>
+        <v>2.5064935064935064E-2</v>
+      </c>
+      <c r="F16" s="36" t="s">
+        <v>225</v>
+      </c>
+      <c r="G16" s="36"/>
+      <c r="H16" s="90" t="s">
+        <v>189</v>
+      </c>
+      <c r="I16" s="93">
+        <f>AVERAGE(C16:E16)</f>
+        <v>2.566810966810967E-2</v>
+      </c>
+      <c r="J16" s="95" t="s">
+        <v>201</v>
+      </c>
+      <c r="K16" s="95" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B17" s="90" t="s">
+        <v>190</v>
+      </c>
+      <c r="C17" s="93">
+        <f>C6/C$9</f>
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="D17" s="93">
+        <f t="shared" ref="D17:E17" si="2">D6/D$9</f>
+        <v>7.9166666666666663E-2</v>
+      </c>
+      <c r="E17" s="93">
+        <f t="shared" si="2"/>
+        <v>7.792207792207792E-2</v>
+      </c>
+      <c r="F17" s="36" t="s">
+        <v>226</v>
+      </c>
+      <c r="G17" s="36"/>
+      <c r="H17" s="90" t="s">
+        <v>190</v>
+      </c>
+      <c r="I17" s="93">
+        <f>AVERAGE(D17:E17)</f>
+        <v>7.8544372294372292E-2</v>
+      </c>
+      <c r="J17" s="95" t="s">
+        <v>203</v>
+      </c>
+      <c r="K17" s="95" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="90" t="s">
+        <v>191</v>
+      </c>
+      <c r="C18" s="93">
+        <f>C7/C$10</f>
+        <v>8.1518481518481525E-2</v>
+      </c>
+      <c r="D18" s="93">
+        <f>D7/D$10</f>
+        <v>7.1150097465886936E-2</v>
+      </c>
+      <c r="E18" s="93">
+        <f>E7/E$10</f>
+        <v>6.210221793635487E-2</v>
+      </c>
+      <c r="F18" s="36" t="s">
+        <v>196</v>
+      </c>
+      <c r="G18" s="36"/>
+      <c r="H18" s="96" t="s">
+        <v>191</v>
+      </c>
+      <c r="I18" s="97">
+        <f>E18</f>
+        <v>6.210221793635487E-2</v>
+      </c>
+      <c r="J18" s="98" t="s">
+        <v>205</v>
+      </c>
+      <c r="K18" s="98" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="90"/>
+      <c r="C19" s="91"/>
+      <c r="D19" s="91"/>
+      <c r="E19" s="91"/>
+      <c r="H19" s="89" t="s">
+        <v>10</v>
+      </c>
+      <c r="I19" s="99">
+        <f>SUM(I15:I18)</f>
+        <v>0.18523274097253675</v>
+      </c>
+      <c r="J19" s="100" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="106" t="s">
+        <v>223</v>
+      </c>
+      <c r="C20" s="106"/>
+      <c r="D20" s="106"/>
+      <c r="E20" s="106"/>
+      <c r="F20" s="106"/>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B21" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H21" s="15" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="H22" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B24" s="89" t="s">
+        <v>211</v>
+      </c>
+      <c r="C24" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="J24" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="K24" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="L24" s="15" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B25" s="90" t="s">
+        <v>213</v>
+      </c>
+      <c r="C25" s="101">
+        <v>0.6</v>
+      </c>
+      <c r="H25" s="90" t="s">
+        <v>188</v>
+      </c>
+      <c r="I25" s="102">
+        <f>$I15*$C25</f>
+        <v>1.1350824644219952E-2</v>
+      </c>
+      <c r="J25" s="102">
+        <f>$I15*(1-$C25)</f>
+        <v>7.5672164294799688E-3</v>
+      </c>
+      <c r="K25" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="L25" s="36" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B26" s="90" t="s">
+        <v>214</v>
+      </c>
+      <c r="C26" s="101">
+        <v>0.4</v>
+      </c>
+      <c r="H26" s="90" t="s">
+        <v>189</v>
+      </c>
+      <c r="I26" s="102">
+        <f t="shared" ref="I26:I28" si="3">$I16*$C26</f>
+        <v>1.0267243867243869E-2</v>
+      </c>
+      <c r="J26" s="102">
+        <f t="shared" ref="J26:J28" si="4">$I16*(1-$C26)</f>
+        <v>1.54008658008658E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B27" s="90" t="s">
+        <v>215</v>
+      </c>
+      <c r="C27" s="101">
+        <v>0</v>
+      </c>
+      <c r="H27" s="90" t="s">
+        <v>190</v>
+      </c>
+      <c r="I27" s="102">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="102">
+        <f t="shared" si="4"/>
+        <v>7.8544372294372292E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="90" t="s">
+        <v>216</v>
+      </c>
+      <c r="C28" s="101">
+        <v>0.3</v>
+      </c>
+      <c r="H28" s="96" t="s">
+        <v>191</v>
+      </c>
+      <c r="I28" s="103">
+        <f t="shared" si="3"/>
+        <v>1.863066538090646E-2</v>
+      </c>
+      <c r="J28" s="103">
+        <f t="shared" si="4"/>
+        <v>4.3471552555448406E-2</v>
+      </c>
+      <c r="K28" s="104"/>
+      <c r="L28" s="104"/>
+    </row>
+    <row r="29" spans="2:12" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="H29" s="89" t="s">
+        <v>10</v>
+      </c>
+      <c r="I29" s="99">
+        <f>SUM(I25:I28)</f>
+        <v>4.0248733892370284E-2</v>
+      </c>
+      <c r="J29" s="99">
+        <f>SUM(J25:J28)</f>
+        <v>0.14498400708016645</v>
+      </c>
+      <c r="K29" s="36" t="s">
+        <v>222</v>
+      </c>
+      <c r="L29" s="105" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="33" spans="17:26" x14ac:dyDescent="0.2">
+      <c r="Q33" s="83"/>
+      <c r="R33" s="92" t="s">
+        <v>187</v>
+      </c>
+      <c r="S33" s="92"/>
+      <c r="U33" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="V33" s="36" t="s">
+        <v>239</v>
+      </c>
+      <c r="W33" s="36" t="s">
+        <v>240</v>
+      </c>
+      <c r="X33" s="114"/>
+      <c r="Y33" s="36" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="34" spans="17:26" x14ac:dyDescent="0.2">
+      <c r="Q34" s="83"/>
+      <c r="R34" s="89">
+        <v>2003</v>
+      </c>
+      <c r="S34" s="89">
+        <v>2004</v>
+      </c>
+      <c r="U34" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="V34" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="W34" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="X34" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="Y34" s="15" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="35" spans="17:26" x14ac:dyDescent="0.2">
+      <c r="Q35" s="90" t="s">
+        <v>191</v>
+      </c>
+      <c r="R35" s="91">
+        <v>25000</v>
+      </c>
+      <c r="S35" s="91">
+        <v>28000</v>
+      </c>
+      <c r="U35">
+        <v>2003</v>
+      </c>
+      <c r="V35" s="53">
+        <f>R35/R37</f>
+        <v>40</v>
+      </c>
+      <c r="W35" s="53">
+        <f>V35*R36</f>
+        <v>30</v>
+      </c>
+      <c r="X35">
+        <v>3</v>
+      </c>
+      <c r="Y35" s="113">
+        <f>W35*(1+$R$47)^X35</f>
+        <v>32.78181</v>
+      </c>
+    </row>
+    <row r="36" spans="17:26" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q36" s="90" t="s">
+        <v>227</v>
+      </c>
+      <c r="R36" s="101">
+        <v>0.75</v>
+      </c>
+      <c r="S36" s="101">
+        <v>0.75</v>
+      </c>
+      <c r="U36" s="104">
+        <v>2004</v>
+      </c>
+      <c r="V36" s="111">
+        <f>S35/S37</f>
+        <v>43.410852713178294</v>
+      </c>
+      <c r="W36" s="111">
+        <f>V36*S36</f>
+        <v>32.558139534883722</v>
+      </c>
+      <c r="X36" s="112">
+        <f>X35-1</f>
+        <v>2</v>
+      </c>
+      <c r="Y36" s="111">
+        <f>W36*(1+$R$47)^X36</f>
+        <v>34.540930232558139</v>
+      </c>
+      <c r="Z36" s="104"/>
+    </row>
+    <row r="37" spans="17:26" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="Q37" s="90" t="s">
+        <v>228</v>
+      </c>
+      <c r="R37" s="90">
+        <v>625</v>
+      </c>
+      <c r="S37" s="90">
+        <v>645</v>
+      </c>
+      <c r="X37" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="Y37" s="115">
+        <f>AVERAGE(Y35:Y36)</f>
+        <v>33.661370116279073</v>
+      </c>
+      <c r="Z37" s="36" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="38" spans="17:26" x14ac:dyDescent="0.2">
+      <c r="Q38" s="90" t="s">
+        <v>229</v>
+      </c>
+      <c r="R38" s="90">
+        <v>640</v>
+      </c>
+      <c r="S38" s="90">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="39" spans="17:26" x14ac:dyDescent="0.2">
+      <c r="Q39" s="90" t="s">
+        <v>194</v>
+      </c>
+      <c r="R39" s="91">
+        <v>435000</v>
+      </c>
+      <c r="S39" s="91">
+        <v>450000</v>
+      </c>
+      <c r="X39" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y39" s="58">
+        <f>Y37+SUM(R43:R45)</f>
+        <v>96.161370116279073</v>
+      </c>
+      <c r="Z39" s="36" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="40" spans="17:26" x14ac:dyDescent="0.2">
+      <c r="Q40" s="90" t="s">
+        <v>195</v>
+      </c>
+      <c r="R40" s="91">
+        <v>460000</v>
+      </c>
+      <c r="S40" s="90" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="41" spans="17:26" x14ac:dyDescent="0.2">
+      <c r="U41" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="V41" s="36" t="s">
+        <v>251</v>
+      </c>
+      <c r="W41" s="36" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="42" spans="17:26" x14ac:dyDescent="0.2">
+      <c r="Q42" s="89" t="s">
+        <v>231</v>
+      </c>
+      <c r="R42" s="89" t="s">
+        <v>217</v>
+      </c>
+      <c r="S42" s="89" t="s">
+        <v>218</v>
+      </c>
+      <c r="U42" s="89" t="s">
+        <v>237</v>
+      </c>
+      <c r="V42" s="89" t="s">
+        <v>250</v>
+      </c>
+      <c r="W42" s="89" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="43" spans="17:26" x14ac:dyDescent="0.2">
+      <c r="Q43" s="90" t="s">
+        <v>213</v>
+      </c>
+      <c r="R43" s="91">
+        <v>60</v>
+      </c>
+      <c r="S43" s="107">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="U43">
+        <v>2003</v>
+      </c>
+      <c r="V43" s="63">
+        <f>R35*(1-R36)</f>
+        <v>6250</v>
+      </c>
+      <c r="W43" s="116">
+        <f>V43/R39</f>
+        <v>1.4367816091954023E-2</v>
+      </c>
+      <c r="X43" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="44" spans="17:26" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q44" s="90" t="s">
+        <v>214</v>
+      </c>
+      <c r="R44" s="109">
+        <v>2.5</v>
+      </c>
+      <c r="S44" s="107">
+        <v>0.02</v>
+      </c>
+      <c r="U44" s="104">
+        <v>2004</v>
+      </c>
+      <c r="V44" s="120">
+        <f>S35*(1-S36)</f>
+        <v>7000</v>
+      </c>
+      <c r="W44" s="118">
+        <f>V44/S39</f>
+        <v>1.5555555555555555E-2</v>
+      </c>
+      <c r="X44" s="121"/>
+    </row>
+    <row r="45" spans="17:26" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="Q45" s="90" t="s">
+        <v>215</v>
+      </c>
+      <c r="R45" s="90">
+        <v>0</v>
+      </c>
+      <c r="S45" s="107">
+        <v>0.12</v>
+      </c>
+      <c r="V45" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="W45" s="117">
+        <f>AVERAGE(W43:W44)</f>
+        <v>1.4961685823754789E-2</v>
+      </c>
+      <c r="X45" s="36" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="47" spans="17:26" x14ac:dyDescent="0.2">
+      <c r="Q47" s="89" t="s">
+        <v>244</v>
+      </c>
+      <c r="R47" s="19">
+        <v>0.03</v>
+      </c>
+      <c r="V47" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="W47" s="119">
+        <f>W45+SUM(S43:S45)</f>
+        <v>0.17996168582375477</v>
+      </c>
+      <c r="X47" s="36" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="49" spans="32:42" x14ac:dyDescent="0.2">
+      <c r="AJ49" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="AM49" s="36" t="s">
+        <v>271</v>
+      </c>
+      <c r="AN49" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="50" spans="32:42" x14ac:dyDescent="0.2">
+      <c r="AG50" s="89" t="s">
+        <v>253</v>
+      </c>
+      <c r="AH50" s="89" t="s">
+        <v>212</v>
+      </c>
+      <c r="AK50" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="AL50" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="AM50" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="AN50" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="AO50" s="15" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="51" spans="32:42" x14ac:dyDescent="0.2">
+      <c r="AF51" s="90" t="s">
+        <v>216</v>
+      </c>
+      <c r="AG51" s="91">
+        <v>15000</v>
+      </c>
+      <c r="AH51" s="101">
+        <v>0.5</v>
+      </c>
+      <c r="AJ51" s="90" t="s">
+        <v>216</v>
+      </c>
+      <c r="AK51" s="108" t="s">
+        <v>261</v>
+      </c>
+      <c r="AL51" s="113">
+        <f>AG51/AG57</f>
+        <v>11.673151750972762</v>
+      </c>
+      <c r="AM51" s="113">
+        <f>AL51*AH51</f>
+        <v>5.836575875486381</v>
+      </c>
+      <c r="AN51">
+        <v>2.5</v>
+      </c>
+      <c r="AO51" s="113">
+        <f>AM51*(1+$AG$60)^AN51</f>
+        <v>6.1327966563454703</v>
+      </c>
+      <c r="AP51" s="36" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="52" spans="32:42" x14ac:dyDescent="0.2">
+      <c r="AF52" s="90" t="s">
+        <v>213</v>
+      </c>
+      <c r="AG52" s="91">
+        <v>38125</v>
+      </c>
+      <c r="AH52" s="101">
+        <v>0.2</v>
+      </c>
+      <c r="AJ52" s="90" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK52" s="108" t="s">
+        <v>262</v>
+      </c>
+      <c r="AL52" s="113">
+        <f>AG52/$AG$58</f>
+        <v>28.838880484114977</v>
+      </c>
+      <c r="AM52" s="113">
+        <f>AL52*AH52</f>
+        <v>5.7677760968229954</v>
+      </c>
+      <c r="AN52">
+        <v>2</v>
+      </c>
+      <c r="AO52" s="113">
+        <f>AM52*(1+$AG$60)^AN52</f>
+        <v>6.0007942511346446</v>
+      </c>
+    </row>
+    <row r="53" spans="32:42" x14ac:dyDescent="0.2">
+      <c r="AF53" s="90" t="s">
+        <v>214</v>
+      </c>
+      <c r="AG53" s="91">
+        <v>11000</v>
+      </c>
+      <c r="AH53" s="101">
+        <v>0.4</v>
+      </c>
+      <c r="AJ53" s="90" t="s">
+        <v>214</v>
+      </c>
+      <c r="AK53" s="108" t="s">
+        <v>262</v>
+      </c>
+      <c r="AL53" s="113">
+        <f>AG53/$AG$58</f>
+        <v>8.3207261724659602</v>
+      </c>
+      <c r="AM53" s="113">
+        <f>AL53*AH53</f>
+        <v>3.3282904689863844</v>
+      </c>
+      <c r="AN53">
+        <v>2</v>
+      </c>
+      <c r="AO53" s="113">
+        <f>AM53*(1+$AG$60)^AN53</f>
+        <v>3.4627534039334344</v>
+      </c>
+    </row>
+    <row r="54" spans="32:42" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AF54" s="90" t="s">
+        <v>215</v>
+      </c>
+      <c r="AG54" s="91">
+        <v>1525</v>
+      </c>
+      <c r="AH54" s="101">
+        <v>0.1</v>
+      </c>
+      <c r="AJ54" s="96" t="s">
+        <v>215</v>
+      </c>
+      <c r="AK54" s="110" t="s">
+        <v>262</v>
+      </c>
+      <c r="AL54" s="111">
+        <f>AG54/$AG$58</f>
+        <v>1.153555219364599</v>
+      </c>
+      <c r="AM54" s="111">
+        <f>AL54*AH54</f>
+        <v>0.11535552193645991</v>
+      </c>
+      <c r="AN54" s="104">
+        <v>2</v>
+      </c>
+      <c r="AO54" s="111">
+        <f>AM54*(1+$AG$60)^AN54</f>
+        <v>0.12001588502269289</v>
+      </c>
+      <c r="AP54" s="104"/>
+    </row>
+    <row r="55" spans="32:42" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="AF55" s="90" t="s">
+        <v>254</v>
+      </c>
+      <c r="AG55" s="91">
+        <v>385000</v>
+      </c>
+      <c r="AH55" s="90"/>
+      <c r="AN55" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO55" s="58">
+        <f>SUM(AO51:AO54)</f>
+        <v>15.716360196436241</v>
+      </c>
+      <c r="AP55" s="36" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="56" spans="32:42" x14ac:dyDescent="0.2">
+      <c r="AF56" s="90" t="s">
+        <v>255</v>
+      </c>
+      <c r="AG56" s="91">
+        <v>400000</v>
+      </c>
+      <c r="AH56" s="90"/>
+      <c r="AL56" s="36" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="57" spans="32:42" x14ac:dyDescent="0.2">
+      <c r="AF57" s="90" t="s">
+        <v>149</v>
+      </c>
+      <c r="AG57" s="122">
+        <v>1285</v>
+      </c>
+      <c r="AH57" s="90"/>
+      <c r="AJ57" s="123" t="s">
+        <v>266</v>
+      </c>
+      <c r="AK57" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="AL57" s="124" t="s">
+        <v>250</v>
+      </c>
+      <c r="AM57" s="15" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="58" spans="32:42" x14ac:dyDescent="0.2">
+      <c r="AF58" s="90" t="s">
+        <v>256</v>
+      </c>
+      <c r="AG58" s="122">
+        <v>1322</v>
+      </c>
+      <c r="AH58" s="90"/>
+      <c r="AJ58" s="90" t="s">
+        <v>216</v>
+      </c>
+      <c r="AK58" s="108" t="s">
+        <v>49</v>
+      </c>
+      <c r="AL58" s="53">
+        <f>AG51*(1-AH51)</f>
+        <v>7500</v>
+      </c>
+      <c r="AM58" s="125">
+        <f>AL58/AG55</f>
+        <v>1.948051948051948E-2</v>
+      </c>
+      <c r="AN58" s="36" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="59" spans="32:42" x14ac:dyDescent="0.2">
+      <c r="AJ59" s="90" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK59" s="108" t="s">
+        <v>259</v>
+      </c>
+      <c r="AL59" s="53">
+        <f>AG52*(1-AH52)</f>
+        <v>30500</v>
+      </c>
+      <c r="AM59" s="125">
+        <f>AL59/$AG$56</f>
+        <v>7.6249999999999998E-2</v>
+      </c>
+      <c r="AN59" s="36" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="60" spans="32:42" x14ac:dyDescent="0.2">
+      <c r="AF60" s="89" t="s">
+        <v>244</v>
+      </c>
+      <c r="AG60" s="19">
+        <v>0.02</v>
+      </c>
+      <c r="AJ60" s="90" t="s">
+        <v>214</v>
+      </c>
+      <c r="AK60" s="108" t="s">
+        <v>259</v>
+      </c>
+      <c r="AL60" s="53">
+        <f>AG53*(1-AH53)</f>
+        <v>6600</v>
+      </c>
+      <c r="AM60" s="125">
+        <f>AL60/$AG$56</f>
+        <v>1.6500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="32:42" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AF61" s="90" t="s">
+        <v>270</v>
+      </c>
+      <c r="AG61" s="19">
+        <v>0.08</v>
+      </c>
+      <c r="AJ61" s="96" t="s">
+        <v>215</v>
+      </c>
+      <c r="AK61" s="110" t="s">
+        <v>259</v>
+      </c>
+      <c r="AL61" s="126">
+        <f>AG54*(1-AH54)</f>
+        <v>1372.5</v>
+      </c>
+      <c r="AM61" s="127">
+        <f>AL61/$AG$56</f>
+        <v>3.4312499999999998E-3</v>
+      </c>
+      <c r="AN61" s="104"/>
+    </row>
+    <row r="62" spans="32:42" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="AL62" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM62" s="128">
+        <f>SUM(AM58:AM61)</f>
+        <v>0.11566176948051947</v>
+      </c>
+      <c r="AN62" s="36" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="64" spans="32:42" x14ac:dyDescent="0.2">
+      <c r="AJ64" s="123" t="s">
+        <v>269</v>
+      </c>
+      <c r="AK64" s="99">
+        <f>1-AM62-AG61</f>
+        <v>0.80433823051948061</v>
+      </c>
+      <c r="AL64" s="36" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="66" spans="36:40" x14ac:dyDescent="0.2">
+      <c r="AJ66" s="15" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="67" spans="36:40" x14ac:dyDescent="0.2">
+      <c r="AJ67" s="123" t="s">
+        <v>266</v>
+      </c>
+      <c r="AK67" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="AL67" s="124" t="s">
+        <v>234</v>
+      </c>
+      <c r="AM67" s="15" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="68" spans="36:40" x14ac:dyDescent="0.2">
+      <c r="AJ68" s="90" t="s">
+        <v>216</v>
+      </c>
+      <c r="AK68" s="108" t="s">
+        <v>49</v>
+      </c>
+      <c r="AL68" s="53">
+        <f>AG51*AH51</f>
+        <v>7500</v>
+      </c>
+      <c r="AM68" s="125">
+        <f>AL68/AG55</f>
+        <v>1.948051948051948E-2</v>
+      </c>
+      <c r="AN68" s="36" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="69" spans="36:40" x14ac:dyDescent="0.2">
+      <c r="AJ69" s="90" t="s">
+        <v>213</v>
+      </c>
+      <c r="AK69" s="108" t="s">
+        <v>259</v>
+      </c>
+      <c r="AL69" s="53">
+        <f t="shared" ref="AL69:AL71" si="5">AG52*AH52</f>
+        <v>7625</v>
+      </c>
+      <c r="AM69" s="125">
+        <f>AL69/$AG$56</f>
+        <v>1.90625E-2</v>
+      </c>
+      <c r="AN69" s="36" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="70" spans="36:40" x14ac:dyDescent="0.2">
+      <c r="AJ70" s="90" t="s">
+        <v>214</v>
+      </c>
+      <c r="AK70" s="108" t="s">
+        <v>259</v>
+      </c>
+      <c r="AL70" s="53">
+        <f t="shared" si="5"/>
+        <v>4400</v>
+      </c>
+      <c r="AM70" s="125">
+        <f>AL70/$AG$56</f>
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="36:40" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AJ71" s="96" t="s">
+        <v>215</v>
+      </c>
+      <c r="AK71" s="110" t="s">
+        <v>259</v>
+      </c>
+      <c r="AL71" s="126">
+        <f t="shared" si="5"/>
+        <v>152.5</v>
+      </c>
+      <c r="AM71" s="127">
+        <f>AL71/$AG$56</f>
+        <v>3.8125000000000002E-4</v>
+      </c>
+      <c r="AN71" s="104"/>
+    </row>
+    <row r="72" spans="36:40" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="AL72" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM72" s="128">
+        <f>SUM(AM68:AM71)</f>
+        <v>4.9924269480519479E-2</v>
+      </c>
+      <c r="AN72" s="36" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="74" spans="36:40" x14ac:dyDescent="0.2">
+      <c r="AJ74" s="123" t="s">
+        <v>281</v>
+      </c>
+      <c r="AK74" s="99">
+        <f>1-AM72-AM62-AG61</f>
+        <v>0.75441396103896108</v>
+      </c>
+      <c r="AL74" s="36" t="s">
+        <v>282</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="R33:S33"/>
+    <mergeCell ref="Q33:Q34"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:E13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/files/temp-work.xlsx
+++ b/files/temp-work.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/coltongearhart/Desktop/exam5/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3149601-6926-F14E-BCA9-42D79DCD5816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3731D27-291E-BA43-A251-7B425EB5365D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" activeTab="5" xr2:uid="{BB8505BC-BCB7-B340-A120-C046C43AD7BD}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="7" xr2:uid="{BB8505BC-BCB7-B340-A120-C046C43AD7BD}"/>
   </bookViews>
   <sheets>
     <sheet name="2.2.1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,8 @@
     <sheet name="2.3.3" sheetId="4" r:id="rId4"/>
     <sheet name="2.4.3" sheetId="5" r:id="rId5"/>
     <sheet name="2.5.3" sheetId="6" r:id="rId6"/>
+    <sheet name="2.6.1" sheetId="7" r:id="rId7"/>
+    <sheet name="Sheet2" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="314">
   <si>
     <t>Ratio to SAWW</t>
   </si>
@@ -901,12 +903,105 @@
   <si>
     <t>=1-AM72-AM62-AG61</t>
   </si>
+  <si>
+    <t>Calendar / Accident Year</t>
+  </si>
+  <si>
+    <t>Reported Loss and ALAE</t>
+  </si>
+  <si>
+    <t>age-to-ultimate</t>
+  </si>
+  <si>
+    <t>factor</t>
+  </si>
+  <si>
+    <t>12 months to ultimate</t>
+  </si>
+  <si>
+    <t>24 months to ultimate</t>
+  </si>
+  <si>
+    <t>36 months to ultimate</t>
+  </si>
+  <si>
+    <t>48 months to ultimate</t>
+  </si>
+  <si>
+    <t>Trend period</t>
+  </si>
+  <si>
+    <t>Age (as of 12/31/2006)</t>
+  </si>
+  <si>
+    <t>Pure Premium trend</t>
+  </si>
+  <si>
+    <t>Trend</t>
+  </si>
+  <si>
+    <t>Frequency</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Developed loss and ALAE</t>
+  </si>
+  <si>
+    <t>Trended ultimate loss and LAE</t>
+  </si>
+  <si>
+    <t>** Order of operations: Develop losses, then trend</t>
+  </si>
+  <si>
+    <t>=(1+C14)*(1+C15)-1</t>
+  </si>
+  <si>
+    <t>=G3*(1+$H$7)^H3</t>
+  </si>
+  <si>
+    <t>=C3*F3</t>
+  </si>
+  <si>
+    <t>Indicated pure premium and ALAE</t>
+  </si>
+  <si>
+    <t>=SUM(I3:I5)/SUM(D3:D5)</t>
+  </si>
+  <si>
+    <t>Indicated rate</t>
+  </si>
+  <si>
+    <t>Fees</t>
+  </si>
+  <si>
+    <t>Commision</t>
+  </si>
+  <si>
+    <t>Taxes</t>
+  </si>
+  <si>
+    <t>Variable portion of general and other acquisition</t>
+  </si>
+  <si>
+    <t>Ratio / amount per exposure</t>
+  </si>
+  <si>
+    <t>Total fixed expense (per exposure)</t>
+  </si>
+  <si>
+    <t>Profit load</t>
+  </si>
+  <si>
+    <t>=(I9+C22)/(1-SUM(C18:C21))</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="8">
+  <numFmts count="10">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -914,9 +1009,11 @@
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
-    <numFmt numFmtId="172" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="180" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="182" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1019,6 +1116,21 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF00B050"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1034,7 +1146,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1137,13 +1249,44 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1224,6 +1367,54 @@
     <xf numFmtId="6" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="6" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="6" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="6" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="6" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="10" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="14" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="15" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="10" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="6" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1257,21 +1448,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1279,52 +1455,52 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="6" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="6" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="10" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="14" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="10" fontId="15" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="10" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="8" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="8" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="172" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="7" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="6" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="182" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -2399,26 +2575,26 @@
       </c>
     </row>
     <row r="23" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="M23" s="73"/>
-      <c r="N23" s="74"/>
-      <c r="O23" s="70" t="s">
+      <c r="M23" s="113"/>
+      <c r="N23" s="114"/>
+      <c r="O23" s="110" t="s">
         <v>60</v>
       </c>
-      <c r="P23" s="71"/>
-      <c r="Q23" s="71"/>
-      <c r="R23" s="72"/>
-      <c r="S23" s="70" t="s">
+      <c r="P23" s="111"/>
+      <c r="Q23" s="111"/>
+      <c r="R23" s="112"/>
+      <c r="S23" s="110" t="s">
         <v>62</v>
       </c>
-      <c r="T23" s="71"/>
-      <c r="U23" s="71"/>
-      <c r="V23" s="72"/>
-      <c r="W23" s="70" t="s">
+      <c r="T23" s="111"/>
+      <c r="U23" s="111"/>
+      <c r="V23" s="112"/>
+      <c r="W23" s="110" t="s">
         <v>61</v>
       </c>
-      <c r="X23" s="71"/>
-      <c r="Y23" s="71"/>
-      <c r="Z23" s="72"/>
+      <c r="X23" s="111"/>
+      <c r="Y23" s="111"/>
+      <c r="Z23" s="112"/>
     </row>
     <row r="24" spans="2:33" x14ac:dyDescent="0.2">
       <c r="M24" s="24" t="s">
@@ -2484,35 +2660,35 @@
       <c r="R25" s="30">
         <v>0</v>
       </c>
-      <c r="S25" s="79">
+      <c r="S25" s="119">
         <f>SUMPRODUCT(O25:O27,$N$25:$N$27)</f>
         <v>1.0568750000000002</v>
       </c>
-      <c r="T25" s="77">
+      <c r="T25" s="117">
         <f t="shared" ref="T25:V25" si="2">SUMPRODUCT(P25:P27,$N$25:$N$27)</f>
         <v>1.089375</v>
       </c>
-      <c r="U25" s="77">
+      <c r="U25" s="117">
         <f t="shared" si="2"/>
         <v>1.1156250000000001</v>
       </c>
-      <c r="V25" s="75">
+      <c r="V25" s="115">
         <f t="shared" si="2"/>
         <v>1.1418750000000002</v>
       </c>
-      <c r="W25" s="79">
+      <c r="W25" s="119">
         <f>$N$27/S25</f>
         <v>1.0928444707273803</v>
       </c>
-      <c r="X25" s="77">
+      <c r="X25" s="117">
         <f t="shared" ref="X25:Z25" si="3">$N$27/T25</f>
         <v>1.060240963855422</v>
       </c>
-      <c r="Y25" s="77">
+      <c r="Y25" s="117">
         <f t="shared" si="3"/>
         <v>1.0352941176470589</v>
       </c>
-      <c r="Z25" s="75">
+      <c r="Z25" s="115">
         <f t="shared" si="3"/>
         <v>1.0114942528735633</v>
       </c>
@@ -2537,14 +2713,14 @@
       <c r="R26" s="30">
         <v>0.125</v>
       </c>
-      <c r="S26" s="79"/>
-      <c r="T26" s="77"/>
-      <c r="U26" s="77"/>
-      <c r="V26" s="75"/>
-      <c r="W26" s="79"/>
-      <c r="X26" s="77"/>
-      <c r="Y26" s="77"/>
-      <c r="Z26" s="75"/>
+      <c r="S26" s="119"/>
+      <c r="T26" s="117"/>
+      <c r="U26" s="117"/>
+      <c r="V26" s="115"/>
+      <c r="W26" s="119"/>
+      <c r="X26" s="117"/>
+      <c r="Y26" s="117"/>
+      <c r="Z26" s="115"/>
     </row>
     <row r="27" spans="2:33" x14ac:dyDescent="0.2">
       <c r="M27" s="28">
@@ -2566,14 +2742,14 @@
       <c r="R27" s="31">
         <v>0.875</v>
       </c>
-      <c r="S27" s="80"/>
-      <c r="T27" s="78"/>
-      <c r="U27" s="78"/>
-      <c r="V27" s="76"/>
-      <c r="W27" s="80"/>
-      <c r="X27" s="78"/>
-      <c r="Y27" s="78"/>
-      <c r="Z27" s="76"/>
+      <c r="S27" s="120"/>
+      <c r="T27" s="118"/>
+      <c r="U27" s="118"/>
+      <c r="V27" s="116"/>
+      <c r="W27" s="120"/>
+      <c r="X27" s="118"/>
+      <c r="Y27" s="118"/>
+      <c r="Z27" s="116"/>
     </row>
     <row r="28" spans="2:33" x14ac:dyDescent="0.2">
       <c r="N28" s="32" t="s">
@@ -2654,23 +2830,23 @@
       </c>
     </row>
     <row r="37" spans="15:41" x14ac:dyDescent="0.2">
-      <c r="AE37" s="83"/>
-      <c r="AF37" s="83"/>
-      <c r="AG37" s="82" t="s">
+      <c r="AE37" s="107"/>
+      <c r="AF37" s="107"/>
+      <c r="AG37" s="108" t="s">
         <v>72</v>
       </c>
-      <c r="AH37" s="82"/>
-      <c r="AI37" s="82"/>
-      <c r="AJ37" s="82" t="s">
+      <c r="AH37" s="108"/>
+      <c r="AI37" s="108"/>
+      <c r="AJ37" s="108" t="s">
         <v>76</v>
       </c>
-      <c r="AK37" s="82"/>
-      <c r="AL37" s="82"/>
-      <c r="AM37" s="82" t="s">
+      <c r="AK37" s="108"/>
+      <c r="AL37" s="108"/>
+      <c r="AM37" s="108" t="s">
         <v>77</v>
       </c>
-      <c r="AN37" s="82"/>
-      <c r="AO37" s="82"/>
+      <c r="AN37" s="108"/>
+      <c r="AO37" s="108"/>
     </row>
     <row r="38" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE38" s="15" t="s">
@@ -2719,18 +2895,18 @@
         <f>0.5*3/4*3/4</f>
         <v>0.28125</v>
       </c>
-      <c r="AJ39" s="81"/>
-      <c r="AK39" s="81">
+      <c r="AJ39" s="106"/>
+      <c r="AK39" s="106">
         <f>SUMPRODUCT(AH39:AH42,AF39:AF42)</f>
         <v>1.0636875000000001</v>
       </c>
-      <c r="AL39" s="81"/>
-      <c r="AM39" s="81"/>
-      <c r="AN39" s="81">
+      <c r="AL39" s="106"/>
+      <c r="AM39" s="106"/>
+      <c r="AN39" s="106">
         <f>$AF$42/AK39</f>
         <v>1.0512015982137612</v>
       </c>
-      <c r="AO39" s="81"/>
+      <c r="AO39" s="106"/>
     </row>
     <row r="40" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE40">
@@ -2744,12 +2920,12 @@
         <f>1-AH39-AH41</f>
         <v>0.59375</v>
       </c>
-      <c r="AJ40" s="81"/>
-      <c r="AK40" s="81"/>
-      <c r="AL40" s="81"/>
-      <c r="AM40" s="81"/>
-      <c r="AN40" s="81"/>
-      <c r="AO40" s="81"/>
+      <c r="AJ40" s="106"/>
+      <c r="AK40" s="106"/>
+      <c r="AL40" s="106"/>
+      <c r="AM40" s="106"/>
+      <c r="AN40" s="106"/>
+      <c r="AO40" s="106"/>
     </row>
     <row r="41" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE41">
@@ -2762,12 +2938,12 @@
       <c r="AH41">
         <v>0.125</v>
       </c>
-      <c r="AJ41" s="81"/>
-      <c r="AK41" s="81"/>
-      <c r="AL41" s="81"/>
-      <c r="AM41" s="81"/>
-      <c r="AN41" s="81"/>
-      <c r="AO41" s="81"/>
+      <c r="AJ41" s="106"/>
+      <c r="AK41" s="106"/>
+      <c r="AL41" s="106"/>
+      <c r="AM41" s="106"/>
+      <c r="AN41" s="106"/>
+      <c r="AO41" s="106"/>
     </row>
     <row r="42" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE42">
@@ -2780,31 +2956,31 @@
       <c r="AH42">
         <v>0</v>
       </c>
-      <c r="AJ42" s="81"/>
-      <c r="AK42" s="81"/>
-      <c r="AL42" s="81"/>
-      <c r="AM42" s="81"/>
-      <c r="AN42" s="81"/>
-      <c r="AO42" s="81"/>
+      <c r="AJ42" s="106"/>
+      <c r="AK42" s="106"/>
+      <c r="AL42" s="106"/>
+      <c r="AM42" s="106"/>
+      <c r="AN42" s="106"/>
+      <c r="AO42" s="106"/>
     </row>
     <row r="44" spans="15:41" x14ac:dyDescent="0.2">
-      <c r="AE44" s="83"/>
-      <c r="AF44" s="83"/>
-      <c r="AG44" s="82" t="s">
+      <c r="AE44" s="107"/>
+      <c r="AF44" s="107"/>
+      <c r="AG44" s="108" t="s">
         <v>72</v>
       </c>
-      <c r="AH44" s="82"/>
-      <c r="AI44" s="82"/>
-      <c r="AJ44" s="82" t="s">
+      <c r="AH44" s="108"/>
+      <c r="AI44" s="108"/>
+      <c r="AJ44" s="108" t="s">
         <v>76</v>
       </c>
-      <c r="AK44" s="82"/>
-      <c r="AL44" s="82"/>
-      <c r="AM44" s="82" t="s">
+      <c r="AK44" s="108"/>
+      <c r="AL44" s="108"/>
+      <c r="AM44" s="108" t="s">
         <v>77</v>
       </c>
-      <c r="AN44" s="82"/>
-      <c r="AO44" s="82"/>
+      <c r="AN44" s="108"/>
+      <c r="AO44" s="108"/>
     </row>
     <row r="45" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE45" s="15" t="s">
@@ -2852,18 +3028,18 @@
       <c r="AH46">
         <v>0</v>
       </c>
-      <c r="AJ46" s="81"/>
-      <c r="AK46" s="81">
+      <c r="AJ46" s="106"/>
+      <c r="AK46" s="106">
         <f>SUMPRODUCT(AH46:AH49,AF46:AF49)</f>
         <v>1.1161437500000002</v>
       </c>
-      <c r="AL46" s="81"/>
-      <c r="AM46" s="81"/>
-      <c r="AN46" s="81">
+      <c r="AL46" s="106"/>
+      <c r="AM46" s="106"/>
+      <c r="AN46" s="106">
         <f>$AF$49/AK46</f>
         <v>1.0017974835230676</v>
       </c>
-      <c r="AO46" s="81"/>
+      <c r="AO46" s="106"/>
     </row>
     <row r="47" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE47">
@@ -2876,12 +3052,12 @@
       <c r="AH47">
         <v>0.5</v>
       </c>
-      <c r="AJ47" s="81"/>
-      <c r="AK47" s="81"/>
-      <c r="AL47" s="81"/>
-      <c r="AM47" s="81"/>
-      <c r="AN47" s="81"/>
-      <c r="AO47" s="81"/>
+      <c r="AJ47" s="106"/>
+      <c r="AK47" s="106"/>
+      <c r="AL47" s="106"/>
+      <c r="AM47" s="106"/>
+      <c r="AN47" s="106"/>
+      <c r="AO47" s="106"/>
     </row>
     <row r="48" spans="15:41" x14ac:dyDescent="0.2">
       <c r="O48" t="s">
@@ -2897,12 +3073,12 @@
       <c r="AH48">
         <v>0.375</v>
       </c>
-      <c r="AJ48" s="81"/>
-      <c r="AK48" s="81"/>
-      <c r="AL48" s="81"/>
-      <c r="AM48" s="81"/>
-      <c r="AN48" s="81"/>
-      <c r="AO48" s="81"/>
+      <c r="AJ48" s="106"/>
+      <c r="AK48" s="106"/>
+      <c r="AL48" s="106"/>
+      <c r="AM48" s="106"/>
+      <c r="AN48" s="106"/>
+      <c r="AO48" s="106"/>
     </row>
     <row r="49" spans="31:52" x14ac:dyDescent="0.2">
       <c r="AE49">
@@ -2915,12 +3091,12 @@
       <c r="AH49">
         <v>0.125</v>
       </c>
-      <c r="AJ49" s="81"/>
-      <c r="AK49" s="81"/>
-      <c r="AL49" s="81"/>
-      <c r="AM49" s="81"/>
-      <c r="AN49" s="81"/>
-      <c r="AO49" s="81"/>
+      <c r="AJ49" s="106"/>
+      <c r="AK49" s="106"/>
+      <c r="AL49" s="106"/>
+      <c r="AM49" s="106"/>
+      <c r="AN49" s="106"/>
+      <c r="AO49" s="106"/>
     </row>
     <row r="53" spans="31:52" x14ac:dyDescent="0.2">
       <c r="AS53" s="15" t="s">
@@ -2970,20 +3146,20 @@
       </c>
     </row>
     <row r="58" spans="31:52" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="AS58" s="83"/>
-      <c r="AT58" s="83"/>
-      <c r="AU58" s="82" t="s">
+      <c r="AS58" s="107"/>
+      <c r="AT58" s="107"/>
+      <c r="AU58" s="108" t="s">
         <v>72</v>
       </c>
-      <c r="AV58" s="82"/>
-      <c r="AW58" s="84" t="s">
+      <c r="AV58" s="108"/>
+      <c r="AW58" s="109" t="s">
         <v>76</v>
       </c>
-      <c r="AX58" s="84"/>
-      <c r="AY58" s="82" t="s">
+      <c r="AX58" s="109"/>
+      <c r="AY58" s="108" t="s">
         <v>77</v>
       </c>
-      <c r="AZ58" s="82"/>
+      <c r="AZ58" s="108"/>
     </row>
     <row r="59" spans="31:52" x14ac:dyDescent="0.2">
       <c r="AS59" s="15" t="s">
@@ -3023,13 +3199,13 @@
         <f>1/16</f>
         <v>6.25E-2</v>
       </c>
-      <c r="AW60" s="81"/>
-      <c r="AX60" s="81">
+      <c r="AW60" s="106"/>
+      <c r="AX60" s="106">
         <f>SUMPRODUCT(AV60:AV62,AT60:AT62)</f>
         <v>1.0993750000000002</v>
       </c>
-      <c r="AY60" s="81"/>
-      <c r="AZ60" s="81">
+      <c r="AY60" s="106"/>
+      <c r="AZ60" s="106">
         <f>$AT$62/AX60</f>
         <v>1.0505969300739058</v>
       </c>
@@ -3046,10 +3222,10 @@
         <f>0.5-AV60</f>
         <v>0.4375</v>
       </c>
-      <c r="AW61" s="81"/>
-      <c r="AX61" s="81"/>
-      <c r="AY61" s="81"/>
-      <c r="AZ61" s="81"/>
+      <c r="AW61" s="106"/>
+      <c r="AX61" s="106"/>
+      <c r="AY61" s="106"/>
+      <c r="AZ61" s="106"/>
     </row>
     <row r="62" spans="31:52" x14ac:dyDescent="0.2">
       <c r="AS62">
@@ -3062,10 +3238,10 @@
       <c r="AV62">
         <v>0.5</v>
       </c>
-      <c r="AW62" s="81"/>
-      <c r="AX62" s="81"/>
-      <c r="AY62" s="81"/>
-      <c r="AZ62" s="81"/>
+      <c r="AW62" s="106"/>
+      <c r="AX62" s="106"/>
+      <c r="AY62" s="106"/>
+      <c r="AZ62" s="106"/>
     </row>
     <row r="63" spans="31:52" x14ac:dyDescent="0.2">
       <c r="AW63" s="23"/>
@@ -3075,15 +3251,23 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="AW60:AW62"/>
-    <mergeCell ref="AZ60:AZ62"/>
-    <mergeCell ref="AY60:AY62"/>
-    <mergeCell ref="AX60:AX62"/>
-    <mergeCell ref="AO46:AO49"/>
-    <mergeCell ref="AS58:AT58"/>
-    <mergeCell ref="AU58:AV58"/>
-    <mergeCell ref="AW58:AX58"/>
-    <mergeCell ref="AY58:AZ58"/>
+    <mergeCell ref="W23:Z23"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="Z25:Z27"/>
+    <mergeCell ref="Y25:Y27"/>
+    <mergeCell ref="X25:X27"/>
+    <mergeCell ref="W25:W27"/>
+    <mergeCell ref="O23:R23"/>
+    <mergeCell ref="S25:S27"/>
+    <mergeCell ref="T25:T27"/>
+    <mergeCell ref="U25:U27"/>
+    <mergeCell ref="V25:V27"/>
+    <mergeCell ref="S23:V23"/>
+    <mergeCell ref="AJ46:AJ49"/>
+    <mergeCell ref="AK46:AK49"/>
+    <mergeCell ref="AL46:AL49"/>
+    <mergeCell ref="AM46:AM49"/>
+    <mergeCell ref="AN46:AN49"/>
     <mergeCell ref="AM37:AO37"/>
     <mergeCell ref="AE44:AF44"/>
     <mergeCell ref="AG44:AI44"/>
@@ -3098,23 +3282,15 @@
     <mergeCell ref="AL39:AL42"/>
     <mergeCell ref="AK39:AK42"/>
     <mergeCell ref="AJ39:AJ42"/>
-    <mergeCell ref="AJ46:AJ49"/>
-    <mergeCell ref="AK46:AK49"/>
-    <mergeCell ref="AL46:AL49"/>
-    <mergeCell ref="AM46:AM49"/>
-    <mergeCell ref="AN46:AN49"/>
-    <mergeCell ref="W23:Z23"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="Z25:Z27"/>
-    <mergeCell ref="Y25:Y27"/>
-    <mergeCell ref="X25:X27"/>
-    <mergeCell ref="W25:W27"/>
-    <mergeCell ref="O23:R23"/>
-    <mergeCell ref="S25:S27"/>
-    <mergeCell ref="T25:T27"/>
-    <mergeCell ref="U25:U27"/>
-    <mergeCell ref="V25:V27"/>
-    <mergeCell ref="S23:V23"/>
+    <mergeCell ref="AW60:AW62"/>
+    <mergeCell ref="AZ60:AZ62"/>
+    <mergeCell ref="AY60:AY62"/>
+    <mergeCell ref="AX60:AX62"/>
+    <mergeCell ref="AO46:AO49"/>
+    <mergeCell ref="AS58:AT58"/>
+    <mergeCell ref="AU58:AV58"/>
+    <mergeCell ref="AW58:AX58"/>
+    <mergeCell ref="AY58:AZ58"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3534,7 +3710,7 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B3" s="85" t="s">
+      <c r="B3" s="123" t="s">
         <v>96</v>
       </c>
       <c r="C3" s="11" t="s">
@@ -3542,7 +3718,7 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="85"/>
+      <c r="B4" s="123"/>
       <c r="C4" s="11" t="s">
         <v>98</v>
       </c>
@@ -3646,7 +3822,7 @@
       <c r="F10" s="12"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B11" s="85" t="s">
+      <c r="B11" s="123" t="s">
         <v>96</v>
       </c>
       <c r="C11" s="11" t="s">
@@ -3654,7 +3830,7 @@
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B12" s="85"/>
+      <c r="B12" s="123"/>
       <c r="C12" s="11" t="s">
         <v>98</v>
       </c>
@@ -3754,7 +3930,7 @@
       <c r="G16" s="12"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B18" s="85" t="s">
+      <c r="B18" s="123" t="s">
         <v>96</v>
       </c>
       <c r="C18" s="11" t="s">
@@ -3762,7 +3938,7 @@
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B19" s="85"/>
+      <c r="B19" s="123"/>
       <c r="C19" s="39" t="s">
         <v>103</v>
       </c>
@@ -4062,7 +4238,7 @@
       </c>
     </row>
     <row r="49" spans="9:13" x14ac:dyDescent="0.2">
-      <c r="I49" s="85" t="s">
+      <c r="I49" s="123" t="s">
         <v>96</v>
       </c>
       <c r="J49" s="11" t="s">
@@ -4070,7 +4246,7 @@
       </c>
     </row>
     <row r="50" spans="9:13" x14ac:dyDescent="0.2">
-      <c r="I50" s="85"/>
+      <c r="I50" s="123"/>
       <c r="J50" s="11" t="s">
         <v>134</v>
       </c>
@@ -4254,10 +4430,10 @@
     </row>
     <row r="73" spans="9:23" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="74" spans="9:23" x14ac:dyDescent="0.2">
-      <c r="Q74" s="87" t="s">
+      <c r="Q74" s="122" t="s">
         <v>149</v>
       </c>
-      <c r="R74" s="87" t="s">
+      <c r="R74" s="122" t="s">
         <v>96</v>
       </c>
       <c r="S74" s="11" t="s">
@@ -4265,15 +4441,15 @@
       </c>
     </row>
     <row r="75" spans="9:23" x14ac:dyDescent="0.2">
-      <c r="Q75" s="87"/>
-      <c r="R75" s="87"/>
+      <c r="Q75" s="122"/>
+      <c r="R75" s="122"/>
       <c r="S75" s="11" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="76" spans="9:23" x14ac:dyDescent="0.2">
-      <c r="Q76" s="87"/>
-      <c r="R76" s="87"/>
+      <c r="Q76" s="122"/>
+      <c r="R76" s="122"/>
       <c r="S76" s="11">
         <v>12</v>
       </c>
@@ -4384,10 +4560,10 @@
       <c r="U81" s="12"/>
     </row>
     <row r="83" spans="17:23" x14ac:dyDescent="0.2">
-      <c r="Q83" s="87" t="s">
+      <c r="Q83" s="122" t="s">
         <v>149</v>
       </c>
-      <c r="R83" s="87" t="s">
+      <c r="R83" s="122" t="s">
         <v>96</v>
       </c>
       <c r="S83" s="11" t="s">
@@ -4395,15 +4571,15 @@
       </c>
     </row>
     <row r="84" spans="17:23" x14ac:dyDescent="0.2">
-      <c r="Q84" s="87"/>
-      <c r="R84" s="87"/>
+      <c r="Q84" s="122"/>
+      <c r="R84" s="122"/>
       <c r="S84" s="11" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="85" spans="17:23" x14ac:dyDescent="0.2">
-      <c r="Q85" s="87"/>
-      <c r="R85" s="87"/>
+      <c r="Q85" s="122"/>
+      <c r="R85" s="122"/>
       <c r="S85" s="39" t="s">
         <v>103</v>
       </c>
@@ -4696,16 +4872,16 @@
       </c>
     </row>
     <row r="116" spans="25:29" x14ac:dyDescent="0.2">
-      <c r="Y116" s="88" t="s">
+      <c r="Y116" s="124" t="s">
         <v>158</v>
       </c>
-      <c r="Z116" s="88"/>
-      <c r="AA116" s="88"/>
-      <c r="AB116" s="88"/>
-      <c r="AC116" s="88"/>
+      <c r="Z116" s="124"/>
+      <c r="AA116" s="124"/>
+      <c r="AB116" s="124"/>
+      <c r="AC116" s="124"/>
     </row>
     <row r="117" spans="25:29" x14ac:dyDescent="0.2">
-      <c r="Y117" s="85" t="s">
+      <c r="Y117" s="123" t="s">
         <v>96</v>
       </c>
       <c r="Z117" s="11" t="s">
@@ -4713,7 +4889,7 @@
       </c>
     </row>
     <row r="118" spans="25:29" x14ac:dyDescent="0.2">
-      <c r="Y118" s="85"/>
+      <c r="Y118" s="123"/>
       <c r="Z118" s="11">
         <v>12</v>
       </c>
@@ -4783,7 +4959,7 @@
       <c r="AB122" s="12"/>
     </row>
     <row r="124" spans="25:29" x14ac:dyDescent="0.2">
-      <c r="Y124" s="85" t="s">
+      <c r="Y124" s="123" t="s">
         <v>96</v>
       </c>
       <c r="Z124" s="11" t="s">
@@ -4791,7 +4967,7 @@
       </c>
     </row>
     <row r="125" spans="25:29" x14ac:dyDescent="0.2">
-      <c r="Y125" s="85"/>
+      <c r="Y125" s="123"/>
       <c r="Z125" s="40" t="s">
         <v>103</v>
       </c>
@@ -5015,15 +5191,15 @@
       <c r="Y148" s="3"/>
     </row>
     <row r="150" spans="25:28" x14ac:dyDescent="0.2">
-      <c r="Y150" s="82" t="s">
+      <c r="Y150" s="108" t="s">
         <v>173</v>
       </c>
-      <c r="Z150" s="82"/>
-      <c r="AA150" s="82"/>
-      <c r="AB150" s="82"/>
+      <c r="Z150" s="108"/>
+      <c r="AA150" s="108"/>
+      <c r="AB150" s="108"/>
     </row>
     <row r="151" spans="25:28" x14ac:dyDescent="0.2">
-      <c r="Y151" s="86" t="s">
+      <c r="Y151" s="121" t="s">
         <v>96</v>
       </c>
       <c r="Z151" s="11" t="s">
@@ -5031,7 +5207,7 @@
       </c>
     </row>
     <row r="152" spans="25:28" x14ac:dyDescent="0.2">
-      <c r="Y152" s="86"/>
+      <c r="Y152" s="121"/>
       <c r="Z152" s="40" t="s">
         <v>103</v>
       </c>
@@ -5230,6 +5406,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="I49:I50"/>
+    <mergeCell ref="Y124:Y125"/>
     <mergeCell ref="Y151:Y152"/>
     <mergeCell ref="Y150:AB150"/>
     <mergeCell ref="R74:R76"/>
@@ -5238,11 +5419,6 @@
     <mergeCell ref="R83:R85"/>
     <mergeCell ref="Y117:Y118"/>
     <mergeCell ref="Y116:AC116"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="I49:I50"/>
-    <mergeCell ref="Y124:Y125"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5472,183 +5648,183 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B2" s="83"/>
-      <c r="C2" s="92" t="s">
+      <c r="B2" s="107"/>
+      <c r="C2" s="126" t="s">
         <v>187</v>
       </c>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
+      <c r="D2" s="126"/>
+      <c r="E2" s="126"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B3" s="83"/>
-      <c r="C3" s="89">
+      <c r="B3" s="107"/>
+      <c r="C3" s="70">
         <v>2021</v>
       </c>
-      <c r="D3" s="89">
+      <c r="D3" s="70">
         <v>2022</v>
       </c>
-      <c r="E3" s="89">
+      <c r="E3" s="70">
         <v>2023</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B4" s="90" t="s">
+      <c r="B4" s="71" t="s">
         <v>188</v>
       </c>
-      <c r="C4" s="91">
+      <c r="C4" s="72">
         <v>10000</v>
       </c>
-      <c r="D4" s="91">
+      <c r="D4" s="72">
         <v>11100</v>
       </c>
-      <c r="E4" s="91">
+      <c r="E4" s="72">
         <v>10500</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B5" s="90" t="s">
+      <c r="B5" s="71" t="s">
         <v>189</v>
       </c>
-      <c r="C5" s="91">
+      <c r="C5" s="72">
         <v>900</v>
       </c>
-      <c r="D5" s="91">
+      <c r="D5" s="72">
         <v>888</v>
       </c>
-      <c r="E5" s="91">
+      <c r="E5" s="72">
         <v>965</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B6" s="90" t="s">
+      <c r="B6" s="71" t="s">
         <v>190</v>
       </c>
-      <c r="C6" s="91">
+      <c r="C6" s="72">
         <v>9000</v>
       </c>
-      <c r="D6" s="91">
+      <c r="D6" s="72">
         <v>2850</v>
       </c>
-      <c r="E6" s="91">
+      <c r="E6" s="72">
         <v>3000</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B7" s="90" t="s">
+      <c r="B7" s="71" t="s">
         <v>191</v>
       </c>
-      <c r="C7" s="91">
+      <c r="C7" s="72">
         <v>40800</v>
       </c>
-      <c r="D7" s="91">
+      <c r="D7" s="72">
         <v>36500</v>
       </c>
-      <c r="E7" s="91">
+      <c r="E7" s="72">
         <v>32200</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B8" s="90" t="s">
+      <c r="B8" s="71" t="s">
         <v>192</v>
       </c>
-      <c r="C8" s="91">
+      <c r="C8" s="72">
         <v>32000</v>
       </c>
-      <c r="D8" s="91">
+      <c r="D8" s="72">
         <v>33500</v>
       </c>
-      <c r="E8" s="91">
+      <c r="E8" s="72">
         <v>37000</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B9" s="90" t="s">
+      <c r="B9" s="71" t="s">
         <v>193</v>
       </c>
-      <c r="C9" s="91">
+      <c r="C9" s="72">
         <v>33000</v>
       </c>
-      <c r="D9" s="91">
+      <c r="D9" s="72">
         <v>36000</v>
       </c>
-      <c r="E9" s="91">
+      <c r="E9" s="72">
         <v>38500</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B10" s="90" t="s">
+      <c r="B10" s="71" t="s">
         <v>194</v>
       </c>
-      <c r="C10" s="91">
+      <c r="C10" s="72">
         <v>500500</v>
       </c>
-      <c r="D10" s="91">
+      <c r="D10" s="72">
         <v>513000</v>
       </c>
-      <c r="E10" s="91">
+      <c r="E10" s="72">
         <v>518500</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B11" s="90" t="s">
+      <c r="B11" s="71" t="s">
         <v>195</v>
       </c>
-      <c r="C11" s="91">
+      <c r="C11" s="72">
         <v>545000</v>
       </c>
-      <c r="D11" s="91">
+      <c r="D11" s="72">
         <v>560000</v>
       </c>
-      <c r="E11" s="91">
+      <c r="E11" s="72">
         <v>565000</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B13" s="83"/>
-      <c r="C13" s="92" t="s">
+      <c r="B13" s="107"/>
+      <c r="C13" s="126" t="s">
         <v>187</v>
       </c>
-      <c r="D13" s="92"/>
-      <c r="E13" s="92"/>
+      <c r="D13" s="126"/>
+      <c r="E13" s="126"/>
       <c r="H13" s="15" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B14" s="83"/>
-      <c r="C14" s="89">
+      <c r="B14" s="107"/>
+      <c r="C14" s="70">
         <v>2021</v>
       </c>
-      <c r="D14" s="89">
+      <c r="D14" s="70">
         <v>2022</v>
       </c>
-      <c r="E14" s="89">
+      <c r="E14" s="70">
         <v>2023</v>
       </c>
-      <c r="H14" s="89"/>
-      <c r="I14" s="94" t="s">
+      <c r="H14" s="70"/>
+      <c r="I14" s="74" t="s">
         <v>197</v>
       </c>
-      <c r="J14" s="94" t="s">
+      <c r="J14" s="74" t="s">
         <v>198</v>
       </c>
-      <c r="K14" s="94" t="s">
+      <c r="K14" s="74" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B15" s="90" t="s">
+      <c r="B15" s="71" t="s">
         <v>188</v>
       </c>
-      <c r="C15" s="93">
+      <c r="C15" s="73">
         <f>C4/C$11</f>
         <v>1.834862385321101E-2</v>
       </c>
-      <c r="D15" s="93">
+      <c r="D15" s="73">
         <f t="shared" ref="D15:E15" si="0">D4/D$11</f>
         <v>1.982142857142857E-2</v>
       </c>
-      <c r="E15" s="93">
+      <c r="E15" s="73">
         <f t="shared" si="0"/>
         <v>1.8584070796460177E-2</v>
       </c>
@@ -5656,33 +5832,33 @@
         <v>224</v>
       </c>
       <c r="G15" s="36"/>
-      <c r="H15" s="90" t="s">
+      <c r="H15" s="71" t="s">
         <v>188</v>
       </c>
-      <c r="I15" s="93">
+      <c r="I15" s="73">
         <f>AVERAGE(C15:E15)</f>
         <v>1.8918041073699921E-2</v>
       </c>
-      <c r="J15" s="95" t="s">
+      <c r="J15" s="75" t="s">
         <v>201</v>
       </c>
-      <c r="K15" s="95" t="s">
+      <c r="K15" s="75" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B16" s="90" t="s">
+      <c r="B16" s="71" t="s">
         <v>189</v>
       </c>
-      <c r="C16" s="93">
+      <c r="C16" s="73">
         <f>C5/C$9</f>
         <v>2.7272727272727271E-2</v>
       </c>
-      <c r="D16" s="93">
+      <c r="D16" s="73">
         <f t="shared" ref="D16:E16" si="1">D5/D$9</f>
         <v>2.4666666666666667E-2</v>
       </c>
-      <c r="E16" s="93">
+      <c r="E16" s="73">
         <f t="shared" si="1"/>
         <v>2.5064935064935064E-2</v>
       </c>
@@ -5690,33 +5866,33 @@
         <v>225</v>
       </c>
       <c r="G16" s="36"/>
-      <c r="H16" s="90" t="s">
+      <c r="H16" s="71" t="s">
         <v>189</v>
       </c>
-      <c r="I16" s="93">
+      <c r="I16" s="73">
         <f>AVERAGE(C16:E16)</f>
         <v>2.566810966810967E-2</v>
       </c>
-      <c r="J16" s="95" t="s">
+      <c r="J16" s="75" t="s">
         <v>201</v>
       </c>
-      <c r="K16" s="95" t="s">
+      <c r="K16" s="75" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B17" s="90" t="s">
+      <c r="B17" s="71" t="s">
         <v>190</v>
       </c>
-      <c r="C17" s="93">
+      <c r="C17" s="73">
         <f>C6/C$9</f>
         <v>0.27272727272727271</v>
       </c>
-      <c r="D17" s="93">
+      <c r="D17" s="73">
         <f t="shared" ref="D17:E17" si="2">D6/D$9</f>
         <v>7.9166666666666663E-2</v>
       </c>
-      <c r="E17" s="93">
+      <c r="E17" s="73">
         <f t="shared" si="2"/>
         <v>7.792207792207792E-2</v>
       </c>
@@ -5724,33 +5900,33 @@
         <v>226</v>
       </c>
       <c r="G17" s="36"/>
-      <c r="H17" s="90" t="s">
+      <c r="H17" s="71" t="s">
         <v>190</v>
       </c>
-      <c r="I17" s="93">
+      <c r="I17" s="73">
         <f>AVERAGE(D17:E17)</f>
         <v>7.8544372294372292E-2</v>
       </c>
-      <c r="J17" s="95" t="s">
+      <c r="J17" s="75" t="s">
         <v>203</v>
       </c>
-      <c r="K17" s="95" t="s">
+      <c r="K17" s="75" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="18" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="90" t="s">
+      <c r="B18" s="71" t="s">
         <v>191</v>
       </c>
-      <c r="C18" s="93">
+      <c r="C18" s="73">
         <f>C7/C$10</f>
         <v>8.1518481518481525E-2</v>
       </c>
-      <c r="D18" s="93">
+      <c r="D18" s="73">
         <f>D7/D$10</f>
         <v>7.1150097465886936E-2</v>
       </c>
-      <c r="E18" s="93">
+      <c r="E18" s="73">
         <f>E7/E$10</f>
         <v>6.210221793635487E-2</v>
       </c>
@@ -5758,44 +5934,44 @@
         <v>196</v>
       </c>
       <c r="G18" s="36"/>
-      <c r="H18" s="96" t="s">
+      <c r="H18" s="76" t="s">
         <v>191</v>
       </c>
-      <c r="I18" s="97">
+      <c r="I18" s="77">
         <f>E18</f>
         <v>6.210221793635487E-2</v>
       </c>
-      <c r="J18" s="98" t="s">
+      <c r="J18" s="78" t="s">
         <v>205</v>
       </c>
-      <c r="K18" s="98" t="s">
+      <c r="K18" s="78" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="19" spans="2:12" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="90"/>
-      <c r="C19" s="91"/>
-      <c r="D19" s="91"/>
-      <c r="E19" s="91"/>
-      <c r="H19" s="89" t="s">
+      <c r="B19" s="71"/>
+      <c r="C19" s="72"/>
+      <c r="D19" s="72"/>
+      <c r="E19" s="72"/>
+      <c r="H19" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="I19" s="99">
+      <c r="I19" s="79">
         <f>SUM(I15:I18)</f>
         <v>0.18523274097253675</v>
       </c>
-      <c r="J19" s="100" t="s">
+      <c r="J19" s="80" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="20" spans="2:12" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="106" t="s">
+      <c r="B20" s="125" t="s">
         <v>223</v>
       </c>
-      <c r="C20" s="106"/>
-      <c r="D20" s="106"/>
-      <c r="E20" s="106"/>
-      <c r="F20" s="106"/>
+      <c r="C20" s="125"/>
+      <c r="D20" s="125"/>
+      <c r="E20" s="125"/>
+      <c r="F20" s="125"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
@@ -5811,10 +5987,10 @@
       </c>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B24" s="89" t="s">
+      <c r="B24" s="70" t="s">
         <v>211</v>
       </c>
-      <c r="C24" s="89" t="s">
+      <c r="C24" s="70" t="s">
         <v>212</v>
       </c>
       <c r="I24" s="15" t="s">
@@ -5831,20 +6007,20 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="90" t="s">
+      <c r="B25" s="71" t="s">
         <v>213</v>
       </c>
-      <c r="C25" s="101">
+      <c r="C25" s="81">
         <v>0.6</v>
       </c>
-      <c r="H25" s="90" t="s">
+      <c r="H25" s="71" t="s">
         <v>188</v>
       </c>
-      <c r="I25" s="102">
+      <c r="I25" s="82">
         <f>$I15*$C25</f>
         <v>1.1350824644219952E-2</v>
       </c>
-      <c r="J25" s="102">
+      <c r="J25" s="82">
         <f>$I15*(1-$C25)</f>
         <v>7.5672164294799688E-3</v>
       </c>
@@ -5856,89 +6032,89 @@
       </c>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B26" s="90" t="s">
+      <c r="B26" s="71" t="s">
         <v>214</v>
       </c>
-      <c r="C26" s="101">
+      <c r="C26" s="81">
         <v>0.4</v>
       </c>
-      <c r="H26" s="90" t="s">
+      <c r="H26" s="71" t="s">
         <v>189</v>
       </c>
-      <c r="I26" s="102">
+      <c r="I26" s="82">
         <f t="shared" ref="I26:I28" si="3">$I16*$C26</f>
         <v>1.0267243867243869E-2</v>
       </c>
-      <c r="J26" s="102">
+      <c r="J26" s="82">
         <f t="shared" ref="J26:J28" si="4">$I16*(1-$C26)</f>
         <v>1.54008658008658E-2</v>
       </c>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B27" s="90" t="s">
+      <c r="B27" s="71" t="s">
         <v>215</v>
       </c>
-      <c r="C27" s="101">
+      <c r="C27" s="81">
         <v>0</v>
       </c>
-      <c r="H27" s="90" t="s">
+      <c r="H27" s="71" t="s">
         <v>190</v>
       </c>
-      <c r="I27" s="102">
+      <c r="I27" s="82">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J27" s="102">
+      <c r="J27" s="82">
         <f t="shared" si="4"/>
         <v>7.8544372294372292E-2</v>
       </c>
     </row>
     <row r="28" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="90" t="s">
+      <c r="B28" s="71" t="s">
         <v>216</v>
       </c>
-      <c r="C28" s="101">
+      <c r="C28" s="81">
         <v>0.3</v>
       </c>
-      <c r="H28" s="96" t="s">
+      <c r="H28" s="76" t="s">
         <v>191</v>
       </c>
-      <c r="I28" s="103">
+      <c r="I28" s="83">
         <f t="shared" si="3"/>
         <v>1.863066538090646E-2</v>
       </c>
-      <c r="J28" s="103">
+      <c r="J28" s="83">
         <f t="shared" si="4"/>
         <v>4.3471552555448406E-2</v>
       </c>
-      <c r="K28" s="104"/>
-      <c r="L28" s="104"/>
+      <c r="K28" s="84"/>
+      <c r="L28" s="84"/>
     </row>
     <row r="29" spans="2:12" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="H29" s="89" t="s">
+      <c r="H29" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="I29" s="99">
+      <c r="I29" s="79">
         <f>SUM(I25:I28)</f>
         <v>4.0248733892370284E-2</v>
       </c>
-      <c r="J29" s="99">
+      <c r="J29" s="79">
         <f>SUM(J25:J28)</f>
         <v>0.14498400708016645</v>
       </c>
       <c r="K29" s="36" t="s">
         <v>222</v>
       </c>
-      <c r="L29" s="105" t="s">
+      <c r="L29" s="85" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="33" spans="17:26" x14ac:dyDescent="0.2">
-      <c r="Q33" s="83"/>
-      <c r="R33" s="92" t="s">
+      <c r="Q33" s="107"/>
+      <c r="R33" s="126" t="s">
         <v>187</v>
       </c>
-      <c r="S33" s="92"/>
+      <c r="S33" s="126"/>
       <c r="U33" s="15" t="s">
         <v>232</v>
       </c>
@@ -5948,17 +6124,17 @@
       <c r="W33" s="36" t="s">
         <v>240</v>
       </c>
-      <c r="X33" s="114"/>
+      <c r="X33" s="93"/>
       <c r="Y33" s="36" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="34" spans="17:26" x14ac:dyDescent="0.2">
-      <c r="Q34" s="83"/>
-      <c r="R34" s="89">
+      <c r="Q34" s="107"/>
+      <c r="R34" s="70">
         <v>2003</v>
       </c>
-      <c r="S34" s="89">
+      <c r="S34" s="70">
         <v>2004</v>
       </c>
       <c r="U34" s="15" t="s">
@@ -5978,13 +6154,13 @@
       </c>
     </row>
     <row r="35" spans="17:26" x14ac:dyDescent="0.2">
-      <c r="Q35" s="90" t="s">
+      <c r="Q35" s="71" t="s">
         <v>191</v>
       </c>
-      <c r="R35" s="91">
+      <c r="R35" s="72">
         <v>25000</v>
       </c>
-      <c r="S35" s="91">
+      <c r="S35" s="72">
         <v>28000</v>
       </c>
       <c r="U35">
@@ -6001,56 +6177,56 @@
       <c r="X35">
         <v>3</v>
       </c>
-      <c r="Y35" s="113">
+      <c r="Y35" s="92">
         <f>W35*(1+$R$47)^X35</f>
         <v>32.78181</v>
       </c>
     </row>
     <row r="36" spans="17:26" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="Q36" s="90" t="s">
+      <c r="Q36" s="71" t="s">
         <v>227</v>
       </c>
-      <c r="R36" s="101">
+      <c r="R36" s="81">
         <v>0.75</v>
       </c>
-      <c r="S36" s="101">
+      <c r="S36" s="81">
         <v>0.75</v>
       </c>
-      <c r="U36" s="104">
+      <c r="U36" s="84">
         <v>2004</v>
       </c>
-      <c r="V36" s="111">
+      <c r="V36" s="90">
         <f>S35/S37</f>
         <v>43.410852713178294</v>
       </c>
-      <c r="W36" s="111">
+      <c r="W36" s="90">
         <f>V36*S36</f>
         <v>32.558139534883722</v>
       </c>
-      <c r="X36" s="112">
+      <c r="X36" s="91">
         <f>X35-1</f>
         <v>2</v>
       </c>
-      <c r="Y36" s="111">
+      <c r="Y36" s="90">
         <f>W36*(1+$R$47)^X36</f>
         <v>34.540930232558139</v>
       </c>
-      <c r="Z36" s="104"/>
+      <c r="Z36" s="84"/>
     </row>
     <row r="37" spans="17:26" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="Q37" s="90" t="s">
+      <c r="Q37" s="71" t="s">
         <v>228</v>
       </c>
-      <c r="R37" s="90">
+      <c r="R37" s="71">
         <v>625</v>
       </c>
-      <c r="S37" s="90">
+      <c r="S37" s="71">
         <v>645</v>
       </c>
       <c r="X37" s="15" t="s">
         <v>238</v>
       </c>
-      <c r="Y37" s="115">
+      <c r="Y37" s="92">
         <f>AVERAGE(Y35:Y36)</f>
         <v>33.661370116279073</v>
       </c>
@@ -6059,24 +6235,24 @@
       </c>
     </row>
     <row r="38" spans="17:26" x14ac:dyDescent="0.2">
-      <c r="Q38" s="90" t="s">
+      <c r="Q38" s="71" t="s">
         <v>229</v>
       </c>
-      <c r="R38" s="90">
+      <c r="R38" s="71">
         <v>640</v>
       </c>
-      <c r="S38" s="90">
+      <c r="S38" s="71">
         <v>700</v>
       </c>
     </row>
     <row r="39" spans="17:26" x14ac:dyDescent="0.2">
-      <c r="Q39" s="90" t="s">
+      <c r="Q39" s="71" t="s">
         <v>194</v>
       </c>
-      <c r="R39" s="91">
+      <c r="R39" s="72">
         <v>435000</v>
       </c>
-      <c r="S39" s="91">
+      <c r="S39" s="72">
         <v>450000</v>
       </c>
       <c r="X39" s="15" t="s">
@@ -6091,13 +6267,13 @@
       </c>
     </row>
     <row r="40" spans="17:26" x14ac:dyDescent="0.2">
-      <c r="Q40" s="90" t="s">
+      <c r="Q40" s="71" t="s">
         <v>195</v>
       </c>
-      <c r="R40" s="91">
+      <c r="R40" s="72">
         <v>460000</v>
       </c>
-      <c r="S40" s="90" t="s">
+      <c r="S40" s="71" t="s">
         <v>230</v>
       </c>
     </row>
@@ -6113,33 +6289,33 @@
       </c>
     </row>
     <row r="42" spans="17:26" x14ac:dyDescent="0.2">
-      <c r="Q42" s="89" t="s">
+      <c r="Q42" s="70" t="s">
         <v>231</v>
       </c>
-      <c r="R42" s="89" t="s">
+      <c r="R42" s="70" t="s">
         <v>217</v>
       </c>
-      <c r="S42" s="89" t="s">
+      <c r="S42" s="70" t="s">
         <v>218</v>
       </c>
-      <c r="U42" s="89" t="s">
+      <c r="U42" s="70" t="s">
         <v>237</v>
       </c>
-      <c r="V42" s="89" t="s">
+      <c r="V42" s="70" t="s">
         <v>250</v>
       </c>
-      <c r="W42" s="89" t="s">
+      <c r="W42" s="70" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="43" spans="17:26" x14ac:dyDescent="0.2">
-      <c r="Q43" s="90" t="s">
+      <c r="Q43" s="71" t="s">
         <v>213</v>
       </c>
-      <c r="R43" s="91">
+      <c r="R43" s="72">
         <v>60</v>
       </c>
-      <c r="S43" s="107">
+      <c r="S43" s="86">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="U43">
@@ -6149,7 +6325,7 @@
         <f>R35*(1-R36)</f>
         <v>6250</v>
       </c>
-      <c r="W43" s="116">
+      <c r="W43" s="94">
         <f>V43/R39</f>
         <v>1.4367816091954023E-2</v>
       </c>
@@ -6158,42 +6334,42 @@
       </c>
     </row>
     <row r="44" spans="17:26" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="Q44" s="90" t="s">
+      <c r="Q44" s="71" t="s">
         <v>214</v>
       </c>
-      <c r="R44" s="109">
+      <c r="R44" s="88">
         <v>2.5</v>
       </c>
-      <c r="S44" s="107">
+      <c r="S44" s="86">
         <v>0.02</v>
       </c>
-      <c r="U44" s="104">
+      <c r="U44" s="84">
         <v>2004</v>
       </c>
-      <c r="V44" s="120">
+      <c r="V44" s="98">
         <f>S35*(1-S36)</f>
         <v>7000</v>
       </c>
-      <c r="W44" s="118">
+      <c r="W44" s="96">
         <f>V44/S39</f>
         <v>1.5555555555555555E-2</v>
       </c>
-      <c r="X44" s="121"/>
+      <c r="X44" s="99"/>
     </row>
     <row r="45" spans="17:26" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="Q45" s="90" t="s">
+      <c r="Q45" s="71" t="s">
         <v>215</v>
       </c>
-      <c r="R45" s="90">
+      <c r="R45" s="71">
         <v>0</v>
       </c>
-      <c r="S45" s="107">
+      <c r="S45" s="86">
         <v>0.12</v>
       </c>
       <c r="V45" s="15" t="s">
         <v>238</v>
       </c>
-      <c r="W45" s="117">
+      <c r="W45" s="95">
         <f>AVERAGE(W43:W44)</f>
         <v>1.4961685823754789E-2</v>
       </c>
@@ -6202,7 +6378,7 @@
       </c>
     </row>
     <row r="47" spans="17:26" x14ac:dyDescent="0.2">
-      <c r="Q47" s="89" t="s">
+      <c r="Q47" s="70" t="s">
         <v>244</v>
       </c>
       <c r="R47" s="19">
@@ -6211,7 +6387,7 @@
       <c r="V47" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="W47" s="119">
+      <c r="W47" s="97">
         <f>W45+SUM(S43:S45)</f>
         <v>0.17996168582375477</v>
       </c>
@@ -6231,10 +6407,10 @@
       </c>
     </row>
     <row r="50" spans="32:42" x14ac:dyDescent="0.2">
-      <c r="AG50" s="89" t="s">
+      <c r="AG50" s="70" t="s">
         <v>253</v>
       </c>
-      <c r="AH50" s="89" t="s">
+      <c r="AH50" s="70" t="s">
         <v>212</v>
       </c>
       <c r="AK50" s="15" t="s">
@@ -6254,33 +6430,33 @@
       </c>
     </row>
     <row r="51" spans="32:42" x14ac:dyDescent="0.2">
-      <c r="AF51" s="90" t="s">
+      <c r="AF51" s="71" t="s">
         <v>216</v>
       </c>
-      <c r="AG51" s="91">
+      <c r="AG51" s="72">
         <v>15000</v>
       </c>
-      <c r="AH51" s="101">
+      <c r="AH51" s="81">
         <v>0.5</v>
       </c>
-      <c r="AJ51" s="90" t="s">
+      <c r="AJ51" s="71" t="s">
         <v>216</v>
       </c>
-      <c r="AK51" s="108" t="s">
+      <c r="AK51" s="87" t="s">
         <v>261</v>
       </c>
-      <c r="AL51" s="113">
+      <c r="AL51" s="92">
         <f>AG51/AG57</f>
         <v>11.673151750972762</v>
       </c>
-      <c r="AM51" s="113">
+      <c r="AM51" s="92">
         <f>AL51*AH51</f>
         <v>5.836575875486381</v>
       </c>
       <c r="AN51">
         <v>2.5</v>
       </c>
-      <c r="AO51" s="113">
+      <c r="AO51" s="92">
         <f>AM51*(1+$AG$60)^AN51</f>
         <v>6.1327966563454703</v>
       </c>
@@ -6289,110 +6465,110 @@
       </c>
     </row>
     <row r="52" spans="32:42" x14ac:dyDescent="0.2">
-      <c r="AF52" s="90" t="s">
+      <c r="AF52" s="71" t="s">
         <v>213</v>
       </c>
-      <c r="AG52" s="91">
+      <c r="AG52" s="72">
         <v>38125</v>
       </c>
-      <c r="AH52" s="101">
+      <c r="AH52" s="81">
         <v>0.2</v>
       </c>
-      <c r="AJ52" s="90" t="s">
+      <c r="AJ52" s="71" t="s">
         <v>213</v>
       </c>
-      <c r="AK52" s="108" t="s">
+      <c r="AK52" s="87" t="s">
         <v>262</v>
       </c>
-      <c r="AL52" s="113">
+      <c r="AL52" s="92">
         <f>AG52/$AG$58</f>
         <v>28.838880484114977</v>
       </c>
-      <c r="AM52" s="113">
+      <c r="AM52" s="92">
         <f>AL52*AH52</f>
         <v>5.7677760968229954</v>
       </c>
       <c r="AN52">
         <v>2</v>
       </c>
-      <c r="AO52" s="113">
+      <c r="AO52" s="92">
         <f>AM52*(1+$AG$60)^AN52</f>
         <v>6.0007942511346446</v>
       </c>
     </row>
     <row r="53" spans="32:42" x14ac:dyDescent="0.2">
-      <c r="AF53" s="90" t="s">
+      <c r="AF53" s="71" t="s">
         <v>214</v>
       </c>
-      <c r="AG53" s="91">
+      <c r="AG53" s="72">
         <v>11000</v>
       </c>
-      <c r="AH53" s="101">
+      <c r="AH53" s="81">
         <v>0.4</v>
       </c>
-      <c r="AJ53" s="90" t="s">
+      <c r="AJ53" s="71" t="s">
         <v>214</v>
       </c>
-      <c r="AK53" s="108" t="s">
+      <c r="AK53" s="87" t="s">
         <v>262</v>
       </c>
-      <c r="AL53" s="113">
+      <c r="AL53" s="92">
         <f>AG53/$AG$58</f>
         <v>8.3207261724659602</v>
       </c>
-      <c r="AM53" s="113">
+      <c r="AM53" s="92">
         <f>AL53*AH53</f>
         <v>3.3282904689863844</v>
       </c>
       <c r="AN53">
         <v>2</v>
       </c>
-      <c r="AO53" s="113">
+      <c r="AO53" s="92">
         <f>AM53*(1+$AG$60)^AN53</f>
         <v>3.4627534039334344</v>
       </c>
     </row>
     <row r="54" spans="32:42" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="AF54" s="90" t="s">
+      <c r="AF54" s="71" t="s">
         <v>215</v>
       </c>
-      <c r="AG54" s="91">
+      <c r="AG54" s="72">
         <v>1525</v>
       </c>
-      <c r="AH54" s="101">
+      <c r="AH54" s="81">
         <v>0.1</v>
       </c>
-      <c r="AJ54" s="96" t="s">
+      <c r="AJ54" s="76" t="s">
         <v>215</v>
       </c>
-      <c r="AK54" s="110" t="s">
+      <c r="AK54" s="89" t="s">
         <v>262</v>
       </c>
-      <c r="AL54" s="111">
+      <c r="AL54" s="90">
         <f>AG54/$AG$58</f>
         <v>1.153555219364599</v>
       </c>
-      <c r="AM54" s="111">
+      <c r="AM54" s="90">
         <f>AL54*AH54</f>
         <v>0.11535552193645991</v>
       </c>
-      <c r="AN54" s="104">
+      <c r="AN54" s="84">
         <v>2</v>
       </c>
-      <c r="AO54" s="111">
+      <c r="AO54" s="90">
         <f>AM54*(1+$AG$60)^AN54</f>
         <v>0.12001588502269289</v>
       </c>
-      <c r="AP54" s="104"/>
+      <c r="AP54" s="84"/>
     </row>
     <row r="55" spans="32:42" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="AF55" s="90" t="s">
+      <c r="AF55" s="71" t="s">
         <v>254</v>
       </c>
-      <c r="AG55" s="91">
+      <c r="AG55" s="72">
         <v>385000</v>
       </c>
-      <c r="AH55" s="90"/>
+      <c r="AH55" s="71"/>
       <c r="AN55" s="15" t="s">
         <v>10</v>
       </c>
@@ -6405,32 +6581,32 @@
       </c>
     </row>
     <row r="56" spans="32:42" x14ac:dyDescent="0.2">
-      <c r="AF56" s="90" t="s">
+      <c r="AF56" s="71" t="s">
         <v>255</v>
       </c>
-      <c r="AG56" s="91">
+      <c r="AG56" s="72">
         <v>400000</v>
       </c>
-      <c r="AH56" s="90"/>
+      <c r="AH56" s="71"/>
       <c r="AL56" s="36" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="57" spans="32:42" x14ac:dyDescent="0.2">
-      <c r="AF57" s="90" t="s">
+      <c r="AF57" s="71" t="s">
         <v>149</v>
       </c>
-      <c r="AG57" s="122">
+      <c r="AG57" s="100">
         <v>1285</v>
       </c>
-      <c r="AH57" s="90"/>
-      <c r="AJ57" s="123" t="s">
+      <c r="AH57" s="71"/>
+      <c r="AJ57" s="70" t="s">
         <v>266</v>
       </c>
       <c r="AK57" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="AL57" s="124" t="s">
+      <c r="AL57" s="101" t="s">
         <v>250</v>
       </c>
       <c r="AM57" s="15" t="s">
@@ -6438,24 +6614,24 @@
       </c>
     </row>
     <row r="58" spans="32:42" x14ac:dyDescent="0.2">
-      <c r="AF58" s="90" t="s">
+      <c r="AF58" s="71" t="s">
         <v>256</v>
       </c>
-      <c r="AG58" s="122">
+      <c r="AG58" s="100">
         <v>1322</v>
       </c>
-      <c r="AH58" s="90"/>
-      <c r="AJ58" s="90" t="s">
+      <c r="AH58" s="71"/>
+      <c r="AJ58" s="71" t="s">
         <v>216</v>
       </c>
-      <c r="AK58" s="108" t="s">
+      <c r="AK58" s="87" t="s">
         <v>49</v>
       </c>
       <c r="AL58" s="53">
         <f>AG51*(1-AH51)</f>
         <v>7500</v>
       </c>
-      <c r="AM58" s="125">
+      <c r="AM58" s="102">
         <f>AL58/AG55</f>
         <v>1.948051948051948E-2</v>
       </c>
@@ -6464,17 +6640,17 @@
       </c>
     </row>
     <row r="59" spans="32:42" x14ac:dyDescent="0.2">
-      <c r="AJ59" s="90" t="s">
+      <c r="AJ59" s="71" t="s">
         <v>213</v>
       </c>
-      <c r="AK59" s="108" t="s">
+      <c r="AK59" s="87" t="s">
         <v>259</v>
       </c>
       <c r="AL59" s="53">
         <f>AG52*(1-AH52)</f>
         <v>30500</v>
       </c>
-      <c r="AM59" s="125">
+      <c r="AM59" s="102">
         <f>AL59/$AG$56</f>
         <v>7.6249999999999998E-2</v>
       </c>
@@ -6483,55 +6659,55 @@
       </c>
     </row>
     <row r="60" spans="32:42" x14ac:dyDescent="0.2">
-      <c r="AF60" s="89" t="s">
+      <c r="AF60" s="70" t="s">
         <v>244</v>
       </c>
       <c r="AG60" s="19">
         <v>0.02</v>
       </c>
-      <c r="AJ60" s="90" t="s">
+      <c r="AJ60" s="71" t="s">
         <v>214</v>
       </c>
-      <c r="AK60" s="108" t="s">
+      <c r="AK60" s="87" t="s">
         <v>259</v>
       </c>
       <c r="AL60" s="53">
         <f>AG53*(1-AH53)</f>
         <v>6600</v>
       </c>
-      <c r="AM60" s="125">
+      <c r="AM60" s="102">
         <f>AL60/$AG$56</f>
         <v>1.6500000000000001E-2</v>
       </c>
     </row>
     <row r="61" spans="32:42" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="AF61" s="90" t="s">
+      <c r="AF61" s="71" t="s">
         <v>270</v>
       </c>
       <c r="AG61" s="19">
         <v>0.08</v>
       </c>
-      <c r="AJ61" s="96" t="s">
+      <c r="AJ61" s="76" t="s">
         <v>215</v>
       </c>
-      <c r="AK61" s="110" t="s">
+      <c r="AK61" s="89" t="s">
         <v>259</v>
       </c>
-      <c r="AL61" s="126">
+      <c r="AL61" s="103">
         <f>AG54*(1-AH54)</f>
         <v>1372.5</v>
       </c>
-      <c r="AM61" s="127">
+      <c r="AM61" s="104">
         <f>AL61/$AG$56</f>
         <v>3.4312499999999998E-3</v>
       </c>
-      <c r="AN61" s="104"/>
+      <c r="AN61" s="84"/>
     </row>
     <row r="62" spans="32:42" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="AL62" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="AM62" s="128">
+      <c r="AM62" s="105">
         <f>SUM(AM58:AM61)</f>
         <v>0.11566176948051947</v>
       </c>
@@ -6540,10 +6716,10 @@
       </c>
     </row>
     <row r="64" spans="32:42" x14ac:dyDescent="0.2">
-      <c r="AJ64" s="123" t="s">
+      <c r="AJ64" s="70" t="s">
         <v>269</v>
       </c>
-      <c r="AK64" s="99">
+      <c r="AK64" s="79">
         <f>1-AM62-AG61</f>
         <v>0.80433823051948061</v>
       </c>
@@ -6557,13 +6733,13 @@
       </c>
     </row>
     <row r="67" spans="36:40" x14ac:dyDescent="0.2">
-      <c r="AJ67" s="123" t="s">
+      <c r="AJ67" s="70" t="s">
         <v>266</v>
       </c>
       <c r="AK67" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="AL67" s="124" t="s">
+      <c r="AL67" s="101" t="s">
         <v>234</v>
       </c>
       <c r="AM67" s="15" t="s">
@@ -6571,17 +6747,17 @@
       </c>
     </row>
     <row r="68" spans="36:40" x14ac:dyDescent="0.2">
-      <c r="AJ68" s="90" t="s">
+      <c r="AJ68" s="71" t="s">
         <v>216</v>
       </c>
-      <c r="AK68" s="108" t="s">
+      <c r="AK68" s="87" t="s">
         <v>49</v>
       </c>
       <c r="AL68" s="53">
         <f>AG51*AH51</f>
         <v>7500</v>
       </c>
-      <c r="AM68" s="125">
+      <c r="AM68" s="102">
         <f>AL68/AG55</f>
         <v>1.948051948051948E-2</v>
       </c>
@@ -6590,17 +6766,17 @@
       </c>
     </row>
     <row r="69" spans="36:40" x14ac:dyDescent="0.2">
-      <c r="AJ69" s="90" t="s">
+      <c r="AJ69" s="71" t="s">
         <v>213</v>
       </c>
-      <c r="AK69" s="108" t="s">
+      <c r="AK69" s="87" t="s">
         <v>259</v>
       </c>
       <c r="AL69" s="53">
         <f t="shared" ref="AL69:AL71" si="5">AG52*AH52</f>
         <v>7625</v>
       </c>
-      <c r="AM69" s="125">
+      <c r="AM69" s="102">
         <f>AL69/$AG$56</f>
         <v>1.90625E-2</v>
       </c>
@@ -6609,43 +6785,43 @@
       </c>
     </row>
     <row r="70" spans="36:40" x14ac:dyDescent="0.2">
-      <c r="AJ70" s="90" t="s">
+      <c r="AJ70" s="71" t="s">
         <v>214</v>
       </c>
-      <c r="AK70" s="108" t="s">
+      <c r="AK70" s="87" t="s">
         <v>259</v>
       </c>
       <c r="AL70" s="53">
         <f t="shared" si="5"/>
         <v>4400</v>
       </c>
-      <c r="AM70" s="125">
+      <c r="AM70" s="102">
         <f>AL70/$AG$56</f>
         <v>1.0999999999999999E-2</v>
       </c>
     </row>
     <row r="71" spans="36:40" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="AJ71" s="96" t="s">
+      <c r="AJ71" s="76" t="s">
         <v>215</v>
       </c>
-      <c r="AK71" s="110" t="s">
+      <c r="AK71" s="89" t="s">
         <v>259</v>
       </c>
-      <c r="AL71" s="126">
+      <c r="AL71" s="103">
         <f t="shared" si="5"/>
         <v>152.5</v>
       </c>
-      <c r="AM71" s="127">
+      <c r="AM71" s="104">
         <f>AL71/$AG$56</f>
         <v>3.8125000000000002E-4</v>
       </c>
-      <c r="AN71" s="104"/>
+      <c r="AN71" s="84"/>
     </row>
     <row r="72" spans="36:40" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="AL72" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="AM72" s="128">
+      <c r="AM72" s="105">
         <f>SUM(AM68:AM71)</f>
         <v>4.9924269480519479E-2</v>
       </c>
@@ -6654,10 +6830,10 @@
       </c>
     </row>
     <row r="74" spans="36:40" x14ac:dyDescent="0.2">
-      <c r="AJ74" s="123" t="s">
+      <c r="AJ74" s="70" t="s">
         <v>281</v>
       </c>
-      <c r="AK74" s="99">
+      <c r="AK74" s="79">
         <f>1-AM72-AM62-AG61</f>
         <v>0.75441396103896108</v>
       </c>
@@ -6677,4 +6853,301 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FFBD237-AC88-AB4B-A1F6-5996C6CE41DE}">
+  <dimension ref="B1:J22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="12.1640625" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="26.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="14.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="G1" s="36" t="s">
+        <v>302</v>
+      </c>
+      <c r="I1" s="36" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2" spans="2:10" s="127" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B2" s="132" t="s">
+        <v>283</v>
+      </c>
+      <c r="C2" s="133" t="s">
+        <v>284</v>
+      </c>
+      <c r="D2" s="134" t="s">
+        <v>149</v>
+      </c>
+      <c r="E2" s="132" t="s">
+        <v>292</v>
+      </c>
+      <c r="F2" s="133" t="s">
+        <v>165</v>
+      </c>
+      <c r="G2" s="133" t="s">
+        <v>297</v>
+      </c>
+      <c r="H2" s="133" t="s">
+        <v>291</v>
+      </c>
+      <c r="I2" s="134" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B3" s="135">
+        <v>2003</v>
+      </c>
+      <c r="C3" s="136">
+        <v>2000000</v>
+      </c>
+      <c r="D3" s="137">
+        <v>2000</v>
+      </c>
+      <c r="E3" s="141">
+        <v>48</v>
+      </c>
+      <c r="F3" s="142">
+        <v>1</v>
+      </c>
+      <c r="G3" s="143">
+        <f>C3*F3</f>
+        <v>2000000</v>
+      </c>
+      <c r="H3" s="144">
+        <v>5.25</v>
+      </c>
+      <c r="I3" s="152">
+        <f>G3*(1+$H$7)^H3</f>
+        <v>2202041.100392635</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B4" s="135">
+        <v>2004</v>
+      </c>
+      <c r="C4" s="136">
+        <v>2300000</v>
+      </c>
+      <c r="D4" s="137">
+        <v>2300</v>
+      </c>
+      <c r="E4" s="141">
+        <v>36</v>
+      </c>
+      <c r="F4" s="142">
+        <v>1.05</v>
+      </c>
+      <c r="G4" s="143">
+        <f>C4*F4</f>
+        <v>2415000</v>
+      </c>
+      <c r="H4" s="145">
+        <f>H3-1</f>
+        <v>4.25</v>
+      </c>
+      <c r="I4" s="152">
+        <f>G4*(1+$H$7)^H4</f>
+        <v>2610667.2839706494</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B5" s="138">
+        <v>2005</v>
+      </c>
+      <c r="C5" s="139">
+        <v>1900000</v>
+      </c>
+      <c r="D5" s="140">
+        <v>1900</v>
+      </c>
+      <c r="E5" s="146">
+        <v>24</v>
+      </c>
+      <c r="F5" s="147">
+        <v>1.2</v>
+      </c>
+      <c r="G5" s="148">
+        <f>C5*F5</f>
+        <v>2280000</v>
+      </c>
+      <c r="H5" s="149">
+        <f>H4-1</f>
+        <v>3.25</v>
+      </c>
+      <c r="I5" s="153">
+        <f>G5*(1+$H$7)^H5</f>
+        <v>2419960.0994248562</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="E6" s="129" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B7" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>293</v>
+      </c>
+      <c r="H7" s="82">
+        <f>(1+C14)*(1+C15)-1</f>
+        <v>1.8499999999999961E-2</v>
+      </c>
+      <c r="I7" s="36" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B8" s="71" t="s">
+        <v>287</v>
+      </c>
+      <c r="C8" s="128">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B9" s="71" t="s">
+        <v>288</v>
+      </c>
+      <c r="C9" s="128">
+        <v>1.2</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="I9" s="151">
+        <f>SUM(I3:I5)/SUM(D3:D5)</f>
+        <v>1166.5594328690549</v>
+      </c>
+      <c r="J9" s="36" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B10" s="71" t="s">
+        <v>289</v>
+      </c>
+      <c r="C10" s="128">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B11" s="71" t="s">
+        <v>290</v>
+      </c>
+      <c r="C11" s="128">
+        <v>1</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="I11" s="151">
+        <f>(I9+C22)/(1-SUM(C18:C21))</f>
+        <v>1582.0792438254066</v>
+      </c>
+      <c r="J11" s="36" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B13" s="70" t="s">
+        <v>294</v>
+      </c>
+      <c r="C13" s="130" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B14" s="71" t="s">
+        <v>295</v>
+      </c>
+      <c r="C14" s="131">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B15" s="71" t="s">
+        <v>296</v>
+      </c>
+      <c r="C15" s="131">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B17" s="15" t="s">
+        <v>306</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>307</v>
+      </c>
+      <c r="C18" s="19">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>308</v>
+      </c>
+      <c r="C19" s="19">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>309</v>
+      </c>
+      <c r="C20" s="19">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>312</v>
+      </c>
+      <c r="C21" s="19">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>311</v>
+      </c>
+      <c r="C22" s="150">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D40ABDFF-5D42-FA49-91E6-920BDEC7DF05}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/files/temp-work.xlsx
+++ b/files/temp-work.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/coltongearhart/Desktop/exam5/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3731D27-291E-BA43-A251-7B425EB5365D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F804E0-6658-9A40-ADBF-21AA3EB8EE78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="7" xr2:uid="{BB8505BC-BCB7-B340-A120-C046C43AD7BD}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17620" activeTab="8" xr2:uid="{BB8505BC-BCB7-B340-A120-C046C43AD7BD}"/>
   </bookViews>
   <sheets>
     <sheet name="2.2.1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,8 @@
     <sheet name="2.4.3" sheetId="5" r:id="rId5"/>
     <sheet name="2.5.3" sheetId="6" r:id="rId6"/>
     <sheet name="2.6.1" sheetId="7" r:id="rId7"/>
-    <sheet name="Sheet2" sheetId="8" r:id="rId8"/>
+    <sheet name="3.1.3" sheetId="8" r:id="rId8"/>
+    <sheet name="3.1.4" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,8 +43,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="382">
   <si>
     <t>Ratio to SAWW</t>
   </si>
@@ -995,6 +1018,210 @@
   </si>
   <si>
     <t>=(I9+C22)/(1-SUM(C18:C21))</t>
+  </si>
+  <si>
+    <t>Territory</t>
+  </si>
+  <si>
+    <t>Married</t>
+  </si>
+  <si>
+    <t>Single</t>
+  </si>
+  <si>
+    <t>Marital Status</t>
+  </si>
+  <si>
+    <t>Current Relativity</t>
+  </si>
+  <si>
+    <t>Loss &amp; LAE</t>
+  </si>
+  <si>
+    <t>Exposures</t>
+  </si>
+  <si>
+    <t>=SUMPRODUCT($I$5:$I$7,K5:K7)/SUM(K5:K7)</t>
+  </si>
+  <si>
+    <t>Weighted avg territory by marital status</t>
+  </si>
+  <si>
+    <t>Adjusted exposures</t>
+  </si>
+  <si>
+    <t>Indicated adjusted pure premium</t>
+  </si>
+  <si>
+    <t>Indicated relativity</t>
+  </si>
+  <si>
+    <t>=SUM(C28:C29)</t>
+  </si>
+  <si>
+    <t>=SUM(C28:E28)</t>
+  </si>
+  <si>
+    <t>=SUMIFS($D$19:$D$24,$B$19:$B$24,C$28,$C$19:$C$24,$B29)</t>
+  </si>
+  <si>
+    <t>=xlookup(&lt;…&gt;)</t>
+  </si>
+  <si>
+    <t>=I13*J13</t>
+  </si>
+  <si>
+    <t>=L13/K13</t>
+  </si>
+  <si>
+    <t>=M13/$M$15</t>
+  </si>
+  <si>
+    <t>Indicated relativity to base</t>
+  </si>
+  <si>
+    <t>=N13/$N$13</t>
+  </si>
+  <si>
+    <t>Premium</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Reported Loss &amp; LAE</t>
+  </si>
+  <si>
+    <t>Earned Premium at CRL</t>
+  </si>
+  <si>
+    <t>Current Rates</t>
+  </si>
+  <si>
+    <t>Loss ratio</t>
+  </si>
+  <si>
+    <t>=SUM(R37:R40)</t>
+  </si>
+  <si>
+    <t>=SUM(S37:S40)</t>
+  </si>
+  <si>
+    <t>=S37/R37</t>
+  </si>
+  <si>
+    <t>=T37/$T$41</t>
+  </si>
+  <si>
+    <t>Indicated change factor</t>
+  </si>
+  <si>
+    <t>Current relativity</t>
+  </si>
+  <si>
+    <t>=Q37/$Q$37</t>
+  </si>
+  <si>
+    <t>=U37*V37</t>
+  </si>
+  <si>
+    <t>=W37/$W$37</t>
+  </si>
+  <si>
+    <t>Incurred losses &amp; ALAE</t>
+  </si>
+  <si>
+    <t>Claim Count</t>
+  </si>
+  <si>
+    <t>Credibility</t>
+  </si>
+  <si>
+    <t>Credibiilty standard</t>
+  </si>
+  <si>
+    <t>Complement of credibility</t>
+  </si>
+  <si>
+    <t>Credibility-weighted indicated change factor</t>
+  </si>
+  <si>
+    <t>Credibility-weighted indicated relativity</t>
+  </si>
+  <si>
+    <t>Re-based</t>
+  </si>
+  <si>
+    <t>=D4/C4</t>
+  </si>
+  <si>
+    <t>=G4/$G$7</t>
+  </si>
+  <si>
+    <t>=MIN(1,SQRT(E4/$C$9))</t>
+  </si>
+  <si>
+    <t>=I4*H4+(1-I4)*$C$10</t>
+  </si>
+  <si>
+    <t>=F4*J4</t>
+  </si>
+  <si>
+    <t>=K4/$K$5</t>
+  </si>
+  <si>
+    <t>Developed Incurred Loss and ALAE Total for Accident Years 2009 and 2010</t>
+  </si>
+  <si>
+    <t>Annual Pure Premium Trend</t>
+  </si>
+  <si>
+    <t>Indicated pure premium</t>
+  </si>
+  <si>
+    <t>Credibility standard (exposures)</t>
+  </si>
+  <si>
+    <t>=SUMPRODUCT(R19:R21,P19:P21)/P22</t>
+  </si>
+  <si>
+    <t>=R19/$R$22</t>
+  </si>
+  <si>
+    <t>=T19/$T$22</t>
+  </si>
+  <si>
+    <t>=MIN(1, SQRT(P19/$P$30))</t>
+  </si>
+  <si>
+    <t>=V19*U19+(1-V19)*S19</t>
+  </si>
+  <si>
+    <t>=W19/$W$19</t>
+  </si>
+  <si>
+    <t>Normalized current relativity (hust rebasing to total)</t>
+  </si>
+  <si>
+    <t>Indicated relativity to total (based on new data)</t>
+  </si>
+  <si>
+    <t>Credibility-weighted indicated relativities (using current relativities as complement)</t>
+  </si>
+  <si>
+    <t>Trended losses and LAE</t>
+  </si>
+  <si>
+    <t>=R19/P19</t>
+  </si>
+  <si>
+    <t>=Q19*(1+P25)^$P$31</t>
+  </si>
+  <si>
+    <t>=SUM(R19:R21)</t>
   </si>
 </sst>
 </file>
@@ -1010,10 +1237,10 @@
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="180" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="182" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="169" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="170" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1131,6 +1358,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1146,7 +1379,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -1280,13 +1513,65 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="208">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1404,6 +1689,80 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="6" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1466,41 +1825,35 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="180" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="182" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -2575,26 +2928,26 @@
       </c>
     </row>
     <row r="23" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="M23" s="113"/>
-      <c r="N23" s="114"/>
-      <c r="O23" s="110" t="s">
+      <c r="M23" s="179"/>
+      <c r="N23" s="180"/>
+      <c r="O23" s="176" t="s">
         <v>60</v>
       </c>
-      <c r="P23" s="111"/>
-      <c r="Q23" s="111"/>
-      <c r="R23" s="112"/>
-      <c r="S23" s="110" t="s">
+      <c r="P23" s="177"/>
+      <c r="Q23" s="177"/>
+      <c r="R23" s="178"/>
+      <c r="S23" s="176" t="s">
         <v>62</v>
       </c>
-      <c r="T23" s="111"/>
-      <c r="U23" s="111"/>
-      <c r="V23" s="112"/>
-      <c r="W23" s="110" t="s">
+      <c r="T23" s="177"/>
+      <c r="U23" s="177"/>
+      <c r="V23" s="178"/>
+      <c r="W23" s="176" t="s">
         <v>61</v>
       </c>
-      <c r="X23" s="111"/>
-      <c r="Y23" s="111"/>
-      <c r="Z23" s="112"/>
+      <c r="X23" s="177"/>
+      <c r="Y23" s="177"/>
+      <c r="Z23" s="178"/>
     </row>
     <row r="24" spans="2:33" x14ac:dyDescent="0.2">
       <c r="M24" s="24" t="s">
@@ -2660,35 +3013,35 @@
       <c r="R25" s="30">
         <v>0</v>
       </c>
-      <c r="S25" s="119">
+      <c r="S25" s="185">
         <f>SUMPRODUCT(O25:O27,$N$25:$N$27)</f>
         <v>1.0568750000000002</v>
       </c>
-      <c r="T25" s="117">
+      <c r="T25" s="183">
         <f t="shared" ref="T25:V25" si="2">SUMPRODUCT(P25:P27,$N$25:$N$27)</f>
         <v>1.089375</v>
       </c>
-      <c r="U25" s="117">
+      <c r="U25" s="183">
         <f t="shared" si="2"/>
         <v>1.1156250000000001</v>
       </c>
-      <c r="V25" s="115">
+      <c r="V25" s="181">
         <f t="shared" si="2"/>
         <v>1.1418750000000002</v>
       </c>
-      <c r="W25" s="119">
+      <c r="W25" s="185">
         <f>$N$27/S25</f>
         <v>1.0928444707273803</v>
       </c>
-      <c r="X25" s="117">
+      <c r="X25" s="183">
         <f t="shared" ref="X25:Z25" si="3">$N$27/T25</f>
         <v>1.060240963855422</v>
       </c>
-      <c r="Y25" s="117">
+      <c r="Y25" s="183">
         <f t="shared" si="3"/>
         <v>1.0352941176470589</v>
       </c>
-      <c r="Z25" s="115">
+      <c r="Z25" s="181">
         <f t="shared" si="3"/>
         <v>1.0114942528735633</v>
       </c>
@@ -2713,14 +3066,14 @@
       <c r="R26" s="30">
         <v>0.125</v>
       </c>
-      <c r="S26" s="119"/>
-      <c r="T26" s="117"/>
-      <c r="U26" s="117"/>
-      <c r="V26" s="115"/>
-      <c r="W26" s="119"/>
-      <c r="X26" s="117"/>
-      <c r="Y26" s="117"/>
-      <c r="Z26" s="115"/>
+      <c r="S26" s="185"/>
+      <c r="T26" s="183"/>
+      <c r="U26" s="183"/>
+      <c r="V26" s="181"/>
+      <c r="W26" s="185"/>
+      <c r="X26" s="183"/>
+      <c r="Y26" s="183"/>
+      <c r="Z26" s="181"/>
     </row>
     <row r="27" spans="2:33" x14ac:dyDescent="0.2">
       <c r="M27" s="28">
@@ -2742,14 +3095,14 @@
       <c r="R27" s="31">
         <v>0.875</v>
       </c>
-      <c r="S27" s="120"/>
-      <c r="T27" s="118"/>
-      <c r="U27" s="118"/>
-      <c r="V27" s="116"/>
-      <c r="W27" s="120"/>
-      <c r="X27" s="118"/>
-      <c r="Y27" s="118"/>
-      <c r="Z27" s="116"/>
+      <c r="S27" s="186"/>
+      <c r="T27" s="184"/>
+      <c r="U27" s="184"/>
+      <c r="V27" s="182"/>
+      <c r="W27" s="186"/>
+      <c r="X27" s="184"/>
+      <c r="Y27" s="184"/>
+      <c r="Z27" s="182"/>
     </row>
     <row r="28" spans="2:33" x14ac:dyDescent="0.2">
       <c r="N28" s="32" t="s">
@@ -2830,23 +3183,23 @@
       </c>
     </row>
     <row r="37" spans="15:41" x14ac:dyDescent="0.2">
-      <c r="AE37" s="107"/>
-      <c r="AF37" s="107"/>
-      <c r="AG37" s="108" t="s">
+      <c r="AE37" s="173"/>
+      <c r="AF37" s="173"/>
+      <c r="AG37" s="174" t="s">
         <v>72</v>
       </c>
-      <c r="AH37" s="108"/>
-      <c r="AI37" s="108"/>
-      <c r="AJ37" s="108" t="s">
+      <c r="AH37" s="174"/>
+      <c r="AI37" s="174"/>
+      <c r="AJ37" s="174" t="s">
         <v>76</v>
       </c>
-      <c r="AK37" s="108"/>
-      <c r="AL37" s="108"/>
-      <c r="AM37" s="108" t="s">
+      <c r="AK37" s="174"/>
+      <c r="AL37" s="174"/>
+      <c r="AM37" s="174" t="s">
         <v>77</v>
       </c>
-      <c r="AN37" s="108"/>
-      <c r="AO37" s="108"/>
+      <c r="AN37" s="174"/>
+      <c r="AO37" s="174"/>
     </row>
     <row r="38" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE38" s="15" t="s">
@@ -2895,18 +3248,18 @@
         <f>0.5*3/4*3/4</f>
         <v>0.28125</v>
       </c>
-      <c r="AJ39" s="106"/>
-      <c r="AK39" s="106">
+      <c r="AJ39" s="172"/>
+      <c r="AK39" s="172">
         <f>SUMPRODUCT(AH39:AH42,AF39:AF42)</f>
         <v>1.0636875000000001</v>
       </c>
-      <c r="AL39" s="106"/>
-      <c r="AM39" s="106"/>
-      <c r="AN39" s="106">
+      <c r="AL39" s="172"/>
+      <c r="AM39" s="172"/>
+      <c r="AN39" s="172">
         <f>$AF$42/AK39</f>
         <v>1.0512015982137612</v>
       </c>
-      <c r="AO39" s="106"/>
+      <c r="AO39" s="172"/>
     </row>
     <row r="40" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE40">
@@ -2920,12 +3273,12 @@
         <f>1-AH39-AH41</f>
         <v>0.59375</v>
       </c>
-      <c r="AJ40" s="106"/>
-      <c r="AK40" s="106"/>
-      <c r="AL40" s="106"/>
-      <c r="AM40" s="106"/>
-      <c r="AN40" s="106"/>
-      <c r="AO40" s="106"/>
+      <c r="AJ40" s="172"/>
+      <c r="AK40" s="172"/>
+      <c r="AL40" s="172"/>
+      <c r="AM40" s="172"/>
+      <c r="AN40" s="172"/>
+      <c r="AO40" s="172"/>
     </row>
     <row r="41" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE41">
@@ -2938,12 +3291,12 @@
       <c r="AH41">
         <v>0.125</v>
       </c>
-      <c r="AJ41" s="106"/>
-      <c r="AK41" s="106"/>
-      <c r="AL41" s="106"/>
-      <c r="AM41" s="106"/>
-      <c r="AN41" s="106"/>
-      <c r="AO41" s="106"/>
+      <c r="AJ41" s="172"/>
+      <c r="AK41" s="172"/>
+      <c r="AL41" s="172"/>
+      <c r="AM41" s="172"/>
+      <c r="AN41" s="172"/>
+      <c r="AO41" s="172"/>
     </row>
     <row r="42" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE42">
@@ -2956,31 +3309,31 @@
       <c r="AH42">
         <v>0</v>
       </c>
-      <c r="AJ42" s="106"/>
-      <c r="AK42" s="106"/>
-      <c r="AL42" s="106"/>
-      <c r="AM42" s="106"/>
-      <c r="AN42" s="106"/>
-      <c r="AO42" s="106"/>
+      <c r="AJ42" s="172"/>
+      <c r="AK42" s="172"/>
+      <c r="AL42" s="172"/>
+      <c r="AM42" s="172"/>
+      <c r="AN42" s="172"/>
+      <c r="AO42" s="172"/>
     </row>
     <row r="44" spans="15:41" x14ac:dyDescent="0.2">
-      <c r="AE44" s="107"/>
-      <c r="AF44" s="107"/>
-      <c r="AG44" s="108" t="s">
+      <c r="AE44" s="173"/>
+      <c r="AF44" s="173"/>
+      <c r="AG44" s="174" t="s">
         <v>72</v>
       </c>
-      <c r="AH44" s="108"/>
-      <c r="AI44" s="108"/>
-      <c r="AJ44" s="108" t="s">
+      <c r="AH44" s="174"/>
+      <c r="AI44" s="174"/>
+      <c r="AJ44" s="174" t="s">
         <v>76</v>
       </c>
-      <c r="AK44" s="108"/>
-      <c r="AL44" s="108"/>
-      <c r="AM44" s="108" t="s">
+      <c r="AK44" s="174"/>
+      <c r="AL44" s="174"/>
+      <c r="AM44" s="174" t="s">
         <v>77</v>
       </c>
-      <c r="AN44" s="108"/>
-      <c r="AO44" s="108"/>
+      <c r="AN44" s="174"/>
+      <c r="AO44" s="174"/>
     </row>
     <row r="45" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE45" s="15" t="s">
@@ -3028,18 +3381,18 @@
       <c r="AH46">
         <v>0</v>
       </c>
-      <c r="AJ46" s="106"/>
-      <c r="AK46" s="106">
+      <c r="AJ46" s="172"/>
+      <c r="AK46" s="172">
         <f>SUMPRODUCT(AH46:AH49,AF46:AF49)</f>
         <v>1.1161437500000002</v>
       </c>
-      <c r="AL46" s="106"/>
-      <c r="AM46" s="106"/>
-      <c r="AN46" s="106">
+      <c r="AL46" s="172"/>
+      <c r="AM46" s="172"/>
+      <c r="AN46" s="172">
         <f>$AF$49/AK46</f>
         <v>1.0017974835230676</v>
       </c>
-      <c r="AO46" s="106"/>
+      <c r="AO46" s="172"/>
     </row>
     <row r="47" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE47">
@@ -3052,12 +3405,12 @@
       <c r="AH47">
         <v>0.5</v>
       </c>
-      <c r="AJ47" s="106"/>
-      <c r="AK47" s="106"/>
-      <c r="AL47" s="106"/>
-      <c r="AM47" s="106"/>
-      <c r="AN47" s="106"/>
-      <c r="AO47" s="106"/>
+      <c r="AJ47" s="172"/>
+      <c r="AK47" s="172"/>
+      <c r="AL47" s="172"/>
+      <c r="AM47" s="172"/>
+      <c r="AN47" s="172"/>
+      <c r="AO47" s="172"/>
     </row>
     <row r="48" spans="15:41" x14ac:dyDescent="0.2">
       <c r="O48" t="s">
@@ -3073,12 +3426,12 @@
       <c r="AH48">
         <v>0.375</v>
       </c>
-      <c r="AJ48" s="106"/>
-      <c r="AK48" s="106"/>
-      <c r="AL48" s="106"/>
-      <c r="AM48" s="106"/>
-      <c r="AN48" s="106"/>
-      <c r="AO48" s="106"/>
+      <c r="AJ48" s="172"/>
+      <c r="AK48" s="172"/>
+      <c r="AL48" s="172"/>
+      <c r="AM48" s="172"/>
+      <c r="AN48" s="172"/>
+      <c r="AO48" s="172"/>
     </row>
     <row r="49" spans="31:52" x14ac:dyDescent="0.2">
       <c r="AE49">
@@ -3091,12 +3444,12 @@
       <c r="AH49">
         <v>0.125</v>
       </c>
-      <c r="AJ49" s="106"/>
-      <c r="AK49" s="106"/>
-      <c r="AL49" s="106"/>
-      <c r="AM49" s="106"/>
-      <c r="AN49" s="106"/>
-      <c r="AO49" s="106"/>
+      <c r="AJ49" s="172"/>
+      <c r="AK49" s="172"/>
+      <c r="AL49" s="172"/>
+      <c r="AM49" s="172"/>
+      <c r="AN49" s="172"/>
+      <c r="AO49" s="172"/>
     </row>
     <row r="53" spans="31:52" x14ac:dyDescent="0.2">
       <c r="AS53" s="15" t="s">
@@ -3146,20 +3499,20 @@
       </c>
     </row>
     <row r="58" spans="31:52" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="AS58" s="107"/>
-      <c r="AT58" s="107"/>
-      <c r="AU58" s="108" t="s">
+      <c r="AS58" s="173"/>
+      <c r="AT58" s="173"/>
+      <c r="AU58" s="174" t="s">
         <v>72</v>
       </c>
-      <c r="AV58" s="108"/>
-      <c r="AW58" s="109" t="s">
+      <c r="AV58" s="174"/>
+      <c r="AW58" s="175" t="s">
         <v>76</v>
       </c>
-      <c r="AX58" s="109"/>
-      <c r="AY58" s="108" t="s">
+      <c r="AX58" s="175"/>
+      <c r="AY58" s="174" t="s">
         <v>77</v>
       </c>
-      <c r="AZ58" s="108"/>
+      <c r="AZ58" s="174"/>
     </row>
     <row r="59" spans="31:52" x14ac:dyDescent="0.2">
       <c r="AS59" s="15" t="s">
@@ -3199,13 +3552,13 @@
         <f>1/16</f>
         <v>6.25E-2</v>
       </c>
-      <c r="AW60" s="106"/>
-      <c r="AX60" s="106">
+      <c r="AW60" s="172"/>
+      <c r="AX60" s="172">
         <f>SUMPRODUCT(AV60:AV62,AT60:AT62)</f>
         <v>1.0993750000000002</v>
       </c>
-      <c r="AY60" s="106"/>
-      <c r="AZ60" s="106">
+      <c r="AY60" s="172"/>
+      <c r="AZ60" s="172">
         <f>$AT$62/AX60</f>
         <v>1.0505969300739058</v>
       </c>
@@ -3222,10 +3575,10 @@
         <f>0.5-AV60</f>
         <v>0.4375</v>
       </c>
-      <c r="AW61" s="106"/>
-      <c r="AX61" s="106"/>
-      <c r="AY61" s="106"/>
-      <c r="AZ61" s="106"/>
+      <c r="AW61" s="172"/>
+      <c r="AX61" s="172"/>
+      <c r="AY61" s="172"/>
+      <c r="AZ61" s="172"/>
     </row>
     <row r="62" spans="31:52" x14ac:dyDescent="0.2">
       <c r="AS62">
@@ -3238,10 +3591,10 @@
       <c r="AV62">
         <v>0.5</v>
       </c>
-      <c r="AW62" s="106"/>
-      <c r="AX62" s="106"/>
-      <c r="AY62" s="106"/>
-      <c r="AZ62" s="106"/>
+      <c r="AW62" s="172"/>
+      <c r="AX62" s="172"/>
+      <c r="AY62" s="172"/>
+      <c r="AZ62" s="172"/>
     </row>
     <row r="63" spans="31:52" x14ac:dyDescent="0.2">
       <c r="AW63" s="23"/>
@@ -3710,7 +4063,7 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B3" s="123" t="s">
+      <c r="B3" s="189" t="s">
         <v>96</v>
       </c>
       <c r="C3" s="11" t="s">
@@ -3718,7 +4071,7 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="123"/>
+      <c r="B4" s="189"/>
       <c r="C4" s="11" t="s">
         <v>98</v>
       </c>
@@ -3822,7 +4175,7 @@
       <c r="F10" s="12"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B11" s="123" t="s">
+      <c r="B11" s="189" t="s">
         <v>96</v>
       </c>
       <c r="C11" s="11" t="s">
@@ -3830,7 +4183,7 @@
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B12" s="123"/>
+      <c r="B12" s="189"/>
       <c r="C12" s="11" t="s">
         <v>98</v>
       </c>
@@ -3930,7 +4283,7 @@
       <c r="G16" s="12"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B18" s="123" t="s">
+      <c r="B18" s="189" t="s">
         <v>96</v>
       </c>
       <c r="C18" s="11" t="s">
@@ -3938,7 +4291,7 @@
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B19" s="123"/>
+      <c r="B19" s="189"/>
       <c r="C19" s="39" t="s">
         <v>103</v>
       </c>
@@ -4238,7 +4591,7 @@
       </c>
     </row>
     <row r="49" spans="9:13" x14ac:dyDescent="0.2">
-      <c r="I49" s="123" t="s">
+      <c r="I49" s="189" t="s">
         <v>96</v>
       </c>
       <c r="J49" s="11" t="s">
@@ -4246,7 +4599,7 @@
       </c>
     </row>
     <row r="50" spans="9:13" x14ac:dyDescent="0.2">
-      <c r="I50" s="123"/>
+      <c r="I50" s="189"/>
       <c r="J50" s="11" t="s">
         <v>134</v>
       </c>
@@ -4430,10 +4783,10 @@
     </row>
     <row r="73" spans="9:23" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="74" spans="9:23" x14ac:dyDescent="0.2">
-      <c r="Q74" s="122" t="s">
+      <c r="Q74" s="188" t="s">
         <v>149</v>
       </c>
-      <c r="R74" s="122" t="s">
+      <c r="R74" s="188" t="s">
         <v>96</v>
       </c>
       <c r="S74" s="11" t="s">
@@ -4441,15 +4794,15 @@
       </c>
     </row>
     <row r="75" spans="9:23" x14ac:dyDescent="0.2">
-      <c r="Q75" s="122"/>
-      <c r="R75" s="122"/>
+      <c r="Q75" s="188"/>
+      <c r="R75" s="188"/>
       <c r="S75" s="11" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="76" spans="9:23" x14ac:dyDescent="0.2">
-      <c r="Q76" s="122"/>
-      <c r="R76" s="122"/>
+      <c r="Q76" s="188"/>
+      <c r="R76" s="188"/>
       <c r="S76" s="11">
         <v>12</v>
       </c>
@@ -4560,10 +4913,10 @@
       <c r="U81" s="12"/>
     </row>
     <row r="83" spans="17:23" x14ac:dyDescent="0.2">
-      <c r="Q83" s="122" t="s">
+      <c r="Q83" s="188" t="s">
         <v>149</v>
       </c>
-      <c r="R83" s="122" t="s">
+      <c r="R83" s="188" t="s">
         <v>96</v>
       </c>
       <c r="S83" s="11" t="s">
@@ -4571,15 +4924,15 @@
       </c>
     </row>
     <row r="84" spans="17:23" x14ac:dyDescent="0.2">
-      <c r="Q84" s="122"/>
-      <c r="R84" s="122"/>
+      <c r="Q84" s="188"/>
+      <c r="R84" s="188"/>
       <c r="S84" s="11" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="85" spans="17:23" x14ac:dyDescent="0.2">
-      <c r="Q85" s="122"/>
-      <c r="R85" s="122"/>
+      <c r="Q85" s="188"/>
+      <c r="R85" s="188"/>
       <c r="S85" s="39" t="s">
         <v>103</v>
       </c>
@@ -4872,16 +5225,16 @@
       </c>
     </row>
     <row r="116" spans="25:29" x14ac:dyDescent="0.2">
-      <c r="Y116" s="124" t="s">
+      <c r="Y116" s="190" t="s">
         <v>158</v>
       </c>
-      <c r="Z116" s="124"/>
-      <c r="AA116" s="124"/>
-      <c r="AB116" s="124"/>
-      <c r="AC116" s="124"/>
+      <c r="Z116" s="190"/>
+      <c r="AA116" s="190"/>
+      <c r="AB116" s="190"/>
+      <c r="AC116" s="190"/>
     </row>
     <row r="117" spans="25:29" x14ac:dyDescent="0.2">
-      <c r="Y117" s="123" t="s">
+      <c r="Y117" s="189" t="s">
         <v>96</v>
       </c>
       <c r="Z117" s="11" t="s">
@@ -4889,7 +5242,7 @@
       </c>
     </row>
     <row r="118" spans="25:29" x14ac:dyDescent="0.2">
-      <c r="Y118" s="123"/>
+      <c r="Y118" s="189"/>
       <c r="Z118" s="11">
         <v>12</v>
       </c>
@@ -4959,7 +5312,7 @@
       <c r="AB122" s="12"/>
     </row>
     <row r="124" spans="25:29" x14ac:dyDescent="0.2">
-      <c r="Y124" s="123" t="s">
+      <c r="Y124" s="189" t="s">
         <v>96</v>
       </c>
       <c r="Z124" s="11" t="s">
@@ -4967,7 +5320,7 @@
       </c>
     </row>
     <row r="125" spans="25:29" x14ac:dyDescent="0.2">
-      <c r="Y125" s="123"/>
+      <c r="Y125" s="189"/>
       <c r="Z125" s="40" t="s">
         <v>103</v>
       </c>
@@ -5191,15 +5544,15 @@
       <c r="Y148" s="3"/>
     </row>
     <row r="150" spans="25:28" x14ac:dyDescent="0.2">
-      <c r="Y150" s="108" t="s">
+      <c r="Y150" s="174" t="s">
         <v>173</v>
       </c>
-      <c r="Z150" s="108"/>
-      <c r="AA150" s="108"/>
-      <c r="AB150" s="108"/>
+      <c r="Z150" s="174"/>
+      <c r="AA150" s="174"/>
+      <c r="AB150" s="174"/>
     </row>
     <row r="151" spans="25:28" x14ac:dyDescent="0.2">
-      <c r="Y151" s="121" t="s">
+      <c r="Y151" s="187" t="s">
         <v>96</v>
       </c>
       <c r="Z151" s="11" t="s">
@@ -5207,7 +5560,7 @@
       </c>
     </row>
     <row r="152" spans="25:28" x14ac:dyDescent="0.2">
-      <c r="Y152" s="121"/>
+      <c r="Y152" s="187"/>
       <c r="Z152" s="40" t="s">
         <v>103</v>
       </c>
@@ -5648,15 +6001,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B2" s="107"/>
-      <c r="C2" s="126" t="s">
+      <c r="B2" s="173"/>
+      <c r="C2" s="192" t="s">
         <v>187</v>
       </c>
-      <c r="D2" s="126"/>
-      <c r="E2" s="126"/>
+      <c r="D2" s="192"/>
+      <c r="E2" s="192"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B3" s="107"/>
+      <c r="B3" s="173"/>
       <c r="C3" s="70">
         <v>2021</v>
       </c>
@@ -5780,18 +6133,18 @@
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B13" s="107"/>
-      <c r="C13" s="126" t="s">
+      <c r="B13" s="173"/>
+      <c r="C13" s="192" t="s">
         <v>187</v>
       </c>
-      <c r="D13" s="126"/>
-      <c r="E13" s="126"/>
+      <c r="D13" s="192"/>
+      <c r="E13" s="192"/>
       <c r="H13" s="15" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B14" s="107"/>
+      <c r="B14" s="173"/>
       <c r="C14" s="70">
         <v>2021</v>
       </c>
@@ -5965,13 +6318,13 @@
       </c>
     </row>
     <row r="20" spans="2:12" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="125" t="s">
+      <c r="B20" s="191" t="s">
         <v>223</v>
       </c>
-      <c r="C20" s="125"/>
-      <c r="D20" s="125"/>
-      <c r="E20" s="125"/>
-      <c r="F20" s="125"/>
+      <c r="C20" s="191"/>
+      <c r="D20" s="191"/>
+      <c r="E20" s="191"/>
+      <c r="F20" s="191"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
@@ -6110,11 +6463,11 @@
       </c>
     </row>
     <row r="33" spans="17:26" x14ac:dyDescent="0.2">
-      <c r="Q33" s="107"/>
-      <c r="R33" s="126" t="s">
+      <c r="Q33" s="173"/>
+      <c r="R33" s="192" t="s">
         <v>187</v>
       </c>
-      <c r="S33" s="126"/>
+      <c r="S33" s="192"/>
       <c r="U33" s="15" t="s">
         <v>232</v>
       </c>
@@ -6130,7 +6483,7 @@
       </c>
     </row>
     <row r="34" spans="17:26" x14ac:dyDescent="0.2">
-      <c r="Q34" s="107"/>
+      <c r="Q34" s="173"/>
       <c r="R34" s="70">
         <v>2003</v>
       </c>
@@ -6879,120 +7232,120 @@
         <v>301</v>
       </c>
     </row>
-    <row r="2" spans="2:10" s="127" customFormat="1" ht="34" x14ac:dyDescent="0.2">
-      <c r="B2" s="132" t="s">
+    <row r="2" spans="2:10" s="106" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="B2" s="111" t="s">
         <v>283</v>
       </c>
-      <c r="C2" s="133" t="s">
+      <c r="C2" s="112" t="s">
         <v>284</v>
       </c>
-      <c r="D2" s="134" t="s">
+      <c r="D2" s="113" t="s">
         <v>149</v>
       </c>
-      <c r="E2" s="132" t="s">
+      <c r="E2" s="111" t="s">
         <v>292</v>
       </c>
-      <c r="F2" s="133" t="s">
+      <c r="F2" s="112" t="s">
         <v>165</v>
       </c>
-      <c r="G2" s="133" t="s">
+      <c r="G2" s="112" t="s">
         <v>297</v>
       </c>
-      <c r="H2" s="133" t="s">
+      <c r="H2" s="112" t="s">
         <v>291</v>
       </c>
-      <c r="I2" s="134" t="s">
+      <c r="I2" s="113" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B3" s="135">
+      <c r="B3" s="114">
         <v>2003</v>
       </c>
-      <c r="C3" s="136">
+      <c r="C3" s="100">
         <v>2000000</v>
       </c>
-      <c r="D3" s="137">
+      <c r="D3" s="115">
         <v>2000</v>
       </c>
-      <c r="E3" s="141">
+      <c r="E3" s="119">
         <v>48</v>
       </c>
-      <c r="F3" s="142">
+      <c r="F3" s="107">
         <v>1</v>
       </c>
-      <c r="G3" s="143">
+      <c r="G3" s="120">
         <f>C3*F3</f>
         <v>2000000</v>
       </c>
-      <c r="H3" s="144">
+      <c r="H3" s="121">
         <v>5.25</v>
       </c>
-      <c r="I3" s="152">
+      <c r="I3" s="128">
         <f>G3*(1+$H$7)^H3</f>
         <v>2202041.100392635</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B4" s="135">
+      <c r="B4" s="114">
         <v>2004</v>
       </c>
-      <c r="C4" s="136">
+      <c r="C4" s="100">
         <v>2300000</v>
       </c>
-      <c r="D4" s="137">
+      <c r="D4" s="115">
         <v>2300</v>
       </c>
-      <c r="E4" s="141">
+      <c r="E4" s="119">
         <v>36</v>
       </c>
-      <c r="F4" s="142">
+      <c r="F4" s="107">
         <v>1.05</v>
       </c>
-      <c r="G4" s="143">
+      <c r="G4" s="120">
         <f>C4*F4</f>
         <v>2415000</v>
       </c>
-      <c r="H4" s="145">
+      <c r="H4" s="38">
         <f>H3-1</f>
         <v>4.25</v>
       </c>
-      <c r="I4" s="152">
+      <c r="I4" s="128">
         <f>G4*(1+$H$7)^H4</f>
         <v>2610667.2839706494</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B5" s="138">
+      <c r="B5" s="116">
         <v>2005</v>
       </c>
-      <c r="C5" s="139">
+      <c r="C5" s="117">
         <v>1900000</v>
       </c>
-      <c r="D5" s="140">
+      <c r="D5" s="118">
         <v>1900</v>
       </c>
-      <c r="E5" s="146">
+      <c r="E5" s="122">
         <v>24</v>
       </c>
-      <c r="F5" s="147">
+      <c r="F5" s="123">
         <v>1.2</v>
       </c>
-      <c r="G5" s="148">
+      <c r="G5" s="124">
         <f>C5*F5</f>
         <v>2280000</v>
       </c>
-      <c r="H5" s="149">
+      <c r="H5" s="125">
         <f>H4-1</f>
         <v>3.25</v>
       </c>
-      <c r="I5" s="153">
+      <c r="I5" s="129">
         <f>G5*(1+$H$7)^H5</f>
         <v>2419960.0994248562</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="E6" s="129" t="s">
+      <c r="E6" s="108" t="s">
         <v>299</v>
       </c>
     </row>
@@ -7018,7 +7371,7 @@
       <c r="B8" s="71" t="s">
         <v>287</v>
       </c>
-      <c r="C8" s="128">
+      <c r="C8" s="107">
         <v>1.4</v>
       </c>
     </row>
@@ -7026,13 +7379,13 @@
       <c r="B9" s="71" t="s">
         <v>288</v>
       </c>
-      <c r="C9" s="128">
+      <c r="C9" s="107">
         <v>1.2</v>
       </c>
       <c r="H9" s="15" t="s">
         <v>303</v>
       </c>
-      <c r="I9" s="151">
+      <c r="I9" s="127">
         <f>SUM(I3:I5)/SUM(D3:D5)</f>
         <v>1166.5594328690549</v>
       </c>
@@ -7044,7 +7397,7 @@
       <c r="B10" s="71" t="s">
         <v>289</v>
       </c>
-      <c r="C10" s="128">
+      <c r="C10" s="107">
         <v>1.05</v>
       </c>
     </row>
@@ -7052,13 +7405,13 @@
       <c r="B11" s="71" t="s">
         <v>290</v>
       </c>
-      <c r="C11" s="128">
+      <c r="C11" s="107">
         <v>1</v>
       </c>
       <c r="H11" s="15" t="s">
         <v>305</v>
       </c>
-      <c r="I11" s="151">
+      <c r="I11" s="127">
         <f>(I9+C22)/(1-SUM(C18:C21))</f>
         <v>1582.0792438254066</v>
       </c>
@@ -7070,7 +7423,7 @@
       <c r="B13" s="70" t="s">
         <v>294</v>
       </c>
-      <c r="C13" s="130" t="s">
+      <c r="C13" s="109" t="s">
         <v>108</v>
       </c>
     </row>
@@ -7078,7 +7431,7 @@
       <c r="B14" s="71" t="s">
         <v>295</v>
       </c>
-      <c r="C14" s="131">
+      <c r="C14" s="110">
         <v>0.05</v>
       </c>
     </row>
@@ -7086,7 +7439,7 @@
       <c r="B15" s="71" t="s">
         <v>296</v>
       </c>
-      <c r="C15" s="131">
+      <c r="C15" s="110">
         <v>-0.03</v>
       </c>
     </row>
@@ -7134,7 +7487,7 @@
       <c r="B22" t="s">
         <v>311</v>
       </c>
-      <c r="C22" s="150">
+      <c r="C22" s="126">
         <v>20</v>
       </c>
     </row>
@@ -7145,9 +7498,1398 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D40ABDFF-5D42-FA49-91E6-920BDEC7DF05}">
-  <dimension ref="A1"/>
+  <dimension ref="B2:X42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5" customWidth="1"/>
+    <col min="9" max="9" width="33.1640625" customWidth="1"/>
+    <col min="10" max="10" width="34" customWidth="1"/>
+    <col min="11" max="11" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.83203125" customWidth="1"/>
+    <col min="13" max="13" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22.1640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="18.83203125" customWidth="1"/>
+    <col min="24" max="24" width="26.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="I2" s="193" t="s">
+        <v>329</v>
+      </c>
+      <c r="J2" s="193"/>
+      <c r="K2" s="193"/>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="J3" s="192" t="s">
+        <v>317</v>
+      </c>
+      <c r="K3" s="192"/>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B4" s="139" t="s">
+        <v>320</v>
+      </c>
+      <c r="C4" s="196" t="s">
+        <v>314</v>
+      </c>
+      <c r="D4" s="197"/>
+      <c r="E4" s="197"/>
+      <c r="F4" s="194" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="70" t="s">
+        <v>314</v>
+      </c>
+      <c r="I4" s="70" t="s">
+        <v>108</v>
+      </c>
+      <c r="J4" s="70" t="s">
+        <v>315</v>
+      </c>
+      <c r="K4" s="70" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B5" s="139" t="s">
+        <v>317</v>
+      </c>
+      <c r="C5" s="137">
+        <v>1</v>
+      </c>
+      <c r="D5" s="137">
+        <v>2</v>
+      </c>
+      <c r="E5" s="137">
+        <v>3</v>
+      </c>
+      <c r="F5" s="195"/>
+      <c r="H5" s="71">
+        <v>1</v>
+      </c>
+      <c r="I5" s="22">
+        <f>_xlfn.XLOOKUP(H5,$B$15:$B$17,$C$15:$C$17)</f>
+        <v>0.6</v>
+      </c>
+      <c r="J5" s="22" cm="1">
+        <f t="array" ref="J5">_xlfn.XLOOKUP($H5,$C$5:$E$5,_xlfn.XLOOKUP(J$4,$B$6:$B$7,$C$6:$E$7))</f>
+        <v>123</v>
+      </c>
+      <c r="K5" s="22" cm="1">
+        <f t="array" ref="K5">_xlfn.XLOOKUP($H5,$C$5:$E$5,_xlfn.XLOOKUP(K$4,$B$6:$B$7,$C$6:$E$7))</f>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B6" s="133" t="s">
+        <v>315</v>
+      </c>
+      <c r="C6" s="135">
+        <v>123</v>
+      </c>
+      <c r="D6" s="135">
+        <v>79</v>
+      </c>
+      <c r="E6" s="135">
+        <v>87</v>
+      </c>
+      <c r="F6" s="147">
+        <f>SUM(C6:E6)</f>
+        <v>289</v>
+      </c>
+      <c r="H6" s="71">
+        <v>2</v>
+      </c>
+      <c r="I6" s="22">
+        <f t="shared" ref="I6:I7" si="0">_xlfn.XLOOKUP(H6,$B$15:$B$17,$C$15:$C$17)</f>
+        <v>1</v>
+      </c>
+      <c r="J6" s="22" cm="1">
+        <f t="array" ref="J6">_xlfn.XLOOKUP($H6,$C$5:$E$5,_xlfn.XLOOKUP(J$4,$B$6:$B$7,$C$6:$E$7))</f>
+        <v>79</v>
+      </c>
+      <c r="K6" s="22" cm="1">
+        <f t="array" ref="K6">_xlfn.XLOOKUP($H6,$C$5:$E$5,_xlfn.XLOOKUP(K$4,$B$6:$B$7,$C$6:$E$7))</f>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B7" s="133" t="s">
+        <v>316</v>
+      </c>
+      <c r="C7" s="71">
+        <v>74</v>
+      </c>
+      <c r="D7" s="71">
+        <v>123</v>
+      </c>
+      <c r="E7" s="71">
+        <v>33</v>
+      </c>
+      <c r="F7" s="147">
+        <f>SUM(C7:E7)</f>
+        <v>230</v>
+      </c>
+      <c r="H7" s="131">
+        <v>3</v>
+      </c>
+      <c r="I7" s="145">
+        <f t="shared" si="0"/>
+        <v>0.9</v>
+      </c>
+      <c r="J7" s="145" cm="1">
+        <f t="array" ref="J7">_xlfn.XLOOKUP($H7,$C$5:$E$5,_xlfn.XLOOKUP(J$4,$B$6:$B$7,$C$6:$E$7))</f>
+        <v>87</v>
+      </c>
+      <c r="K7" s="145" cm="1">
+        <f t="array" ref="K7">_xlfn.XLOOKUP($H7,$C$5:$E$5,_xlfn.XLOOKUP(K$4,$B$6:$B$7,$C$6:$E$7))</f>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B8" s="139" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="146">
+        <f>SUM(C6:C7)</f>
+        <v>197</v>
+      </c>
+      <c r="D8" s="146">
+        <f t="shared" ref="D8:F8" si="1">SUM(D6:D7)</f>
+        <v>202</v>
+      </c>
+      <c r="E8" s="146">
+        <f t="shared" si="1"/>
+        <v>120</v>
+      </c>
+      <c r="F8" s="138">
+        <f t="shared" si="1"/>
+        <v>519</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>322</v>
+      </c>
+      <c r="J8" s="43">
+        <f>SUMPRODUCT($I$5:$I$7,J5:J7)/SUM(J5:J7)</f>
+        <v>0.79965397923875436</v>
+      </c>
+      <c r="K8" s="43">
+        <f>SUMPRODUCT($I$5:$I$7,K5:K7)/SUM(K5:K7)</f>
+        <v>0.85695652173913039</v>
+      </c>
+      <c r="L8" s="36" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="I9" s="15"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="43"/>
+      <c r="L9" s="36"/>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B10" s="140" t="s">
+        <v>317</v>
+      </c>
+      <c r="C10" s="141" t="s">
+        <v>318</v>
+      </c>
+      <c r="D10" s="71"/>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B11" s="114" t="s">
+        <v>315</v>
+      </c>
+      <c r="C11" s="130">
+        <v>1</v>
+      </c>
+      <c r="D11" s="71"/>
+      <c r="I11" s="193" t="s">
+        <v>329</v>
+      </c>
+      <c r="J11" s="193"/>
+      <c r="K11" s="36" t="s">
+        <v>330</v>
+      </c>
+      <c r="L11" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="M11" s="36" t="s">
+        <v>331</v>
+      </c>
+      <c r="N11" s="36" t="s">
+        <v>332</v>
+      </c>
+      <c r="O11" s="36" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B12" s="116" t="s">
+        <v>316</v>
+      </c>
+      <c r="C12" s="132">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="D12" s="71"/>
+      <c r="H12" s="70" t="s">
+        <v>317</v>
+      </c>
+      <c r="I12" s="70" t="s">
+        <v>320</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>322</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="N12" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="O12" s="15" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B13" s="71"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="H13" s="71" t="s">
+        <v>315</v>
+      </c>
+      <c r="I13" s="22">
+        <f>_xlfn.XLOOKUP(H13,$B$6:$B$7,$F$6:$F$7)</f>
+        <v>289</v>
+      </c>
+      <c r="J13" s="43">
+        <f>_xlfn.XLOOKUP(H13,$J$4:$K$4,$J$8:$K$8)</f>
+        <v>0.79965397923875436</v>
+      </c>
+      <c r="K13" s="22">
+        <f>I13*J13</f>
+        <v>231.10000000000002</v>
+      </c>
+      <c r="L13" s="155">
+        <f>_xlfn.XLOOKUP(H13,$B$30:$B$31,$F$30:$F$31)</f>
+        <v>24300</v>
+      </c>
+      <c r="M13" s="156">
+        <f>L13/K13</f>
+        <v>105.1492860233665</v>
+      </c>
+      <c r="N13" s="43">
+        <f>M13/$M$15</f>
+        <v>0.90049848550411082</v>
+      </c>
+      <c r="O13" s="43">
+        <f>N13/$N$13</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B14" s="140" t="s">
+        <v>314</v>
+      </c>
+      <c r="C14" s="141" t="s">
+        <v>318</v>
+      </c>
+      <c r="H14" s="131" t="s">
+        <v>316</v>
+      </c>
+      <c r="I14" s="145">
+        <f>_xlfn.XLOOKUP(H14,$B$6:$B$7,$F$6:$F$7)</f>
+        <v>230</v>
+      </c>
+      <c r="J14" s="157">
+        <f>_xlfn.XLOOKUP(H14,$J$4:$K$4,$J$8:$K$8)</f>
+        <v>0.85695652173913039</v>
+      </c>
+      <c r="K14" s="145">
+        <f>I14*J14</f>
+        <v>197.1</v>
+      </c>
+      <c r="L14" s="158">
+        <f>_xlfn.XLOOKUP(H14,$B$30:$B$31,$F$30:$F$31)</f>
+        <v>25700</v>
+      </c>
+      <c r="M14" s="159">
+        <f>L14/K14</f>
+        <v>130.39066463723998</v>
+      </c>
+      <c r="N14" s="157">
+        <f t="shared" ref="N14:N15" si="2">M14/$M$15</f>
+        <v>1.1166656519533233</v>
+      </c>
+      <c r="O14" s="160">
+        <f>N14/$N$13</f>
+        <v>1.2400527817969613</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B15" s="114">
+        <v>1</v>
+      </c>
+      <c r="C15" s="130">
+        <v>0.6</v>
+      </c>
+      <c r="H15" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" s="22">
+        <f>SUM(I13:I14)</f>
+        <v>519</v>
+      </c>
+      <c r="K15" s="22">
+        <f>SUM(K13:K14)</f>
+        <v>428.20000000000005</v>
+      </c>
+      <c r="L15" s="155">
+        <f>SUM(L13:L14)</f>
+        <v>50000</v>
+      </c>
+      <c r="M15" s="156">
+        <f>L15/K15</f>
+        <v>116.76786548341894</v>
+      </c>
+      <c r="N15" s="43">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O15" s="43">
+        <f>N15/$N$13</f>
+        <v>1.1104960375809927</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B16" s="114">
+        <v>2</v>
+      </c>
+      <c r="C16" s="130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B17" s="116">
+        <v>3</v>
+      </c>
+      <c r="C17" s="132">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B19" s="140" t="s">
+        <v>314</v>
+      </c>
+      <c r="C19" s="144" t="s">
+        <v>317</v>
+      </c>
+      <c r="D19" s="141" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B20" s="114">
+        <v>1</v>
+      </c>
+      <c r="C20" s="71" t="s">
+        <v>315</v>
+      </c>
+      <c r="D20" s="142">
+        <v>7760</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B21" s="114">
+        <v>1</v>
+      </c>
+      <c r="C21" s="71" t="s">
+        <v>316</v>
+      </c>
+      <c r="D21" s="142">
+        <v>5789</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B22" s="114">
+        <v>2</v>
+      </c>
+      <c r="C22" s="71" t="s">
+        <v>315</v>
+      </c>
+      <c r="D22" s="142">
+        <v>8307</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B23" s="114">
+        <v>2</v>
+      </c>
+      <c r="C23" s="71" t="s">
+        <v>316</v>
+      </c>
+      <c r="D23" s="142">
+        <v>16038</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B24" s="114">
+        <v>3</v>
+      </c>
+      <c r="C24" s="71" t="s">
+        <v>315</v>
+      </c>
+      <c r="D24" s="142">
+        <v>8233</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B25" s="116">
+        <v>3</v>
+      </c>
+      <c r="C25" s="131" t="s">
+        <v>316</v>
+      </c>
+      <c r="D25" s="143">
+        <v>3873</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B26" s="71"/>
+      <c r="C26" s="71"/>
+      <c r="D26" s="72"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="C27" s="154" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B28" s="139" t="s">
+        <v>319</v>
+      </c>
+      <c r="C28" s="196" t="s">
+        <v>314</v>
+      </c>
+      <c r="D28" s="197"/>
+      <c r="E28" s="197"/>
+      <c r="F28" s="194" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B29" s="140" t="s">
+        <v>317</v>
+      </c>
+      <c r="C29" s="140">
+        <v>1</v>
+      </c>
+      <c r="D29" s="144">
+        <v>2</v>
+      </c>
+      <c r="E29" s="141">
+        <v>3</v>
+      </c>
+      <c r="F29" s="198"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B30" s="148" t="s">
+        <v>315</v>
+      </c>
+      <c r="C30" s="68">
+        <f t="shared" ref="C30:E31" si="3">SUMIFS($D$20:$D$25,$B$20:$B$25,C$29,$C$20:$C$25,$B30)</f>
+        <v>7760</v>
+      </c>
+      <c r="D30" s="68">
+        <f t="shared" si="3"/>
+        <v>8307</v>
+      </c>
+      <c r="E30" s="68">
+        <f t="shared" si="3"/>
+        <v>8233</v>
+      </c>
+      <c r="F30" s="149">
+        <f>SUM(C30:E30)</f>
+        <v>24300</v>
+      </c>
+      <c r="G30" s="36" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B31" s="134" t="s">
+        <v>316</v>
+      </c>
+      <c r="C31" s="68">
+        <f t="shared" si="3"/>
+        <v>5789</v>
+      </c>
+      <c r="D31" s="68">
+        <f t="shared" si="3"/>
+        <v>16038</v>
+      </c>
+      <c r="E31" s="68">
+        <f t="shared" si="3"/>
+        <v>3873</v>
+      </c>
+      <c r="F31" s="150">
+        <f>SUM(C31:E31)</f>
+        <v>25700</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B32" s="136" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="151">
+        <f>SUM(C30:C31)</f>
+        <v>13549</v>
+      </c>
+      <c r="D32" s="152">
+        <f t="shared" ref="D32" si="4">SUM(D30:D31)</f>
+        <v>24345</v>
+      </c>
+      <c r="E32" s="152">
+        <f t="shared" ref="E32" si="5">SUM(E30:E31)</f>
+        <v>12106</v>
+      </c>
+      <c r="F32" s="153">
+        <f t="shared" ref="F32" si="6">SUM(F30:F31)</f>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="33" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="C33" s="36" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="35" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="T35" s="36" t="s">
+        <v>344</v>
+      </c>
+      <c r="U35" s="36" t="s">
+        <v>345</v>
+      </c>
+      <c r="V35" s="36" t="s">
+        <v>348</v>
+      </c>
+      <c r="W35" s="36" t="s">
+        <v>349</v>
+      </c>
+      <c r="X35" s="36" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="36" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="P36" s="70" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q36" s="161" t="s">
+        <v>340</v>
+      </c>
+      <c r="R36" s="70" t="s">
+        <v>339</v>
+      </c>
+      <c r="S36" s="70" t="s">
+        <v>338</v>
+      </c>
+      <c r="T36" s="70" t="s">
+        <v>341</v>
+      </c>
+      <c r="U36" s="70" t="s">
+        <v>346</v>
+      </c>
+      <c r="V36" s="70" t="s">
+        <v>347</v>
+      </c>
+      <c r="W36" s="70" t="s">
+        <v>325</v>
+      </c>
+      <c r="X36" s="70" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="37" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="P37" s="71" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q37" s="165">
+        <v>110</v>
+      </c>
+      <c r="R37" s="165">
+        <v>575000</v>
+      </c>
+      <c r="S37" s="165">
+        <v>330000</v>
+      </c>
+      <c r="T37" s="94">
+        <f>S37/R37</f>
+        <v>0.57391304347826089</v>
+      </c>
+      <c r="U37" s="43">
+        <f>T37/$T$41</f>
+        <v>0.88104664402173916</v>
+      </c>
+      <c r="V37" s="43">
+        <f>Q37/$Q$37</f>
+        <v>1</v>
+      </c>
+      <c r="W37" s="43">
+        <f>U37*V37</f>
+        <v>0.88104664402173916</v>
+      </c>
+      <c r="X37" s="164">
+        <f>W37/$W$37</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="P38" s="71" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q38" s="165">
+        <v>55</v>
+      </c>
+      <c r="R38" s="165">
+        <v>716667</v>
+      </c>
+      <c r="S38" s="165">
+        <v>525000</v>
+      </c>
+      <c r="T38" s="94">
+        <f t="shared" ref="T38:T41" si="7">S38/R38</f>
+        <v>0.73255779881032612</v>
+      </c>
+      <c r="U38" s="43">
+        <f t="shared" ref="U38:U40" si="8">T38/$T$41</f>
+        <v>1.1245912556406952</v>
+      </c>
+      <c r="V38" s="43">
+        <f t="shared" ref="V38:V40" si="9">Q38/$Q$37</f>
+        <v>0.5</v>
+      </c>
+      <c r="W38" s="43">
+        <f t="shared" ref="W38:W40" si="10">U38*V38</f>
+        <v>0.56229562782034759</v>
+      </c>
+      <c r="X38" s="164">
+        <f t="shared" ref="X38:X40" si="11">W38/$W$37</f>
+        <v>0.63821323381202666</v>
+      </c>
+    </row>
+    <row r="39" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="P39" s="71" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q39" s="165">
+        <v>100</v>
+      </c>
+      <c r="R39" s="165">
+        <v>416667</v>
+      </c>
+      <c r="S39" s="165">
+        <v>290000</v>
+      </c>
+      <c r="T39" s="94">
+        <f t="shared" si="7"/>
+        <v>0.69599944320044549</v>
+      </c>
+      <c r="U39" s="43">
+        <f t="shared" si="8"/>
+        <v>1.068468438975249</v>
+      </c>
+      <c r="V39" s="43">
+        <f t="shared" si="9"/>
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="W39" s="43">
+        <f t="shared" si="10"/>
+        <v>0.97133494452295366</v>
+      </c>
+      <c r="X39" s="164">
+        <f t="shared" si="11"/>
+        <v>1.10247845686021</v>
+      </c>
+    </row>
+    <row r="40" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="P40" s="131" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q40" s="166">
+        <v>160</v>
+      </c>
+      <c r="R40" s="166">
+        <v>256667</v>
+      </c>
+      <c r="S40" s="166">
+        <v>135000</v>
+      </c>
+      <c r="T40" s="163">
+        <f t="shared" si="7"/>
+        <v>0.52597334289176245</v>
+      </c>
+      <c r="U40" s="157">
+        <f t="shared" si="8"/>
+        <v>0.80745167559035635</v>
+      </c>
+      <c r="V40" s="157">
+        <f t="shared" si="9"/>
+        <v>1.4545454545454546</v>
+      </c>
+      <c r="W40" s="157">
+        <f t="shared" si="10"/>
+        <v>1.1744751644950637</v>
+      </c>
+      <c r="X40" s="160">
+        <f t="shared" si="11"/>
+        <v>1.3330453869433097</v>
+      </c>
+    </row>
+    <row r="41" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="P41" s="162" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q41" s="22"/>
+      <c r="R41" s="155">
+        <f>SUM(R37:R40)</f>
+        <v>1965001</v>
+      </c>
+      <c r="S41" s="155">
+        <f>SUM(S37:S40)</f>
+        <v>1280000</v>
+      </c>
+      <c r="T41" s="94">
+        <f t="shared" si="7"/>
+        <v>0.65139915959330297</v>
+      </c>
+      <c r="U41" s="43">
+        <f>T41/$T$41</f>
+        <v>1</v>
+      </c>
+      <c r="V41" s="43"/>
+      <c r="W41" s="43"/>
+    </row>
+    <row r="42" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="R42" s="36" t="s">
+        <v>342</v>
+      </c>
+      <c r="S42" s="36" t="s">
+        <v>343</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="C4:E4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74A825C0-165C-2E40-9F26-17C3BD9140D6}">
+  <dimension ref="B2:AE46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="34" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="33" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="29" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="29.1640625" customWidth="1"/>
+    <col min="19" max="19" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="26.83203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="41.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="G2" s="36" t="s">
+        <v>359</v>
+      </c>
+      <c r="H2" s="36" t="s">
+        <v>360</v>
+      </c>
+      <c r="I2" s="36" t="s">
+        <v>361</v>
+      </c>
+      <c r="J2" s="36" t="s">
+        <v>362</v>
+      </c>
+      <c r="K2" s="36" t="s">
+        <v>363</v>
+      </c>
+      <c r="L2" s="36" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B3" s="70" t="s">
+        <v>314</v>
+      </c>
+      <c r="C3" s="70" t="s">
+        <v>335</v>
+      </c>
+      <c r="D3" s="70" t="s">
+        <v>351</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="G3" s="70" t="s">
+        <v>341</v>
+      </c>
+      <c r="H3" s="70" t="s">
+        <v>346</v>
+      </c>
+      <c r="I3" s="70" t="s">
+        <v>353</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="L3" s="70" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B4" s="71">
+        <v>1</v>
+      </c>
+      <c r="C4" s="72">
+        <v>520000</v>
+      </c>
+      <c r="D4" s="72">
+        <v>420000</v>
+      </c>
+      <c r="E4" s="71">
+        <v>600</v>
+      </c>
+      <c r="F4" s="71">
+        <v>0.6</v>
+      </c>
+      <c r="G4" s="94">
+        <f>D4/C4</f>
+        <v>0.80769230769230771</v>
+      </c>
+      <c r="H4" s="43">
+        <f>G4/$G$7</f>
+        <v>1.0543766578249336</v>
+      </c>
+      <c r="I4" s="43">
+        <f>MIN(1,SQRT(E4/$C$9))</f>
+        <v>0.74466680511954475</v>
+      </c>
+      <c r="J4" s="43">
+        <f>I4*H4+(1-I4)*$C$10</f>
+        <v>1.040492492055572</v>
+      </c>
+      <c r="K4" s="43">
+        <f>F4*J4</f>
+        <v>0.62429549523334316</v>
+      </c>
+      <c r="L4" s="164">
+        <f>K4/$K$5</f>
+        <v>0.64274637190756034</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B5" s="71">
+        <v>2</v>
+      </c>
+      <c r="C5" s="72">
+        <v>1680000</v>
+      </c>
+      <c r="D5" s="72">
+        <v>1250000</v>
+      </c>
+      <c r="E5" s="100">
+        <v>1320</v>
+      </c>
+      <c r="F5" s="71">
+        <v>1</v>
+      </c>
+      <c r="G5" s="94">
+        <f t="shared" ref="G5:G7" si="0">D5/C5</f>
+        <v>0.74404761904761907</v>
+      </c>
+      <c r="H5" s="43">
+        <f t="shared" ref="H5:H7" si="1">G5/$G$7</f>
+        <v>0.97129368988974896</v>
+      </c>
+      <c r="I5" s="43">
+        <f>MIN(1,SQRT(E5/$C$9))</f>
+        <v>1</v>
+      </c>
+      <c r="J5" s="43">
+        <f>I5*H5+(1-I5)*$C$10</f>
+        <v>0.97129368988974896</v>
+      </c>
+      <c r="K5" s="43">
+        <f>F5*J5</f>
+        <v>0.97129368988974896</v>
+      </c>
+      <c r="L5" s="164">
+        <f t="shared" ref="L5:L6" si="2">K5/$K$5</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B6" s="131">
+        <v>3</v>
+      </c>
+      <c r="C6" s="167">
+        <v>450000</v>
+      </c>
+      <c r="D6" s="167">
+        <v>360000</v>
+      </c>
+      <c r="E6" s="131">
+        <v>390</v>
+      </c>
+      <c r="F6" s="131">
+        <v>0.52</v>
+      </c>
+      <c r="G6" s="163">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="H6" s="157">
+        <f t="shared" si="1"/>
+        <v>1.0443349753694582</v>
+      </c>
+      <c r="I6" s="157">
+        <f>MIN(1,SQRT(E6/$C$9))</f>
+        <v>0.60036957194757756</v>
+      </c>
+      <c r="J6" s="157">
+        <f>I6*H6+(1-I6)*$C$10</f>
+        <v>1.026617370184868</v>
+      </c>
+      <c r="K6" s="157">
+        <f>F6*J6</f>
+        <v>0.53384103249613135</v>
+      </c>
+      <c r="L6" s="160">
+        <f t="shared" si="2"/>
+        <v>0.54961855312446983</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B7" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="170">
+        <v>2650000</v>
+      </c>
+      <c r="D7" s="170">
+        <v>2030000</v>
+      </c>
+      <c r="E7" s="171">
+        <v>2310</v>
+      </c>
+      <c r="G7" s="94">
+        <f t="shared" si="0"/>
+        <v>0.76603773584905666</v>
+      </c>
+      <c r="H7" s="43">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B9" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="C9" s="168">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B10" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="C10" s="169">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <f>H4*F4</f>
+        <v>0.63262599469496017</v>
+      </c>
+      <c r="J10">
+        <f>I4*I10+(1-I4)*C10</f>
+        <v>0.72642877318552523</v>
+      </c>
+      <c r="K10">
+        <f>J10/$J$11</f>
+        <v>0.7478981699839744</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="I11">
+        <f t="shared" ref="I11:I12" si="3">H5*F5</f>
+        <v>0.97129368988974896</v>
+      </c>
+      <c r="J11">
+        <f t="shared" ref="J11:J12" si="4">I5*I11+(1-I5)*C11</f>
+        <v>0.97129368988974896</v>
+      </c>
+      <c r="K11">
+        <f>J11/$J$11</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="I12">
+        <f t="shared" si="3"/>
+        <v>0.54305418719211829</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="4"/>
+        <v>0.32603320990887169</v>
+      </c>
+      <c r="K12">
+        <f>J12/$J$11</f>
+        <v>0.33566902915417846</v>
+      </c>
+    </row>
+    <row r="17" spans="15:25" x14ac:dyDescent="0.2">
+      <c r="O17" s="200"/>
+      <c r="Q17" s="70"/>
+      <c r="R17" s="154" t="s">
+        <v>380</v>
+      </c>
+      <c r="S17" s="200"/>
+      <c r="T17" s="36" t="s">
+        <v>370</v>
+      </c>
+      <c r="U17" s="36" t="s">
+        <v>379</v>
+      </c>
+      <c r="V17" s="36" t="s">
+        <v>371</v>
+      </c>
+      <c r="W17" s="36" t="s">
+        <v>372</v>
+      </c>
+      <c r="X17" s="36" t="s">
+        <v>373</v>
+      </c>
+      <c r="Y17" s="36" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="18" spans="15:25" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O18" s="200" t="s">
+        <v>314</v>
+      </c>
+      <c r="P18" s="70" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q18" s="202" t="s">
+        <v>365</v>
+      </c>
+      <c r="R18" s="202" t="s">
+        <v>378</v>
+      </c>
+      <c r="S18" s="200" t="s">
+        <v>318</v>
+      </c>
+      <c r="T18" s="202" t="s">
+        <v>375</v>
+      </c>
+      <c r="U18" s="200" t="s">
+        <v>367</v>
+      </c>
+      <c r="V18" s="202" t="s">
+        <v>376</v>
+      </c>
+      <c r="W18" s="200" t="s">
+        <v>353</v>
+      </c>
+      <c r="X18" s="202" t="s">
+        <v>377</v>
+      </c>
+      <c r="Y18" s="200" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="19" spans="15:25" x14ac:dyDescent="0.2">
+      <c r="O19" s="71" t="s">
+        <v>38</v>
+      </c>
+      <c r="P19" s="100">
+        <v>20000</v>
+      </c>
+      <c r="Q19" s="72">
+        <v>500000</v>
+      </c>
+      <c r="R19" s="68">
+        <f>Q19*(1+P25)^$P$31</f>
+        <v>428687.49999999994</v>
+      </c>
+      <c r="S19" s="204">
+        <v>1</v>
+      </c>
+      <c r="T19" s="43">
+        <f>S19/$S$22</f>
+        <v>0.91954022988505757</v>
+      </c>
+      <c r="U19" s="92">
+        <f>R19/P19</f>
+        <v>21.434374999999996</v>
+      </c>
+      <c r="V19" s="43">
+        <f>U19/$U$22</f>
+        <v>0.96721427060565435</v>
+      </c>
+      <c r="W19" s="43">
+        <f>MIN(1, SQRT(P19/$P$30))</f>
+        <v>1</v>
+      </c>
+      <c r="X19" s="43">
+        <f>W19*V19+(1-W19)*T19</f>
+        <v>0.96721427060565435</v>
+      </c>
+      <c r="Y19" s="43">
+        <f>X19/$X$19</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="15:25" x14ac:dyDescent="0.2">
+      <c r="O20" s="71" t="s">
+        <v>39</v>
+      </c>
+      <c r="P20" s="100">
+        <v>5000</v>
+      </c>
+      <c r="Q20" s="72">
+        <v>125000</v>
+      </c>
+      <c r="R20" s="68">
+        <f t="shared" ref="R20:R21" si="5">Q20*(1+P26)^$P$31</f>
+        <v>125000</v>
+      </c>
+      <c r="S20" s="204">
+        <v>0.95</v>
+      </c>
+      <c r="T20" s="43">
+        <f t="shared" ref="T20:T22" si="6">S20/$S$22</f>
+        <v>0.87356321839080464</v>
+      </c>
+      <c r="U20" s="92">
+        <f t="shared" ref="U20:U21" si="7">R20/P20</f>
+        <v>25</v>
+      </c>
+      <c r="V20" s="43">
+        <f>U20/$U$22</f>
+        <v>1.128111118945216</v>
+      </c>
+      <c r="W20" s="43">
+        <f>MIN(1, SQRT(P20/$P$30))</f>
+        <v>0.67267279399631252</v>
+      </c>
+      <c r="X20" s="43">
+        <f t="shared" ref="X20:X21" si="8">W20*V20+(1-W20)*T20</f>
+        <v>1.044790665862636</v>
+      </c>
+      <c r="Y20" s="43">
+        <f t="shared" ref="Y20:Y22" si="9">X20/$X$19</f>
+        <v>1.0802060077219544</v>
+      </c>
+    </row>
+    <row r="21" spans="15:25" x14ac:dyDescent="0.2">
+      <c r="O21" s="131" t="s">
+        <v>336</v>
+      </c>
+      <c r="P21" s="117">
+        <v>15000</v>
+      </c>
+      <c r="Q21" s="167">
+        <v>250000</v>
+      </c>
+      <c r="R21" s="69">
+        <f t="shared" si="5"/>
+        <v>332750.00000000012</v>
+      </c>
+      <c r="S21" s="205">
+        <v>1.25</v>
+      </c>
+      <c r="T21" s="157">
+        <f t="shared" si="6"/>
+        <v>1.149425287356322</v>
+      </c>
+      <c r="U21" s="203">
+        <f t="shared" si="7"/>
+        <v>22.183333333333341</v>
+      </c>
+      <c r="V21" s="157">
+        <f t="shared" ref="V20:V22" si="10">U21/$U$22</f>
+        <v>1.0010105995440552</v>
+      </c>
+      <c r="W21" s="157">
+        <f>MIN(1, SQRT(P21/$P$30))</f>
+        <v>1</v>
+      </c>
+      <c r="X21" s="157">
+        <f t="shared" si="8"/>
+        <v>1.0010105995440552</v>
+      </c>
+      <c r="Y21" s="157">
+        <f t="shared" si="9"/>
+        <v>1.0349419254507464</v>
+      </c>
+    </row>
+    <row r="22" spans="15:25" x14ac:dyDescent="0.2">
+      <c r="O22" s="71" t="s">
+        <v>10</v>
+      </c>
+      <c r="P22" s="100">
+        <v>40000</v>
+      </c>
+      <c r="Q22" s="72">
+        <v>875000</v>
+      </c>
+      <c r="R22" s="68">
+        <f>SUM(R19:R21)</f>
+        <v>886437.50000000012</v>
+      </c>
+      <c r="S22" s="22">
+        <f>SUMPRODUCT(S19:S21,P19:P21)/P22</f>
+        <v>1.0874999999999999</v>
+      </c>
+      <c r="T22" s="43">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="U22" s="92">
+        <f>R22/P22</f>
+        <v>22.160937500000003</v>
+      </c>
+      <c r="V22" s="43">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="W22" s="43">
+        <f>MIN(1, SQRT(P22/$P$30))</f>
+        <v>1</v>
+      </c>
+      <c r="X22" s="22">
+        <f>W22*V22+(1-W22)*T22</f>
+        <v>1</v>
+      </c>
+      <c r="Y22" s="43">
+        <f>X22/$X$19</f>
+        <v>1.0338970695436656</v>
+      </c>
+    </row>
+    <row r="23" spans="15:25" x14ac:dyDescent="0.2">
+      <c r="R23" s="36" t="s">
+        <v>381</v>
+      </c>
+      <c r="S23" s="36" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="24" spans="15:25" x14ac:dyDescent="0.2">
+      <c r="O24" s="200" t="s">
+        <v>314</v>
+      </c>
+      <c r="P24" s="70" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="25" spans="15:25" x14ac:dyDescent="0.2">
+      <c r="O25" s="71" t="s">
+        <v>38</v>
+      </c>
+      <c r="P25" s="81">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="26" spans="15:25" x14ac:dyDescent="0.2">
+      <c r="O26" s="71" t="s">
+        <v>39</v>
+      </c>
+      <c r="P26" s="81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="15:25" x14ac:dyDescent="0.2">
+      <c r="O27" s="131" t="s">
+        <v>336</v>
+      </c>
+      <c r="P27" s="201">
+        <v>0.1</v>
+      </c>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="206"/>
+    </row>
+    <row r="28" spans="15:25" x14ac:dyDescent="0.2">
+      <c r="O28" s="71" t="s">
+        <v>10</v>
+      </c>
+      <c r="P28" s="81">
+        <v>0</v>
+      </c>
+      <c r="S28" s="63"/>
+    </row>
+    <row r="30" spans="15:25" x14ac:dyDescent="0.2">
+      <c r="O30" s="70" t="s">
+        <v>368</v>
+      </c>
+      <c r="P30" s="199">
+        <v>11050</v>
+      </c>
+    </row>
+    <row r="31" spans="15:25" x14ac:dyDescent="0.2">
+      <c r="O31" s="70" t="s">
+        <v>235</v>
+      </c>
+      <c r="P31" s="207">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="31:31" x14ac:dyDescent="0.2">
+      <c r="AE46" s="63"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/files/temp-work.xlsx
+++ b/files/temp-work.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/coltongearhart/Desktop/exam5/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F804E0-6658-9A40-ADBF-21AA3EB8EE78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8FEE72D-4904-2F4A-AB64-A63F10EB9C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17620" activeTab="8" xr2:uid="{BB8505BC-BCB7-B340-A120-C046C43AD7BD}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17620" activeTab="10" xr2:uid="{BB8505BC-BCB7-B340-A120-C046C43AD7BD}"/>
   </bookViews>
   <sheets>
     <sheet name="2.2.1" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,8 @@
     <sheet name="2.6.1" sheetId="7" r:id="rId7"/>
     <sheet name="3.1.3" sheetId="8" r:id="rId8"/>
     <sheet name="3.1.4" sheetId="9" r:id="rId9"/>
+    <sheet name="3.3.2" sheetId="11" r:id="rId10"/>
+    <sheet name="3.3.3" sheetId="12" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -66,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="466">
   <si>
     <t>Ratio to SAWW</t>
   </si>
@@ -1223,14 +1225,267 @@
   <si>
     <t>=SUM(R19:R21)</t>
   </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>Ground-up Uncensored Loss Amount</t>
+  </si>
+  <si>
+    <t>Basic limit</t>
+  </si>
+  <si>
+    <t>Increased limit</t>
+  </si>
+  <si>
+    <t>="LAS("&amp;TEXT(C17,"#,###")&amp;") = "</t>
+  </si>
+  <si>
+    <t>=$D$15/COUNTA($B$5:$B$14)</t>
+  </si>
+  <si>
+    <t>=I5/I4</t>
+  </si>
+  <si>
+    <t>LAS(4,000,000 xs 1,000,000) =</t>
+  </si>
+  <si>
+    <t>=$F$15/COUNTIF($B$9:$B$14,"&lt;&gt;0")</t>
+  </si>
+  <si>
+    <t>OR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">… = </t>
+  </si>
+  <si>
+    <t>=(I5-I4)/(COUNTIF(F5:F14,"&lt;&gt;0")/COUNTA(F5:F14))</t>
+  </si>
+  <si>
+    <t>Size of Loss</t>
+  </si>
+  <si>
+    <t>Policy Limit</t>
+  </si>
+  <si>
+    <t>X &lt;= 100,000</t>
+  </si>
+  <si>
+    <t>$100,000 &lt; X &lt;= $300,000</t>
+  </si>
+  <si>
+    <t>$300,000 &lt; X &lt;= $500,000</t>
+  </si>
+  <si>
+    <t>Censored Loss Distribution by Policy Limit</t>
+  </si>
+  <si>
+    <t>Censored Claim Distribution by Policy Limit</t>
+  </si>
+  <si>
+    <t>=(SUM(N21:P21)+SUM(N20*SUM(O30:P31)))/SUM(N32:P32)</t>
+  </si>
+  <si>
+    <t>=T21/T19</t>
+  </si>
+  <si>
+    <t>="LAS("&amp;TEXT(N20,"$#,###")&amp;") = "</t>
+  </si>
+  <si>
+    <t>=T19+(SUM(O22:P22)+P31*O20-N20*SUM(O30:P31))/SUM(O32:P32)</t>
+  </si>
+  <si>
+    <t>Ground-Up Uncensored Loss</t>
+  </si>
+  <si>
+    <t>Assume no risk load</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basic Limit = </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ULAE Provision as % of Loss (Basic Limit) = </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ULAE Provision as % of Loss (Increased Limit) = </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected Frequency (Basic Limit) = </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expected Frequency (Increased Limit) = </t>
+  </si>
+  <si>
+    <t>with ULAE load</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Increased limit = </t>
+  </si>
+  <si>
+    <t>with frequency load</t>
+  </si>
+  <si>
+    <t>="LAS("&amp;TEXT($AB$42,"$#,###")&amp;") = "</t>
+  </si>
+  <si>
+    <t>=AC40/COUNT(AC34:AC39)</t>
+  </si>
+  <si>
+    <t>=AG33*(1+AB43)</t>
+  </si>
+  <si>
+    <t>=AG34*AB45</t>
+  </si>
+  <si>
+    <t>=AD40/COUNT(AD34:AD39)</t>
+  </si>
+  <si>
+    <t>=AG37*(1+AB44)</t>
+  </si>
+  <si>
+    <t>=AG38*AB46</t>
+  </si>
+  <si>
+    <t>=AG39/AG35</t>
+  </si>
+  <si>
+    <t>Deductible</t>
+  </si>
+  <si>
+    <t>Full coverage</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>Reported Claim Counts</t>
+  </si>
+  <si>
+    <t>Net Reported Losses</t>
+  </si>
+  <si>
+    <t>Net Reported Losses Assuming $750 Deductible</t>
+  </si>
+  <si>
+    <t>Net Reported Losses Assuming $1000 Deductible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B = </t>
+  </si>
+  <si>
+    <t xml:space="preserve">D = </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicated deductible relativity = </t>
+  </si>
+  <si>
+    <t>="LER("&amp;TEXT(C12,"$#,###")&amp;") = "</t>
+  </si>
+  <si>
+    <t>=LET(x,SUMIFS($E$5:$E$9,$B$5:$B$9,"&lt;="&amp;C12),(x-SUMIFS($F$5:$F$9,$B$5:$B$9,"&lt;="&amp;C12))/x)</t>
+  </si>
+  <si>
+    <t>=1-I5</t>
+  </si>
+  <si>
+    <t>Ground-up Severity</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>Premium for a policy with no deductible = $350</t>
+  </si>
+  <si>
+    <t>Ground-up expected loss ratio = 60.9%</t>
+  </si>
+  <si>
+    <t>Fixed expenses = $31.70</t>
+  </si>
+  <si>
+    <t>Variable underwriting expense provision = 22%</t>
+  </si>
+  <si>
+    <t>Profit provision = 2%</t>
+  </si>
+  <si>
+    <t>Allocated loss adjustment expenses (ALAE) are 10% of loss and are the responsibility of the insurer.</t>
+  </si>
+  <si>
+    <t>Plus fixed expenses</t>
+  </si>
+  <si>
+    <t>Total (or Expected value)</t>
+  </si>
+  <si>
+    <t>Adjusted for VER and profit provision</t>
+  </si>
+  <si>
+    <t>Expected losses (with deductible)</t>
+  </si>
+  <si>
+    <t>Plus ALAE (not affected by deductible)</t>
+  </si>
+  <si>
+    <t>=X14*X15*X24</t>
+  </si>
+  <si>
+    <t>=X27+X14*X15*(X19)</t>
+  </si>
+  <si>
+    <t>=X28+X16</t>
+  </si>
+  <si>
+    <t>=X29/(1-X17-X18)</t>
+  </si>
+  <si>
+    <t>=X28-X27</t>
+  </si>
+  <si>
+    <t>=U21/R21</t>
+  </si>
+  <si>
+    <t>=1-X22</t>
+  </si>
+  <si>
+    <t>="LER("&amp;TEXT($S$24,"$#,###")&amp;") = "</t>
+  </si>
+  <si>
+    <t>="Paid loss with D = "&amp;TEXT($S$24,"$#,###")</t>
+  </si>
+  <si>
+    <t>=MAX(R15-$S$24,0)</t>
+  </si>
+  <si>
+    <t>=R15-T15</t>
+  </si>
+  <si>
+    <t>=SUMPRODUCT(R15:R20,$S$15:$S$20)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="10">
+  <numFmts count="12">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
@@ -1239,8 +1494,9 @@
     <numFmt numFmtId="168" formatCode="0.0%"/>
     <numFmt numFmtId="169" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="170" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="178" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1361,6 +1617,13 @@
     <font>
       <b/>
       <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF0070C0"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1566,12 +1829,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="208">
+  <cellXfs count="248">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1762,6 +2026,38 @@
     <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="6" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="6" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="6" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1843,20 +2139,55 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="8" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="7" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
@@ -2580,6 +2911,1310 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2379A799-393D-9B4C-A096-4CF8838C6329}">
+  <dimension ref="B2:AH48"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="16.6640625" customWidth="1"/>
+    <col min="5" max="6" width="17.5" customWidth="1"/>
+    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="44.1640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="29.33203125" customWidth="1"/>
+    <col min="32" max="32" width="17" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="234" t="s">
+        <v>177</v>
+      </c>
+      <c r="C2" s="234" t="s">
+        <v>388</v>
+      </c>
+      <c r="D2" s="234" t="str">
+        <f>"LAS("&amp;TEXT($C$17,"#,###")&amp;")"</f>
+        <v>LAS(1,000,000)</v>
+      </c>
+      <c r="E2" s="234" t="str">
+        <f>"LAS("&amp;TEXT($C$18,"#,###")&amp;")"</f>
+        <v>LAS(5,000,000)</v>
+      </c>
+      <c r="F2" s="234" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B3" s="234"/>
+      <c r="C3" s="234"/>
+      <c r="D3" s="234"/>
+      <c r="E3" s="234"/>
+      <c r="F3" s="234"/>
+      <c r="H3" s="36" t="s">
+        <v>391</v>
+      </c>
+      <c r="I3" s="36" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="234"/>
+      <c r="C4" s="234"/>
+      <c r="D4" s="234"/>
+      <c r="E4" s="234"/>
+      <c r="F4" s="234"/>
+      <c r="H4" s="184" t="str">
+        <f>"LAS("&amp;TEXT(C17,"#,###")&amp;") = "</f>
+        <v xml:space="preserve">LAS(1,000,000) = </v>
+      </c>
+      <c r="I4" s="182">
+        <f>$D$15/COUNTA($B$5:$B$14)</f>
+        <v>775000</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B5" s="71" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="180">
+        <v>250000</v>
+      </c>
+      <c r="D5" s="182">
+        <f>IF($C5&lt;$C$17,$C5,$C$17)</f>
+        <v>250000</v>
+      </c>
+      <c r="E5" s="182">
+        <f>IF($C5&lt;$C$18,$C5,$C$18)</f>
+        <v>250000</v>
+      </c>
+      <c r="F5" s="182">
+        <f>MAX(IF($C5&lt;$C$17,0,IF($C5&lt;$C$18,$C5,$C$18))-$C$17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="184" t="str">
+        <f>"LAS("&amp;TEXT(C18,"#,###")&amp;") = "</f>
+        <v xml:space="preserve">LAS(5,000,000) = </v>
+      </c>
+      <c r="I5" s="182">
+        <f>$E$15/COUNTA($B$5:$B$14)</f>
+        <v>2445000</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B6" s="71" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="180">
+        <v>300000</v>
+      </c>
+      <c r="D6" s="182">
+        <f t="shared" ref="D6:D14" si="0">IF($C6&lt;$C$17,$C6,$C$17)</f>
+        <v>300000</v>
+      </c>
+      <c r="E6" s="182">
+        <f t="shared" ref="E6:E14" si="1">IF($C6&lt;$C$18,$C6,$C$18)</f>
+        <v>300000</v>
+      </c>
+      <c r="F6" s="182">
+        <f t="shared" ref="F6:F14" si="2">MAX(IF($C6&lt;$C$17,0,IF($C6&lt;$C$18,$C6,$C$18))-$C$17,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B7" s="71" t="s">
+        <v>336</v>
+      </c>
+      <c r="C7" s="180">
+        <v>450000</v>
+      </c>
+      <c r="D7" s="182">
+        <f t="shared" si="0"/>
+        <v>450000</v>
+      </c>
+      <c r="E7" s="182">
+        <f t="shared" si="1"/>
+        <v>450000</v>
+      </c>
+      <c r="F7" s="182">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="184"/>
+      <c r="I7" s="36" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B8" s="71" t="s">
+        <v>337</v>
+      </c>
+      <c r="C8" s="180">
+        <v>750000</v>
+      </c>
+      <c r="D8" s="182">
+        <f t="shared" si="0"/>
+        <v>750000</v>
+      </c>
+      <c r="E8" s="182">
+        <f t="shared" si="1"/>
+        <v>750000</v>
+      </c>
+      <c r="F8" s="182">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="184" t="str">
+        <f>"ILF("&amp;TEXT(C18,"#,###")&amp;") = "</f>
+        <v xml:space="preserve">ILF(5,000,000) = </v>
+      </c>
+      <c r="I8" s="185">
+        <f>I5/I4</f>
+        <v>3.1548387096774193</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B9" s="71" t="s">
+        <v>382</v>
+      </c>
+      <c r="C9" s="180">
+        <v>1200000</v>
+      </c>
+      <c r="D9" s="182">
+        <f t="shared" si="0"/>
+        <v>1000000</v>
+      </c>
+      <c r="E9" s="182">
+        <f t="shared" si="1"/>
+        <v>1200000</v>
+      </c>
+      <c r="F9" s="182">
+        <f t="shared" si="2"/>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B10" s="71" t="s">
+        <v>383</v>
+      </c>
+      <c r="C10" s="180">
+        <v>2500000</v>
+      </c>
+      <c r="D10" s="182">
+        <f t="shared" si="0"/>
+        <v>1000000</v>
+      </c>
+      <c r="E10" s="182">
+        <f t="shared" si="1"/>
+        <v>2500000</v>
+      </c>
+      <c r="F10" s="182">
+        <f t="shared" si="2"/>
+        <v>1500000</v>
+      </c>
+      <c r="H10" s="36" t="s">
+        <v>394</v>
+      </c>
+      <c r="I10" s="36" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B11" s="71" t="s">
+        <v>384</v>
+      </c>
+      <c r="C11" s="180">
+        <v>4000000</v>
+      </c>
+      <c r="D11" s="182">
+        <f t="shared" si="0"/>
+        <v>1000000</v>
+      </c>
+      <c r="E11" s="182">
+        <f t="shared" si="1"/>
+        <v>4000000</v>
+      </c>
+      <c r="F11" s="182">
+        <f t="shared" si="2"/>
+        <v>3000000</v>
+      </c>
+      <c r="H11" s="184" t="str">
+        <f>"LAS("&amp;TEXT($C$18-$C$17,"#,###")&amp;" xs "&amp;TEXT($C$17,"#,###")&amp;") ="</f>
+        <v>LAS(4,000,000 xs 1,000,000) =</v>
+      </c>
+      <c r="I11" s="186">
+        <f>$F$15/COUNTIF($B$9:$B$14,"&lt;&gt;0")</f>
+        <v>2783333.3333333335</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B12" s="71" t="s">
+        <v>385</v>
+      </c>
+      <c r="C12" s="180">
+        <v>7500000</v>
+      </c>
+      <c r="D12" s="182">
+        <f t="shared" si="0"/>
+        <v>1000000</v>
+      </c>
+      <c r="E12" s="182">
+        <f t="shared" si="1"/>
+        <v>5000000</v>
+      </c>
+      <c r="F12" s="182">
+        <f t="shared" si="2"/>
+        <v>4000000</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B13" s="71" t="s">
+        <v>386</v>
+      </c>
+      <c r="C13" s="180">
+        <v>9000000</v>
+      </c>
+      <c r="D13" s="182">
+        <f t="shared" si="0"/>
+        <v>1000000</v>
+      </c>
+      <c r="E13" s="182">
+        <f t="shared" si="1"/>
+        <v>5000000</v>
+      </c>
+      <c r="F13" s="182">
+        <f t="shared" si="2"/>
+        <v>4000000</v>
+      </c>
+      <c r="I13" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="76" t="s">
+        <v>387</v>
+      </c>
+      <c r="C14" s="181">
+        <v>15000000</v>
+      </c>
+      <c r="D14" s="183">
+        <f t="shared" si="0"/>
+        <v>1000000</v>
+      </c>
+      <c r="E14" s="183">
+        <f t="shared" si="1"/>
+        <v>5000000</v>
+      </c>
+      <c r="F14" s="183">
+        <f t="shared" si="2"/>
+        <v>4000000</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="71" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="180">
+        <f>SUM(C5:C14)</f>
+        <v>40950000</v>
+      </c>
+      <c r="D15" s="182">
+        <f>SUM(D5:D14)</f>
+        <v>7750000</v>
+      </c>
+      <c r="E15" s="182">
+        <f>SUM(E5:E14)</f>
+        <v>24450000</v>
+      </c>
+      <c r="F15" s="182">
+        <f>SUM(F5:F14)</f>
+        <v>16700000</v>
+      </c>
+      <c r="I15" s="36" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="H16" s="184" t="s">
+        <v>397</v>
+      </c>
+      <c r="I16" s="186">
+        <f>(I5-I4)/(COUNTIF(F5:F14,"&lt;&gt;0")/COUNTA(F5:F14))</f>
+        <v>2783333.3333333335</v>
+      </c>
+    </row>
+    <row r="17" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="B17" s="71" t="s">
+        <v>389</v>
+      </c>
+      <c r="C17" s="180">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="18" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="B18" s="71" t="s">
+        <v>390</v>
+      </c>
+      <c r="C18" s="180">
+        <v>5000000</v>
+      </c>
+      <c r="M18" t="s">
+        <v>404</v>
+      </c>
+      <c r="S18" s="36" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="19" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="M19" s="227" t="s">
+        <v>399</v>
+      </c>
+      <c r="N19" s="229" t="s">
+        <v>400</v>
+      </c>
+      <c r="O19" s="230"/>
+      <c r="P19" s="231"/>
+      <c r="S19" s="22" t="str">
+        <f>"LAS("&amp;TEXT(N20,"$#,###")&amp;") = "</f>
+        <v xml:space="preserve">LAS($100,000) = </v>
+      </c>
+      <c r="T19" s="92">
+        <f>(SUM(N21:P21)+SUM(N20*SUM(O30:P31)))/SUM(N32:P32)</f>
+        <v>76726.030739204682</v>
+      </c>
+      <c r="U19" s="36" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="20" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="M20" s="228"/>
+      <c r="N20" s="187">
+        <v>100000</v>
+      </c>
+      <c r="O20" s="187">
+        <v>300000</v>
+      </c>
+      <c r="P20" s="188">
+        <v>500000</v>
+      </c>
+      <c r="S20" s="22"/>
+      <c r="T20" s="22"/>
+      <c r="U20" s="93"/>
+    </row>
+    <row r="21" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="M21" s="148" t="s">
+        <v>401</v>
+      </c>
+      <c r="N21" s="189">
+        <v>97000000</v>
+      </c>
+      <c r="O21" s="189">
+        <v>46000000</v>
+      </c>
+      <c r="P21" s="190">
+        <v>11000000</v>
+      </c>
+      <c r="S21" s="22" t="str">
+        <f>"LAS("&amp;TEXT(O20,"$#,###")&amp;") = "</f>
+        <v xml:space="preserve">LAS($300,000) = </v>
+      </c>
+      <c r="T21" s="92">
+        <f>T19+(SUM(O22:P22)+P31*O20-N20*SUM(O30:P31))/SUM(O32:P32)</f>
+        <v>163266.01490389195</v>
+      </c>
+      <c r="U21" s="36" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="22" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="M22" s="133" t="s">
+        <v>402</v>
+      </c>
+      <c r="N22" s="71"/>
+      <c r="O22" s="72">
+        <v>150000000</v>
+      </c>
+      <c r="P22" s="142">
+        <v>107000000</v>
+      </c>
+      <c r="S22" s="22"/>
+      <c r="T22" s="22"/>
+      <c r="U22" s="93"/>
+    </row>
+    <row r="23" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="M23" s="134" t="s">
+        <v>403</v>
+      </c>
+      <c r="N23" s="131"/>
+      <c r="O23" s="131"/>
+      <c r="P23" s="143">
+        <v>160000000</v>
+      </c>
+      <c r="S23" s="22" t="str">
+        <f>"ILF("&amp;TEXT(O20,"$#,###")&amp;") = "</f>
+        <v xml:space="preserve">ILF($300,000) = </v>
+      </c>
+      <c r="T23" s="164">
+        <f>T21/T19</f>
+        <v>2.1279090463944454</v>
+      </c>
+      <c r="U23" s="36" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="24" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="M24" s="134" t="s">
+        <v>10</v>
+      </c>
+      <c r="N24" s="167">
+        <v>97000000</v>
+      </c>
+      <c r="O24" s="167">
+        <v>196000000</v>
+      </c>
+      <c r="P24" s="143">
+        <v>278000000</v>
+      </c>
+    </row>
+    <row r="26" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="M26" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="27" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="M27" s="232" t="s">
+        <v>399</v>
+      </c>
+      <c r="N27" s="229" t="s">
+        <v>400</v>
+      </c>
+      <c r="O27" s="230"/>
+      <c r="P27" s="231"/>
+    </row>
+    <row r="28" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="M28" s="233"/>
+      <c r="N28" s="191">
+        <v>100000</v>
+      </c>
+      <c r="O28" s="187">
+        <v>300000</v>
+      </c>
+      <c r="P28" s="188">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="29" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="M29" s="148" t="s">
+        <v>401</v>
+      </c>
+      <c r="N29" s="179">
+        <v>1573</v>
+      </c>
+      <c r="O29" s="135">
+        <v>753</v>
+      </c>
+      <c r="P29" s="192">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="30" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="M30" s="133" t="s">
+        <v>402</v>
+      </c>
+      <c r="N30" s="114"/>
+      <c r="O30" s="71">
+        <v>637</v>
+      </c>
+      <c r="P30" s="130">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="31" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="M31" s="134" t="s">
+        <v>403</v>
+      </c>
+      <c r="N31" s="116"/>
+      <c r="O31" s="131"/>
+      <c r="P31" s="132">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="32" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="M32" s="116" t="s">
+        <v>10</v>
+      </c>
+      <c r="N32" s="193">
+        <v>1573</v>
+      </c>
+      <c r="O32" s="194">
+        <v>1390</v>
+      </c>
+      <c r="P32" s="195">
+        <v>1136</v>
+      </c>
+      <c r="AF32" s="36" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="33" spans="27:34" x14ac:dyDescent="0.2">
+      <c r="AA33" s="70" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB33" s="70" t="s">
+        <v>410</v>
+      </c>
+      <c r="AC33" s="70" t="str">
+        <f>"LAS("&amp;TEXT($AB$42,"$#,###")&amp;")"</f>
+        <v>LAS($1,000,000)</v>
+      </c>
+      <c r="AD33" s="70" t="str">
+        <f>"LAS("&amp;TEXT($AB$48,"$#,###")&amp;")"</f>
+        <v>LAS($5,000,000)</v>
+      </c>
+      <c r="AF33" s="22" t="str">
+        <f>"LAS("&amp;TEXT($AB$42,"$#,###")&amp;") = "</f>
+        <v xml:space="preserve">LAS($1,000,000) = </v>
+      </c>
+      <c r="AG33" s="199">
+        <f>AC40/COUNT(AC34:AC39)</f>
+        <v>775000</v>
+      </c>
+      <c r="AH33" s="36" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="34" spans="27:34" x14ac:dyDescent="0.2">
+      <c r="AA34" s="71">
+        <v>1</v>
+      </c>
+      <c r="AB34" s="72">
+        <v>300000</v>
+      </c>
+      <c r="AC34" s="68">
+        <f>MIN(AB34,$AB$42)</f>
+        <v>300000</v>
+      </c>
+      <c r="AD34" s="68">
+        <f>MIN(AB34,$AB$48)</f>
+        <v>300000</v>
+      </c>
+      <c r="AF34" t="s">
+        <v>417</v>
+      </c>
+      <c r="AG34" s="155">
+        <f>AG33*(1+AB43)</f>
+        <v>852500.00000000012</v>
+      </c>
+      <c r="AH34" s="36" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="35" spans="27:34" x14ac:dyDescent="0.2">
+      <c r="AA35" s="71">
+        <v>2</v>
+      </c>
+      <c r="AB35" s="72">
+        <v>600000</v>
+      </c>
+      <c r="AC35" s="68">
+        <f t="shared" ref="AC35:AC39" si="3">MIN(AB35,$AB$42)</f>
+        <v>600000</v>
+      </c>
+      <c r="AD35" s="68">
+        <f t="shared" ref="AD35:AD39" si="4">MIN(AB35,$AB$48)</f>
+        <v>600000</v>
+      </c>
+      <c r="AF35" t="s">
+        <v>419</v>
+      </c>
+      <c r="AG35" s="155">
+        <f>AG34*AB45</f>
+        <v>127875.00000000001</v>
+      </c>
+      <c r="AH35" s="36" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="36" spans="27:34" x14ac:dyDescent="0.2">
+      <c r="AA36" s="71">
+        <v>3</v>
+      </c>
+      <c r="AB36" s="72">
+        <v>750000</v>
+      </c>
+      <c r="AC36" s="68">
+        <f t="shared" si="3"/>
+        <v>750000</v>
+      </c>
+      <c r="AD36" s="68">
+        <f t="shared" si="4"/>
+        <v>750000</v>
+      </c>
+      <c r="AH36" s="93"/>
+    </row>
+    <row r="37" spans="27:34" x14ac:dyDescent="0.2">
+      <c r="AA37" s="71">
+        <v>4</v>
+      </c>
+      <c r="AB37" s="72">
+        <v>1250000</v>
+      </c>
+      <c r="AC37" s="68">
+        <f t="shared" si="3"/>
+        <v>1000000</v>
+      </c>
+      <c r="AD37" s="68">
+        <f t="shared" si="4"/>
+        <v>1250000</v>
+      </c>
+      <c r="AF37" s="22" t="str">
+        <f>"LAS("&amp;TEXT($AB$48,"$#,###")&amp;") = "</f>
+        <v xml:space="preserve">LAS($5,000,000) = </v>
+      </c>
+      <c r="AG37" s="199">
+        <f>AD40/COUNT(AD34:AD39)</f>
+        <v>2066666.6666666667</v>
+      </c>
+      <c r="AH37" s="36" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="38" spans="27:34" x14ac:dyDescent="0.2">
+      <c r="AA38" s="71">
+        <v>5</v>
+      </c>
+      <c r="AB38" s="72">
+        <v>4500000</v>
+      </c>
+      <c r="AC38" s="68">
+        <f t="shared" si="3"/>
+        <v>1000000</v>
+      </c>
+      <c r="AD38" s="68">
+        <f t="shared" si="4"/>
+        <v>4500000</v>
+      </c>
+      <c r="AF38" t="s">
+        <v>417</v>
+      </c>
+      <c r="AG38" s="155">
+        <f>AG37*(1+AB44)</f>
+        <v>2480000</v>
+      </c>
+      <c r="AH38" s="36" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="39" spans="27:34" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AA39" s="76">
+        <v>6</v>
+      </c>
+      <c r="AB39" s="197">
+        <v>10000000</v>
+      </c>
+      <c r="AC39" s="198">
+        <f t="shared" si="3"/>
+        <v>1000000</v>
+      </c>
+      <c r="AD39" s="198">
+        <f t="shared" si="4"/>
+        <v>5000000</v>
+      </c>
+      <c r="AF39" t="s">
+        <v>419</v>
+      </c>
+      <c r="AG39" s="155">
+        <f>AG38*AB46</f>
+        <v>248000</v>
+      </c>
+      <c r="AH39" s="36" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="40" spans="27:34" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="AA40" s="71" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB40" s="68">
+        <f>SUM(AB34:AB39)</f>
+        <v>17400000</v>
+      </c>
+      <c r="AC40" s="68">
+        <f>SUM(AC34:AC39)</f>
+        <v>4650000</v>
+      </c>
+      <c r="AD40" s="68">
+        <f>SUM(AD34:AD39)</f>
+        <v>12400000</v>
+      </c>
+      <c r="AH40" s="93"/>
+    </row>
+    <row r="41" spans="27:34" x14ac:dyDescent="0.2">
+      <c r="AF41" s="22" t="str">
+        <f>"ILF("&amp;TEXT($AB$48,"$#,###")&amp;") = "</f>
+        <v xml:space="preserve">ILF($5,000,000) = </v>
+      </c>
+      <c r="AG41" s="164">
+        <f>AG39/AG35</f>
+        <v>1.9393939393939392</v>
+      </c>
+      <c r="AH41" s="36" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="42" spans="27:34" x14ac:dyDescent="0.2">
+      <c r="AA42" s="56" t="s">
+        <v>412</v>
+      </c>
+      <c r="AB42" s="72">
+        <v>1000000</v>
+      </c>
+      <c r="AC42" s="72"/>
+      <c r="AD42" s="72"/>
+    </row>
+    <row r="43" spans="27:34" x14ac:dyDescent="0.2">
+      <c r="AA43" s="56" t="s">
+        <v>413</v>
+      </c>
+      <c r="AB43" s="110">
+        <v>0.1</v>
+      </c>
+      <c r="AC43" s="110"/>
+      <c r="AD43" s="110"/>
+    </row>
+    <row r="44" spans="27:34" x14ac:dyDescent="0.2">
+      <c r="AA44" s="56" t="s">
+        <v>414</v>
+      </c>
+      <c r="AB44" s="110">
+        <v>0.2</v>
+      </c>
+      <c r="AC44" s="110"/>
+      <c r="AD44" s="110"/>
+    </row>
+    <row r="45" spans="27:34" x14ac:dyDescent="0.2">
+      <c r="AA45" s="56" t="s">
+        <v>415</v>
+      </c>
+      <c r="AB45" s="196">
+        <v>0.15</v>
+      </c>
+      <c r="AC45" s="196"/>
+      <c r="AD45" s="196"/>
+    </row>
+    <row r="46" spans="27:34" x14ac:dyDescent="0.2">
+      <c r="AA46" s="56" t="s">
+        <v>416</v>
+      </c>
+      <c r="AB46" s="196">
+        <v>0.1</v>
+      </c>
+      <c r="AC46" s="196"/>
+      <c r="AD46" s="196"/>
+    </row>
+    <row r="47" spans="27:34" x14ac:dyDescent="0.2">
+      <c r="AA47" s="56" t="s">
+        <v>411</v>
+      </c>
+      <c r="AB47" s="72"/>
+      <c r="AC47" s="72"/>
+      <c r="AD47" s="72"/>
+    </row>
+    <row r="48" spans="27:34" x14ac:dyDescent="0.2">
+      <c r="AA48" s="56" t="s">
+        <v>418</v>
+      </c>
+      <c r="AB48" s="72">
+        <v>5000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="M19:M20"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="M27:M28"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="F2:F4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6818ACD0-71ED-BF49-8DC3-DBE331265C1F}">
+  <dimension ref="A4:AA31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="23.1640625" customWidth="1"/>
+    <col min="8" max="8" width="34.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="30" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="82.5" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="1:24" ht="51" x14ac:dyDescent="0.2">
+      <c r="B4" s="174" t="s">
+        <v>428</v>
+      </c>
+      <c r="C4" s="174" t="s">
+        <v>431</v>
+      </c>
+      <c r="D4" s="174" t="s">
+        <v>432</v>
+      </c>
+      <c r="E4" s="174" t="s">
+        <v>433</v>
+      </c>
+      <c r="F4" s="174" t="s">
+        <v>434</v>
+      </c>
+      <c r="H4" s="239" t="s">
+        <v>438</v>
+      </c>
+      <c r="I4" s="239" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A5" s="71" t="s">
+        <v>429</v>
+      </c>
+      <c r="B5" s="72">
+        <v>0</v>
+      </c>
+      <c r="C5" s="71">
+        <v>990</v>
+      </c>
+      <c r="D5" s="72">
+        <v>1347000</v>
+      </c>
+      <c r="E5" s="72">
+        <v>772000</v>
+      </c>
+      <c r="F5" s="72">
+        <v>605000</v>
+      </c>
+      <c r="H5" s="184" t="str">
+        <f>"LER("&amp;TEXT(C12,"$#,###")&amp;") = "</f>
+        <v xml:space="preserve">LER($750) = </v>
+      </c>
+      <c r="I5" s="237">
+        <f>_xlfn.LET(_xlpm.x,SUMIFS($E$5:$E$9,$B$5:$B$9,"&lt;="&amp;C12),(_xlpm.x-SUMIFS($F$5:$F$9,$B$5:$B$9,"&lt;="&amp;C12))/_xlpm.x)</f>
+        <v>0.11610325752919484</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="B6" s="72">
+        <v>250</v>
+      </c>
+      <c r="C6" s="100">
+        <v>2770</v>
+      </c>
+      <c r="D6" s="72">
+        <v>5167000</v>
+      </c>
+      <c r="E6" s="72">
+        <v>4024000</v>
+      </c>
+      <c r="F6" s="72">
+        <v>3505000</v>
+      </c>
+      <c r="H6" s="56"/>
+      <c r="I6" s="236"/>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="B7" s="72">
+        <v>500</v>
+      </c>
+      <c r="C7" s="100">
+        <v>4360</v>
+      </c>
+      <c r="D7" s="72">
+        <v>9198000</v>
+      </c>
+      <c r="E7" s="72">
+        <v>8244000</v>
+      </c>
+      <c r="F7" s="72">
+        <v>7345000</v>
+      </c>
+      <c r="H7" s="56" t="s">
+        <v>437</v>
+      </c>
+      <c r="I7" s="238">
+        <f>1-I5</f>
+        <v>0.88389674247080519</v>
+      </c>
+      <c r="J7" s="36" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="B8" s="72">
+        <v>750</v>
+      </c>
+      <c r="C8" s="100">
+        <v>1350</v>
+      </c>
+      <c r="D8" s="72">
+        <v>3230000</v>
+      </c>
+      <c r="E8" s="72">
+        <v>3230000</v>
+      </c>
+      <c r="F8" s="72">
+        <v>2926000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="197">
+        <v>1000</v>
+      </c>
+      <c r="C9" s="76">
+        <v>500</v>
+      </c>
+      <c r="D9" s="197">
+        <v>1692000</v>
+      </c>
+      <c r="E9" s="76" t="s">
+        <v>430</v>
+      </c>
+      <c r="F9" s="197">
+        <v>1692000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="71" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="100">
+        <v>9970</v>
+      </c>
+      <c r="D10" s="72">
+        <v>20634000</v>
+      </c>
+      <c r="E10" s="71"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="B12" s="56" t="s">
+        <v>435</v>
+      </c>
+      <c r="C12" s="235">
+        <v>750</v>
+      </c>
+      <c r="T12" s="36" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="B13" s="56" t="s">
+        <v>436</v>
+      </c>
+      <c r="C13" s="235">
+        <v>1000</v>
+      </c>
+      <c r="T13" s="36" t="s">
+        <v>463</v>
+      </c>
+      <c r="U13" s="36" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="R14" s="70" t="s">
+        <v>441</v>
+      </c>
+      <c r="S14" s="70" t="s">
+        <v>442</v>
+      </c>
+      <c r="T14" s="246" t="str">
+        <f>"Paid loss with D = "&amp;TEXT($S$24,"$#,###")</f>
+        <v>Paid loss with D = $500</v>
+      </c>
+      <c r="U14" s="246" t="str">
+        <f>"Eliminated loss with D = "&amp;TEXT($S$24,"$#,###")</f>
+        <v>Eliminated loss with D = $500</v>
+      </c>
+      <c r="W14" t="s">
+        <v>443</v>
+      </c>
+      <c r="X14" s="243">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="R15" s="72">
+        <v>100</v>
+      </c>
+      <c r="S15" s="81">
+        <v>0.2</v>
+      </c>
+      <c r="T15" s="68">
+        <f>MAX(R15-$S$24,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U15" s="53">
+        <f>R15-T15</f>
+        <v>100</v>
+      </c>
+      <c r="W15" t="s">
+        <v>444</v>
+      </c>
+      <c r="X15" s="244">
+        <v>0.60899999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="R16" s="72">
+        <v>250</v>
+      </c>
+      <c r="S16" s="81">
+        <v>0.1</v>
+      </c>
+      <c r="T16" s="68">
+        <f t="shared" ref="T16:T20" si="0">MAX(R16-$S$24,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U16" s="53">
+        <f t="shared" ref="U16:U20" si="1">R16-T16</f>
+        <v>250</v>
+      </c>
+      <c r="W16" t="s">
+        <v>445</v>
+      </c>
+      <c r="X16" s="242">
+        <v>31.7</v>
+      </c>
+    </row>
+    <row r="17" spans="17:27" x14ac:dyDescent="0.2">
+      <c r="R17" s="72">
+        <v>500</v>
+      </c>
+      <c r="S17" s="81">
+        <v>0.15</v>
+      </c>
+      <c r="T17" s="68">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="53">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="W17" t="s">
+        <v>446</v>
+      </c>
+      <c r="X17" s="19">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="18" spans="17:27" x14ac:dyDescent="0.2">
+      <c r="R18" s="72">
+        <v>1000</v>
+      </c>
+      <c r="S18" s="81">
+        <v>0.3</v>
+      </c>
+      <c r="T18" s="68">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="U18" s="53">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="W18" t="s">
+        <v>447</v>
+      </c>
+      <c r="X18" s="19">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="19" spans="17:27" x14ac:dyDescent="0.2">
+      <c r="R19" s="72">
+        <v>3000</v>
+      </c>
+      <c r="S19" s="81">
+        <v>0.2</v>
+      </c>
+      <c r="T19" s="68">
+        <f t="shared" si="0"/>
+        <v>2500</v>
+      </c>
+      <c r="U19" s="53">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="W19" t="s">
+        <v>448</v>
+      </c>
+      <c r="X19" s="19">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="20" spans="17:27" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q20" s="84"/>
+      <c r="R20" s="197">
+        <v>8000</v>
+      </c>
+      <c r="S20" s="240">
+        <v>0.05</v>
+      </c>
+      <c r="T20" s="198">
+        <f t="shared" si="0"/>
+        <v>7500</v>
+      </c>
+      <c r="U20" s="103">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="21" spans="17:27" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="Q21" t="s">
+        <v>450</v>
+      </c>
+      <c r="R21" s="155">
+        <f>SUMPRODUCT(R15:R20,$S$15:$S$20)</f>
+        <v>1420</v>
+      </c>
+      <c r="S21" s="241">
+        <f>SUM(S15:S20)</f>
+        <v>1</v>
+      </c>
+      <c r="T21" s="155">
+        <f>SUMPRODUCT(T15:T20,$S$15:$S$20)</f>
+        <v>1025</v>
+      </c>
+      <c r="U21" s="155">
+        <f>SUMPRODUCT(U15:U20,$S$15:$S$20)</f>
+        <v>395</v>
+      </c>
+      <c r="W21" s="36" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="22" spans="17:27" x14ac:dyDescent="0.2">
+      <c r="R22" s="36" t="s">
+        <v>465</v>
+      </c>
+      <c r="W22" s="35" t="str">
+        <f>"LER("&amp;TEXT($S$24,"$#,###")&amp;") = "</f>
+        <v xml:space="preserve">LER($500) = </v>
+      </c>
+      <c r="X22" s="245">
+        <f>U21/R21</f>
+        <v>0.27816901408450706</v>
+      </c>
+      <c r="Y22" s="36" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="23" spans="17:27" x14ac:dyDescent="0.2">
+      <c r="R23" s="56" t="s">
+        <v>435</v>
+      </c>
+      <c r="S23" s="243">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="17:27" x14ac:dyDescent="0.2">
+      <c r="R24" s="56" t="s">
+        <v>436</v>
+      </c>
+      <c r="S24" s="243">
+        <v>500</v>
+      </c>
+      <c r="W24" t="s">
+        <v>437</v>
+      </c>
+      <c r="X24" s="43">
+        <f>1-X22</f>
+        <v>0.721830985915493</v>
+      </c>
+      <c r="Y24" s="36" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="27" spans="17:27" x14ac:dyDescent="0.2">
+      <c r="W27" t="s">
+        <v>452</v>
+      </c>
+      <c r="X27" s="156">
+        <f>X14*X15*X24</f>
+        <v>153.85827464788733</v>
+      </c>
+      <c r="Y27" s="36" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="28" spans="17:27" x14ac:dyDescent="0.2">
+      <c r="W28" t="s">
+        <v>453</v>
+      </c>
+      <c r="X28" s="156">
+        <f>X27+X14*X15*(X19)</f>
+        <v>175.17327464788733</v>
+      </c>
+      <c r="Y28" s="36" t="s">
+        <v>455</v>
+      </c>
+      <c r="Z28" s="156">
+        <f>X28-X27</f>
+        <v>21.314999999999998</v>
+      </c>
+      <c r="AA28" s="36" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="29" spans="17:27" x14ac:dyDescent="0.2">
+      <c r="W29" t="s">
+        <v>449</v>
+      </c>
+      <c r="X29" s="156">
+        <f>X28+X16</f>
+        <v>206.87327464788731</v>
+      </c>
+      <c r="Y29" s="36" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="30" spans="17:27" x14ac:dyDescent="0.2">
+      <c r="W30" t="s">
+        <v>451</v>
+      </c>
+      <c r="X30" s="127">
+        <f>X29/(1-X17-X18)</f>
+        <v>272.20167716827279</v>
+      </c>
+      <c r="Y30" s="36" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="31" spans="17:27" x14ac:dyDescent="0.2">
+      <c r="X31" s="247"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9D6021E-A4E6-FC4B-9E7D-448791DEE1BE}">
   <dimension ref="B2:AZ63"/>
@@ -2928,26 +4563,26 @@
       </c>
     </row>
     <row r="23" spans="2:33" x14ac:dyDescent="0.2">
-      <c r="M23" s="179"/>
-      <c r="N23" s="180"/>
-      <c r="O23" s="176" t="s">
+      <c r="M23" s="207"/>
+      <c r="N23" s="208"/>
+      <c r="O23" s="204" t="s">
         <v>60</v>
       </c>
-      <c r="P23" s="177"/>
-      <c r="Q23" s="177"/>
-      <c r="R23" s="178"/>
-      <c r="S23" s="176" t="s">
+      <c r="P23" s="205"/>
+      <c r="Q23" s="205"/>
+      <c r="R23" s="206"/>
+      <c r="S23" s="204" t="s">
         <v>62</v>
       </c>
-      <c r="T23" s="177"/>
-      <c r="U23" s="177"/>
-      <c r="V23" s="178"/>
-      <c r="W23" s="176" t="s">
+      <c r="T23" s="205"/>
+      <c r="U23" s="205"/>
+      <c r="V23" s="206"/>
+      <c r="W23" s="204" t="s">
         <v>61</v>
       </c>
-      <c r="X23" s="177"/>
-      <c r="Y23" s="177"/>
-      <c r="Z23" s="178"/>
+      <c r="X23" s="205"/>
+      <c r="Y23" s="205"/>
+      <c r="Z23" s="206"/>
     </row>
     <row r="24" spans="2:33" x14ac:dyDescent="0.2">
       <c r="M24" s="24" t="s">
@@ -3013,35 +4648,35 @@
       <c r="R25" s="30">
         <v>0</v>
       </c>
-      <c r="S25" s="185">
+      <c r="S25" s="213">
         <f>SUMPRODUCT(O25:O27,$N$25:$N$27)</f>
         <v>1.0568750000000002</v>
       </c>
-      <c r="T25" s="183">
+      <c r="T25" s="211">
         <f t="shared" ref="T25:V25" si="2">SUMPRODUCT(P25:P27,$N$25:$N$27)</f>
         <v>1.089375</v>
       </c>
-      <c r="U25" s="183">
+      <c r="U25" s="211">
         <f t="shared" si="2"/>
         <v>1.1156250000000001</v>
       </c>
-      <c r="V25" s="181">
+      <c r="V25" s="209">
         <f t="shared" si="2"/>
         <v>1.1418750000000002</v>
       </c>
-      <c r="W25" s="185">
+      <c r="W25" s="213">
         <f>$N$27/S25</f>
         <v>1.0928444707273803</v>
       </c>
-      <c r="X25" s="183">
+      <c r="X25" s="211">
         <f t="shared" ref="X25:Z25" si="3">$N$27/T25</f>
         <v>1.060240963855422</v>
       </c>
-      <c r="Y25" s="183">
+      <c r="Y25" s="211">
         <f t="shared" si="3"/>
         <v>1.0352941176470589</v>
       </c>
-      <c r="Z25" s="181">
+      <c r="Z25" s="209">
         <f t="shared" si="3"/>
         <v>1.0114942528735633</v>
       </c>
@@ -3066,14 +4701,14 @@
       <c r="R26" s="30">
         <v>0.125</v>
       </c>
-      <c r="S26" s="185"/>
-      <c r="T26" s="183"/>
-      <c r="U26" s="183"/>
-      <c r="V26" s="181"/>
-      <c r="W26" s="185"/>
-      <c r="X26" s="183"/>
-      <c r="Y26" s="183"/>
-      <c r="Z26" s="181"/>
+      <c r="S26" s="213"/>
+      <c r="T26" s="211"/>
+      <c r="U26" s="211"/>
+      <c r="V26" s="209"/>
+      <c r="W26" s="213"/>
+      <c r="X26" s="211"/>
+      <c r="Y26" s="211"/>
+      <c r="Z26" s="209"/>
     </row>
     <row r="27" spans="2:33" x14ac:dyDescent="0.2">
       <c r="M27" s="28">
@@ -3095,14 +4730,14 @@
       <c r="R27" s="31">
         <v>0.875</v>
       </c>
-      <c r="S27" s="186"/>
-      <c r="T27" s="184"/>
-      <c r="U27" s="184"/>
-      <c r="V27" s="182"/>
-      <c r="W27" s="186"/>
-      <c r="X27" s="184"/>
-      <c r="Y27" s="184"/>
-      <c r="Z27" s="182"/>
+      <c r="S27" s="214"/>
+      <c r="T27" s="212"/>
+      <c r="U27" s="212"/>
+      <c r="V27" s="210"/>
+      <c r="W27" s="214"/>
+      <c r="X27" s="212"/>
+      <c r="Y27" s="212"/>
+      <c r="Z27" s="210"/>
     </row>
     <row r="28" spans="2:33" x14ac:dyDescent="0.2">
       <c r="N28" s="32" t="s">
@@ -3183,23 +4818,23 @@
       </c>
     </row>
     <row r="37" spans="15:41" x14ac:dyDescent="0.2">
-      <c r="AE37" s="173"/>
-      <c r="AF37" s="173"/>
-      <c r="AG37" s="174" t="s">
+      <c r="AE37" s="201"/>
+      <c r="AF37" s="201"/>
+      <c r="AG37" s="202" t="s">
         <v>72</v>
       </c>
-      <c r="AH37" s="174"/>
-      <c r="AI37" s="174"/>
-      <c r="AJ37" s="174" t="s">
+      <c r="AH37" s="202"/>
+      <c r="AI37" s="202"/>
+      <c r="AJ37" s="202" t="s">
         <v>76</v>
       </c>
-      <c r="AK37" s="174"/>
-      <c r="AL37" s="174"/>
-      <c r="AM37" s="174" t="s">
+      <c r="AK37" s="202"/>
+      <c r="AL37" s="202"/>
+      <c r="AM37" s="202" t="s">
         <v>77</v>
       </c>
-      <c r="AN37" s="174"/>
-      <c r="AO37" s="174"/>
+      <c r="AN37" s="202"/>
+      <c r="AO37" s="202"/>
     </row>
     <row r="38" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE38" s="15" t="s">
@@ -3248,18 +4883,18 @@
         <f>0.5*3/4*3/4</f>
         <v>0.28125</v>
       </c>
-      <c r="AJ39" s="172"/>
-      <c r="AK39" s="172">
+      <c r="AJ39" s="200"/>
+      <c r="AK39" s="200">
         <f>SUMPRODUCT(AH39:AH42,AF39:AF42)</f>
         <v>1.0636875000000001</v>
       </c>
-      <c r="AL39" s="172"/>
-      <c r="AM39" s="172"/>
-      <c r="AN39" s="172">
+      <c r="AL39" s="200"/>
+      <c r="AM39" s="200"/>
+      <c r="AN39" s="200">
         <f>$AF$42/AK39</f>
         <v>1.0512015982137612</v>
       </c>
-      <c r="AO39" s="172"/>
+      <c r="AO39" s="200"/>
     </row>
     <row r="40" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE40">
@@ -3273,12 +4908,12 @@
         <f>1-AH39-AH41</f>
         <v>0.59375</v>
       </c>
-      <c r="AJ40" s="172"/>
-      <c r="AK40" s="172"/>
-      <c r="AL40" s="172"/>
-      <c r="AM40" s="172"/>
-      <c r="AN40" s="172"/>
-      <c r="AO40" s="172"/>
+      <c r="AJ40" s="200"/>
+      <c r="AK40" s="200"/>
+      <c r="AL40" s="200"/>
+      <c r="AM40" s="200"/>
+      <c r="AN40" s="200"/>
+      <c r="AO40" s="200"/>
     </row>
     <row r="41" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE41">
@@ -3291,12 +4926,12 @@
       <c r="AH41">
         <v>0.125</v>
       </c>
-      <c r="AJ41" s="172"/>
-      <c r="AK41" s="172"/>
-      <c r="AL41" s="172"/>
-      <c r="AM41" s="172"/>
-      <c r="AN41" s="172"/>
-      <c r="AO41" s="172"/>
+      <c r="AJ41" s="200"/>
+      <c r="AK41" s="200"/>
+      <c r="AL41" s="200"/>
+      <c r="AM41" s="200"/>
+      <c r="AN41" s="200"/>
+      <c r="AO41" s="200"/>
     </row>
     <row r="42" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE42">
@@ -3309,31 +4944,31 @@
       <c r="AH42">
         <v>0</v>
       </c>
-      <c r="AJ42" s="172"/>
-      <c r="AK42" s="172"/>
-      <c r="AL42" s="172"/>
-      <c r="AM42" s="172"/>
-      <c r="AN42" s="172"/>
-      <c r="AO42" s="172"/>
+      <c r="AJ42" s="200"/>
+      <c r="AK42" s="200"/>
+      <c r="AL42" s="200"/>
+      <c r="AM42" s="200"/>
+      <c r="AN42" s="200"/>
+      <c r="AO42" s="200"/>
     </row>
     <row r="44" spans="15:41" x14ac:dyDescent="0.2">
-      <c r="AE44" s="173"/>
-      <c r="AF44" s="173"/>
-      <c r="AG44" s="174" t="s">
+      <c r="AE44" s="201"/>
+      <c r="AF44" s="201"/>
+      <c r="AG44" s="202" t="s">
         <v>72</v>
       </c>
-      <c r="AH44" s="174"/>
-      <c r="AI44" s="174"/>
-      <c r="AJ44" s="174" t="s">
+      <c r="AH44" s="202"/>
+      <c r="AI44" s="202"/>
+      <c r="AJ44" s="202" t="s">
         <v>76</v>
       </c>
-      <c r="AK44" s="174"/>
-      <c r="AL44" s="174"/>
-      <c r="AM44" s="174" t="s">
+      <c r="AK44" s="202"/>
+      <c r="AL44" s="202"/>
+      <c r="AM44" s="202" t="s">
         <v>77</v>
       </c>
-      <c r="AN44" s="174"/>
-      <c r="AO44" s="174"/>
+      <c r="AN44" s="202"/>
+      <c r="AO44" s="202"/>
     </row>
     <row r="45" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE45" s="15" t="s">
@@ -3381,18 +5016,18 @@
       <c r="AH46">
         <v>0</v>
       </c>
-      <c r="AJ46" s="172"/>
-      <c r="AK46" s="172">
+      <c r="AJ46" s="200"/>
+      <c r="AK46" s="200">
         <f>SUMPRODUCT(AH46:AH49,AF46:AF49)</f>
         <v>1.1161437500000002</v>
       </c>
-      <c r="AL46" s="172"/>
-      <c r="AM46" s="172"/>
-      <c r="AN46" s="172">
+      <c r="AL46" s="200"/>
+      <c r="AM46" s="200"/>
+      <c r="AN46" s="200">
         <f>$AF$49/AK46</f>
         <v>1.0017974835230676</v>
       </c>
-      <c r="AO46" s="172"/>
+      <c r="AO46" s="200"/>
     </row>
     <row r="47" spans="15:41" x14ac:dyDescent="0.2">
       <c r="AE47">
@@ -3405,12 +5040,12 @@
       <c r="AH47">
         <v>0.5</v>
       </c>
-      <c r="AJ47" s="172"/>
-      <c r="AK47" s="172"/>
-      <c r="AL47" s="172"/>
-      <c r="AM47" s="172"/>
-      <c r="AN47" s="172"/>
-      <c r="AO47" s="172"/>
+      <c r="AJ47" s="200"/>
+      <c r="AK47" s="200"/>
+      <c r="AL47" s="200"/>
+      <c r="AM47" s="200"/>
+      <c r="AN47" s="200"/>
+      <c r="AO47" s="200"/>
     </row>
     <row r="48" spans="15:41" x14ac:dyDescent="0.2">
       <c r="O48" t="s">
@@ -3426,12 +5061,12 @@
       <c r="AH48">
         <v>0.375</v>
       </c>
-      <c r="AJ48" s="172"/>
-      <c r="AK48" s="172"/>
-      <c r="AL48" s="172"/>
-      <c r="AM48" s="172"/>
-      <c r="AN48" s="172"/>
-      <c r="AO48" s="172"/>
+      <c r="AJ48" s="200"/>
+      <c r="AK48" s="200"/>
+      <c r="AL48" s="200"/>
+      <c r="AM48" s="200"/>
+      <c r="AN48" s="200"/>
+      <c r="AO48" s="200"/>
     </row>
     <row r="49" spans="31:52" x14ac:dyDescent="0.2">
       <c r="AE49">
@@ -3444,12 +5079,12 @@
       <c r="AH49">
         <v>0.125</v>
       </c>
-      <c r="AJ49" s="172"/>
-      <c r="AK49" s="172"/>
-      <c r="AL49" s="172"/>
-      <c r="AM49" s="172"/>
-      <c r="AN49" s="172"/>
-      <c r="AO49" s="172"/>
+      <c r="AJ49" s="200"/>
+      <c r="AK49" s="200"/>
+      <c r="AL49" s="200"/>
+      <c r="AM49" s="200"/>
+      <c r="AN49" s="200"/>
+      <c r="AO49" s="200"/>
     </row>
     <row r="53" spans="31:52" x14ac:dyDescent="0.2">
       <c r="AS53" s="15" t="s">
@@ -3499,20 +5134,20 @@
       </c>
     </row>
     <row r="58" spans="31:52" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="AS58" s="173"/>
-      <c r="AT58" s="173"/>
-      <c r="AU58" s="174" t="s">
+      <c r="AS58" s="201"/>
+      <c r="AT58" s="201"/>
+      <c r="AU58" s="202" t="s">
         <v>72</v>
       </c>
-      <c r="AV58" s="174"/>
-      <c r="AW58" s="175" t="s">
+      <c r="AV58" s="202"/>
+      <c r="AW58" s="203" t="s">
         <v>76</v>
       </c>
-      <c r="AX58" s="175"/>
-      <c r="AY58" s="174" t="s">
+      <c r="AX58" s="203"/>
+      <c r="AY58" s="202" t="s">
         <v>77</v>
       </c>
-      <c r="AZ58" s="174"/>
+      <c r="AZ58" s="202"/>
     </row>
     <row r="59" spans="31:52" x14ac:dyDescent="0.2">
       <c r="AS59" s="15" t="s">
@@ -3552,13 +5187,13 @@
         <f>1/16</f>
         <v>6.25E-2</v>
       </c>
-      <c r="AW60" s="172"/>
-      <c r="AX60" s="172">
+      <c r="AW60" s="200"/>
+      <c r="AX60" s="200">
         <f>SUMPRODUCT(AV60:AV62,AT60:AT62)</f>
         <v>1.0993750000000002</v>
       </c>
-      <c r="AY60" s="172"/>
-      <c r="AZ60" s="172">
+      <c r="AY60" s="200"/>
+      <c r="AZ60" s="200">
         <f>$AT$62/AX60</f>
         <v>1.0505969300739058</v>
       </c>
@@ -3575,10 +5210,10 @@
         <f>0.5-AV60</f>
         <v>0.4375</v>
       </c>
-      <c r="AW61" s="172"/>
-      <c r="AX61" s="172"/>
-      <c r="AY61" s="172"/>
-      <c r="AZ61" s="172"/>
+      <c r="AW61" s="200"/>
+      <c r="AX61" s="200"/>
+      <c r="AY61" s="200"/>
+      <c r="AZ61" s="200"/>
     </row>
     <row r="62" spans="31:52" x14ac:dyDescent="0.2">
       <c r="AS62">
@@ -3591,10 +5226,10 @@
       <c r="AV62">
         <v>0.5</v>
       </c>
-      <c r="AW62" s="172"/>
-      <c r="AX62" s="172"/>
-      <c r="AY62" s="172"/>
-      <c r="AZ62" s="172"/>
+      <c r="AW62" s="200"/>
+      <c r="AX62" s="200"/>
+      <c r="AY62" s="200"/>
+      <c r="AZ62" s="200"/>
     </row>
     <row r="63" spans="31:52" x14ac:dyDescent="0.2">
       <c r="AW63" s="23"/>
@@ -4063,7 +5698,7 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B3" s="189" t="s">
+      <c r="B3" s="217" t="s">
         <v>96</v>
       </c>
       <c r="C3" s="11" t="s">
@@ -4071,7 +5706,7 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="189"/>
+      <c r="B4" s="217"/>
       <c r="C4" s="11" t="s">
         <v>98</v>
       </c>
@@ -4175,7 +5810,7 @@
       <c r="F10" s="12"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B11" s="189" t="s">
+      <c r="B11" s="217" t="s">
         <v>96</v>
       </c>
       <c r="C11" s="11" t="s">
@@ -4183,7 +5818,7 @@
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B12" s="189"/>
+      <c r="B12" s="217"/>
       <c r="C12" s="11" t="s">
         <v>98</v>
       </c>
@@ -4283,7 +5918,7 @@
       <c r="G16" s="12"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B18" s="189" t="s">
+      <c r="B18" s="217" t="s">
         <v>96</v>
       </c>
       <c r="C18" s="11" t="s">
@@ -4291,7 +5926,7 @@
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B19" s="189"/>
+      <c r="B19" s="217"/>
       <c r="C19" s="39" t="s">
         <v>103</v>
       </c>
@@ -4591,7 +6226,7 @@
       </c>
     </row>
     <row r="49" spans="9:13" x14ac:dyDescent="0.2">
-      <c r="I49" s="189" t="s">
+      <c r="I49" s="217" t="s">
         <v>96</v>
       </c>
       <c r="J49" s="11" t="s">
@@ -4599,7 +6234,7 @@
       </c>
     </row>
     <row r="50" spans="9:13" x14ac:dyDescent="0.2">
-      <c r="I50" s="189"/>
+      <c r="I50" s="217"/>
       <c r="J50" s="11" t="s">
         <v>134</v>
       </c>
@@ -4783,10 +6418,10 @@
     </row>
     <row r="73" spans="9:23" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="74" spans="9:23" x14ac:dyDescent="0.2">
-      <c r="Q74" s="188" t="s">
+      <c r="Q74" s="216" t="s">
         <v>149</v>
       </c>
-      <c r="R74" s="188" t="s">
+      <c r="R74" s="216" t="s">
         <v>96</v>
       </c>
       <c r="S74" s="11" t="s">
@@ -4794,15 +6429,15 @@
       </c>
     </row>
     <row r="75" spans="9:23" x14ac:dyDescent="0.2">
-      <c r="Q75" s="188"/>
-      <c r="R75" s="188"/>
+      <c r="Q75" s="216"/>
+      <c r="R75" s="216"/>
       <c r="S75" s="11" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="76" spans="9:23" x14ac:dyDescent="0.2">
-      <c r="Q76" s="188"/>
-      <c r="R76" s="188"/>
+      <c r="Q76" s="216"/>
+      <c r="R76" s="216"/>
       <c r="S76" s="11">
         <v>12</v>
       </c>
@@ -4913,10 +6548,10 @@
       <c r="U81" s="12"/>
     </row>
     <row r="83" spans="17:23" x14ac:dyDescent="0.2">
-      <c r="Q83" s="188" t="s">
+      <c r="Q83" s="216" t="s">
         <v>149</v>
       </c>
-      <c r="R83" s="188" t="s">
+      <c r="R83" s="216" t="s">
         <v>96</v>
       </c>
       <c r="S83" s="11" t="s">
@@ -4924,15 +6559,15 @@
       </c>
     </row>
     <row r="84" spans="17:23" x14ac:dyDescent="0.2">
-      <c r="Q84" s="188"/>
-      <c r="R84" s="188"/>
+      <c r="Q84" s="216"/>
+      <c r="R84" s="216"/>
       <c r="S84" s="11" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="85" spans="17:23" x14ac:dyDescent="0.2">
-      <c r="Q85" s="188"/>
-      <c r="R85" s="188"/>
+      <c r="Q85" s="216"/>
+      <c r="R85" s="216"/>
       <c r="S85" s="39" t="s">
         <v>103</v>
       </c>
@@ -5225,16 +6860,16 @@
       </c>
     </row>
     <row r="116" spans="25:29" x14ac:dyDescent="0.2">
-      <c r="Y116" s="190" t="s">
+      <c r="Y116" s="218" t="s">
         <v>158</v>
       </c>
-      <c r="Z116" s="190"/>
-      <c r="AA116" s="190"/>
-      <c r="AB116" s="190"/>
-      <c r="AC116" s="190"/>
+      <c r="Z116" s="218"/>
+      <c r="AA116" s="218"/>
+      <c r="AB116" s="218"/>
+      <c r="AC116" s="218"/>
     </row>
     <row r="117" spans="25:29" x14ac:dyDescent="0.2">
-      <c r="Y117" s="189" t="s">
+      <c r="Y117" s="217" t="s">
         <v>96</v>
       </c>
       <c r="Z117" s="11" t="s">
@@ -5242,7 +6877,7 @@
       </c>
     </row>
     <row r="118" spans="25:29" x14ac:dyDescent="0.2">
-      <c r="Y118" s="189"/>
+      <c r="Y118" s="217"/>
       <c r="Z118" s="11">
         <v>12</v>
       </c>
@@ -5312,7 +6947,7 @@
       <c r="AB122" s="12"/>
     </row>
     <row r="124" spans="25:29" x14ac:dyDescent="0.2">
-      <c r="Y124" s="189" t="s">
+      <c r="Y124" s="217" t="s">
         <v>96</v>
       </c>
       <c r="Z124" s="11" t="s">
@@ -5320,7 +6955,7 @@
       </c>
     </row>
     <row r="125" spans="25:29" x14ac:dyDescent="0.2">
-      <c r="Y125" s="189"/>
+      <c r="Y125" s="217"/>
       <c r="Z125" s="40" t="s">
         <v>103</v>
       </c>
@@ -5544,15 +7179,15 @@
       <c r="Y148" s="3"/>
     </row>
     <row r="150" spans="25:28" x14ac:dyDescent="0.2">
-      <c r="Y150" s="174" t="s">
+      <c r="Y150" s="202" t="s">
         <v>173</v>
       </c>
-      <c r="Z150" s="174"/>
-      <c r="AA150" s="174"/>
-      <c r="AB150" s="174"/>
+      <c r="Z150" s="202"/>
+      <c r="AA150" s="202"/>
+      <c r="AB150" s="202"/>
     </row>
     <row r="151" spans="25:28" x14ac:dyDescent="0.2">
-      <c r="Y151" s="187" t="s">
+      <c r="Y151" s="215" t="s">
         <v>96</v>
       </c>
       <c r="Z151" s="11" t="s">
@@ -5560,7 +7195,7 @@
       </c>
     </row>
     <row r="152" spans="25:28" x14ac:dyDescent="0.2">
-      <c r="Y152" s="187"/>
+      <c r="Y152" s="215"/>
       <c r="Z152" s="40" t="s">
         <v>103</v>
       </c>
@@ -6001,15 +7636,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B2" s="173"/>
-      <c r="C2" s="192" t="s">
+      <c r="B2" s="201"/>
+      <c r="C2" s="220" t="s">
         <v>187</v>
       </c>
-      <c r="D2" s="192"/>
-      <c r="E2" s="192"/>
+      <c r="D2" s="220"/>
+      <c r="E2" s="220"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B3" s="173"/>
+      <c r="B3" s="201"/>
       <c r="C3" s="70">
         <v>2021</v>
       </c>
@@ -6133,18 +7768,18 @@
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B13" s="173"/>
-      <c r="C13" s="192" t="s">
+      <c r="B13" s="201"/>
+      <c r="C13" s="220" t="s">
         <v>187</v>
       </c>
-      <c r="D13" s="192"/>
-      <c r="E13" s="192"/>
+      <c r="D13" s="220"/>
+      <c r="E13" s="220"/>
       <c r="H13" s="15" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B14" s="173"/>
+      <c r="B14" s="201"/>
       <c r="C14" s="70">
         <v>2021</v>
       </c>
@@ -6318,13 +7953,13 @@
       </c>
     </row>
     <row r="20" spans="2:12" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="191" t="s">
+      <c r="B20" s="219" t="s">
         <v>223</v>
       </c>
-      <c r="C20" s="191"/>
-      <c r="D20" s="191"/>
-      <c r="E20" s="191"/>
-      <c r="F20" s="191"/>
+      <c r="C20" s="219"/>
+      <c r="D20" s="219"/>
+      <c r="E20" s="219"/>
+      <c r="F20" s="219"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
@@ -6463,11 +8098,11 @@
       </c>
     </row>
     <row r="33" spans="17:26" x14ac:dyDescent="0.2">
-      <c r="Q33" s="173"/>
-      <c r="R33" s="192" t="s">
+      <c r="Q33" s="201"/>
+      <c r="R33" s="220" t="s">
         <v>187</v>
       </c>
-      <c r="S33" s="192"/>
+      <c r="S33" s="220"/>
       <c r="U33" s="15" t="s">
         <v>232</v>
       </c>
@@ -6483,7 +8118,7 @@
       </c>
     </row>
     <row r="34" spans="17:26" x14ac:dyDescent="0.2">
-      <c r="Q34" s="173"/>
+      <c r="Q34" s="201"/>
       <c r="R34" s="70">
         <v>2003</v>
       </c>
@@ -7522,28 +9157,28 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="I2" s="193" t="s">
+      <c r="I2" s="221" t="s">
         <v>329</v>
       </c>
-      <c r="J2" s="193"/>
-      <c r="K2" s="193"/>
+      <c r="J2" s="221"/>
+      <c r="K2" s="221"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="J3" s="192" t="s">
+      <c r="J3" s="220" t="s">
         <v>317</v>
       </c>
-      <c r="K3" s="192"/>
+      <c r="K3" s="220"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B4" s="139" t="s">
         <v>320</v>
       </c>
-      <c r="C4" s="196" t="s">
+      <c r="C4" s="224" t="s">
         <v>314</v>
       </c>
-      <c r="D4" s="197"/>
-      <c r="E4" s="197"/>
-      <c r="F4" s="194" t="s">
+      <c r="D4" s="225"/>
+      <c r="E4" s="225"/>
+      <c r="F4" s="222" t="s">
         <v>10</v>
       </c>
       <c r="H4" s="70" t="s">
@@ -7572,7 +9207,7 @@
       <c r="E5" s="137">
         <v>3</v>
       </c>
-      <c r="F5" s="195"/>
+      <c r="F5" s="223"/>
       <c r="H5" s="71">
         <v>1</v>
       </c>
@@ -7713,10 +9348,10 @@
         <v>1</v>
       </c>
       <c r="D11" s="71"/>
-      <c r="I11" s="193" t="s">
+      <c r="I11" s="221" t="s">
         <v>329</v>
       </c>
-      <c r="J11" s="193"/>
+      <c r="J11" s="221"/>
       <c r="K11" s="36" t="s">
         <v>330</v>
       </c>
@@ -7983,12 +9618,12 @@
       <c r="B28" s="139" t="s">
         <v>319</v>
       </c>
-      <c r="C28" s="196" t="s">
+      <c r="C28" s="224" t="s">
         <v>314</v>
       </c>
-      <c r="D28" s="197"/>
-      <c r="E28" s="197"/>
-      <c r="F28" s="194" t="s">
+      <c r="D28" s="225"/>
+      <c r="E28" s="225"/>
+      <c r="F28" s="222" t="s">
         <v>10</v>
       </c>
     </row>
@@ -8005,7 +9640,7 @@
       <c r="E29" s="141">
         <v>3</v>
       </c>
-      <c r="F29" s="198"/>
+      <c r="F29" s="226"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="148" t="s">
@@ -8590,12 +10225,12 @@
       </c>
     </row>
     <row r="17" spans="15:25" x14ac:dyDescent="0.2">
-      <c r="O17" s="200"/>
+      <c r="O17" s="70"/>
       <c r="Q17" s="70"/>
       <c r="R17" s="154" t="s">
         <v>380</v>
       </c>
-      <c r="S17" s="200"/>
+      <c r="S17" s="70"/>
       <c r="T17" s="36" t="s">
         <v>370</v>
       </c>
@@ -8616,37 +10251,37 @@
       </c>
     </row>
     <row r="18" spans="15:25" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="O18" s="200" t="s">
+      <c r="O18" s="70" t="s">
         <v>314</v>
       </c>
       <c r="P18" s="70" t="s">
         <v>149</v>
       </c>
-      <c r="Q18" s="202" t="s">
+      <c r="Q18" s="174" t="s">
         <v>365</v>
       </c>
-      <c r="R18" s="202" t="s">
+      <c r="R18" s="174" t="s">
         <v>378</v>
       </c>
-      <c r="S18" s="200" t="s">
+      <c r="S18" s="70" t="s">
         <v>318</v>
       </c>
-      <c r="T18" s="202" t="s">
+      <c r="T18" s="174" t="s">
         <v>375</v>
       </c>
-      <c r="U18" s="200" t="s">
+      <c r="U18" s="70" t="s">
         <v>367</v>
       </c>
-      <c r="V18" s="202" t="s">
+      <c r="V18" s="174" t="s">
         <v>376</v>
       </c>
-      <c r="W18" s="200" t="s">
+      <c r="W18" s="70" t="s">
         <v>353</v>
       </c>
-      <c r="X18" s="202" t="s">
+      <c r="X18" s="174" t="s">
         <v>377</v>
       </c>
-      <c r="Y18" s="200" t="s">
+      <c r="Y18" s="70" t="s">
         <v>358</v>
       </c>
     </row>
@@ -8664,7 +10299,7 @@
         <f>Q19*(1+P25)^$P$31</f>
         <v>428687.49999999994</v>
       </c>
-      <c r="S19" s="204">
+      <c r="S19" s="176">
         <v>1</v>
       </c>
       <c r="T19" s="43">
@@ -8706,7 +10341,7 @@
         <f t="shared" ref="R20:R21" si="5">Q20*(1+P26)^$P$31</f>
         <v>125000</v>
       </c>
-      <c r="S20" s="204">
+      <c r="S20" s="176">
         <v>0.95</v>
       </c>
       <c r="T20" s="43">
@@ -8730,7 +10365,7 @@
         <v>1.044790665862636</v>
       </c>
       <c r="Y20" s="43">
-        <f t="shared" ref="Y20:Y22" si="9">X20/$X$19</f>
+        <f t="shared" ref="Y20:Y21" si="9">X20/$X$19</f>
         <v>1.0802060077219544</v>
       </c>
     </row>
@@ -8748,19 +10383,19 @@
         <f t="shared" si="5"/>
         <v>332750.00000000012</v>
       </c>
-      <c r="S21" s="205">
+      <c r="S21" s="177">
         <v>1.25</v>
       </c>
       <c r="T21" s="157">
         <f t="shared" si="6"/>
         <v>1.149425287356322</v>
       </c>
-      <c r="U21" s="203">
+      <c r="U21" s="175">
         <f t="shared" si="7"/>
         <v>22.183333333333341</v>
       </c>
       <c r="V21" s="157">
-        <f t="shared" ref="V20:V22" si="10">U21/$U$22</f>
+        <f t="shared" ref="V21:V22" si="10">U21/$U$22</f>
         <v>1.0010105995440552</v>
       </c>
       <c r="W21" s="157">
@@ -8828,7 +10463,7 @@
       </c>
     </row>
     <row r="24" spans="15:25" x14ac:dyDescent="0.2">
-      <c r="O24" s="200" t="s">
+      <c r="O24" s="70" t="s">
         <v>314</v>
       </c>
       <c r="P24" s="70" t="s">
@@ -8855,11 +10490,10 @@
       <c r="O27" s="131" t="s">
         <v>336</v>
       </c>
-      <c r="P27" s="201">
+      <c r="P27" s="173">
         <v>0.1</v>
       </c>
       <c r="Q27" s="1"/>
-      <c r="R27" s="206"/>
     </row>
     <row r="28" spans="15:25" x14ac:dyDescent="0.2">
       <c r="O28" s="71" t="s">
@@ -8874,7 +10508,7 @@
       <c r="O30" s="70" t="s">
         <v>368</v>
       </c>
-      <c r="P30" s="199">
+      <c r="P30" s="172">
         <v>11050</v>
       </c>
     </row>
@@ -8882,7 +10516,7 @@
       <c r="O31" s="70" t="s">
         <v>235</v>
       </c>
-      <c r="P31" s="207">
+      <c r="P31" s="178">
         <v>3</v>
       </c>
     </row>
